--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>297989</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>38.7000007629395</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>38.060001373291</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>38.5400009155273</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>38.2000007629395</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>505826</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>38.310001373291</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>37.189998626709</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>38.0999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>38.1699981689453</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>390796</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>38.9099998474121</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>38.2799987792969</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>38.4099998474121</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>38.9099998474121</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>498639</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>39.5400009155273</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>38.8699989318848</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>39.0900001525879</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>39.4799995422363</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>284385</v>
+        <v>398589</v>
       </c>
       <c r="C2715" t="n">
-        <v>39.0999984741211</v>
+        <v>39.3199996948242</v>
       </c>
       <c r="D2715" t="n">
-        <v>38.2299995422363</v>
+        <v>38.7900009155273</v>
       </c>
       <c r="E2715" t="n">
-        <v>38.6500015258789</v>
+        <v>39.3199996948242</v>
       </c>
       <c r="F2715" t="n">
-        <v>39.0999984741211</v>
+        <v>38.7900009155273</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>527869</v>
+        <v>284385</v>
       </c>
       <c r="C2716" t="n">
-        <v>38.939998626709</v>
+        <v>39.0999984741211</v>
       </c>
       <c r="D2716" t="n">
-        <v>38.0999984741211</v>
+        <v>38.2299995422363</v>
       </c>
       <c r="E2716" t="n">
-        <v>38.7700004577637</v>
+        <v>38.6500015258789</v>
       </c>
       <c r="F2716" t="n">
-        <v>38.3600006103516</v>
+        <v>39.0999984741211</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>229509</v>
+        <v>527869</v>
       </c>
       <c r="C2717" t="n">
         <v>38.939998626709</v>
       </c>
       <c r="D2717" t="n">
-        <v>38.3499984741211</v>
+        <v>38.0999984741211</v>
       </c>
       <c r="E2717" t="n">
-        <v>38.5099983215332</v>
+        <v>38.7700004577637</v>
       </c>
       <c r="F2717" t="n">
-        <v>38.3499984741211</v>
+        <v>38.3600006103516</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>299593</v>
+        <v>229509</v>
       </c>
       <c r="C2718" t="n">
-        <v>38.8899993896484</v>
+        <v>38.939998626709</v>
       </c>
       <c r="D2718" t="n">
-        <v>38.2799987792969</v>
+        <v>38.3499984741211</v>
       </c>
       <c r="E2718" t="n">
-        <v>38.2799987792969</v>
+        <v>38.5099983215332</v>
       </c>
       <c r="F2718" t="n">
-        <v>38.8800010681152</v>
+        <v>38.3499984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>297989</v>
+        <v>299593</v>
       </c>
       <c r="C2719" t="n">
-        <v>38.7000007629395</v>
+        <v>38.8899993896484</v>
       </c>
       <c r="D2719" t="n">
-        <v>38.060001373291</v>
+        <v>38.2799987792969</v>
       </c>
       <c r="E2719" t="n">
-        <v>38.5400009155273</v>
+        <v>38.2799987792969</v>
       </c>
       <c r="F2719" t="n">
-        <v>38.2000007629395</v>
+        <v>38.8800010681152</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>505826</v>
+        <v>297989</v>
       </c>
       <c r="C2720" t="n">
-        <v>38.310001373291</v>
+        <v>38.7000007629395</v>
       </c>
       <c r="D2720" t="n">
-        <v>37.189998626709</v>
+        <v>38.060001373291</v>
       </c>
       <c r="E2720" t="n">
-        <v>38.0999984741211</v>
+        <v>38.5400009155273</v>
       </c>
       <c r="F2720" t="n">
-        <v>38.1699981689453</v>
+        <v>38.2000007629395</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>390796</v>
+        <v>505826</v>
       </c>
       <c r="C2721" t="n">
-        <v>38.9099998474121</v>
+        <v>38.310001373291</v>
       </c>
       <c r="D2721" t="n">
-        <v>38.2799987792969</v>
+        <v>37.189998626709</v>
       </c>
       <c r="E2721" t="n">
-        <v>38.4099998474121</v>
+        <v>38.0999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>38.9099998474121</v>
+        <v>38.1699981689453</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>498639</v>
+        <v>390796</v>
       </c>
       <c r="C2722" t="n">
-        <v>39.5400009155273</v>
+        <v>38.9099998474121</v>
       </c>
       <c r="D2722" t="n">
-        <v>38.8699989318848</v>
+        <v>38.2799987792969</v>
       </c>
       <c r="E2722" t="n">
-        <v>39.0900001525879</v>
+        <v>38.4099998474121</v>
       </c>
       <c r="F2722" t="n">
-        <v>39.4799995422363</v>
+        <v>38.9099998474121</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>569695</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>39.4199981689453</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>38.9199981689453</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>39.3600006103516</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>39.0499992370605</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>37.9500007629395</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>37.5999984741211</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>529059</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>38.25</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>37.5499992370605</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>37.6500015258789</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>37.6500015258789</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>37.7700004577637</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>748820</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>37.7599983215332</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>36.4900016784668</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>37.3499984741211</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>37.3499984741211</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>36.75</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>545870</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>36.9199981689453</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>36.2900009155273</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>36.4500007629395</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>36.4500007629395</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>36.6199989318848</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>409055</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>36.7900009155273</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>36.810001373291</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>730134</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>37.0900001525879</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>36.1399993896484</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>36.9900016784668</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -456,7 +456,7 @@
         <v>20.3089122772217</v>
       </c>
       <c r="G3" t="n">
-        <v>10.0991821289062</v>
+        <v>10.0991830825806</v>
       </c>
       <c r="H3" t="n">
         <v>1139662</v>
@@ -514,7 +514,7 @@
         <v>19.3316287994385</v>
       </c>
       <c r="G5" t="n">
-        <v>9.61320018768311</v>
+        <v>9.61319923400879</v>
       </c>
       <c r="H5" t="n">
         <v>1415018</v>
@@ -543,7 +543,7 @@
         <v>18.8011016845703</v>
       </c>
       <c r="G6" t="n">
-        <v>9.34938049316406</v>
+        <v>9.34938144683838</v>
       </c>
       <c r="H6" t="n">
         <v>933755</v>
@@ -572,7 +572,7 @@
         <v>18.8476390838623</v>
       </c>
       <c r="G7" t="n">
-        <v>9.37252330780029</v>
+        <v>9.37252235412598</v>
       </c>
       <c r="H7" t="n">
         <v>1038503</v>
@@ -601,7 +601,7 @@
         <v>19.3967819213867</v>
       </c>
       <c r="G8" t="n">
-        <v>9.64559936523438</v>
+        <v>9.64559841156006</v>
       </c>
       <c r="H8" t="n">
         <v>1092313</v>
@@ -630,7 +630,7 @@
         <v>18.9686374664307</v>
       </c>
       <c r="G9" t="n">
-        <v>9.43269348144531</v>
+        <v>9.432692527771</v>
       </c>
       <c r="H9" t="n">
         <v>1190425</v>
@@ -659,7 +659,7 @@
         <v>18.242654800415</v>
       </c>
       <c r="G10" t="n">
-        <v>9.07167816162109</v>
+        <v>9.07167625427246</v>
       </c>
       <c r="H10" t="n">
         <v>1319004</v>
@@ -688,7 +688,7 @@
         <v>17.7028198242188</v>
       </c>
       <c r="G11" t="n">
-        <v>8.8032283782959</v>
+        <v>8.80322933197021</v>
       </c>
       <c r="H11" t="n">
         <v>1256919</v>
@@ -775,7 +775,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G14" t="n">
-        <v>8.35427379608154</v>
+        <v>8.35427474975586</v>
       </c>
       <c r="H14" t="n">
         <v>1409747</v>
@@ -804,7 +804,7 @@
         <v>17.5632076263428</v>
       </c>
       <c r="G15" t="n">
-        <v>8.73380088806152</v>
+        <v>8.73380279541016</v>
       </c>
       <c r="H15" t="n">
         <v>1491895</v>
@@ -891,7 +891,7 @@
         <v>18.0378894805908</v>
       </c>
       <c r="G18" t="n">
-        <v>8.96985149383545</v>
+        <v>8.96985244750977</v>
       </c>
       <c r="H18" t="n">
         <v>929991</v>
@@ -920,7 +920,7 @@
         <v>17.8331241607666</v>
       </c>
       <c r="G19" t="n">
-        <v>8.86802577972412</v>
+        <v>8.86802673339844</v>
       </c>
       <c r="H19" t="n">
         <v>927042</v>
@@ -949,7 +949,7 @@
         <v>17.3119068145752</v>
       </c>
       <c r="G20" t="n">
-        <v>8.60883617401123</v>
+        <v>8.60883808135986</v>
       </c>
       <c r="H20" t="n">
         <v>963207</v>
@@ -978,7 +978,7 @@
         <v>18.0099678039551</v>
       </c>
       <c r="G21" t="n">
-        <v>8.95596694946289</v>
+        <v>8.95596599578857</v>
       </c>
       <c r="H21" t="n">
         <v>934449</v>
@@ -1094,7 +1094,7 @@
         <v>17.060604095459</v>
       </c>
       <c r="G25" t="n">
-        <v>8.48386859893799</v>
+        <v>8.48386764526367</v>
       </c>
       <c r="H25" t="n">
         <v>794101</v>
@@ -1123,7 +1123,7 @@
         <v>16.688304901123</v>
       </c>
       <c r="G26" t="n">
-        <v>8.29873180389404</v>
+        <v>8.29873371124268</v>
       </c>
       <c r="H26" t="n">
         <v>1057416</v>
@@ -1181,7 +1181,7 @@
         <v>14.9198846817017</v>
       </c>
       <c r="G28" t="n">
-        <v>7.41933631896973</v>
+        <v>7.41933536529541</v>
       </c>
       <c r="H28" t="n">
         <v>1560532</v>
@@ -1268,7 +1268,7 @@
         <v>14.5662002563477</v>
       </c>
       <c r="G31" t="n">
-        <v>7.24345731735229</v>
+        <v>7.24345588684082</v>
       </c>
       <c r="H31" t="n">
         <v>1726080</v>
@@ -1326,7 +1326,7 @@
         <v>14.9291915893555</v>
       </c>
       <c r="G33" t="n">
-        <v>7.42396402359009</v>
+        <v>7.42396354675293</v>
       </c>
       <c r="H33" t="n">
         <v>992196</v>
@@ -1471,7 +1471,7 @@
         <v>16.1298561096191</v>
       </c>
       <c r="G38" t="n">
-        <v>8.02102851867676</v>
+        <v>8.02102947235107</v>
       </c>
       <c r="H38" t="n">
         <v>709750</v>
@@ -1500,7 +1500,7 @@
         <v>15.5807151794434</v>
       </c>
       <c r="G39" t="n">
-        <v>7.74795198440552</v>
+        <v>7.74795293807983</v>
       </c>
       <c r="H39" t="n">
         <v>525121</v>
@@ -1587,7 +1587,7 @@
         <v>16.5393848419189</v>
       </c>
       <c r="G42" t="n">
-        <v>8.22467803955078</v>
+        <v>8.2246789932251</v>
       </c>
       <c r="H42" t="n">
         <v>679369</v>
@@ -1616,7 +1616,7 @@
         <v>17.3119068145752</v>
       </c>
       <c r="G43" t="n">
-        <v>8.60883617401123</v>
+        <v>8.60883808135986</v>
       </c>
       <c r="H43" t="n">
         <v>925913</v>
@@ -1645,7 +1645,7 @@
         <v>17.628360748291</v>
       </c>
       <c r="G44" t="n">
-        <v>8.76620101928711</v>
+        <v>8.76620292663574</v>
       </c>
       <c r="H44" t="n">
         <v>1052689</v>
@@ -1674,7 +1674,7 @@
         <v>17.6562824249268</v>
       </c>
       <c r="G45" t="n">
-        <v>8.78008651733398</v>
+        <v>8.7800874710083</v>
       </c>
       <c r="H45" t="n">
         <v>689765</v>
@@ -1732,7 +1732,7 @@
         <v>17.2560615539551</v>
       </c>
       <c r="G47" t="n">
-        <v>8.5810661315918</v>
+        <v>8.58106517791748</v>
       </c>
       <c r="H47" t="n">
         <v>1269243</v>
@@ -1761,7 +1761,7 @@
         <v>17.488748550415</v>
       </c>
       <c r="G48" t="n">
-        <v>8.69677639007568</v>
+        <v>8.69677734375</v>
       </c>
       <c r="H48" t="n">
         <v>1249776</v>
@@ -1790,7 +1790,7 @@
         <v>17.8517398834229</v>
       </c>
       <c r="G49" t="n">
-        <v>8.87728309631348</v>
+        <v>8.87728404998779</v>
       </c>
       <c r="H49" t="n">
         <v>1175554</v>
@@ -1819,7 +1819,7 @@
         <v>17.9820442199707</v>
       </c>
       <c r="G50" t="n">
-        <v>8.94208240509033</v>
+        <v>8.94208145141602</v>
       </c>
       <c r="H50" t="n">
         <v>2741312</v>
@@ -1848,7 +1848,7 @@
         <v>18.5498008728027</v>
       </c>
       <c r="G51" t="n">
-        <v>9.22441577911377</v>
+        <v>9.22441482543945</v>
       </c>
       <c r="H51" t="n">
         <v>1790410</v>
@@ -1877,7 +1877,7 @@
         <v>18.3264217376709</v>
       </c>
       <c r="G52" t="n">
-        <v>9.11333274841309</v>
+        <v>9.1133337020874</v>
       </c>
       <c r="H52" t="n">
         <v>1265956</v>
@@ -1964,7 +1964,7 @@
         <v>18.0099678039551</v>
       </c>
       <c r="G55" t="n">
-        <v>8.95596694946289</v>
+        <v>8.95596599578857</v>
       </c>
       <c r="H55" t="n">
         <v>1630405</v>
@@ -1993,7 +1993,7 @@
         <v>18.5777225494385</v>
       </c>
       <c r="G56" t="n">
-        <v>9.23829936981201</v>
+        <v>9.23830032348633</v>
       </c>
       <c r="H56" t="n">
         <v>1585761</v>
@@ -2022,7 +2022,7 @@
         <v>18.5404930114746</v>
       </c>
       <c r="G57" t="n">
-        <v>9.2197847366333</v>
+        <v>9.21978569030762</v>
       </c>
       <c r="H57" t="n">
         <v>877559</v>
@@ -2051,7 +2051,7 @@
         <v>18.3729572296143</v>
       </c>
       <c r="G58" t="n">
-        <v>9.136474609375</v>
+        <v>9.13647270202637</v>
       </c>
       <c r="H58" t="n">
         <v>1032573</v>
@@ -2080,7 +2080,7 @@
         <v>18.2984981536865</v>
       </c>
       <c r="G59" t="n">
-        <v>9.09944725036621</v>
+        <v>9.09944820404053</v>
       </c>
       <c r="H59" t="n">
         <v>645748</v>
@@ -2138,7 +2138,7 @@
         <v>18.242654800415</v>
       </c>
       <c r="G61" t="n">
-        <v>9.07167816162109</v>
+        <v>9.07167625427246</v>
       </c>
       <c r="H61" t="n">
         <v>769902</v>
@@ -2167,7 +2167,7 @@
         <v>18.4474182128906</v>
       </c>
       <c r="G62" t="n">
-        <v>9.17350101470947</v>
+        <v>9.17350292205811</v>
       </c>
       <c r="H62" t="n">
         <v>902526</v>
@@ -2196,7 +2196,7 @@
         <v>18.8476390838623</v>
       </c>
       <c r="G63" t="n">
-        <v>9.37252330780029</v>
+        <v>9.37252235412598</v>
       </c>
       <c r="H63" t="n">
         <v>1496702</v>
@@ -2283,7 +2283,7 @@
         <v>18.6614894866943</v>
       </c>
       <c r="G66" t="n">
-        <v>9.27995586395264</v>
+        <v>9.27995491027832</v>
       </c>
       <c r="H66" t="n">
         <v>1946521</v>
@@ -2312,7 +2312,7 @@
         <v>18.8011016845703</v>
       </c>
       <c r="G67" t="n">
-        <v>9.34938049316406</v>
+        <v>9.34938144683838</v>
       </c>
       <c r="H67" t="n">
         <v>942840</v>
@@ -2428,7 +2428,7 @@
         <v>18.4846477508545</v>
       </c>
       <c r="G71" t="n">
-        <v>9.19201564788818</v>
+        <v>9.19201469421387</v>
       </c>
       <c r="H71" t="n">
         <v>1170492</v>
@@ -2544,7 +2544,7 @@
         <v>20.0203819274902</v>
       </c>
       <c r="G75" t="n">
-        <v>9.95570278167725</v>
+        <v>9.95570087432861</v>
       </c>
       <c r="H75" t="n">
         <v>825610</v>
@@ -2602,7 +2602,7 @@
         <v>20.0110740661621</v>
       </c>
       <c r="G77" t="n">
-        <v>9.95107460021973</v>
+        <v>9.95107364654541</v>
       </c>
       <c r="H77" t="n">
         <v>874470</v>
@@ -2631,7 +2631,7 @@
         <v>19.9179992675781</v>
       </c>
       <c r="G78" t="n">
-        <v>9.90478897094727</v>
+        <v>9.90478992462158</v>
       </c>
       <c r="H78" t="n">
         <v>909812</v>
@@ -2689,7 +2689,7 @@
         <v>19.7597713470459</v>
       </c>
       <c r="G80" t="n">
-        <v>9.82610511779785</v>
+        <v>9.82610702514648</v>
       </c>
       <c r="H80" t="n">
         <v>1181674</v>
@@ -2718,7 +2718,7 @@
         <v>19.8807697296143</v>
       </c>
       <c r="G81" t="n">
-        <v>9.8862771987915</v>
+        <v>9.88627624511719</v>
       </c>
       <c r="H81" t="n">
         <v>854167</v>
@@ -2747,7 +2747,7 @@
         <v>20.3740653991699</v>
       </c>
       <c r="G82" t="n">
-        <v>10.1315822601318</v>
+        <v>10.1315813064575</v>
       </c>
       <c r="H82" t="n">
         <v>2117873</v>
@@ -2776,7 +2776,7 @@
         <v>20.569522857666</v>
       </c>
       <c r="G83" t="n">
-        <v>10.228777885437</v>
+        <v>10.22878074646</v>
       </c>
       <c r="H83" t="n">
         <v>1626344</v>
@@ -2805,7 +2805,7 @@
         <v>20.4578323364258</v>
       </c>
       <c r="G84" t="n">
-        <v>10.1732378005981</v>
+        <v>10.1732368469238</v>
       </c>
       <c r="H84" t="n">
         <v>1114038</v>
@@ -2834,7 +2834,7 @@
         <v>20.1041488647461</v>
       </c>
       <c r="G85" t="n">
-        <v>9.99735832214355</v>
+        <v>9.99735927581787</v>
       </c>
       <c r="H85" t="n">
         <v>901819</v>
@@ -2863,7 +2863,7 @@
         <v>19.4247035980225</v>
       </c>
       <c r="G86" t="n">
-        <v>9.65948486328125</v>
+        <v>9.65948390960693</v>
       </c>
       <c r="H86" t="n">
         <v>1530945</v>
@@ -2892,7 +2892,7 @@
         <v>19.5177783966064</v>
       </c>
       <c r="G87" t="n">
-        <v>9.70576953887939</v>
+        <v>9.70577049255371</v>
       </c>
       <c r="H87" t="n">
         <v>978597</v>
@@ -2950,7 +2950,7 @@
         <v>18.1588859558105</v>
       </c>
       <c r="G89" t="n">
-        <v>9.03002166748047</v>
+        <v>9.03002071380615</v>
       </c>
       <c r="H89" t="n">
         <v>1939059</v>
@@ -3095,7 +3095,7 @@
         <v>17.7400493621826</v>
       </c>
       <c r="G94" t="n">
-        <v>8.82174396514893</v>
+        <v>8.82174205780029</v>
       </c>
       <c r="H94" t="n">
         <v>836887</v>
@@ -3124,7 +3124,7 @@
         <v>17.9634284973145</v>
       </c>
       <c r="G95" t="n">
-        <v>8.93282508850098</v>
+        <v>8.93282413482666</v>
       </c>
       <c r="H95" t="n">
         <v>941183</v>
@@ -3182,7 +3182,7 @@
         <v>17.6469745635986</v>
       </c>
       <c r="G97" t="n">
-        <v>8.77545833587646</v>
+        <v>8.77545738220215</v>
       </c>
       <c r="H97" t="n">
         <v>739465</v>
@@ -3211,7 +3211,7 @@
         <v>17.3491363525391</v>
       </c>
       <c r="G98" t="n">
-        <v>8.62734889984131</v>
+        <v>8.62734985351562</v>
       </c>
       <c r="H98" t="n">
         <v>695305</v>
@@ -3240,7 +3240,7 @@
         <v>18.0378894805908</v>
       </c>
       <c r="G99" t="n">
-        <v>8.96985149383545</v>
+        <v>8.96985244750977</v>
       </c>
       <c r="H99" t="n">
         <v>1090211</v>
@@ -3269,7 +3269,7 @@
         <v>17.6097450256348</v>
       </c>
       <c r="G100" t="n">
-        <v>8.98885631561279</v>
+        <v>8.98885726928711</v>
       </c>
       <c r="H100" t="n">
         <v>696281</v>
@@ -3327,7 +3327,7 @@
         <v>18.6987209320068</v>
       </c>
       <c r="G102" t="n">
-        <v>9.54472064971924</v>
+        <v>9.54471969604492</v>
       </c>
       <c r="H102" t="n">
         <v>1374411</v>
@@ -3385,7 +3385,7 @@
         <v>18.3915729522705</v>
       </c>
       <c r="G104" t="n">
-        <v>9.38793754577637</v>
+        <v>9.38793659210205</v>
       </c>
       <c r="H104" t="n">
         <v>644357</v>
@@ -3414,7 +3414,7 @@
         <v>18.7545642852783</v>
       </c>
       <c r="G105" t="n">
-        <v>9.57322597503662</v>
+        <v>9.57322692871094</v>
       </c>
       <c r="H105" t="n">
         <v>554705</v>
@@ -3443,7 +3443,7 @@
         <v>18.3915729522705</v>
       </c>
       <c r="G106" t="n">
-        <v>9.38793754577637</v>
+        <v>9.38793659210205</v>
       </c>
       <c r="H106" t="n">
         <v>1058066</v>
@@ -3559,7 +3559,7 @@
         <v>17.4142875671387</v>
       </c>
       <c r="G110" t="n">
-        <v>8.88908576965332</v>
+        <v>8.88908386230469</v>
       </c>
       <c r="H110" t="n">
         <v>691022</v>
@@ -3588,7 +3588,7 @@
         <v>17.6004371643066</v>
       </c>
       <c r="G111" t="n">
-        <v>8.98410511016846</v>
+        <v>8.98410415649414</v>
       </c>
       <c r="H111" t="n">
         <v>654171</v>
@@ -3646,7 +3646,7 @@
         <v>17.3584423065186</v>
       </c>
       <c r="G113" t="n">
-        <v>8.8605785369873</v>
+        <v>8.86057758331299</v>
       </c>
       <c r="H113" t="n">
         <v>559096</v>
@@ -3675,7 +3675,7 @@
         <v>16.3160057067871</v>
       </c>
       <c r="G114" t="n">
-        <v>8.32846927642822</v>
+        <v>8.32847023010254</v>
       </c>
       <c r="H114" t="n">
         <v>1195069</v>
@@ -3733,7 +3733,7 @@
         <v>15.3107986450195</v>
       </c>
       <c r="G116" t="n">
-        <v>7.81536436080933</v>
+        <v>7.81536245346069</v>
       </c>
       <c r="H116" t="n">
         <v>1765822</v>
@@ -3762,7 +3762,7 @@
         <v>15.6365604400635</v>
       </c>
       <c r="G117" t="n">
-        <v>7.98164749145508</v>
+        <v>7.98164796829224</v>
       </c>
       <c r="H117" t="n">
         <v>1316058</v>
@@ -3791,7 +3791,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G118" t="n">
-        <v>8.05291271209717</v>
+        <v>8.05291366577148</v>
       </c>
       <c r="H118" t="n">
         <v>1965848</v>
@@ -3849,7 +3849,7 @@
         <v>17.3584423065186</v>
       </c>
       <c r="G120" t="n">
-        <v>8.8605785369873</v>
+        <v>8.86057758331299</v>
       </c>
       <c r="H120" t="n">
         <v>1671975</v>
@@ -3878,7 +3878,7 @@
         <v>17.3677501678467</v>
       </c>
       <c r="G121" t="n">
-        <v>8.86532974243164</v>
+        <v>8.86532878875732</v>
       </c>
       <c r="H121" t="n">
         <v>863019</v>
@@ -3936,7 +3936,7 @@
         <v>18.1402702331543</v>
       </c>
       <c r="G123" t="n">
-        <v>9.2596607208252</v>
+        <v>9.25966167449951</v>
       </c>
       <c r="H123" t="n">
         <v>897320</v>
@@ -3965,7 +3965,7 @@
         <v>15.6458683013916</v>
       </c>
       <c r="G124" t="n">
-        <v>7.98639917373657</v>
+        <v>7.98640012741089</v>
       </c>
       <c r="H124" t="n">
         <v>2529165</v>
@@ -3994,7 +3994,7 @@
         <v>13.79368019104</v>
       </c>
       <c r="G125" t="n">
-        <v>7.04095315933228</v>
+        <v>7.04095363616943</v>
       </c>
       <c r="H125" t="n">
         <v>2110454</v>
@@ -4023,7 +4023,7 @@
         <v>13.9984436035156</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14547491073608</v>
+        <v>7.14547348022461</v>
       </c>
       <c r="H126" t="n">
         <v>1958416</v>
@@ -4081,7 +4081,7 @@
         <v>13.579607963562</v>
       </c>
       <c r="G128" t="n">
-        <v>6.93168163299561</v>
+        <v>6.93168210983276</v>
       </c>
       <c r="H128" t="n">
         <v>2242320</v>
@@ -4168,7 +4168,7 @@
         <v>12.6953983306885</v>
       </c>
       <c r="G131" t="n">
-        <v>6.48033809661865</v>
+        <v>6.48033761978149</v>
       </c>
       <c r="H131" t="n">
         <v>1637699</v>
@@ -4226,7 +4226,7 @@
         <v>12.2486391067505</v>
       </c>
       <c r="G133" t="n">
-        <v>6.25229120254517</v>
+        <v>6.25229167938232</v>
       </c>
       <c r="H133" t="n">
         <v>1390549</v>
@@ -4255,7 +4255,7 @@
         <v>12.6767826080322</v>
       </c>
       <c r="G134" t="n">
-        <v>6.47083759307861</v>
+        <v>6.47083568572998</v>
       </c>
       <c r="H134" t="n">
         <v>1339495</v>
@@ -4284,7 +4284,7 @@
         <v>12.9746217727661</v>
       </c>
       <c r="G135" t="n">
-        <v>6.62286758422852</v>
+        <v>6.6228666305542</v>
       </c>
       <c r="H135" t="n">
         <v>1861100</v>
@@ -4313,7 +4313,7 @@
         <v>13.6540679931641</v>
       </c>
       <c r="G136" t="n">
-        <v>6.96968841552734</v>
+        <v>6.96968936920166</v>
       </c>
       <c r="H136" t="n">
         <v>1723762</v>
@@ -4342,7 +4342,7 @@
         <v>13.3189992904663</v>
       </c>
       <c r="G137" t="n">
-        <v>6.79865455627441</v>
+        <v>6.7986536026001</v>
       </c>
       <c r="H137" t="n">
         <v>902199</v>
@@ -4371,7 +4371,7 @@
         <v>13.7657566070557</v>
       </c>
       <c r="G138" t="n">
-        <v>7.02670097351074</v>
+        <v>7.02670049667358</v>
       </c>
       <c r="H138" t="n">
         <v>1294765</v>
@@ -4400,7 +4400,7 @@
         <v>13.7657566070557</v>
       </c>
       <c r="G139" t="n">
-        <v>7.02670097351074</v>
+        <v>7.02670049667358</v>
       </c>
       <c r="H139" t="n">
         <v>978688</v>
@@ -4429,7 +4429,7 @@
         <v>14.165979385376</v>
       </c>
       <c r="G140" t="n">
-        <v>7.23099231719971</v>
+        <v>7.23099279403687</v>
       </c>
       <c r="H140" t="n">
         <v>1308419</v>
@@ -4487,7 +4487,7 @@
         <v>14.1287488937378</v>
       </c>
       <c r="G142" t="n">
-        <v>7.21198892593384</v>
+        <v>7.211989402771</v>
       </c>
       <c r="H142" t="n">
         <v>826386</v>
@@ -4516,7 +4516,7 @@
         <v>14.4079732894897</v>
       </c>
       <c r="G143" t="n">
-        <v>7.3545184135437</v>
+        <v>7.35451889038086</v>
       </c>
       <c r="H143" t="n">
         <v>1143708</v>
@@ -4545,7 +4545,7 @@
         <v>14.2497463226318</v>
       </c>
       <c r="G144" t="n">
-        <v>7.27375173568726</v>
+        <v>7.27375268936157</v>
       </c>
       <c r="H144" t="n">
         <v>602071</v>
@@ -4574,7 +4574,7 @@
         <v>14.6778898239136</v>
       </c>
       <c r="G145" t="n">
-        <v>7.49229574203491</v>
+        <v>7.49229764938354</v>
       </c>
       <c r="H145" t="n">
         <v>879507</v>
@@ -4603,7 +4603,7 @@
         <v>14.4452028274536</v>
       </c>
       <c r="G146" t="n">
-        <v>7.37352323532104</v>
+        <v>7.37352228164673</v>
       </c>
       <c r="H146" t="n">
         <v>877418</v>
@@ -4690,7 +4690,7 @@
         <v>13.0863122940063</v>
       </c>
       <c r="G149" t="n">
-        <v>6.67988014221191</v>
+        <v>6.67987871170044</v>
       </c>
       <c r="H149" t="n">
         <v>1664978</v>
@@ -4719,7 +4719,7 @@
         <v>12.7977800369263</v>
       </c>
       <c r="G150" t="n">
-        <v>6.53259801864624</v>
+        <v>6.53259944915771</v>
       </c>
       <c r="H150" t="n">
         <v>1403849</v>
@@ -4748,7 +4748,7 @@
         <v>12.4068660736084</v>
       </c>
       <c r="G151" t="n">
-        <v>6.33305835723877</v>
+        <v>6.33305740356445</v>
       </c>
       <c r="H151" t="n">
         <v>1257013</v>
@@ -4777,7 +4777,7 @@
         <v>12.5464782714844</v>
       </c>
       <c r="G152" t="n">
-        <v>6.40432262420654</v>
+        <v>6.40432357788086</v>
       </c>
       <c r="H152" t="n">
         <v>1038379</v>
@@ -4806,7 +4806,7 @@
         <v>12.75124168396</v>
       </c>
       <c r="G153" t="n">
-        <v>6.50884342193604</v>
+        <v>6.50884294509888</v>
       </c>
       <c r="H153" t="n">
         <v>992648</v>
@@ -4835,7 +4835,7 @@
         <v>12.9746217727661</v>
       </c>
       <c r="G154" t="n">
-        <v>6.62286758422852</v>
+        <v>6.6228666305542</v>
       </c>
       <c r="H154" t="n">
         <v>1035242</v>
@@ -4864,7 +4864,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G155" t="n">
-        <v>6.8176589012146</v>
+        <v>6.81765604019165</v>
       </c>
       <c r="H155" t="n">
         <v>1301733</v>
@@ -4922,7 +4922,7 @@
         <v>13.5423784255981</v>
       </c>
       <c r="G157" t="n">
-        <v>6.91267824172974</v>
+        <v>6.91267776489258</v>
       </c>
       <c r="H157" t="n">
         <v>668173</v>
@@ -4980,7 +4980,7 @@
         <v>13.672682762146</v>
       </c>
       <c r="G159" t="n">
-        <v>6.97919082641602</v>
+        <v>6.97919130325317</v>
       </c>
       <c r="H159" t="n">
         <v>673395</v>
@@ -5009,7 +5009,7 @@
         <v>13.225923538208</v>
       </c>
       <c r="G160" t="n">
-        <v>6.75114488601685</v>
+        <v>6.75114440917969</v>
       </c>
       <c r="H160" t="n">
         <v>1068721</v>
@@ -5038,7 +5038,7 @@
         <v>12.8350095748901</v>
       </c>
       <c r="G161" t="n">
-        <v>6.55160140991211</v>
+        <v>6.55160236358643</v>
       </c>
       <c r="H161" t="n">
         <v>788798</v>
@@ -5067,7 +5067,7 @@
         <v>13.3003835678101</v>
       </c>
       <c r="G162" t="n">
-        <v>6.78915119171143</v>
+        <v>6.78915166854858</v>
       </c>
       <c r="H162" t="n">
         <v>798059</v>
@@ -5125,7 +5125,7 @@
         <v>12.75124168396</v>
       </c>
       <c r="G164" t="n">
-        <v>6.50884342193604</v>
+        <v>6.50884294509888</v>
       </c>
       <c r="H164" t="n">
         <v>888466</v>
@@ -5154,7 +5154,7 @@
         <v>12.9839286804199</v>
       </c>
       <c r="G165" t="n">
-        <v>6.62761878967285</v>
+        <v>6.62761831283569</v>
       </c>
       <c r="H165" t="n">
         <v>763641</v>
@@ -5212,7 +5212,7 @@
         <v>12.8350095748901</v>
       </c>
       <c r="G167" t="n">
-        <v>6.55160140991211</v>
+        <v>6.55160236358643</v>
       </c>
       <c r="H167" t="n">
         <v>957198</v>
@@ -5241,7 +5241,7 @@
         <v>13.0118522644043</v>
       </c>
       <c r="G168" t="n">
-        <v>6.64187145233154</v>
+        <v>6.64187240600586</v>
       </c>
       <c r="H168" t="n">
         <v>619541</v>
@@ -5299,7 +5299,7 @@
         <v>12.6860904693604</v>
       </c>
       <c r="G170" t="n">
-        <v>6.47558784484863</v>
+        <v>6.47558736801147</v>
       </c>
       <c r="H170" t="n">
         <v>799125</v>
@@ -5328,7 +5328,7 @@
         <v>12.8070869445801</v>
       </c>
       <c r="G171" t="n">
-        <v>6.53734970092773</v>
+        <v>6.53734827041626</v>
       </c>
       <c r="H171" t="n">
         <v>959793</v>
@@ -5357,7 +5357,7 @@
         <v>12.9839286804199</v>
       </c>
       <c r="G172" t="n">
-        <v>6.62761878967285</v>
+        <v>6.62761831283569</v>
       </c>
       <c r="H172" t="n">
         <v>1467796</v>
@@ -5444,7 +5444,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G175" t="n">
-        <v>6.8176589012146</v>
+        <v>6.81765604019165</v>
       </c>
       <c r="H175" t="n">
         <v>704858</v>
@@ -5473,7 +5473,7 @@
         <v>13.365535736084</v>
       </c>
       <c r="G176" t="n">
-        <v>6.8224081993103</v>
+        <v>6.82240867614746</v>
       </c>
       <c r="H176" t="n">
         <v>1052233</v>
@@ -5502,7 +5502,7 @@
         <v>13.579607963562</v>
       </c>
       <c r="G177" t="n">
-        <v>6.93168163299561</v>
+        <v>6.93168210983276</v>
       </c>
       <c r="H177" t="n">
         <v>1117409</v>
@@ -5531,7 +5531,7 @@
         <v>13.486533164978</v>
       </c>
       <c r="G178" t="n">
-        <v>6.88417291641235</v>
+        <v>6.88417196273804</v>
       </c>
       <c r="H178" t="n">
         <v>945978</v>
@@ -5560,7 +5560,7 @@
         <v>13.0863122940063</v>
       </c>
       <c r="G179" t="n">
-        <v>6.67988014221191</v>
+        <v>6.67987871170044</v>
       </c>
       <c r="H179" t="n">
         <v>1112661</v>
@@ -5589,7 +5589,7 @@
         <v>12.9001617431641</v>
       </c>
       <c r="G180" t="n">
-        <v>6.58485984802246</v>
+        <v>6.58485889434814</v>
       </c>
       <c r="H180" t="n">
         <v>949324</v>
@@ -5618,7 +5618,7 @@
         <v>12.9560070037842</v>
       </c>
       <c r="G181" t="n">
-        <v>6.61336517333984</v>
+        <v>6.61336660385132</v>
       </c>
       <c r="H181" t="n">
         <v>810204</v>
@@ -5647,7 +5647,7 @@
         <v>12.9001617431641</v>
       </c>
       <c r="G182" t="n">
-        <v>6.58485984802246</v>
+        <v>6.58485889434814</v>
       </c>
       <c r="H182" t="n">
         <v>814899</v>
@@ -5705,7 +5705,7 @@
         <v>12.5650930404663</v>
       </c>
       <c r="G184" t="n">
-        <v>6.41382455825806</v>
+        <v>6.41382265090942</v>
       </c>
       <c r="H184" t="n">
         <v>1046187</v>
@@ -5734,7 +5734,7 @@
         <v>12.3510208129883</v>
       </c>
       <c r="G185" t="n">
-        <v>6.30455112457275</v>
+        <v>6.30455160140991</v>
       </c>
       <c r="H185" t="n">
         <v>658084</v>
@@ -5763,7 +5763,7 @@
         <v>12.4534034729004</v>
       </c>
       <c r="G186" t="n">
-        <v>6.35681390762329</v>
+        <v>6.35681247711182</v>
       </c>
       <c r="H186" t="n">
         <v>571911</v>
@@ -5821,7 +5821,7 @@
         <v>12.7605495452881</v>
       </c>
       <c r="G188" t="n">
-        <v>6.51359510421753</v>
+        <v>6.51359462738037</v>
       </c>
       <c r="H188" t="n">
         <v>980114</v>
@@ -5879,7 +5879,7 @@
         <v>11.9414920806885</v>
       </c>
       <c r="G190" t="n">
-        <v>6.09550762176514</v>
+        <v>6.09550857543945</v>
       </c>
       <c r="H190" t="n">
         <v>1576015</v>
@@ -5908,7 +5908,7 @@
         <v>12.1462564468384</v>
       </c>
       <c r="G191" t="n">
-        <v>6.20003032684326</v>
+        <v>6.2000298500061</v>
       </c>
       <c r="H191" t="n">
         <v>1264960</v>
@@ -5937,7 +5937,7 @@
         <v>12.3324060440063</v>
       </c>
       <c r="G192" t="n">
-        <v>6.29505014419556</v>
+        <v>6.2950496673584</v>
       </c>
       <c r="H192" t="n">
         <v>1170339</v>
@@ -5966,7 +5966,7 @@
         <v>12.1927938461304</v>
       </c>
       <c r="G193" t="n">
-        <v>6.22378587722778</v>
+        <v>6.22378540039062</v>
       </c>
       <c r="H193" t="n">
         <v>1328972</v>
@@ -5995,7 +5995,7 @@
         <v>12.7047052383423</v>
       </c>
       <c r="G194" t="n">
-        <v>6.48508834838867</v>
+        <v>6.48508787155151</v>
       </c>
       <c r="H194" t="n">
         <v>1713998</v>
@@ -6024,7 +6024,7 @@
         <v>12.9466991424561</v>
       </c>
       <c r="G195" t="n">
-        <v>6.60861492156982</v>
+        <v>6.60861301422119</v>
       </c>
       <c r="H195" t="n">
         <v>1924520</v>
@@ -6053,7 +6053,7 @@
         <v>13.2166156768799</v>
       </c>
       <c r="G196" t="n">
-        <v>6.74639368057251</v>
+        <v>6.74639225006104</v>
       </c>
       <c r="H196" t="n">
         <v>1565361</v>
@@ -6082,7 +6082,7 @@
         <v>13.4958410263062</v>
       </c>
       <c r="G197" t="n">
-        <v>6.88892269134521</v>
+        <v>6.88892364501953</v>
       </c>
       <c r="H197" t="n">
         <v>2130285</v>
@@ -6169,7 +6169,7 @@
         <v>14.1566705703735</v>
       </c>
       <c r="G200" t="n">
-        <v>7.22624111175537</v>
+        <v>7.22624158859253</v>
       </c>
       <c r="H200" t="n">
         <v>2121391</v>
@@ -6198,7 +6198,7 @@
         <v>13.9891366958618</v>
       </c>
       <c r="G201" t="n">
-        <v>7.14072465896606</v>
+        <v>7.14072513580322</v>
       </c>
       <c r="H201" t="n">
         <v>1316501</v>
@@ -6227,7 +6227,7 @@
         <v>13.7750654220581</v>
       </c>
       <c r="G202" t="n">
-        <v>7.03145027160645</v>
+        <v>7.03145170211792</v>
       </c>
       <c r="H202" t="n">
         <v>2461347</v>
@@ -6256,7 +6256,7 @@
         <v>13.9239845275879</v>
       </c>
       <c r="G203" t="n">
-        <v>7.10746765136719</v>
+        <v>7.10746717453003</v>
       </c>
       <c r="H203" t="n">
         <v>1101505</v>
@@ -6285,7 +6285,7 @@
         <v>13.6540679931641</v>
       </c>
       <c r="G204" t="n">
-        <v>6.96968841552734</v>
+        <v>6.96968936920166</v>
       </c>
       <c r="H204" t="n">
         <v>1456074</v>
@@ -6314,7 +6314,7 @@
         <v>13.7564496994019</v>
       </c>
       <c r="G205" t="n">
-        <v>7.02195024490356</v>
+        <v>7.02194881439209</v>
       </c>
       <c r="H205" t="n">
         <v>1322738</v>
@@ -6343,7 +6343,7 @@
         <v>13.9891366958618</v>
       </c>
       <c r="G206" t="n">
-        <v>7.14072465896606</v>
+        <v>7.14072513580322</v>
       </c>
       <c r="H206" t="n">
         <v>583960</v>
@@ -6372,7 +6372,7 @@
         <v>14.0356740951538</v>
       </c>
       <c r="G207" t="n">
-        <v>7.16447925567627</v>
+        <v>7.16447877883911</v>
       </c>
       <c r="H207" t="n">
         <v>887180</v>
@@ -6459,7 +6459,7 @@
         <v>13.9239845275879</v>
       </c>
       <c r="G210" t="n">
-        <v>7.10746765136719</v>
+        <v>7.10746717453003</v>
       </c>
       <c r="H210" t="n">
         <v>1043584</v>
@@ -6488,7 +6488,7 @@
         <v>14.0542888641357</v>
       </c>
       <c r="G211" t="n">
-        <v>7.17398166656494</v>
+        <v>7.17398118972778</v>
       </c>
       <c r="H211" t="n">
         <v>824076</v>
@@ -6517,7 +6517,7 @@
         <v>14.240439414978</v>
       </c>
       <c r="G212" t="n">
-        <v>7.26900100708008</v>
+        <v>7.26900053024292</v>
       </c>
       <c r="H212" t="n">
         <v>1234266</v>
@@ -6546,7 +6546,7 @@
         <v>13.8309097290039</v>
       </c>
       <c r="G213" t="n">
-        <v>7.0599570274353</v>
+        <v>7.05995845794678</v>
       </c>
       <c r="H213" t="n">
         <v>1865753</v>
@@ -6575,7 +6575,7 @@
         <v>13.6075296401978</v>
       </c>
       <c r="G214" t="n">
-        <v>6.94593334197998</v>
+        <v>6.9459342956543</v>
       </c>
       <c r="H214" t="n">
         <v>1150843</v>
@@ -6604,7 +6604,7 @@
         <v>13.4213809967041</v>
       </c>
       <c r="G215" t="n">
-        <v>6.85091543197632</v>
+        <v>6.850914478302</v>
       </c>
       <c r="H215" t="n">
         <v>629318</v>
@@ -6633,7 +6633,7 @@
         <v>12.9560070037842</v>
       </c>
       <c r="G216" t="n">
-        <v>6.61336517333984</v>
+        <v>6.61336660385132</v>
       </c>
       <c r="H216" t="n">
         <v>2014598</v>
@@ -6662,7 +6662,7 @@
         <v>13.179386138916</v>
       </c>
       <c r="G217" t="n">
-        <v>6.72738885879517</v>
+        <v>6.72739028930664</v>
       </c>
       <c r="H217" t="n">
         <v>892718</v>
@@ -6720,7 +6720,7 @@
         <v>13.2538461685181</v>
       </c>
       <c r="G219" t="n">
-        <v>6.76539707183838</v>
+        <v>6.7653980255127</v>
       </c>
       <c r="H219" t="n">
         <v>715497</v>
@@ -6749,7 +6749,7 @@
         <v>14.2218236923218</v>
       </c>
       <c r="G220" t="n">
-        <v>7.25949954986572</v>
+        <v>7.25949859619141</v>
       </c>
       <c r="H220" t="n">
         <v>4015584</v>
@@ -6865,7 +6865,7 @@
         <v>15.7389421463013</v>
       </c>
       <c r="G224" t="n">
-        <v>8.03390693664551</v>
+        <v>8.03390789031982</v>
       </c>
       <c r="H224" t="n">
         <v>3139728</v>
@@ -6894,7 +6894,7 @@
         <v>15.6179447174072</v>
       </c>
       <c r="G225" t="n">
-        <v>7.97214555740356</v>
+        <v>7.9721474647522</v>
       </c>
       <c r="H225" t="n">
         <v>2372479</v>
@@ -6923,7 +6923,7 @@
         <v>15.1618785858154</v>
       </c>
       <c r="G226" t="n">
-        <v>7.73934841156006</v>
+        <v>7.73934745788574</v>
       </c>
       <c r="H226" t="n">
         <v>1616476</v>
@@ -6981,7 +6981,7 @@
         <v>14.7058134078979</v>
       </c>
       <c r="G228" t="n">
-        <v>7.50655126571655</v>
+        <v>7.50655031204224</v>
       </c>
       <c r="H228" t="n">
         <v>2118027</v>
@@ -7010,7 +7010,7 @@
         <v>13.7285280227661</v>
       </c>
       <c r="G229" t="n">
-        <v>7.48119068145752</v>
+        <v>7.4811897277832</v>
       </c>
       <c r="H229" t="n">
         <v>2904384</v>
@@ -7039,7 +7039,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G230" t="n">
-        <v>7.27831077575684</v>
+        <v>7.27830982208252</v>
       </c>
       <c r="H230" t="n">
         <v>2662302</v>
@@ -7068,7 +7068,7 @@
         <v>13.3841514587402</v>
       </c>
       <c r="G231" t="n">
-        <v>7.29352807998657</v>
+        <v>7.29352760314941</v>
       </c>
       <c r="H231" t="n">
         <v>2165235</v>
@@ -7097,7 +7097,7 @@
         <v>13.2166156768799</v>
       </c>
       <c r="G232" t="n">
-        <v>7.20223140716553</v>
+        <v>7.20223045349121</v>
       </c>
       <c r="H232" t="n">
         <v>1002226</v>
@@ -7126,7 +7126,7 @@
         <v>13.225923538208</v>
       </c>
       <c r="G233" t="n">
-        <v>7.20730352401733</v>
+        <v>7.20730304718018</v>
       </c>
       <c r="H233" t="n">
         <v>859349</v>
@@ -7184,7 +7184,7 @@
         <v>12.8815469741821</v>
       </c>
       <c r="G235" t="n">
-        <v>7.01963901519775</v>
+        <v>7.01963996887207</v>
       </c>
       <c r="H235" t="n">
         <v>1410424</v>
@@ -7213,7 +7213,7 @@
         <v>13.1049270629883</v>
       </c>
       <c r="G236" t="n">
-        <v>7.14136695861816</v>
+        <v>7.14136743545532</v>
       </c>
       <c r="H236" t="n">
         <v>2008644</v>
@@ -7242,7 +7242,7 @@
         <v>13.3096914291382</v>
       </c>
       <c r="G237" t="n">
-        <v>7.25295209884644</v>
+        <v>7.25295162200928</v>
       </c>
       <c r="H237" t="n">
         <v>1489850</v>
@@ -7271,7 +7271,7 @@
         <v>13.1980009078979</v>
       </c>
       <c r="G238" t="n">
-        <v>7.1920862197876</v>
+        <v>7.19208717346191</v>
       </c>
       <c r="H238" t="n">
         <v>1515042</v>
@@ -7300,7 +7300,7 @@
         <v>13.4958410263062</v>
       </c>
       <c r="G239" t="n">
-        <v>7.35439109802246</v>
+        <v>7.3543906211853</v>
       </c>
       <c r="H239" t="n">
         <v>2793136</v>
@@ -7358,7 +7358,7 @@
         <v>14.5941228866577</v>
       </c>
       <c r="G241" t="n">
-        <v>7.95288610458374</v>
+        <v>7.95288705825806</v>
       </c>
       <c r="H241" t="n">
         <v>2620407</v>
@@ -7387,7 +7387,7 @@
         <v>14.9198846817017</v>
       </c>
       <c r="G242" t="n">
-        <v>8.13040542602539</v>
+        <v>8.13040637969971</v>
       </c>
       <c r="H242" t="n">
         <v>2256729</v>
@@ -7532,7 +7532,7 @@
         <v>14.8640403747559</v>
       </c>
       <c r="G247" t="n">
-        <v>8.09997272491455</v>
+        <v>8.09997367858887</v>
       </c>
       <c r="H247" t="n">
         <v>1692467</v>
@@ -7619,7 +7619,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G250" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H250" t="n">
         <v>1191300</v>
@@ -7648,7 +7648,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G251" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H251" t="n">
         <v>1163304</v>
@@ -7706,7 +7706,7 @@
         <v>14.8826551437378</v>
       </c>
       <c r="G253" t="n">
-        <v>8.11011695861816</v>
+        <v>8.11011791229248</v>
       </c>
       <c r="H253" t="n">
         <v>716397</v>
@@ -7735,7 +7735,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G254" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H254" t="n">
         <v>536435</v>
@@ -7764,7 +7764,7 @@
         <v>14.7430419921875</v>
       </c>
       <c r="G255" t="n">
-        <v>8.03403663635254</v>
+        <v>8.03403759002686</v>
       </c>
       <c r="H255" t="n">
         <v>637989</v>
@@ -7822,7 +7822,7 @@
         <v>14.7616567611694</v>
       </c>
       <c r="G257" t="n">
-        <v>8.04418087005615</v>
+        <v>8.04418182373047</v>
       </c>
       <c r="H257" t="n">
         <v>491051</v>
@@ -7851,7 +7851,7 @@
         <v>15.0222673416138</v>
       </c>
       <c r="G258" t="n">
-        <v>8.18619728088379</v>
+        <v>8.18619632720947</v>
       </c>
       <c r="H258" t="n">
         <v>989103</v>
@@ -7880,7 +7880,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G259" t="n">
-        <v>8.59702968597412</v>
+        <v>8.5970287322998</v>
       </c>
       <c r="H259" t="n">
         <v>2711349</v>
@@ -7909,7 +7909,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G260" t="n">
-        <v>8.63760471343994</v>
+        <v>8.63760375976562</v>
       </c>
       <c r="H260" t="n">
         <v>1389851</v>
@@ -7996,7 +7996,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G263" t="n">
-        <v>8.59702968597412</v>
+        <v>8.5970287322998</v>
       </c>
       <c r="H263" t="n">
         <v>1770736</v>
@@ -8025,7 +8025,7 @@
         <v>15.6737899780273</v>
       </c>
       <c r="G264" t="n">
-        <v>8.54123783111572</v>
+        <v>8.54123687744141</v>
       </c>
       <c r="H264" t="n">
         <v>1167328</v>
@@ -8054,7 +8054,7 @@
         <v>16.1577796936035</v>
       </c>
       <c r="G265" t="n">
-        <v>8.80498123168945</v>
+        <v>8.80498027801514</v>
       </c>
       <c r="H265" t="n">
         <v>2189374</v>
@@ -8199,7 +8199,7 @@
         <v>16.3718509674072</v>
       </c>
       <c r="G270" t="n">
-        <v>8.92163562774658</v>
+        <v>8.9216365814209</v>
       </c>
       <c r="H270" t="n">
         <v>1906829</v>
@@ -8257,7 +8257,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G272" t="n">
-        <v>8.84048461914062</v>
+        <v>8.84048366546631</v>
       </c>
       <c r="H272" t="n">
         <v>1719302</v>
@@ -8344,7 +8344,7 @@
         <v>16.3904666900635</v>
       </c>
       <c r="G275" t="n">
-        <v>8.93178176879883</v>
+        <v>8.93178081512451</v>
       </c>
       <c r="H275" t="n">
         <v>1778402</v>
@@ -8431,7 +8431,7 @@
         <v>15.6737899780273</v>
       </c>
       <c r="G278" t="n">
-        <v>8.54123783111572</v>
+        <v>8.54123687744141</v>
       </c>
       <c r="H278" t="n">
         <v>1874324</v>
@@ -8489,7 +8489,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G280" t="n">
-        <v>8.63760471343994</v>
+        <v>8.63760375976562</v>
       </c>
       <c r="H280" t="n">
         <v>1769425</v>
@@ -8547,7 +8547,7 @@
         <v>15.7017126083374</v>
       </c>
       <c r="G282" t="n">
-        <v>8.55645370483398</v>
+        <v>8.55645275115967</v>
       </c>
       <c r="H282" t="n">
         <v>1514551</v>
@@ -8605,7 +8605,7 @@
         <v>15.6737899780273</v>
       </c>
       <c r="G284" t="n">
-        <v>8.54123783111572</v>
+        <v>8.54123687744141</v>
       </c>
       <c r="H284" t="n">
         <v>1437933</v>
@@ -8663,7 +8663,7 @@
         <v>15.7017126083374</v>
       </c>
       <c r="G286" t="n">
-        <v>8.55645370483398</v>
+        <v>8.55645275115967</v>
       </c>
       <c r="H286" t="n">
         <v>1117237</v>
@@ -8692,7 +8692,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G287" t="n">
-        <v>8.63760471343994</v>
+        <v>8.63760375976562</v>
       </c>
       <c r="H287" t="n">
         <v>1241506</v>
@@ -8721,7 +8721,7 @@
         <v>16.027473449707</v>
       </c>
       <c r="G288" t="n">
-        <v>8.73397254943848</v>
+        <v>8.73397159576416</v>
       </c>
       <c r="H288" t="n">
         <v>1445220</v>
@@ -8750,7 +8750,7 @@
         <v>16.0740127563477</v>
       </c>
       <c r="G289" t="n">
-        <v>8.75933361053467</v>
+        <v>8.75933265686035</v>
       </c>
       <c r="H289" t="n">
         <v>1296170</v>
@@ -8808,7 +8808,7 @@
         <v>16.0367813110352</v>
       </c>
       <c r="G291" t="n">
-        <v>8.73904514312744</v>
+        <v>8.73904609680176</v>
       </c>
       <c r="H291" t="n">
         <v>1317032</v>
@@ -8837,7 +8837,7 @@
         <v>15.9809370040894</v>
       </c>
       <c r="G292" t="n">
-        <v>8.7086124420166</v>
+        <v>8.70861339569092</v>
       </c>
       <c r="H292" t="n">
         <v>1369141</v>
@@ -8953,7 +8953,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G296" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H296" t="n">
         <v>2779859</v>
@@ -9011,7 +9011,7 @@
         <v>14.8733472824097</v>
       </c>
       <c r="G298" t="n">
-        <v>8.10504531860352</v>
+        <v>8.1050443649292</v>
       </c>
       <c r="H298" t="n">
         <v>1593786</v>
@@ -9127,7 +9127,7 @@
         <v>15.0781116485596</v>
       </c>
       <c r="G302" t="n">
-        <v>8.216628074646</v>
+        <v>8.21662902832031</v>
       </c>
       <c r="H302" t="n">
         <v>1289973</v>
@@ -9156,7 +9156,7 @@
         <v>15.0688037872314</v>
       </c>
       <c r="G303" t="n">
-        <v>8.21155834197998</v>
+        <v>8.21155738830566</v>
       </c>
       <c r="H303" t="n">
         <v>1281552</v>
@@ -9185,7 +9185,7 @@
         <v>15.0222673416138</v>
       </c>
       <c r="G304" t="n">
-        <v>8.18619728088379</v>
+        <v>8.18619632720947</v>
       </c>
       <c r="H304" t="n">
         <v>1165149</v>
@@ -9214,7 +9214,7 @@
         <v>14.9478073120117</v>
       </c>
       <c r="G305" t="n">
-        <v>8.14562129974365</v>
+        <v>8.14562034606934</v>
       </c>
       <c r="H305" t="n">
         <v>1260594</v>
@@ -9243,7 +9243,7 @@
         <v>14.7802715301514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.05432319641113</v>
+        <v>8.05432415008545</v>
       </c>
       <c r="H306" t="n">
         <v>2226802</v>
@@ -9272,7 +9272,7 @@
         <v>14.7151203155518</v>
       </c>
       <c r="G307" t="n">
-        <v>8.01882171630859</v>
+        <v>8.01882076263428</v>
       </c>
       <c r="H307" t="n">
         <v>1737593</v>
@@ -9330,7 +9330,7 @@
         <v>14.4265880584717</v>
       </c>
       <c r="G309" t="n">
-        <v>7.86158847808838</v>
+        <v>7.86159038543701</v>
       </c>
       <c r="H309" t="n">
         <v>1981796</v>
@@ -9359,7 +9359,7 @@
         <v>14.6034297943115</v>
       </c>
       <c r="G310" t="n">
-        <v>7.95795822143555</v>
+        <v>7.95795726776123</v>
       </c>
       <c r="H310" t="n">
         <v>1613226</v>
@@ -9504,7 +9504,7 @@
         <v>14.6778898239136</v>
       </c>
       <c r="G315" t="n">
-        <v>7.99853277206421</v>
+        <v>7.99853372573853</v>
       </c>
       <c r="H315" t="n">
         <v>1274979</v>
@@ -9533,7 +9533,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G316" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H316" t="n">
         <v>1290856</v>
@@ -9562,7 +9562,7 @@
         <v>14.9943437576294</v>
       </c>
       <c r="G317" t="n">
-        <v>8.17098140716553</v>
+        <v>8.17098236083984</v>
       </c>
       <c r="H317" t="n">
         <v>1048653</v>
@@ -9591,7 +9591,7 @@
         <v>14.8826551437378</v>
       </c>
       <c r="G318" t="n">
-        <v>8.11011695861816</v>
+        <v>8.11011791229248</v>
       </c>
       <c r="H318" t="n">
         <v>1471088</v>
@@ -9649,7 +9649,7 @@
         <v>14.8919620513916</v>
       </c>
       <c r="G320" t="n">
-        <v>8.11519050598145</v>
+        <v>8.11518955230713</v>
       </c>
       <c r="H320" t="n">
         <v>1664072</v>
@@ -9707,7 +9707,7 @@
         <v>15.1991090774536</v>
       </c>
       <c r="G322" t="n">
-        <v>8.28256511688232</v>
+        <v>8.28256416320801</v>
       </c>
       <c r="H322" t="n">
         <v>1777515</v>
@@ -9736,7 +9736,7 @@
         <v>15.1804943084717</v>
       </c>
       <c r="G323" t="n">
-        <v>8.27242183685303</v>
+        <v>8.27242088317871</v>
       </c>
       <c r="H323" t="n">
         <v>1559872</v>
@@ -9823,7 +9823,7 @@
         <v>15.6644830703735</v>
       </c>
       <c r="G326" t="n">
-        <v>8.53616428375244</v>
+        <v>8.53616523742676</v>
       </c>
       <c r="H326" t="n">
         <v>2732039</v>
@@ -9852,7 +9852,7 @@
         <v>15.8227100372314</v>
       </c>
       <c r="G327" t="n">
-        <v>8.62238883972168</v>
+        <v>8.622389793396</v>
       </c>
       <c r="H327" t="n">
         <v>1498638</v>
@@ -9881,7 +9881,7 @@
         <v>15.8599395751953</v>
       </c>
       <c r="G328" t="n">
-        <v>8.64267635345459</v>
+        <v>8.64267730712891</v>
       </c>
       <c r="H328" t="n">
         <v>1279031</v>
@@ -9939,7 +9939,7 @@
         <v>16.1019344329834</v>
       </c>
       <c r="G330" t="n">
-        <v>8.7745475769043</v>
+        <v>8.77454853057861</v>
       </c>
       <c r="H330" t="n">
         <v>2102517</v>
@@ -10055,7 +10055,7 @@
         <v>15.8320169448853</v>
       </c>
       <c r="G334" t="n">
-        <v>8.62746143341064</v>
+        <v>8.62746047973633</v>
       </c>
       <c r="H334" t="n">
         <v>1450006</v>
@@ -10084,7 +10084,7 @@
         <v>15.934398651123</v>
       </c>
       <c r="G335" t="n">
-        <v>8.68325233459473</v>
+        <v>8.68325328826904</v>
       </c>
       <c r="H335" t="n">
         <v>950729</v>
@@ -10142,7 +10142,7 @@
         <v>16.6603832244873</v>
       </c>
       <c r="G337" t="n">
-        <v>9.0788688659668</v>
+        <v>9.07886791229248</v>
       </c>
       <c r="H337" t="n">
         <v>1496690</v>
@@ -10171,7 +10171,7 @@
         <v>16.6696891784668</v>
       </c>
       <c r="G338" t="n">
-        <v>9.08393955230713</v>
+        <v>9.08393859863281</v>
       </c>
       <c r="H338" t="n">
         <v>1382101</v>
@@ -10200,7 +10200,7 @@
         <v>16.6324596405029</v>
       </c>
       <c r="G339" t="n">
-        <v>9.06365203857422</v>
+        <v>9.06365299224854</v>
       </c>
       <c r="H339" t="n">
         <v>956801</v>
@@ -10287,7 +10287,7 @@
         <v>16.6696891784668</v>
       </c>
       <c r="G342" t="n">
-        <v>9.08393955230713</v>
+        <v>9.08393859863281</v>
       </c>
       <c r="H342" t="n">
         <v>2272565</v>
@@ -10316,7 +10316,7 @@
         <v>17.2653694152832</v>
       </c>
       <c r="G343" t="n">
-        <v>9.40854740142822</v>
+        <v>9.40854835510254</v>
       </c>
       <c r="H343" t="n">
         <v>4373453</v>
@@ -10345,7 +10345,7 @@
         <v>17.4049816131592</v>
       </c>
       <c r="G344" t="n">
-        <v>9.48462867736816</v>
+        <v>9.48462677001953</v>
       </c>
       <c r="H344" t="n">
         <v>2070466</v>
@@ -10374,7 +10374,7 @@
         <v>17.7307415008545</v>
       </c>
       <c r="G345" t="n">
-        <v>9.66214752197266</v>
+        <v>9.66214656829834</v>
       </c>
       <c r="H345" t="n">
         <v>2677665</v>
@@ -10432,7 +10432,7 @@
         <v>17.907585144043</v>
       </c>
       <c r="G347" t="n">
-        <v>9.75851631164551</v>
+        <v>9.75851535797119</v>
       </c>
       <c r="H347" t="n">
         <v>1870966</v>
@@ -10461,7 +10461,7 @@
         <v>17.7121276855469</v>
       </c>
       <c r="G348" t="n">
-        <v>9.65200328826904</v>
+        <v>9.65200233459473</v>
       </c>
       <c r="H348" t="n">
         <v>2382877</v>
@@ -10490,7 +10490,7 @@
         <v>18.000659942627</v>
       </c>
       <c r="G349" t="n">
-        <v>9.80923652648926</v>
+        <v>9.80923748016357</v>
       </c>
       <c r="H349" t="n">
         <v>1202722</v>
@@ -10519,7 +10519,7 @@
         <v>18.0192737579346</v>
       </c>
       <c r="G350" t="n">
-        <v>9.81937980651855</v>
+        <v>9.81937885284424</v>
       </c>
       <c r="H350" t="n">
         <v>1545277</v>
@@ -10548,7 +10548,7 @@
         <v>17.8889694213867</v>
       </c>
       <c r="G351" t="n">
-        <v>9.74837112426758</v>
+        <v>9.74837207794189</v>
       </c>
       <c r="H351" t="n">
         <v>1138287</v>
@@ -10577,7 +10577,7 @@
         <v>17.535285949707</v>
       </c>
       <c r="G352" t="n">
-        <v>9.55563640594482</v>
+        <v>9.55563545227051</v>
       </c>
       <c r="H352" t="n">
         <v>1889581</v>
@@ -10606,7 +10606,7 @@
         <v>17.488748550415</v>
       </c>
       <c r="G353" t="n">
-        <v>9.53027725219727</v>
+        <v>9.53027534484863</v>
       </c>
       <c r="H353" t="n">
         <v>2235701</v>
@@ -10751,7 +10751,7 @@
         <v>17.4049816131592</v>
       </c>
       <c r="G358" t="n">
-        <v>10.0054750442505</v>
+        <v>10.0054759979248</v>
       </c>
       <c r="H358" t="n">
         <v>1186100</v>
@@ -10838,7 +10838,7 @@
         <v>17.1909084320068</v>
       </c>
       <c r="G361" t="n">
-        <v>9.88241195678711</v>
+        <v>9.88241291046143</v>
       </c>
       <c r="H361" t="n">
         <v>1473782</v>
@@ -10867,7 +10867,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G362" t="n">
-        <v>9.65769195556641</v>
+        <v>9.65769004821777</v>
       </c>
       <c r="H362" t="n">
         <v>1467902</v>
@@ -10925,7 +10925,7 @@
         <v>16.967529296875</v>
       </c>
       <c r="G364" t="n">
-        <v>9.75400161743164</v>
+        <v>9.75400066375732</v>
       </c>
       <c r="H364" t="n">
         <v>1117154</v>
@@ -11012,7 +11012,7 @@
         <v>16.2508544921875</v>
       </c>
       <c r="G367" t="n">
-        <v>9.34201240539551</v>
+        <v>9.34201145172119</v>
       </c>
       <c r="H367" t="n">
         <v>1126137</v>
@@ -11041,7 +11041,7 @@
         <v>16.8837623596191</v>
       </c>
       <c r="G368" t="n">
-        <v>9.70584678649902</v>
+        <v>9.70584583282471</v>
       </c>
       <c r="H368" t="n">
         <v>2069336</v>
@@ -11070,7 +11070,7 @@
         <v>16.8372249603271</v>
       </c>
       <c r="G369" t="n">
-        <v>9.67909336090088</v>
+        <v>9.67909240722656</v>
       </c>
       <c r="H369" t="n">
         <v>857040</v>
@@ -11128,7 +11128,7 @@
         <v>16.5859222412109</v>
       </c>
       <c r="G371" t="n">
-        <v>9.53462886810303</v>
+        <v>9.53462791442871</v>
       </c>
       <c r="H371" t="n">
         <v>1099573</v>
@@ -11186,7 +11186,7 @@
         <v>16.3160057067871</v>
       </c>
       <c r="G373" t="n">
-        <v>9.37946319580078</v>
+        <v>9.3794641494751</v>
       </c>
       <c r="H373" t="n">
         <v>857340</v>
@@ -11215,7 +11215,7 @@
         <v>16.688304901123</v>
       </c>
       <c r="G374" t="n">
-        <v>9.59348487854004</v>
+        <v>9.59348583221436</v>
       </c>
       <c r="H374" t="n">
         <v>774480</v>
@@ -11273,7 +11273,7 @@
         <v>16.688304901123</v>
       </c>
       <c r="G376" t="n">
-        <v>9.59348487854004</v>
+        <v>9.59348583221436</v>
       </c>
       <c r="H376" t="n">
         <v>1019593</v>
@@ -11302,7 +11302,7 @@
         <v>16.8372249603271</v>
       </c>
       <c r="G377" t="n">
-        <v>9.67909336090088</v>
+        <v>9.67909240722656</v>
       </c>
       <c r="H377" t="n">
         <v>848907</v>
@@ -11331,7 +11331,7 @@
         <v>16.5114631652832</v>
       </c>
       <c r="G378" t="n">
-        <v>9.49182605743408</v>
+        <v>9.49182415008545</v>
       </c>
       <c r="H378" t="n">
         <v>873978</v>
@@ -11418,7 +11418,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G381" t="n">
-        <v>9.63093757629395</v>
+        <v>9.63093852996826</v>
       </c>
       <c r="H381" t="n">
         <v>691418</v>
@@ -11505,7 +11505,7 @@
         <v>16.3346214294434</v>
       </c>
       <c r="G384" t="n">
-        <v>9.39016628265381</v>
+        <v>9.39016532897949</v>
       </c>
       <c r="H384" t="n">
         <v>637739</v>
@@ -11534,7 +11534,7 @@
         <v>16.6510753631592</v>
       </c>
       <c r="G385" t="n">
-        <v>9.57208251953125</v>
+        <v>9.57208347320557</v>
       </c>
       <c r="H385" t="n">
         <v>857466</v>
@@ -11592,7 +11592,7 @@
         <v>16.874454498291</v>
       </c>
       <c r="G387" t="n">
-        <v>9.70049571990967</v>
+        <v>9.70049476623535</v>
       </c>
       <c r="H387" t="n">
         <v>2013500</v>
@@ -11737,7 +11737,7 @@
         <v>17.3025989532471</v>
       </c>
       <c r="G392" t="n">
-        <v>9.94661903381348</v>
+        <v>9.94661998748779</v>
       </c>
       <c r="H392" t="n">
         <v>1866757</v>
@@ -11766,7 +11766,7 @@
         <v>17.0792198181152</v>
       </c>
       <c r="G393" t="n">
-        <v>9.81820774078369</v>
+        <v>9.81820869445801</v>
       </c>
       <c r="H393" t="n">
         <v>645461</v>
@@ -11795,7 +11795,7 @@
         <v>16.9302997589111</v>
       </c>
       <c r="G394" t="n">
-        <v>9.73259925842285</v>
+        <v>9.73259830474854</v>
       </c>
       <c r="H394" t="n">
         <v>627732</v>
@@ -11824,7 +11824,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G395" t="n">
-        <v>9.65769195556641</v>
+        <v>9.65769004821777</v>
       </c>
       <c r="H395" t="n">
         <v>803256</v>
@@ -11853,7 +11853,7 @@
         <v>16.8930702209473</v>
       </c>
       <c r="G396" t="n">
-        <v>9.71119785308838</v>
+        <v>9.71119689941406</v>
       </c>
       <c r="H396" t="n">
         <v>1812036</v>
@@ -11940,7 +11940,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G399" t="n">
-        <v>9.65769195556641</v>
+        <v>9.65769004821777</v>
       </c>
       <c r="H399" t="n">
         <v>864759</v>
@@ -11969,7 +11969,7 @@
         <v>17.014066696167</v>
       </c>
       <c r="G400" t="n">
-        <v>9.78075218200684</v>
+        <v>9.78075313568115</v>
       </c>
       <c r="H400" t="n">
         <v>1162930</v>
@@ -11998,7 +11998,7 @@
         <v>17.1164493560791</v>
       </c>
       <c r="G401" t="n">
-        <v>9.83960914611816</v>
+        <v>9.83961009979248</v>
       </c>
       <c r="H401" t="n">
         <v>1151500</v>
@@ -12056,7 +12056,7 @@
         <v>17.581823348999</v>
       </c>
       <c r="G403" t="n">
-        <v>10.1071348190308</v>
+        <v>10.1071357727051</v>
       </c>
       <c r="H403" t="n">
         <v>2502607</v>
@@ -12172,7 +12172,7 @@
         <v>17.5073623657227</v>
       </c>
       <c r="G407" t="n">
-        <v>10.0643310546875</v>
+        <v>10.0643301010132</v>
       </c>
       <c r="H407" t="n">
         <v>616893</v>
@@ -12230,7 +12230,7 @@
         <v>17.6842041015625</v>
       </c>
       <c r="G409" t="n">
-        <v>10.1659898757935</v>
+        <v>10.1659908294678</v>
       </c>
       <c r="H409" t="n">
         <v>1193927</v>
@@ -12317,7 +12317,7 @@
         <v>17.488748550415</v>
       </c>
       <c r="G412" t="n">
-        <v>10.0536298751831</v>
+        <v>10.0536308288574</v>
       </c>
       <c r="H412" t="n">
         <v>886499</v>
@@ -12375,7 +12375,7 @@
         <v>16.9116859436035</v>
       </c>
       <c r="G414" t="n">
-        <v>9.72189998626709</v>
+        <v>9.72189807891846</v>
       </c>
       <c r="H414" t="n">
         <v>1220859</v>
@@ -12433,7 +12433,7 @@
         <v>17.5725154876709</v>
       </c>
       <c r="G416" t="n">
-        <v>10.10178565979</v>
+        <v>10.1017847061157</v>
       </c>
       <c r="H416" t="n">
         <v>1084638</v>
@@ -12462,7 +12462,7 @@
         <v>17.3025989532471</v>
       </c>
       <c r="G417" t="n">
-        <v>9.94661903381348</v>
+        <v>9.94661998748779</v>
       </c>
       <c r="H417" t="n">
         <v>569889</v>
@@ -12491,7 +12491,7 @@
         <v>17.3212127685547</v>
       </c>
       <c r="G418" t="n">
-        <v>9.95732021331787</v>
+        <v>9.95731925964355</v>
       </c>
       <c r="H418" t="n">
         <v>603666</v>
@@ -12549,7 +12549,7 @@
         <v>16.9582214355469</v>
       </c>
       <c r="G420" t="n">
-        <v>9.74864959716797</v>
+        <v>9.74865055084229</v>
       </c>
       <c r="H420" t="n">
         <v>1199704</v>
@@ -12665,7 +12665,7 @@
         <v>16.8651466369629</v>
       </c>
       <c r="G424" t="n">
-        <v>9.69514560699463</v>
+        <v>9.69514465332031</v>
       </c>
       <c r="H424" t="n">
         <v>834174</v>
@@ -12694,7 +12694,7 @@
         <v>16.4556179046631</v>
       </c>
       <c r="G425" t="n">
-        <v>9.45972061157227</v>
+        <v>9.45972156524658</v>
       </c>
       <c r="H425" t="n">
         <v>1374883</v>
@@ -12723,7 +12723,7 @@
         <v>16.4556179046631</v>
       </c>
       <c r="G426" t="n">
-        <v>9.45972061157227</v>
+        <v>9.45972156524658</v>
       </c>
       <c r="H426" t="n">
         <v>535558</v>
@@ -12752,7 +12752,7 @@
         <v>16.4742336273193</v>
       </c>
       <c r="G427" t="n">
-        <v>9.47042274475098</v>
+        <v>9.47042369842529</v>
       </c>
       <c r="H427" t="n">
         <v>824342</v>
@@ -12810,7 +12810,7 @@
         <v>16.4649257659912</v>
       </c>
       <c r="G429" t="n">
-        <v>9.46507167816162</v>
+        <v>9.46507358551025</v>
       </c>
       <c r="H429" t="n">
         <v>465477</v>
@@ -12839,7 +12839,7 @@
         <v>16.3811588287354</v>
       </c>
       <c r="G430" t="n">
-        <v>9.41691875457764</v>
+        <v>9.41691780090332</v>
       </c>
       <c r="H430" t="n">
         <v>394337</v>
@@ -12868,7 +12868,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G431" t="n">
-        <v>9.39551734924316</v>
+        <v>9.39551639556885</v>
       </c>
       <c r="H431" t="n">
         <v>835890</v>
@@ -12926,7 +12926,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G433" t="n">
-        <v>9.39551734924316</v>
+        <v>9.39551639556885</v>
       </c>
       <c r="H433" t="n">
         <v>421258</v>
@@ -12955,7 +12955,7 @@
         <v>16.781379699707</v>
       </c>
       <c r="G434" t="n">
-        <v>9.64699077606201</v>
+        <v>9.6469898223877</v>
       </c>
       <c r="H434" t="n">
         <v>777048</v>
@@ -13013,7 +13013,7 @@
         <v>16.874454498291</v>
       </c>
       <c r="G436" t="n">
-        <v>9.70049571990967</v>
+        <v>9.70049476623535</v>
       </c>
       <c r="H436" t="n">
         <v>1049436</v>
@@ -13129,7 +13129,7 @@
         <v>17.246753692627</v>
       </c>
       <c r="G440" t="n">
-        <v>9.91451644897461</v>
+        <v>9.91451549530029</v>
       </c>
       <c r="H440" t="n">
         <v>522818</v>
@@ -13158,7 +13158,7 @@
         <v>17.1164493560791</v>
       </c>
       <c r="G441" t="n">
-        <v>9.83960914611816</v>
+        <v>9.83961009979248</v>
       </c>
       <c r="H441" t="n">
         <v>425346</v>
@@ -13245,7 +13245,7 @@
         <v>16.688304901123</v>
       </c>
       <c r="G444" t="n">
-        <v>9.59348487854004</v>
+        <v>9.59348583221436</v>
       </c>
       <c r="H444" t="n">
         <v>1039336</v>
@@ -13274,7 +13274,7 @@
         <v>16.781379699707</v>
       </c>
       <c r="G445" t="n">
-        <v>9.64699077606201</v>
+        <v>9.6469898223877</v>
       </c>
       <c r="H445" t="n">
         <v>508530</v>
@@ -13361,7 +13361,7 @@
         <v>17.0326824188232</v>
       </c>
       <c r="G448" t="n">
-        <v>9.79145336151123</v>
+        <v>9.79145431518555</v>
       </c>
       <c r="H448" t="n">
         <v>682483</v>
@@ -13390,7 +13390,7 @@
         <v>17.1629867553711</v>
       </c>
       <c r="G449" t="n">
-        <v>9.86636161804199</v>
+        <v>9.86636257171631</v>
       </c>
       <c r="H449" t="n">
         <v>654849</v>
@@ -13419,7 +13419,7 @@
         <v>17.2560615539551</v>
       </c>
       <c r="G450" t="n">
-        <v>9.91986751556396</v>
+        <v>9.91986656188965</v>
       </c>
       <c r="H450" t="n">
         <v>606113</v>
@@ -13448,7 +13448,7 @@
         <v>16.8651466369629</v>
       </c>
       <c r="G451" t="n">
-        <v>9.69514560699463</v>
+        <v>9.69514465332031</v>
       </c>
       <c r="H451" t="n">
         <v>671978</v>
@@ -13477,7 +13477,7 @@
         <v>16.9768371582031</v>
       </c>
       <c r="G452" t="n">
-        <v>9.75935077667236</v>
+        <v>9.75935173034668</v>
       </c>
       <c r="H452" t="n">
         <v>500233</v>
@@ -13506,7 +13506,7 @@
         <v>16.9768371582031</v>
       </c>
       <c r="G453" t="n">
-        <v>9.75935077667236</v>
+        <v>9.75935173034668</v>
       </c>
       <c r="H453" t="n">
         <v>698353</v>
@@ -13535,7 +13535,7 @@
         <v>16.9582214355469</v>
       </c>
       <c r="G454" t="n">
-        <v>9.74864959716797</v>
+        <v>9.74865055084229</v>
       </c>
       <c r="H454" t="n">
         <v>363293</v>
@@ -13564,7 +13564,7 @@
         <v>16.8837623596191</v>
       </c>
       <c r="G455" t="n">
-        <v>9.70584678649902</v>
+        <v>9.70584583282471</v>
       </c>
       <c r="H455" t="n">
         <v>550780</v>
@@ -13622,7 +13622,7 @@
         <v>16.1577796936035</v>
       </c>
       <c r="G457" t="n">
-        <v>9.28850746154785</v>
+        <v>9.28850650787354</v>
       </c>
       <c r="H457" t="n">
         <v>2623880</v>
@@ -13680,7 +13680,7 @@
         <v>15.9623222351074</v>
       </c>
       <c r="G459" t="n">
-        <v>9.17614364624023</v>
+        <v>9.17614459991455</v>
       </c>
       <c r="H459" t="n">
         <v>1223332</v>
@@ -13738,7 +13738,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G461" t="n">
-        <v>9.1119384765625</v>
+        <v>9.11193943023682</v>
       </c>
       <c r="H461" t="n">
         <v>950657</v>
@@ -13796,7 +13796,7 @@
         <v>15.8971700668335</v>
       </c>
       <c r="G463" t="n">
-        <v>9.13869190216064</v>
+        <v>9.13869094848633</v>
       </c>
       <c r="H463" t="n">
         <v>1521814</v>
@@ -13825,7 +13825,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G464" t="n">
-        <v>9.1119384765625</v>
+        <v>9.11193943023682</v>
       </c>
       <c r="H464" t="n">
         <v>680824</v>
@@ -13883,7 +13883,7 @@
         <v>15.7296352386475</v>
       </c>
       <c r="G466" t="n">
-        <v>9.04238033294678</v>
+        <v>9.04238224029541</v>
       </c>
       <c r="H466" t="n">
         <v>663164</v>
@@ -13941,7 +13941,7 @@
         <v>15.8692474365234</v>
       </c>
       <c r="G468" t="n">
-        <v>9.12263965606689</v>
+        <v>9.12263870239258</v>
       </c>
       <c r="H468" t="n">
         <v>1030051</v>
@@ -13970,7 +13970,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G469" t="n">
-        <v>9.06913280487061</v>
+        <v>9.06913471221924</v>
       </c>
       <c r="H469" t="n">
         <v>810700</v>
@@ -14028,7 +14028,7 @@
         <v>15.9716291427612</v>
       </c>
       <c r="G471" t="n">
-        <v>9.18149566650391</v>
+        <v>9.18149471282959</v>
       </c>
       <c r="H471" t="n">
         <v>1282309</v>
@@ -14057,7 +14057,7 @@
         <v>16.0553970336914</v>
       </c>
       <c r="G472" t="n">
-        <v>9.22965145111084</v>
+        <v>9.22965049743652</v>
       </c>
       <c r="H472" t="n">
         <v>877630</v>
@@ -14115,7 +14115,7 @@
         <v>16.1577796936035</v>
       </c>
       <c r="G474" t="n">
-        <v>9.28850746154785</v>
+        <v>9.28850650787354</v>
       </c>
       <c r="H474" t="n">
         <v>507070</v>
@@ -14173,7 +14173,7 @@
         <v>15.8692474365234</v>
       </c>
       <c r="G476" t="n">
-        <v>9.12263965606689</v>
+        <v>9.12263870239258</v>
       </c>
       <c r="H476" t="n">
         <v>1696146</v>
@@ -14202,7 +14202,7 @@
         <v>15.0315742492676</v>
       </c>
       <c r="G477" t="n">
-        <v>8.64109134674072</v>
+        <v>8.64109230041504</v>
       </c>
       <c r="H477" t="n">
         <v>3822286</v>
@@ -14231,7 +14231,7 @@
         <v>14.6871976852417</v>
       </c>
       <c r="G478" t="n">
-        <v>8.44312381744385</v>
+        <v>8.44312286376953</v>
       </c>
       <c r="H478" t="n">
         <v>3672484</v>
@@ -14405,7 +14405,7 @@
         <v>14.8640403747559</v>
       </c>
       <c r="G484" t="n">
-        <v>8.54478168487549</v>
+        <v>8.54478359222412</v>
       </c>
       <c r="H484" t="n">
         <v>843895</v>
@@ -14434,7 +14434,7 @@
         <v>15.1618785858154</v>
       </c>
       <c r="G485" t="n">
-        <v>8.7160005569458</v>
+        <v>8.71599960327148</v>
       </c>
       <c r="H485" t="n">
         <v>1715781</v>
@@ -14608,7 +14608,7 @@
         <v>14.9850368499756</v>
       </c>
       <c r="G491" t="n">
-        <v>8.61433887481689</v>
+        <v>8.61433982849121</v>
       </c>
       <c r="H491" t="n">
         <v>630608</v>
@@ -14666,7 +14666,7 @@
         <v>14.6034297943115</v>
       </c>
       <c r="G493" t="n">
-        <v>8.39496898651123</v>
+        <v>8.3949670791626</v>
       </c>
       <c r="H493" t="n">
         <v>1094020</v>
@@ -14695,7 +14695,7 @@
         <v>14.5755081176758</v>
       </c>
       <c r="G494" t="n">
-        <v>8.3789176940918</v>
+        <v>8.37891578674316</v>
       </c>
       <c r="H494" t="n">
         <v>1401506</v>
@@ -14753,7 +14753,7 @@
         <v>14.4265880584717</v>
       </c>
       <c r="G496" t="n">
-        <v>8.29330730438232</v>
+        <v>8.29330825805664</v>
       </c>
       <c r="H496" t="n">
         <v>953589</v>
@@ -14811,7 +14811,7 @@
         <v>14.7151203155518</v>
       </c>
       <c r="G498" t="n">
-        <v>8.45917415618896</v>
+        <v>8.45917510986328</v>
       </c>
       <c r="H498" t="n">
         <v>1210613</v>
@@ -14840,7 +14840,7 @@
         <v>14.7709646224976</v>
       </c>
       <c r="G499" t="n">
-        <v>8.49127864837646</v>
+        <v>8.49127769470215</v>
       </c>
       <c r="H499" t="n">
         <v>436325</v>
@@ -14898,7 +14898,7 @@
         <v>14.7616567611694</v>
       </c>
       <c r="G501" t="n">
-        <v>8.48592758178711</v>
+        <v>8.48592662811279</v>
       </c>
       <c r="H501" t="n">
         <v>773704</v>
@@ -14927,7 +14927,7 @@
         <v>14.7988872528076</v>
       </c>
       <c r="G502" t="n">
-        <v>8.50732707977295</v>
+        <v>8.5073299407959</v>
       </c>
       <c r="H502" t="n">
         <v>1373841</v>
@@ -14956,7 +14956,7 @@
         <v>14.6406602859497</v>
       </c>
       <c r="G503" t="n">
-        <v>8.4163703918457</v>
+        <v>8.41636943817139</v>
       </c>
       <c r="H503" t="n">
         <v>1157775</v>
@@ -15014,7 +15014,7 @@
         <v>14.8175020217896</v>
       </c>
       <c r="G505" t="n">
-        <v>8.51802921295166</v>
+        <v>8.51803016662598</v>
       </c>
       <c r="H505" t="n">
         <v>628444</v>
@@ -15043,7 +15043,7 @@
         <v>14.7895803451538</v>
       </c>
       <c r="G506" t="n">
-        <v>8.50197982788086</v>
+        <v>8.50197887420654</v>
       </c>
       <c r="H506" t="n">
         <v>675838</v>
@@ -15072,7 +15072,7 @@
         <v>14.8454246520996</v>
       </c>
       <c r="G507" t="n">
-        <v>8.53408145904541</v>
+        <v>8.53408241271973</v>
       </c>
       <c r="H507" t="n">
         <v>672596</v>
@@ -15101,7 +15101,7 @@
         <v>14.8268098831177</v>
       </c>
       <c r="G508" t="n">
-        <v>8.52338123321533</v>
+        <v>8.52338218688965</v>
       </c>
       <c r="H508" t="n">
         <v>437167</v>
@@ -15130,7 +15130,7 @@
         <v>14.9943437576294</v>
       </c>
       <c r="G509" t="n">
-        <v>8.61969089508057</v>
+        <v>8.61968994140625</v>
       </c>
       <c r="H509" t="n">
         <v>567586</v>
@@ -15188,7 +15188,7 @@
         <v>14.8640403747559</v>
       </c>
       <c r="G511" t="n">
-        <v>8.54478168487549</v>
+        <v>8.54478359222412</v>
       </c>
       <c r="H511" t="n">
         <v>600535</v>
@@ -15217,7 +15217,7 @@
         <v>14.8640403747559</v>
       </c>
       <c r="G512" t="n">
-        <v>8.54478168487549</v>
+        <v>8.54478359222412</v>
       </c>
       <c r="H512" t="n">
         <v>769889</v>
@@ -15275,7 +15275,7 @@
         <v>14.9757289886475</v>
       </c>
       <c r="G514" t="n">
-        <v>8.60898971557617</v>
+        <v>8.60898876190186</v>
       </c>
       <c r="H514" t="n">
         <v>1094826</v>
@@ -15362,7 +15362,7 @@
         <v>15.3759508132935</v>
       </c>
       <c r="G517" t="n">
-        <v>8.83906078338623</v>
+        <v>8.83906269073486</v>
       </c>
       <c r="H517" t="n">
         <v>1463191</v>
@@ -15391,7 +15391,7 @@
         <v>15.3945655822754</v>
       </c>
       <c r="G518" t="n">
-        <v>8.84976291656494</v>
+        <v>8.84976387023926</v>
       </c>
       <c r="H518" t="n">
         <v>1021965</v>
@@ -15420,7 +15420,7 @@
         <v>15.3294134140015</v>
       </c>
       <c r="G519" t="n">
-        <v>8.81230926513672</v>
+        <v>8.81231021881104</v>
       </c>
       <c r="H519" t="n">
         <v>1197971</v>
@@ -15507,7 +15507,7 @@
         <v>17.0978336334229</v>
       </c>
       <c r="G522" t="n">
-        <v>9.82890701293945</v>
+        <v>9.82890796661377</v>
       </c>
       <c r="H522" t="n">
         <v>6840925</v>
@@ -15594,7 +15594,7 @@
         <v>17.5725154876709</v>
       </c>
       <c r="G525" t="n">
-        <v>10.10178565979</v>
+        <v>10.1017847061157</v>
       </c>
       <c r="H525" t="n">
         <v>1827376</v>
@@ -15652,7 +15652,7 @@
         <v>17.6190528869629</v>
       </c>
       <c r="G527" t="n">
-        <v>10.1285381317139</v>
+        <v>10.1285371780396</v>
       </c>
       <c r="H527" t="n">
         <v>1670148</v>
@@ -15681,7 +15681,7 @@
         <v>17.581823348999</v>
       </c>
       <c r="G528" t="n">
-        <v>10.1071348190308</v>
+        <v>10.1071357727051</v>
       </c>
       <c r="H528" t="n">
         <v>1551920</v>
@@ -15797,7 +15797,7 @@
         <v>17.153678894043</v>
       </c>
       <c r="G532" t="n">
-        <v>9.86101150512695</v>
+        <v>9.86101055145264</v>
       </c>
       <c r="H532" t="n">
         <v>1575700</v>
@@ -15855,7 +15855,7 @@
         <v>17.1350631713867</v>
       </c>
       <c r="G534" t="n">
-        <v>9.85030937194824</v>
+        <v>9.85030841827393</v>
       </c>
       <c r="H534" t="n">
         <v>1290237</v>
@@ -15884,7 +15884,7 @@
         <v>17.0280284881592</v>
       </c>
       <c r="G535" t="n">
-        <v>9.78878116607666</v>
+        <v>9.78878021240234</v>
       </c>
       <c r="H535" t="n">
         <v>1219471</v>
@@ -15942,7 +15942,7 @@
         <v>16.5300788879395</v>
       </c>
       <c r="G537" t="n">
-        <v>9.50252819061279</v>
+        <v>9.50252532958984</v>
       </c>
       <c r="H537" t="n">
         <v>3251917</v>
@@ -16000,7 +16000,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G539" t="n">
-        <v>9.63093757629395</v>
+        <v>9.63093852996826</v>
       </c>
       <c r="H539" t="n">
         <v>1352694</v>
@@ -16087,7 +16087,7 @@
         <v>16.3858127593994</v>
       </c>
       <c r="G542" t="n">
-        <v>9.41959476470947</v>
+        <v>9.41959381103516</v>
       </c>
       <c r="H542" t="n">
         <v>1208815</v>
@@ -16116,7 +16116,7 @@
         <v>16.6650352478027</v>
       </c>
       <c r="G543" t="n">
-        <v>9.58010768890381</v>
+        <v>9.58010864257812</v>
       </c>
       <c r="H543" t="n">
         <v>1619931</v>
@@ -16174,7 +16174,7 @@
         <v>16.7953414916992</v>
       </c>
       <c r="G545" t="n">
-        <v>9.65501689910889</v>
+        <v>9.65501594543457</v>
       </c>
       <c r="H545" t="n">
         <v>707813</v>
@@ -16203,7 +16203,7 @@
         <v>16.6743431091309</v>
       </c>
       <c r="G546" t="n">
-        <v>9.5854606628418</v>
+        <v>9.58545970916748</v>
       </c>
       <c r="H546" t="n">
         <v>548096</v>
@@ -16261,7 +16261,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G548" t="n">
-        <v>9.63093757629395</v>
+        <v>9.63093852996826</v>
       </c>
       <c r="H548" t="n">
         <v>1023005</v>
@@ -16406,7 +16406,7 @@
         <v>16.688304901123</v>
       </c>
       <c r="G553" t="n">
-        <v>9.59348487854004</v>
+        <v>9.59348583221436</v>
       </c>
       <c r="H553" t="n">
         <v>1051838</v>
@@ -16464,7 +16464,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G555" t="n">
-        <v>9.34468555450439</v>
+        <v>9.34468460083008</v>
       </c>
       <c r="H555" t="n">
         <v>2578826</v>
@@ -16522,7 +16522,7 @@
         <v>16.7162265777588</v>
       </c>
       <c r="G557" t="n">
-        <v>9.60953903198242</v>
+        <v>9.60953617095947</v>
       </c>
       <c r="H557" t="n">
         <v>1706194</v>
@@ -16551,7 +16551,7 @@
         <v>16.781379699707</v>
       </c>
       <c r="G558" t="n">
-        <v>9.64699077606201</v>
+        <v>9.6469898223877</v>
       </c>
       <c r="H558" t="n">
         <v>1180848</v>
@@ -16638,7 +16638,7 @@
         <v>16.7860336303711</v>
       </c>
       <c r="G561" t="n">
-        <v>9.64966487884521</v>
+        <v>9.64966583251953</v>
       </c>
       <c r="H561" t="n">
         <v>1410491</v>
@@ -16725,7 +16725,7 @@
         <v>16.6650352478027</v>
       </c>
       <c r="G564" t="n">
-        <v>9.58010768890381</v>
+        <v>9.58010864257812</v>
       </c>
       <c r="H564" t="n">
         <v>1689644</v>
@@ -16754,7 +16754,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G565" t="n">
-        <v>9.63093757629395</v>
+        <v>9.63093852996826</v>
       </c>
       <c r="H565" t="n">
         <v>3551986</v>
@@ -16957,7 +16957,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G572" t="n">
-        <v>9.39551734924316</v>
+        <v>9.39551639556885</v>
       </c>
       <c r="H572" t="n">
         <v>1083998</v>
@@ -16986,7 +16986,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G573" t="n">
-        <v>9.32595920562744</v>
+        <v>9.32595825195312</v>
       </c>
       <c r="H573" t="n">
         <v>1192828</v>
@@ -17131,7 +17131,7 @@
         <v>16.3160057067871</v>
       </c>
       <c r="G578" t="n">
-        <v>9.37946319580078</v>
+        <v>9.3794641494751</v>
       </c>
       <c r="H578" t="n">
         <v>764606</v>
@@ -17160,7 +17160,7 @@
         <v>16.5161170959473</v>
       </c>
       <c r="G579" t="n">
-        <v>9.4945011138916</v>
+        <v>9.49450016021729</v>
       </c>
       <c r="H579" t="n">
         <v>1172659</v>
@@ -17247,7 +17247,7 @@
         <v>16.5207691192627</v>
       </c>
       <c r="G582" t="n">
-        <v>9.4971752166748</v>
+        <v>9.49717330932617</v>
       </c>
       <c r="H582" t="n">
         <v>1299325</v>
@@ -17276,7 +17276,7 @@
         <v>15.9762830734253</v>
       </c>
       <c r="G583" t="n">
-        <v>9.18416976928711</v>
+        <v>9.18417072296143</v>
       </c>
       <c r="H583" t="n">
         <v>5404213</v>
@@ -17305,7 +17305,7 @@
         <v>15.9623222351074</v>
       </c>
       <c r="G584" t="n">
-        <v>9.17614364624023</v>
+        <v>9.17614459991455</v>
       </c>
       <c r="H584" t="n">
         <v>1792075</v>
@@ -17363,7 +17363,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G586" t="n">
-        <v>9.34468555450439</v>
+        <v>9.34468460083008</v>
       </c>
       <c r="H586" t="n">
         <v>1262836</v>
@@ -17392,7 +17392,7 @@
         <v>16.2322387695312</v>
       </c>
       <c r="G587" t="n">
-        <v>9.33130931854248</v>
+        <v>9.3313102722168</v>
       </c>
       <c r="H587" t="n">
         <v>1077200</v>
@@ -17421,7 +17421,7 @@
         <v>16.1903553009033</v>
       </c>
       <c r="G588" t="n">
-        <v>9.30723190307617</v>
+        <v>9.30723285675049</v>
       </c>
       <c r="H588" t="n">
         <v>1192757</v>
@@ -17479,7 +17479,7 @@
         <v>16.1252021789551</v>
       </c>
       <c r="G590" t="n">
-        <v>9.26977729797363</v>
+        <v>9.26977825164795</v>
       </c>
       <c r="H590" t="n">
         <v>1678666</v>
@@ -17508,7 +17508,7 @@
         <v>16.0460891723633</v>
       </c>
       <c r="G591" t="n">
-        <v>9.22429847717285</v>
+        <v>9.22430038452148</v>
       </c>
       <c r="H591" t="n">
         <v>1091322</v>
@@ -17595,7 +17595,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G594" t="n">
-        <v>9.32595920562744</v>
+        <v>9.32595825195312</v>
       </c>
       <c r="H594" t="n">
         <v>1512274</v>
@@ -17653,7 +17653,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G596" t="n">
-        <v>9.34468555450439</v>
+        <v>9.34468460083008</v>
       </c>
       <c r="H596" t="n">
         <v>1297293</v>
@@ -17740,7 +17740,7 @@
         <v>16.5254230499268</v>
       </c>
       <c r="G599" t="n">
-        <v>9.49985027313232</v>
+        <v>9.49984931945801</v>
       </c>
       <c r="H599" t="n">
         <v>2558942</v>
@@ -17769,7 +17769,7 @@
         <v>16.3066997528076</v>
       </c>
       <c r="G600" t="n">
-        <v>9.37411308288574</v>
+        <v>9.37411499023438</v>
       </c>
       <c r="H600" t="n">
         <v>2502188</v>
@@ -17798,7 +17798,7 @@
         <v>15.9390525817871</v>
       </c>
       <c r="G601" t="n">
-        <v>9.16276836395264</v>
+        <v>9.16276741027832</v>
       </c>
       <c r="H601" t="n">
         <v>4024349</v>
@@ -17827,7 +17827,7 @@
         <v>15.4690256118774</v>
       </c>
       <c r="G602" t="n">
-        <v>8.89256763458252</v>
+        <v>8.8925666809082</v>
       </c>
       <c r="H602" t="n">
         <v>6600347</v>
@@ -18001,7 +18001,7 @@
         <v>14.2554397583008</v>
       </c>
       <c r="G608" t="n">
-        <v>8.76534843444824</v>
+        <v>8.76534748077393</v>
       </c>
       <c r="H608" t="n">
         <v>2816215</v>
@@ -18117,7 +18117,7 @@
         <v>14.4814052581787</v>
       </c>
       <c r="G612" t="n">
-        <v>8.90428924560547</v>
+        <v>8.90428829193115</v>
       </c>
       <c r="H612" t="n">
         <v>2545280</v>
@@ -18146,7 +18146,7 @@
         <v>14.3242120742798</v>
       </c>
       <c r="G613" t="n">
-        <v>8.80763339996338</v>
+        <v>8.80763530731201</v>
       </c>
       <c r="H613" t="n">
         <v>3300454</v>
@@ -18262,7 +18262,7 @@
         <v>14.3340368270874</v>
       </c>
       <c r="G617" t="n">
-        <v>8.81367683410645</v>
+        <v>8.81367492675781</v>
       </c>
       <c r="H617" t="n">
         <v>2988101</v>
@@ -18320,7 +18320,7 @@
         <v>13.7101774215698</v>
       </c>
       <c r="G619" t="n">
-        <v>8.43007755279541</v>
+        <v>8.43007850646973</v>
       </c>
       <c r="H619" t="n">
         <v>2663239</v>
@@ -18349,7 +18349,7 @@
         <v>13.6856145858765</v>
       </c>
       <c r="G620" t="n">
-        <v>8.4149751663208</v>
+        <v>8.41497611999512</v>
       </c>
       <c r="H620" t="n">
         <v>2306058</v>
@@ -18407,7 +18407,7 @@
         <v>13.2631587982178</v>
       </c>
       <c r="G622" t="n">
-        <v>8.15521621704102</v>
+        <v>8.1552152633667</v>
       </c>
       <c r="H622" t="n">
         <v>1377416</v>
@@ -18436,7 +18436,7 @@
         <v>13.5578956604004</v>
       </c>
       <c r="G623" t="n">
-        <v>8.33644390106201</v>
+        <v>8.3364429473877</v>
       </c>
       <c r="H623" t="n">
         <v>1557399</v>
@@ -18494,7 +18494,7 @@
         <v>13.3810539245605</v>
       </c>
       <c r="G625" t="n">
-        <v>8.227707862854</v>
+        <v>8.22770690917969</v>
       </c>
       <c r="H625" t="n">
         <v>1383351</v>
@@ -18610,7 +18610,7 @@
         <v>13.5087728500366</v>
       </c>
       <c r="G629" t="n">
-        <v>8.30623817443848</v>
+        <v>8.30623912811279</v>
       </c>
       <c r="H629" t="n">
         <v>1127514</v>
@@ -18668,7 +18668,7 @@
         <v>13.2926330566406</v>
       </c>
       <c r="G631" t="n">
-        <v>8.17333984375</v>
+        <v>8.17333889007568</v>
       </c>
       <c r="H631" t="n">
         <v>988112</v>
@@ -18697,7 +18697,7 @@
         <v>13.4007034301758</v>
       </c>
       <c r="G632" t="n">
-        <v>8.23978996276855</v>
+        <v>8.23978900909424</v>
       </c>
       <c r="H632" t="n">
         <v>1087686</v>
@@ -18726,7 +18726,7 @@
         <v>13.0666675567627</v>
       </c>
       <c r="G633" t="n">
-        <v>8.03439903259277</v>
+        <v>8.03439807891846</v>
       </c>
       <c r="H633" t="n">
         <v>812141</v>
@@ -18755,7 +18755,7 @@
         <v>13.0224571228027</v>
       </c>
       <c r="G634" t="n">
-        <v>8.00721549987793</v>
+        <v>8.00721454620361</v>
       </c>
       <c r="H634" t="n">
         <v>601138</v>
@@ -18784,7 +18784,7 @@
         <v>13.1452646255493</v>
       </c>
       <c r="G635" t="n">
-        <v>8.08272552490234</v>
+        <v>8.08272647857666</v>
       </c>
       <c r="H635" t="n">
         <v>879730</v>
@@ -18842,7 +18842,7 @@
         <v>13.0224571228027</v>
       </c>
       <c r="G637" t="n">
-        <v>8.00721549987793</v>
+        <v>8.00721454620361</v>
       </c>
       <c r="H637" t="n">
         <v>640657</v>
@@ -18958,7 +18958,7 @@
         <v>13.0961418151855</v>
       </c>
       <c r="G641" t="n">
-        <v>8.05252170562744</v>
+        <v>8.05252265930176</v>
       </c>
       <c r="H641" t="n">
         <v>599430</v>
@@ -18987,7 +18987,7 @@
         <v>13.1059656143188</v>
       </c>
       <c r="G642" t="n">
-        <v>8.05856227874756</v>
+        <v>8.05856132507324</v>
       </c>
       <c r="H642" t="n">
         <v>447362</v>
@@ -19045,7 +19045,7 @@
         <v>13.5087728500366</v>
       </c>
       <c r="G644" t="n">
-        <v>8.30623817443848</v>
+        <v>8.30623912811279</v>
       </c>
       <c r="H644" t="n">
         <v>823183</v>
@@ -19074,7 +19074,7 @@
         <v>13.0961418151855</v>
       </c>
       <c r="G645" t="n">
-        <v>8.05252170562744</v>
+        <v>8.05252265930176</v>
       </c>
       <c r="H645" t="n">
         <v>1016826</v>
@@ -19103,7 +19103,7 @@
         <v>12.8947381973267</v>
       </c>
       <c r="G646" t="n">
-        <v>7.92868232727051</v>
+        <v>7.92868280410767</v>
       </c>
       <c r="H646" t="n">
         <v>831874</v>
@@ -19248,7 +19248,7 @@
         <v>13.1501770019531</v>
       </c>
       <c r="G651" t="n">
-        <v>8.08574676513672</v>
+        <v>8.08574771881104</v>
       </c>
       <c r="H651" t="n">
         <v>780753</v>
@@ -19277,7 +19277,7 @@
         <v>12.9782466888428</v>
       </c>
       <c r="G652" t="n">
-        <v>7.98003005981445</v>
+        <v>7.98003101348877</v>
       </c>
       <c r="H652" t="n">
         <v>796305</v>
@@ -19393,7 +19393,7 @@
         <v>13.9508790969849</v>
       </c>
       <c r="G656" t="n">
-        <v>8.57808113098145</v>
+        <v>8.57807922363281</v>
       </c>
       <c r="H656" t="n">
         <v>3419024</v>
@@ -19451,7 +19451,7 @@
         <v>13.8919305801392</v>
       </c>
       <c r="G658" t="n">
-        <v>8.54183483123779</v>
+        <v>8.54183292388916</v>
       </c>
       <c r="H658" t="n">
         <v>938616</v>
@@ -19480,7 +19480,7 @@
         <v>14.1129837036133</v>
       </c>
       <c r="G659" t="n">
-        <v>8.67775535583496</v>
+        <v>8.67775440216064</v>
       </c>
       <c r="H659" t="n">
         <v>992401</v>
@@ -19538,7 +19538,7 @@
         <v>13.680703163147</v>
       </c>
       <c r="G661" t="n">
-        <v>8.41195583343506</v>
+        <v>8.41195487976074</v>
       </c>
       <c r="H661" t="n">
         <v>1143545</v>
@@ -19567,7 +19567,7 @@
         <v>13.6168441772461</v>
       </c>
       <c r="G662" t="n">
-        <v>8.37268829345703</v>
+        <v>8.37269020080566</v>
       </c>
       <c r="H662" t="n">
         <v>845804</v>
@@ -19625,7 +19625,7 @@
         <v>14.0884227752686</v>
       </c>
       <c r="G664" t="n">
-        <v>8.66265201568604</v>
+        <v>8.66265296936035</v>
       </c>
       <c r="H664" t="n">
         <v>1112152</v>
@@ -19683,7 +19683,7 @@
         <v>14.0442123413086</v>
       </c>
       <c r="G666" t="n">
-        <v>8.63546752929688</v>
+        <v>8.63546848297119</v>
       </c>
       <c r="H666" t="n">
         <v>1000972</v>
@@ -19712,7 +19712,7 @@
         <v>13.7101774215698</v>
       </c>
       <c r="G667" t="n">
-        <v>8.43007755279541</v>
+        <v>8.43007850646973</v>
       </c>
       <c r="H667" t="n">
         <v>1022021</v>
@@ -19770,7 +19770,7 @@
         <v>14.1670188903809</v>
       </c>
       <c r="G669" t="n">
-        <v>8.71097850799561</v>
+        <v>8.71097946166992</v>
       </c>
       <c r="H669" t="n">
         <v>1549992</v>
@@ -19799,7 +19799,7 @@
         <v>14.05894947052</v>
       </c>
       <c r="G670" t="n">
-        <v>8.64452934265137</v>
+        <v>8.64453125</v>
       </c>
       <c r="H670" t="n">
         <v>1211547</v>
@@ -19828,7 +19828,7 @@
         <v>14.0000009536743</v>
       </c>
       <c r="G671" t="n">
-        <v>8.60828495025635</v>
+        <v>8.60828399658203</v>
       </c>
       <c r="H671" t="n">
         <v>882908</v>
@@ -19857,7 +19857,7 @@
         <v>14.1670188903809</v>
       </c>
       <c r="G672" t="n">
-        <v>8.71097850799561</v>
+        <v>8.71097946166992</v>
       </c>
       <c r="H672" t="n">
         <v>948891</v>
@@ -19886,7 +19886,7 @@
         <v>14.206316947937</v>
       </c>
       <c r="G673" t="n">
-        <v>8.73514366149902</v>
+        <v>8.73514270782471</v>
       </c>
       <c r="H673" t="n">
         <v>734391</v>
@@ -19973,7 +19973,7 @@
         <v>14.1277208328247</v>
       </c>
       <c r="G676" t="n">
-        <v>8.68681621551514</v>
+        <v>8.68681716918945</v>
       </c>
       <c r="H676" t="n">
         <v>551485</v>
@@ -20031,7 +20031,7 @@
         <v>13.8919305801392</v>
       </c>
       <c r="G678" t="n">
-        <v>8.54183483123779</v>
+        <v>8.54183292388916</v>
       </c>
       <c r="H678" t="n">
         <v>862478</v>
@@ -20089,7 +20089,7 @@
         <v>13.6954402923584</v>
       </c>
       <c r="G680" t="n">
-        <v>8.42101669311523</v>
+        <v>8.42101764678955</v>
       </c>
       <c r="H680" t="n">
         <v>960889</v>
@@ -20118,7 +20118,7 @@
         <v>13.4498262405396</v>
       </c>
       <c r="G681" t="n">
-        <v>8.26999473571777</v>
+        <v>8.26999378204346</v>
       </c>
       <c r="H681" t="n">
         <v>931832</v>
@@ -20176,7 +20176,7 @@
         <v>13.3171939849854</v>
       </c>
       <c r="G683" t="n">
-        <v>8.18844223022461</v>
+        <v>8.18844127655029</v>
       </c>
       <c r="H683" t="n">
         <v>976272</v>
@@ -20234,7 +20234,7 @@
         <v>13.3859663009644</v>
       </c>
       <c r="G685" t="n">
-        <v>8.23072910308838</v>
+        <v>8.23072814941406</v>
       </c>
       <c r="H685" t="n">
         <v>975996</v>
@@ -20292,7 +20292,7 @@
         <v>13.4694747924805</v>
       </c>
       <c r="G687" t="n">
-        <v>8.28207492828369</v>
+        <v>8.28207588195801</v>
       </c>
       <c r="H687" t="n">
         <v>968150</v>
@@ -20321,7 +20321,7 @@
         <v>13.5333347320557</v>
       </c>
       <c r="G688" t="n">
-        <v>8.32134246826172</v>
+        <v>8.3213415145874</v>
       </c>
       <c r="H688" t="n">
         <v>604480</v>
@@ -20379,7 +20379,7 @@
         <v>13.3810539245605</v>
       </c>
       <c r="G690" t="n">
-        <v>8.227707862854</v>
+        <v>8.22770690917969</v>
       </c>
       <c r="H690" t="n">
         <v>670224</v>
@@ -20466,7 +20466,7 @@
         <v>13.7347383499146</v>
       </c>
       <c r="G693" t="n">
-        <v>8.44518089294434</v>
+        <v>8.4451789855957</v>
       </c>
       <c r="H693" t="n">
         <v>691896</v>
@@ -20495,7 +20495,7 @@
         <v>13.7642116546631</v>
       </c>
       <c r="G694" t="n">
-        <v>8.46330165863037</v>
+        <v>8.463303565979</v>
       </c>
       <c r="H694" t="n">
         <v>560152</v>
@@ -20524,7 +20524,7 @@
         <v>13.7543869018555</v>
       </c>
       <c r="G695" t="n">
-        <v>8.45726203918457</v>
+        <v>8.45726108551025</v>
       </c>
       <c r="H695" t="n">
         <v>664477</v>
@@ -20553,7 +20553,7 @@
         <v>13.6168441772461</v>
       </c>
       <c r="G696" t="n">
-        <v>8.37268829345703</v>
+        <v>8.37269020080566</v>
       </c>
       <c r="H696" t="n">
         <v>1176783</v>
@@ -20611,7 +20611,7 @@
         <v>13.6021070480347</v>
       </c>
       <c r="G698" t="n">
-        <v>8.36362743377686</v>
+        <v>8.36362838745117</v>
       </c>
       <c r="H698" t="n">
         <v>616001</v>
@@ -20785,7 +20785,7 @@
         <v>13.0912294387817</v>
       </c>
       <c r="G704" t="n">
-        <v>8.04950046539307</v>
+        <v>8.04950141906738</v>
       </c>
       <c r="H704" t="n">
         <v>1312020</v>
@@ -20814,7 +20814,7 @@
         <v>13.0126333236694</v>
       </c>
       <c r="G705" t="n">
-        <v>8.00117492675781</v>
+        <v>8.0011739730835</v>
       </c>
       <c r="H705" t="n">
         <v>604114</v>
@@ -20843,7 +20843,7 @@
         <v>12.8898258209229</v>
       </c>
       <c r="G706" t="n">
-        <v>7.92566204071045</v>
+        <v>7.92566251754761</v>
       </c>
       <c r="H706" t="n">
         <v>1486222</v>
@@ -20930,7 +20930,7 @@
         <v>12.3838605880737</v>
       </c>
       <c r="G709" t="n">
-        <v>7.61455583572388</v>
+        <v>7.61455726623535</v>
       </c>
       <c r="H709" t="n">
         <v>1467022</v>
@@ -20959,7 +20959,7 @@
         <v>11.9270191192627</v>
       </c>
       <c r="G710" t="n">
-        <v>7.33365440368652</v>
+        <v>7.33365488052368</v>
       </c>
       <c r="H710" t="n">
         <v>1711773</v>
@@ -20988,7 +20988,7 @@
         <v>11.8877201080322</v>
       </c>
       <c r="G711" t="n">
-        <v>7.3094916343689</v>
+        <v>7.30949020385742</v>
       </c>
       <c r="H711" t="n">
         <v>1181386</v>
@@ -21075,7 +21075,7 @@
         <v>11.8582468032837</v>
       </c>
       <c r="G714" t="n">
-        <v>7.29136753082275</v>
+        <v>7.2913670539856</v>
       </c>
       <c r="H714" t="n">
         <v>636891</v>
@@ -21104,7 +21104,7 @@
         <v>11.5585975646973</v>
       </c>
       <c r="G715" t="n">
-        <v>7.10711908340454</v>
+        <v>7.10712051391602</v>
       </c>
       <c r="H715" t="n">
         <v>1354953</v>
@@ -21133,7 +21133,7 @@
         <v>11.3866682052612</v>
       </c>
       <c r="G716" t="n">
-        <v>7.00140523910522</v>
+        <v>7.00140476226807</v>
       </c>
       <c r="H716" t="n">
         <v>1329088</v>
@@ -21162,7 +21162,7 @@
         <v>11.126317024231</v>
       </c>
       <c r="G717" t="n">
-        <v>6.84132099151611</v>
+        <v>6.84132051467896</v>
       </c>
       <c r="H717" t="n">
         <v>1181193</v>
@@ -21191,7 +21191,7 @@
         <v>11.0722818374634</v>
       </c>
       <c r="G718" t="n">
-        <v>6.80809545516968</v>
+        <v>6.80809640884399</v>
       </c>
       <c r="H718" t="n">
         <v>1182294</v>
@@ -21278,7 +21278,7 @@
         <v>10.5073690414429</v>
       </c>
       <c r="G721" t="n">
-        <v>6.46074390411377</v>
+        <v>6.46074438095093</v>
       </c>
       <c r="H721" t="n">
         <v>2330935</v>
@@ -21394,7 +21394,7 @@
         <v>10.7922821044922</v>
       </c>
       <c r="G725" t="n">
-        <v>6.63592958450317</v>
+        <v>6.63593149185181</v>
       </c>
       <c r="H725" t="n">
         <v>866210</v>
@@ -21452,7 +21452,7 @@
         <v>10.6498260498047</v>
       </c>
       <c r="G727" t="n">
-        <v>6.54833745956421</v>
+        <v>6.54833698272705</v>
       </c>
       <c r="H727" t="n">
         <v>756757</v>
@@ -21510,7 +21510,7 @@
         <v>10.7529830932617</v>
       </c>
       <c r="G729" t="n">
-        <v>6.61176633834839</v>
+        <v>6.61176681518555</v>
       </c>
       <c r="H729" t="n">
         <v>767109</v>
@@ -21539,7 +21539,7 @@
         <v>10.9396495819092</v>
       </c>
       <c r="G730" t="n">
-        <v>6.72654438018799</v>
+        <v>6.72654294967651</v>
       </c>
       <c r="H730" t="n">
         <v>2039899</v>
@@ -21597,7 +21597,7 @@
         <v>10.4778957366943</v>
       </c>
       <c r="G732" t="n">
-        <v>6.44262170791626</v>
+        <v>6.44262218475342</v>
       </c>
       <c r="H732" t="n">
         <v>873529</v>
@@ -21684,7 +21684,7 @@
         <v>10.4336853027344</v>
       </c>
       <c r="G735" t="n">
-        <v>6.4154372215271</v>
+        <v>6.41543674468994</v>
       </c>
       <c r="H735" t="n">
         <v>917149</v>
@@ -21713,7 +21713,7 @@
         <v>10.3796501159668</v>
       </c>
       <c r="G736" t="n">
-        <v>6.38221263885498</v>
+        <v>6.38221168518066</v>
       </c>
       <c r="H736" t="n">
         <v>1185830</v>
@@ -21829,7 +21829,7 @@
         <v>10.3501758575439</v>
       </c>
       <c r="G740" t="n">
-        <v>6.36408853530884</v>
+        <v>6.364089012146</v>
       </c>
       <c r="H740" t="n">
         <v>685305</v>
@@ -21887,7 +21887,7 @@
         <v>10.9887733459473</v>
       </c>
       <c r="G742" t="n">
-        <v>6.75674867630005</v>
+        <v>6.75674819946289</v>
       </c>
       <c r="H742" t="n">
         <v>1471175</v>
@@ -21916,7 +21916,7 @@
         <v>10.8856153488159</v>
       </c>
       <c r="G743" t="n">
-        <v>6.69331789016724</v>
+        <v>6.69331884384155</v>
       </c>
       <c r="H743" t="n">
         <v>817223</v>
@@ -21945,7 +21945,7 @@
         <v>10.841404914856</v>
       </c>
       <c r="G744" t="n">
-        <v>6.66613483428955</v>
+        <v>6.66613435745239</v>
       </c>
       <c r="H744" t="n">
         <v>513660</v>
@@ -21974,7 +21974,7 @@
         <v>10.772632598877</v>
       </c>
       <c r="G745" t="n">
-        <v>6.62384843826294</v>
+        <v>6.6238489151001</v>
       </c>
       <c r="H745" t="n">
         <v>882742</v>
@@ -22032,7 +22032,7 @@
         <v>11.0919313430786</v>
       </c>
       <c r="G747" t="n">
-        <v>6.82017755508423</v>
+        <v>6.82017803192139</v>
       </c>
       <c r="H747" t="n">
         <v>1455653</v>
@@ -22061,7 +22061,7 @@
         <v>10.8266677856445</v>
       </c>
       <c r="G748" t="n">
-        <v>6.65707302093506</v>
+        <v>6.65707445144653</v>
       </c>
       <c r="H748" t="n">
         <v>933390</v>
@@ -22090,7 +22090,7 @@
         <v>10.8266677856445</v>
       </c>
       <c r="G749" t="n">
-        <v>6.65707302093506</v>
+        <v>6.65707445144653</v>
       </c>
       <c r="H749" t="n">
         <v>667406</v>
@@ -22119,7 +22119,7 @@
         <v>10.4385967254639</v>
       </c>
       <c r="G750" t="n">
-        <v>6.41845703125</v>
+        <v>6.41845798492432</v>
       </c>
       <c r="H750" t="n">
         <v>1227652</v>
@@ -22148,7 +22148,7 @@
         <v>10.5712289810181</v>
       </c>
       <c r="G751" t="n">
-        <v>6.50001049041748</v>
+        <v>6.50001001358032</v>
       </c>
       <c r="H751" t="n">
         <v>1276602</v>
@@ -22177,7 +22177,7 @@
         <v>10.3059663772583</v>
       </c>
       <c r="G752" t="n">
-        <v>6.33690595626831</v>
+        <v>6.33690547943115</v>
       </c>
       <c r="H752" t="n">
         <v>1025160</v>
@@ -22206,7 +22206,7 @@
         <v>10.3354396820068</v>
       </c>
       <c r="G753" t="n">
-        <v>6.35502767562866</v>
+        <v>6.35502815246582</v>
       </c>
       <c r="H753" t="n">
         <v>780315</v>
@@ -22235,7 +22235,7 @@
         <v>10.6743869781494</v>
       </c>
       <c r="G754" t="n">
-        <v>6.56343984603882</v>
+        <v>6.5634388923645</v>
       </c>
       <c r="H754" t="n">
         <v>1537323</v>
@@ -22293,7 +22293,7 @@
         <v>10.7578964233398</v>
       </c>
       <c r="G756" t="n">
-        <v>6.61478710174561</v>
+        <v>6.61478757858276</v>
       </c>
       <c r="H756" t="n">
         <v>996122</v>
@@ -22322,7 +22322,7 @@
         <v>10.5663166046143</v>
       </c>
       <c r="G757" t="n">
-        <v>6.49698972702026</v>
+        <v>6.49698829650879</v>
       </c>
       <c r="H757" t="n">
         <v>910578</v>
@@ -22351,7 +22351,7 @@
         <v>9.90807056427002</v>
       </c>
       <c r="G758" t="n">
-        <v>6.09224843978882</v>
+        <v>6.09224891662598</v>
       </c>
       <c r="H758" t="n">
         <v>2809051</v>
@@ -22409,7 +22409,7 @@
         <v>9.43747520446777</v>
       </c>
       <c r="G760" t="n">
-        <v>5.80288982391357</v>
+        <v>5.80289030075073</v>
       </c>
       <c r="H760" t="n">
         <v>2293598</v>
@@ -22438,7 +22438,7 @@
         <v>9.44729900360107</v>
       </c>
       <c r="G761" t="n">
-        <v>5.80893087387085</v>
+        <v>5.80892992019653</v>
       </c>
       <c r="H761" t="n">
         <v>1380952</v>
@@ -22467,7 +22467,7 @@
         <v>9.14863204956055</v>
       </c>
       <c r="G762" t="n">
-        <v>5.62528705596924</v>
+        <v>5.62528800964355</v>
       </c>
       <c r="H762" t="n">
         <v>1122387</v>
@@ -22525,7 +22525,7 @@
         <v>9.36870288848877</v>
       </c>
       <c r="G764" t="n">
-        <v>5.76060342788696</v>
+        <v>5.76060438156128</v>
       </c>
       <c r="H764" t="n">
         <v>1005107</v>
@@ -22554,7 +22554,7 @@
         <v>9.36870288848877</v>
       </c>
       <c r="G765" t="n">
-        <v>5.76060342788696</v>
+        <v>5.76060438156128</v>
       </c>
       <c r="H765" t="n">
         <v>918875</v>
@@ -22583,7 +22583,7 @@
         <v>9.8167028427124</v>
       </c>
       <c r="G766" t="n">
-        <v>6.0360689163208</v>
+        <v>6.03606939315796</v>
       </c>
       <c r="H766" t="n">
         <v>2352783</v>
@@ -22612,7 +22612,7 @@
         <v>10.192982673645</v>
       </c>
       <c r="G767" t="n">
-        <v>6.26743507385254</v>
+        <v>6.2674355506897</v>
       </c>
       <c r="H767" t="n">
         <v>1708471</v>
@@ -22641,7 +22641,7 @@
         <v>10.1733341217041</v>
       </c>
       <c r="G768" t="n">
-        <v>6.25535345077515</v>
+        <v>6.2553539276123</v>
       </c>
       <c r="H768" t="n">
         <v>1293330</v>
@@ -22670,7 +22670,7 @@
         <v>10.1094751358032</v>
       </c>
       <c r="G769" t="n">
-        <v>6.21608781814575</v>
+        <v>6.21608829498291</v>
       </c>
       <c r="H769" t="n">
         <v>2416603</v>
@@ -22699,7 +22699,7 @@
         <v>9.97193145751953</v>
       </c>
       <c r="G770" t="n">
-        <v>6.13151454925537</v>
+        <v>6.13151550292969</v>
       </c>
       <c r="H770" t="n">
         <v>1780381</v>
@@ -22728,7 +22728,7 @@
         <v>10.1291236877441</v>
       </c>
       <c r="G771" t="n">
-        <v>6.2281699180603</v>
+        <v>6.22816944122314</v>
       </c>
       <c r="H771" t="n">
         <v>1172711</v>
@@ -22786,7 +22786,7 @@
         <v>9.84421062469482</v>
       </c>
       <c r="G773" t="n">
-        <v>6.05298280715942</v>
+        <v>6.05298185348511</v>
       </c>
       <c r="H773" t="n">
         <v>1856324</v>
@@ -22844,7 +22844,7 @@
         <v>9.84912395477295</v>
       </c>
       <c r="G775" t="n">
-        <v>6.05600357055664</v>
+        <v>6.05600452423096</v>
       </c>
       <c r="H775" t="n">
         <v>1140745</v>
@@ -22873,7 +22873,7 @@
         <v>9.93754482269287</v>
       </c>
       <c r="G776" t="n">
-        <v>6.11037158966064</v>
+        <v>6.11037111282349</v>
       </c>
       <c r="H776" t="n">
         <v>1298414</v>
@@ -22931,7 +22931,7 @@
         <v>9.70470333099365</v>
       </c>
       <c r="G778" t="n">
-        <v>5.96720314025879</v>
+        <v>5.96720361709595</v>
       </c>
       <c r="H778" t="n">
         <v>1348415</v>
@@ -22960,7 +22960,7 @@
         <v>9.61431694030762</v>
       </c>
       <c r="G779" t="n">
-        <v>5.91162633895874</v>
+        <v>5.9116268157959</v>
       </c>
       <c r="H779" t="n">
         <v>928126</v>
@@ -23018,7 +23018,7 @@
         <v>10.772632598877</v>
       </c>
       <c r="G781" t="n">
-        <v>6.62384843826294</v>
+        <v>6.6238489151001</v>
       </c>
       <c r="H781" t="n">
         <v>3403879</v>
@@ -23047,7 +23047,7 @@
         <v>10.8905267715454</v>
       </c>
       <c r="G782" t="n">
-        <v>6.69633769989014</v>
+        <v>6.69633817672729</v>
       </c>
       <c r="H782" t="n">
         <v>2315439</v>
@@ -23076,7 +23076,7 @@
         <v>11.2098264694214</v>
       </c>
       <c r="G783" t="n">
-        <v>6.89266872406006</v>
+        <v>6.89266920089722</v>
       </c>
       <c r="H783" t="n">
         <v>3269100</v>
@@ -23134,7 +23134,7 @@
         <v>10.8757905960083</v>
       </c>
       <c r="G785" t="n">
-        <v>6.68727731704712</v>
+        <v>6.68727874755859</v>
       </c>
       <c r="H785" t="n">
         <v>2086028</v>
@@ -23163,7 +23163,7 @@
         <v>10.9200010299683</v>
       </c>
       <c r="G786" t="n">
-        <v>6.7144627571106</v>
+        <v>6.71446228027344</v>
       </c>
       <c r="H786" t="n">
         <v>1140529</v>
@@ -23192,7 +23192,7 @@
         <v>10.9740362167358</v>
       </c>
       <c r="G787" t="n">
-        <v>6.74768733978271</v>
+        <v>6.7476863861084</v>
       </c>
       <c r="H787" t="n">
         <v>818917</v>
@@ -23221,7 +23221,7 @@
         <v>10.9789476394653</v>
       </c>
       <c r="G788" t="n">
-        <v>6.75070762634277</v>
+        <v>6.75070714950562</v>
       </c>
       <c r="H788" t="n">
         <v>1274964</v>
@@ -23250,7 +23250,7 @@
         <v>11.013334274292</v>
       </c>
       <c r="G789" t="n">
-        <v>6.77185106277466</v>
+        <v>6.77184963226318</v>
       </c>
       <c r="H789" t="n">
         <v>786339</v>
@@ -23279,7 +23279,7 @@
         <v>10.8070192337036</v>
       </c>
       <c r="G790" t="n">
-        <v>6.64499235153198</v>
+        <v>6.64499282836914</v>
       </c>
       <c r="H790" t="n">
         <v>1179035</v>
@@ -23308,7 +23308,7 @@
         <v>10.728422164917</v>
       </c>
       <c r="G791" t="n">
-        <v>6.59666442871094</v>
+        <v>6.59666347503662</v>
       </c>
       <c r="H791" t="n">
         <v>1039081</v>
@@ -23337,7 +23337,7 @@
         <v>11.1557912826538</v>
       </c>
       <c r="G792" t="n">
-        <v>6.85944318771362</v>
+        <v>6.85944366455078</v>
       </c>
       <c r="H792" t="n">
         <v>1716177</v>
@@ -23366,7 +23366,7 @@
         <v>11.4259662628174</v>
       </c>
       <c r="G793" t="n">
-        <v>7.02556896209717</v>
+        <v>7.02556848526001</v>
       </c>
       <c r="H793" t="n">
         <v>1596679</v>
@@ -23453,7 +23453,7 @@
         <v>11.8533344268799</v>
       </c>
       <c r="G796" t="n">
-        <v>7.28834819793701</v>
+        <v>7.28834772109985</v>
       </c>
       <c r="H796" t="n">
         <v>1882919</v>
@@ -23482,7 +23482,7 @@
         <v>12.0252637863159</v>
       </c>
       <c r="G797" t="n">
-        <v>7.39406204223633</v>
+        <v>7.39406299591064</v>
       </c>
       <c r="H797" t="n">
         <v>1390523</v>
@@ -23511,7 +23511,7 @@
         <v>12.005615234375</v>
       </c>
       <c r="G798" t="n">
-        <v>7.38198137283325</v>
+        <v>7.38198041915894</v>
       </c>
       <c r="H798" t="n">
         <v>1031140</v>
@@ -23540,7 +23540,7 @@
         <v>12.0350885391235</v>
       </c>
       <c r="G799" t="n">
-        <v>7.40010404586792</v>
+        <v>7.4001030921936</v>
       </c>
       <c r="H799" t="n">
         <v>851696</v>
@@ -23598,7 +23598,7 @@
         <v>12.1382465362549</v>
       </c>
       <c r="G801" t="n">
-        <v>7.4635329246521</v>
+        <v>7.46353387832642</v>
       </c>
       <c r="H801" t="n">
         <v>1251759</v>
@@ -23685,7 +23685,7 @@
         <v>12.1480712890625</v>
       </c>
       <c r="G804" t="n">
-        <v>7.46957492828369</v>
+        <v>7.46957445144653</v>
       </c>
       <c r="H804" t="n">
         <v>1930594</v>
@@ -23714,7 +23714,7 @@
         <v>12.6294746398926</v>
       </c>
       <c r="G805" t="n">
-        <v>7.7655782699585</v>
+        <v>7.76557922363281</v>
       </c>
       <c r="H805" t="n">
         <v>3106680</v>
@@ -23772,7 +23772,7 @@
         <v>12.6736850738525</v>
       </c>
       <c r="G807" t="n">
-        <v>7.79276323318481</v>
+        <v>7.7927622795105</v>
       </c>
       <c r="H807" t="n">
         <v>1099338</v>
@@ -23859,7 +23859,7 @@
         <v>13.1501770019531</v>
       </c>
       <c r="G810" t="n">
-        <v>8.08574676513672</v>
+        <v>8.08574771881104</v>
       </c>
       <c r="H810" t="n">
         <v>4301523</v>
@@ -23888,7 +23888,7 @@
         <v>13.5726327896118</v>
       </c>
       <c r="G811" t="n">
-        <v>8.3455057144165</v>
+        <v>8.34550476074219</v>
       </c>
       <c r="H811" t="n">
         <v>5506554</v>
@@ -23917,7 +23917,7 @@
         <v>13.5726327896118</v>
       </c>
       <c r="G812" t="n">
-        <v>8.3455057144165</v>
+        <v>8.34550476074219</v>
       </c>
       <c r="H812" t="n">
         <v>2655732</v>
@@ -23946,7 +23946,7 @@
         <v>13.6708793640137</v>
       </c>
       <c r="G813" t="n">
-        <v>8.40591430664062</v>
+        <v>8.40591526031494</v>
       </c>
       <c r="H813" t="n">
         <v>1725742</v>
@@ -24004,7 +24004,7 @@
         <v>14.2112302780151</v>
       </c>
       <c r="G815" t="n">
-        <v>8.73816394805908</v>
+        <v>8.7381649017334</v>
       </c>
       <c r="H815" t="n">
         <v>2191230</v>
@@ -24091,7 +24091,7 @@
         <v>14.8449144363403</v>
       </c>
       <c r="G818" t="n">
-        <v>9.12780284881592</v>
+        <v>9.1278018951416</v>
       </c>
       <c r="H818" t="n">
         <v>2384223</v>
@@ -24120,7 +24120,7 @@
         <v>14.5894746780396</v>
       </c>
       <c r="G819" t="n">
-        <v>8.97073841094971</v>
+        <v>8.97073936462402</v>
       </c>
       <c r="H819" t="n">
         <v>2867556</v>
@@ -24178,7 +24178,7 @@
         <v>14.3094749450684</v>
       </c>
       <c r="G821" t="n">
-        <v>8.79857349395752</v>
+        <v>8.7985725402832</v>
       </c>
       <c r="H821" t="n">
         <v>1837891</v>
@@ -24236,7 +24236,7 @@
         <v>14.5403518676758</v>
       </c>
       <c r="G823" t="n">
-        <v>8.94053363800049</v>
+        <v>8.94053268432617</v>
       </c>
       <c r="H823" t="n">
         <v>1306999</v>
@@ -24352,7 +24352,7 @@
         <v>14.9971952438354</v>
       </c>
       <c r="G827" t="n">
-        <v>9.22143650054932</v>
+        <v>9.22143745422363</v>
       </c>
       <c r="H827" t="n">
         <v>1463953</v>
@@ -24381,7 +24381,7 @@
         <v>15.0561418533325</v>
       </c>
       <c r="G828" t="n">
-        <v>9.25768089294434</v>
+        <v>9.25768184661865</v>
       </c>
       <c r="H828" t="n">
         <v>1567073</v>
@@ -24410,7 +24410,7 @@
         <v>15.4687738418579</v>
       </c>
       <c r="G829" t="n">
-        <v>9.511399269104</v>
+        <v>9.51140022277832</v>
       </c>
       <c r="H829" t="n">
         <v>2748948</v>
@@ -24439,7 +24439,7 @@
         <v>15.3950891494751</v>
       </c>
       <c r="G830" t="n">
-        <v>9.46609210968018</v>
+        <v>9.46609115600586</v>
       </c>
       <c r="H830" t="n">
         <v>2042130</v>
@@ -24555,7 +24555,7 @@
         <v>15.6407032012939</v>
       </c>
       <c r="G834" t="n">
-        <v>9.61711502075195</v>
+        <v>9.61711406707764</v>
       </c>
       <c r="H834" t="n">
         <v>1514312</v>
@@ -24584,7 +24584,7 @@
         <v>15.7536859512329</v>
       </c>
       <c r="G835" t="n">
-        <v>9.68658542633057</v>
+        <v>9.68658638000488</v>
       </c>
       <c r="H835" t="n">
         <v>1670247</v>
@@ -24613,7 +24613,7 @@
         <v>15.7684230804443</v>
       </c>
       <c r="G836" t="n">
-        <v>9.69564628601074</v>
+        <v>9.69564723968506</v>
       </c>
       <c r="H836" t="n">
         <v>1574210</v>
@@ -24729,7 +24729,7 @@
         <v>16.7017555236816</v>
       </c>
       <c r="G840" t="n">
-        <v>10.2695322036743</v>
+        <v>10.26953125</v>
       </c>
       <c r="H840" t="n">
         <v>2063718</v>
@@ -24758,7 +24758,7 @@
         <v>16.8982467651367</v>
       </c>
       <c r="G841" t="n">
-        <v>10.3903503417969</v>
+        <v>10.3903493881226</v>
       </c>
       <c r="H841" t="n">
         <v>2699757</v>
@@ -24787,7 +24787,7 @@
         <v>16.9670181274414</v>
       </c>
       <c r="G842" t="n">
-        <v>10.432635307312</v>
+        <v>10.4326362609863</v>
       </c>
       <c r="H842" t="n">
         <v>2529615</v>
@@ -24816,7 +24816,7 @@
         <v>17.3059673309326</v>
       </c>
       <c r="G843" t="n">
-        <v>10.6410484313965</v>
+        <v>10.6410474777222</v>
       </c>
       <c r="H843" t="n">
         <v>3096815</v>
@@ -24845,7 +24845,7 @@
         <v>17.3207035064697</v>
       </c>
       <c r="G844" t="n">
-        <v>10.650110244751</v>
+        <v>10.6501092910767</v>
       </c>
       <c r="H844" t="n">
         <v>2836948</v>
@@ -24874,7 +24874,7 @@
         <v>17.6596508026123</v>
       </c>
       <c r="G845" t="n">
-        <v>10.8585214614868</v>
+        <v>10.8585195541382</v>
       </c>
       <c r="H845" t="n">
         <v>3965629</v>
@@ -24932,7 +24932,7 @@
         <v>17.6350898742676</v>
       </c>
       <c r="G847" t="n">
-        <v>10.8434181213379</v>
+        <v>10.8434200286865</v>
       </c>
       <c r="H847" t="n">
         <v>2467254</v>
@@ -24961,7 +24961,7 @@
         <v>17.4533348083496</v>
       </c>
       <c r="G848" t="n">
-        <v>10.7316617965698</v>
+        <v>10.7316608428955</v>
       </c>
       <c r="H848" t="n">
         <v>1995771</v>
@@ -24990,7 +24990,7 @@
         <v>17.3059673309326</v>
       </c>
       <c r="G849" t="n">
-        <v>10.6410484313965</v>
+        <v>10.6410474777222</v>
       </c>
       <c r="H849" t="n">
         <v>3743215</v>
@@ -25019,7 +25019,7 @@
         <v>17.3747386932373</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6833343505859</v>
+        <v>10.6833333969116</v>
       </c>
       <c r="H850" t="n">
         <v>2672705</v>
@@ -25077,7 +25077,7 @@
         <v>16.5838603973389</v>
       </c>
       <c r="G852" t="n">
-        <v>10.1970415115356</v>
+        <v>10.1970405578613</v>
       </c>
       <c r="H852" t="n">
         <v>4875803</v>
@@ -25135,7 +25135,7 @@
         <v>16.259651184082</v>
       </c>
       <c r="G854" t="n">
-        <v>9.9976921081543</v>
+        <v>9.99769306182861</v>
       </c>
       <c r="H854" t="n">
         <v>3023914</v>
@@ -25164,7 +25164,7 @@
         <v>16.9080715179443</v>
       </c>
       <c r="G855" t="n">
-        <v>10.396390914917</v>
+        <v>10.3963918685913</v>
       </c>
       <c r="H855" t="n">
         <v>2143097</v>
@@ -25193,7 +25193,7 @@
         <v>16.9080715179443</v>
       </c>
       <c r="G856" t="n">
-        <v>10.396390914917</v>
+        <v>10.3963918685913</v>
       </c>
       <c r="H856" t="n">
         <v>2511580</v>
@@ -25222,7 +25222,7 @@
         <v>17.0898265838623</v>
       </c>
       <c r="G857" t="n">
-        <v>10.5081462860107</v>
+        <v>10.5081491470337</v>
       </c>
       <c r="H857" t="n">
         <v>2326049</v>
@@ -25251,7 +25251,7 @@
         <v>16.8982467651367</v>
       </c>
       <c r="G858" t="n">
-        <v>10.3903503417969</v>
+        <v>10.3903493881226</v>
       </c>
       <c r="H858" t="n">
         <v>3866269</v>
@@ -25280,7 +25280,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G859" t="n">
-        <v>10.4833517074585</v>
+        <v>10.4833526611328</v>
       </c>
       <c r="H859" t="n">
         <v>3247249</v>
@@ -25309,7 +25309,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>10.1792945861816</v>
+        <v>10.179295539856</v>
       </c>
       <c r="H860" t="n">
         <v>2899010</v>
@@ -25338,7 +25338,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G861" t="n">
-        <v>10.1759920120239</v>
+        <v>10.1759901046753</v>
       </c>
       <c r="H861" t="n">
         <v>1694296</v>
@@ -25483,7 +25483,7 @@
         <v>14.6800003051758</v>
       </c>
       <c r="G866" t="n">
-        <v>9.70338153839111</v>
+        <v>9.7033805847168</v>
       </c>
       <c r="H866" t="n">
         <v>840013</v>
@@ -25541,7 +25541,7 @@
         <v>14.875</v>
       </c>
       <c r="G868" t="n">
-        <v>9.83227443695068</v>
+        <v>9.83227348327637</v>
       </c>
       <c r="H868" t="n">
         <v>2018019</v>
@@ -25599,7 +25599,7 @@
         <v>15.3149995803833</v>
       </c>
       <c r="G870" t="n">
-        <v>10.1231107711792</v>
+        <v>10.1231117248535</v>
       </c>
       <c r="H870" t="n">
         <v>2827289</v>
@@ -25686,7 +25686,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G873" t="n">
-        <v>9.91159248352051</v>
+        <v>9.91159343719482</v>
       </c>
       <c r="H873" t="n">
         <v>1406400</v>
@@ -25744,7 +25744,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G875" t="n">
-        <v>10.0272674560547</v>
+        <v>10.0272665023804</v>
       </c>
       <c r="H875" t="n">
         <v>1951808</v>
@@ -25773,7 +25773,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G876" t="n">
-        <v>10.199125289917</v>
+        <v>10.1991262435913</v>
       </c>
       <c r="H876" t="n">
         <v>1963251</v>
@@ -25802,7 +25802,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G877" t="n">
-        <v>10.4965724945068</v>
+        <v>10.4965734481812</v>
       </c>
       <c r="H877" t="n">
         <v>3026763</v>
@@ -25831,7 +25831,7 @@
         <v>15.9650001525879</v>
       </c>
       <c r="G878" t="n">
-        <v>10.5527563095093</v>
+        <v>10.5527572631836</v>
       </c>
       <c r="H878" t="n">
         <v>2143105</v>
@@ -25860,7 +25860,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>10.7080898284912</v>
+        <v>10.7080917358398</v>
       </c>
       <c r="H879" t="n">
         <v>1650989</v>
@@ -25889,7 +25889,7 @@
         <v>16.5149993896484</v>
       </c>
       <c r="G880" t="n">
-        <v>10.9163036346436</v>
+        <v>10.9163026809692</v>
       </c>
       <c r="H880" t="n">
         <v>2110305</v>
@@ -25918,7 +25918,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>10.9559631347656</v>
+        <v>10.9559640884399</v>
       </c>
       <c r="H881" t="n">
         <v>1757491</v>
@@ -26034,7 +26034,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G885" t="n">
-        <v>11.0451965332031</v>
+        <v>11.0451974868774</v>
       </c>
       <c r="H885" t="n">
         <v>1304394</v>
@@ -26237,7 +26237,7 @@
         <v>17.4549999237061</v>
       </c>
       <c r="G892" t="n">
-        <v>11.5376358032227</v>
+        <v>11.537636756897</v>
       </c>
       <c r="H892" t="n">
         <v>1923633</v>
@@ -26382,7 +26382,7 @@
         <v>17.5750007629395</v>
       </c>
       <c r="G897" t="n">
-        <v>11.6169548034668</v>
+        <v>11.6169557571411</v>
       </c>
       <c r="H897" t="n">
         <v>1652576</v>
@@ -26411,7 +26411,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G898" t="n">
-        <v>11.5806007385254</v>
+        <v>11.5806016921997</v>
       </c>
       <c r="H898" t="n">
         <v>1093455</v>
@@ -26440,7 +26440,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G899" t="n">
-        <v>11.7128000259399</v>
+        <v>11.7128009796143</v>
       </c>
       <c r="H899" t="n">
         <v>2830779</v>
@@ -26469,7 +26469,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>11.6665296554565</v>
+        <v>11.6665315628052</v>
       </c>
       <c r="H900" t="n">
         <v>1504634</v>
@@ -26585,7 +26585,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G904" t="n">
-        <v>11.378999710083</v>
+        <v>11.3789987564087</v>
       </c>
       <c r="H904" t="n">
         <v>986100</v>
@@ -26701,7 +26701,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G908" t="n">
-        <v>11.4219636917114</v>
+        <v>11.4219627380371</v>
       </c>
       <c r="H908" t="n">
         <v>673027</v>
@@ -26759,7 +26759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G910" t="n">
-        <v>11.0451965332031</v>
+        <v>11.0451974868774</v>
       </c>
       <c r="H910" t="n">
         <v>1699225</v>
@@ -26846,7 +26846,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>11.0253677368164</v>
+        <v>11.0253667831421</v>
       </c>
       <c r="H913" t="n">
         <v>2052281</v>
@@ -26875,7 +26875,7 @@
         <v>16.3649997711182</v>
       </c>
       <c r="G914" t="n">
-        <v>10.8171539306641</v>
+        <v>10.8171548843384</v>
       </c>
       <c r="H914" t="n">
         <v>1924721</v>
@@ -27020,7 +27020,7 @@
         <v>15.75</v>
       </c>
       <c r="G919" t="n">
-        <v>10.4106435775757</v>
+        <v>10.41064453125</v>
       </c>
       <c r="H919" t="n">
         <v>1122984</v>
@@ -27049,7 +27049,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G920" t="n">
-        <v>10.4701328277588</v>
+        <v>10.4701318740845</v>
       </c>
       <c r="H920" t="n">
         <v>1376903</v>
@@ -27078,7 +27078,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>10.1131973266602</v>
+        <v>10.1131963729858</v>
       </c>
       <c r="H921" t="n">
         <v>1373735</v>
@@ -27136,7 +27136,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G923" t="n">
-        <v>10.4701328277588</v>
+        <v>10.4701318740845</v>
       </c>
       <c r="H923" t="n">
         <v>741703</v>
@@ -27194,7 +27194,7 @@
         <v>16.4050006866455</v>
       </c>
       <c r="G925" t="n">
-        <v>10.8435955047607</v>
+        <v>10.8435945510864</v>
       </c>
       <c r="H925" t="n">
         <v>1161838</v>
@@ -27223,7 +27223,7 @@
         <v>16.3349990844727</v>
       </c>
       <c r="G926" t="n">
-        <v>10.797324180603</v>
+        <v>10.7973251342773</v>
       </c>
       <c r="H926" t="n">
         <v>880812</v>
@@ -27281,7 +27281,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G928" t="n">
-        <v>10.6816520690918</v>
+        <v>10.6816511154175</v>
       </c>
       <c r="H928" t="n">
         <v>1032866</v>
@@ -27310,7 +27310,7 @@
         <v>16.0900001525879</v>
       </c>
       <c r="G929" t="n">
-        <v>10.6353816986084</v>
+        <v>10.6353807449341</v>
       </c>
       <c r="H929" t="n">
         <v>696478</v>
@@ -27339,7 +27339,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G930" t="n">
-        <v>10.4337768554688</v>
+        <v>10.4337778091431</v>
       </c>
       <c r="H930" t="n">
         <v>2632099</v>
@@ -27368,7 +27368,7 @@
         <v>16.2749996185303</v>
       </c>
       <c r="G931" t="n">
-        <v>10.7576627731323</v>
+        <v>10.7576637268066</v>
       </c>
       <c r="H931" t="n">
         <v>1280286</v>
@@ -27455,7 +27455,7 @@
         <v>16.4099998474121</v>
       </c>
       <c r="G934" t="n">
-        <v>10.8468980789185</v>
+        <v>10.8468990325928</v>
       </c>
       <c r="H934" t="n">
         <v>756307</v>
@@ -27542,7 +27542,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G937" t="n">
-        <v>11.157564163208</v>
+        <v>11.1575651168823</v>
       </c>
       <c r="H937" t="n">
         <v>960124</v>
@@ -27571,7 +27571,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G938" t="n">
-        <v>11.2765436172485</v>
+        <v>11.2765445709229</v>
       </c>
       <c r="H938" t="n">
         <v>828238</v>
@@ -27600,7 +27600,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G939" t="n">
-        <v>11.0055379867554</v>
+        <v>11.0055370330811</v>
       </c>
       <c r="H939" t="n">
         <v>1495122</v>
@@ -27629,7 +27629,7 @@
         <v>16.6550006866455</v>
       </c>
       <c r="G940" t="n">
-        <v>11.0088424682617</v>
+        <v>11.008843421936</v>
       </c>
       <c r="H940" t="n">
         <v>855841</v>
@@ -27687,7 +27687,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G942" t="n">
-        <v>11.3162059783936</v>
+        <v>11.3162031173706</v>
       </c>
       <c r="H942" t="n">
         <v>1332392</v>
@@ -27716,7 +27716,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G943" t="n">
-        <v>11.2633247375488</v>
+        <v>11.2633266448975</v>
       </c>
       <c r="H943" t="n">
         <v>957720</v>
@@ -27774,7 +27774,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G945" t="n">
-        <v>11.382303237915</v>
+        <v>11.3823022842407</v>
       </c>
       <c r="H945" t="n">
         <v>1033725</v>
@@ -27861,7 +27861,7 @@
         <v>17.2700004577637</v>
       </c>
       <c r="G948" t="n">
-        <v>11.4153537750244</v>
+        <v>11.4153528213501</v>
       </c>
       <c r="H948" t="n">
         <v>1017683</v>
@@ -27890,7 +27890,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G949" t="n">
-        <v>11.4087438583374</v>
+        <v>11.4087429046631</v>
       </c>
       <c r="H949" t="n">
         <v>795386</v>
@@ -27919,7 +27919,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G950" t="n">
-        <v>11.2930679321289</v>
+        <v>11.2930688858032</v>
       </c>
       <c r="H950" t="n">
         <v>1410325</v>
@@ -27948,7 +27948,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G951" t="n">
-        <v>11.3327283859253</v>
+        <v>11.3327302932739</v>
       </c>
       <c r="H951" t="n">
         <v>604671</v>
@@ -27977,7 +27977,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>11.3889122009277</v>
+        <v>11.3889141082764</v>
       </c>
       <c r="H952" t="n">
         <v>560816</v>
@@ -28006,7 +28006,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G953" t="n">
-        <v>11.382303237915</v>
+        <v>11.3823022842407</v>
       </c>
       <c r="H953" t="n">
         <v>879661</v>
@@ -28122,7 +28122,7 @@
         <v>16.4799995422363</v>
       </c>
       <c r="G957" t="n">
-        <v>10.8931674957275</v>
+        <v>10.8931684494019</v>
       </c>
       <c r="H957" t="n">
         <v>778656</v>
@@ -28209,7 +28209,7 @@
         <v>16.4650001525879</v>
       </c>
       <c r="G960" t="n">
-        <v>10.8832530975342</v>
+        <v>10.8832540512085</v>
       </c>
       <c r="H960" t="n">
         <v>1042927</v>
@@ -28238,7 +28238,7 @@
         <v>16.6749992370605</v>
       </c>
       <c r="G961" t="n">
-        <v>11.0220623016357</v>
+        <v>11.0220613479614</v>
       </c>
       <c r="H961" t="n">
         <v>674663</v>
@@ -28267,7 +28267,7 @@
         <v>16.7950000762939</v>
       </c>
       <c r="G962" t="n">
-        <v>11.1013803482056</v>
+        <v>11.1013822555542</v>
       </c>
       <c r="H962" t="n">
         <v>853089</v>
@@ -28296,7 +28296,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>11.0385866165161</v>
+        <v>11.0385875701904</v>
       </c>
       <c r="H963" t="n">
         <v>554209</v>
@@ -28383,7 +28383,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G966" t="n">
-        <v>11.398829460144</v>
+        <v>11.3988285064697</v>
       </c>
       <c r="H966" t="n">
         <v>1569694</v>
@@ -28412,7 +28412,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>11.5178050994873</v>
+        <v>11.5178060531616</v>
       </c>
       <c r="H967" t="n">
         <v>1475410</v>
@@ -28441,7 +28441,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G968" t="n">
-        <v>12.0300779342651</v>
+        <v>12.0300769805908</v>
       </c>
       <c r="H968" t="n">
         <v>4333705</v>
@@ -28470,7 +28470,7 @@
         <v>18.5</v>
       </c>
       <c r="G969" t="n">
-        <v>12.2283744812012</v>
+        <v>12.2283754348755</v>
       </c>
       <c r="H969" t="n">
         <v>3444209</v>
@@ -28499,7 +28499,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>11.9970273971558</v>
+        <v>11.9970264434814</v>
       </c>
       <c r="H970" t="n">
         <v>2046572</v>
@@ -28557,7 +28557,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G972" t="n">
-        <v>12.0697364807129</v>
+        <v>12.0697374343872</v>
       </c>
       <c r="H972" t="n">
         <v>752467</v>
@@ -28586,7 +28586,7 @@
         <v>18.5</v>
       </c>
       <c r="G973" t="n">
-        <v>12.2283744812012</v>
+        <v>12.2283754348755</v>
       </c>
       <c r="H973" t="n">
         <v>1345548</v>
@@ -28673,7 +28673,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G976" t="n">
-        <v>12.1754951477051</v>
+        <v>12.1754961013794</v>
       </c>
       <c r="H976" t="n">
         <v>1812082</v>
@@ -28731,7 +28731,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>12.4597225189209</v>
+        <v>12.4597244262695</v>
       </c>
       <c r="H978" t="n">
         <v>1415620</v>
@@ -28760,7 +28760,7 @@
         <v>19.5</v>
       </c>
       <c r="G979" t="n">
-        <v>12.889368057251</v>
+        <v>12.8893671035767</v>
       </c>
       <c r="H979" t="n">
         <v>5746018</v>
@@ -28818,7 +28818,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>13.5834121704102</v>
+        <v>13.5834112167358</v>
       </c>
       <c r="H981" t="n">
         <v>3841058</v>
@@ -28847,7 +28847,7 @@
         <v>20.5</v>
       </c>
       <c r="G982" t="n">
-        <v>13.5503606796265</v>
+        <v>13.5503597259521</v>
       </c>
       <c r="H982" t="n">
         <v>2467886</v>
@@ -28934,7 +28934,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G985" t="n">
-        <v>14.2774524688721</v>
+        <v>14.2774534225464</v>
       </c>
       <c r="H985" t="n">
         <v>2487850</v>
@@ -29021,7 +29021,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G988" t="n">
-        <v>14.8260774612427</v>
+        <v>14.826078414917</v>
       </c>
       <c r="H988" t="n">
         <v>4467123</v>
@@ -29079,7 +29079,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G990" t="n">
-        <v>15.1896228790283</v>
+        <v>15.189624786377</v>
       </c>
       <c r="H990" t="n">
         <v>2811484</v>
@@ -29108,7 +29108,7 @@
         <v>22.8199996948242</v>
       </c>
       <c r="G991" t="n">
-        <v>15.0838661193848</v>
+        <v>15.0838642120361</v>
       </c>
       <c r="H991" t="n">
         <v>2112024</v>
@@ -29137,7 +29137,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>15.2094564437866</v>
+        <v>15.209454536438</v>
       </c>
       <c r="H992" t="n">
         <v>2233764</v>
@@ -29166,7 +29166,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G993" t="n">
-        <v>15.4804620742798</v>
+        <v>15.4804639816284</v>
       </c>
       <c r="H993" t="n">
         <v>1696088</v>
@@ -29195,7 +29195,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G994" t="n">
-        <v>15.6523189544678</v>
+        <v>15.6523208618164</v>
       </c>
       <c r="H994" t="n">
         <v>2661522</v>
@@ -29224,7 +29224,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5729990005493</v>
+        <v>15.5730009078979</v>
       </c>
       <c r="H995" t="n">
         <v>2216885</v>
@@ -29369,7 +29369,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1000" t="n">
-        <v>14.9252262115479</v>
+        <v>14.9252271652222</v>
       </c>
       <c r="H1000" t="n">
         <v>1853018</v>
@@ -29485,7 +29485,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>14.5088033676147</v>
+        <v>14.5088024139404</v>
       </c>
       <c r="H1004" t="n">
         <v>1966184</v>
@@ -29514,7 +29514,7 @@
         <v>21.7800006866455</v>
       </c>
       <c r="G1005" t="n">
-        <v>14.3964319229126</v>
+        <v>14.3964338302612</v>
       </c>
       <c r="H1005" t="n">
         <v>950366</v>
@@ -29543,7 +29543,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.429482460022</v>
+        <v>14.4294815063477</v>
       </c>
       <c r="H1006" t="n">
         <v>954820</v>
@@ -29572,7 +29572,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.2245759963989</v>
+        <v>14.2245750427246</v>
       </c>
       <c r="H1007" t="n">
         <v>1573908</v>
@@ -29601,7 +29601,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4162626266479</v>
+        <v>14.4162616729736</v>
       </c>
       <c r="H1008" t="n">
         <v>1305129</v>
@@ -29659,7 +29659,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.2377948760986</v>
+        <v>14.2377939224243</v>
       </c>
       <c r="H1010" t="n">
         <v>821275</v>
@@ -29688,7 +29688,7 @@
         <v>21.5</v>
       </c>
       <c r="G1011" t="n">
-        <v>14.2113561630249</v>
+        <v>14.2113542556763</v>
       </c>
       <c r="H1011" t="n">
         <v>1079433</v>
@@ -29717,7 +29717,7 @@
         <v>21.5</v>
       </c>
       <c r="G1012" t="n">
-        <v>14.2113561630249</v>
+        <v>14.2113542556763</v>
       </c>
       <c r="H1012" t="n">
         <v>1144584</v>
@@ -29746,7 +29746,7 @@
         <v>21.4699993133545</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.1915235519409</v>
+        <v>14.1915264129639</v>
       </c>
       <c r="H1013" t="n">
         <v>539394</v>
@@ -29775,7 +29775,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.0130577087402</v>
+        <v>14.0130567550659</v>
       </c>
       <c r="H1014" t="n">
         <v>715340</v>
@@ -29833,7 +29833,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.3105030059814</v>
+        <v>14.3105020523071</v>
       </c>
       <c r="H1016" t="n">
         <v>808769</v>
@@ -29862,7 +29862,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.026273727417</v>
+        <v>14.0262756347656</v>
       </c>
       <c r="H1017" t="n">
         <v>987673</v>
@@ -29891,7 +29891,7 @@
         <v>21.0799999237061</v>
       </c>
       <c r="G1018" t="n">
-        <v>13.9337387084961</v>
+        <v>13.9337377548218</v>
       </c>
       <c r="H1018" t="n">
         <v>1433032</v>
@@ -29978,7 +29978,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>15.5663890838623</v>
+        <v>15.5663909912109</v>
       </c>
       <c r="H1021" t="n">
         <v>4465059</v>
@@ -30036,7 +30036,7 @@
         <v>23.4300003051758</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.4870719909668</v>
+        <v>15.4870700836182</v>
       </c>
       <c r="H1023" t="n">
         <v>2386544</v>
@@ -30065,7 +30065,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.7580814361572</v>
+        <v>15.75807762146</v>
       </c>
       <c r="H1024" t="n">
         <v>1902374</v>
@@ -30094,7 +30094,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1025" t="n">
-        <v>15.8506155014038</v>
+        <v>15.8506164550781</v>
       </c>
       <c r="H1025" t="n">
         <v>3546413</v>
@@ -30123,7 +30123,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6523189544678</v>
+        <v>15.6523208618164</v>
       </c>
       <c r="H1026" t="n">
         <v>1644794</v>
@@ -30152,7 +30152,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.6523189544678</v>
+        <v>15.6523208618164</v>
       </c>
       <c r="H1027" t="n">
         <v>947057</v>
@@ -30181,7 +30181,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.6787605285645</v>
+        <v>15.6787586212158</v>
       </c>
       <c r="H1028" t="n">
         <v>683874</v>
@@ -30210,7 +30210,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1029" t="n">
-        <v>15.6258792877197</v>
+        <v>15.6258821487427</v>
       </c>
       <c r="H1029" t="n">
         <v>1045403</v>
@@ -30239,7 +30239,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1030" t="n">
-        <v>16.0224742889404</v>
+        <v>16.0224761962891</v>
       </c>
       <c r="H1030" t="n">
         <v>2741164</v>
@@ -30355,7 +30355,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.4672422409058</v>
+        <v>15.4672441482544</v>
       </c>
       <c r="H1034" t="n">
         <v>1824357</v>
@@ -30413,7 +30413,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.1565732955933</v>
+        <v>15.1565771102905</v>
       </c>
       <c r="H1036" t="n">
         <v>1474747</v>
@@ -30442,7 +30442,7 @@
         <v>22.1900005340576</v>
       </c>
       <c r="G1037" t="n">
-        <v>14.667441368103</v>
+        <v>14.6674394607544</v>
       </c>
       <c r="H1037" t="n">
         <v>2239964</v>
@@ -30471,7 +30471,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.6872701644897</v>
+        <v>14.6872682571411</v>
       </c>
       <c r="H1038" t="n">
         <v>1267649</v>
@@ -30529,7 +30529,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1040" t="n">
-        <v>15.1896228790283</v>
+        <v>15.189624786377</v>
       </c>
       <c r="H1040" t="n">
         <v>1697631</v>
@@ -30558,7 +30558,7 @@
         <v>22.75</v>
       </c>
       <c r="G1041" t="n">
-        <v>15.0375967025757</v>
+        <v>15.03759765625</v>
       </c>
       <c r="H1041" t="n">
         <v>1616128</v>
@@ -30587,7 +30587,7 @@
         <v>23.0699996948242</v>
       </c>
       <c r="G1042" t="n">
-        <v>15.2491159439087</v>
+        <v>15.2491140365601</v>
       </c>
       <c r="H1042" t="n">
         <v>1431887</v>
@@ -30645,7 +30645,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.4606323242188</v>
+        <v>15.4606304168701</v>
       </c>
       <c r="H1044" t="n">
         <v>1652920</v>
@@ -30761,7 +30761,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.7250280380249</v>
+        <v>15.7250299453735</v>
       </c>
       <c r="H1048" t="n">
         <v>958014</v>
@@ -30877,7 +30877,7 @@
         <v>22.2800006866455</v>
       </c>
       <c r="G1052" t="n">
-        <v>14.7269287109375</v>
+        <v>14.7269296646118</v>
       </c>
       <c r="H1052" t="n">
         <v>5747148</v>
@@ -30964,7 +30964,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7222204208374</v>
+        <v>13.7222185134888</v>
       </c>
       <c r="H1055" t="n">
         <v>2994810</v>
@@ -30993,7 +30993,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1056" t="n">
-        <v>13.0083484649658</v>
+        <v>13.0083465576172</v>
       </c>
       <c r="H1056" t="n">
         <v>4197534</v>
@@ -31051,7 +31051,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.2878637313843</v>
+        <v>12.2878646850586</v>
       </c>
       <c r="H1058" t="n">
         <v>4109843</v>
@@ -31080,7 +31080,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.2878637313843</v>
+        <v>12.2878646850586</v>
       </c>
       <c r="H1059" t="n">
         <v>3080120</v>
@@ -31138,7 +31138,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.6467018127441</v>
+        <v>11.6467008590698</v>
       </c>
       <c r="H1061" t="n">
         <v>3569482</v>
@@ -31196,7 +31196,7 @@
         <v>14.7449998855591</v>
       </c>
       <c r="G1063" t="n">
-        <v>9.74634456634521</v>
+        <v>9.74634552001953</v>
       </c>
       <c r="H1063" t="n">
         <v>5376854</v>
@@ -31225,7 +31225,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.13823127746582</v>
+        <v>9.13823223114014</v>
       </c>
       <c r="H1064" t="n">
         <v>3344891</v>
@@ -31254,7 +31254,7 @@
         <v>14</v>
       </c>
       <c r="G1065" t="n">
-        <v>9.25390625</v>
+        <v>9.25390529632568</v>
       </c>
       <c r="H1065" t="n">
         <v>3289354</v>
@@ -31283,7 +31283,7 @@
         <v>11.7749996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>7.78319454193115</v>
+        <v>7.78319549560547</v>
       </c>
       <c r="H1066" t="n">
         <v>5545350</v>
@@ -31312,7 +31312,7 @@
         <v>13.585000038147</v>
       </c>
       <c r="G1067" t="n">
-        <v>8.97959327697754</v>
+        <v>8.97959232330322</v>
       </c>
       <c r="H1067" t="n">
         <v>4758826</v>
@@ -31370,7 +31370,7 @@
         <v>11.4449996948242</v>
       </c>
       <c r="G1069" t="n">
-        <v>7.56506776809692</v>
+        <v>7.56506681442261</v>
       </c>
       <c r="H1069" t="n">
         <v>2820668</v>
@@ -31399,7 +31399,7 @@
         <v>10.9949998855591</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.26762056350708</v>
+        <v>7.26762008666992</v>
       </c>
       <c r="H1070" t="n">
         <v>1882242</v>
@@ -31428,7 +31428,7 @@
         <v>11.0950002670288</v>
       </c>
       <c r="G1071" t="n">
-        <v>7.33372068405151</v>
+        <v>7.3337197303772</v>
       </c>
       <c r="H1071" t="n">
         <v>2695998</v>
@@ -31457,7 +31457,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.07262706756592</v>
+        <v>7.07262802124023</v>
       </c>
       <c r="H1072" t="n">
         <v>4379838</v>
@@ -31486,7 +31486,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.16847229003906</v>
+        <v>7.16847133636475</v>
       </c>
       <c r="H1073" t="n">
         <v>2363974</v>
@@ -31602,7 +31602,7 @@
         <v>12.914999961853</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.53672790527344</v>
+        <v>8.53672695159912</v>
       </c>
       <c r="H1077" t="n">
         <v>3630973</v>
@@ -31631,7 +31631,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.36817455291748</v>
+        <v>8.3681755065918</v>
       </c>
       <c r="H1078" t="n">
         <v>1887247</v>
@@ -31660,7 +31660,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.71189117431641</v>
+        <v>8.71189212799072</v>
       </c>
       <c r="H1079" t="n">
         <v>1798002</v>
@@ -31747,7 +31747,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.18970680236816</v>
+        <v>8.18970584869385</v>
       </c>
       <c r="H1082" t="n">
         <v>2161807</v>
@@ -31776,7 +31776,7 @@
         <v>12.875</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.51028728485107</v>
+        <v>8.51028919219971</v>
       </c>
       <c r="H1083" t="n">
         <v>1423991</v>
@@ -31805,7 +31805,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.94984817504883</v>
+        <v>8.94984912872314</v>
       </c>
       <c r="H1084" t="n">
         <v>2799447</v>
@@ -31834,7 +31834,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1085" t="n">
-        <v>9.59101295471191</v>
+        <v>9.5910120010376</v>
       </c>
       <c r="H1085" t="n">
         <v>3385462</v>
@@ -31979,7 +31979,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.97628879547119</v>
+        <v>8.97628784179688</v>
       </c>
       <c r="H1090" t="n">
         <v>1363021</v>
@@ -32037,7 +32037,7 @@
         <v>13.2049999237061</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.72841453552246</v>
+        <v>8.72841548919678</v>
       </c>
       <c r="H1092" t="n">
         <v>1003917</v>
@@ -32066,7 +32066,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.80442905426025</v>
+        <v>8.80443000793457</v>
       </c>
       <c r="H1093" t="n">
         <v>1415630</v>
@@ -32211,7 +32211,7 @@
         <v>16</v>
       </c>
       <c r="G1098" t="n">
-        <v>10.5758924484253</v>
+        <v>10.575891494751</v>
       </c>
       <c r="H1098" t="n">
         <v>2982572</v>
@@ -32269,7 +32269,7 @@
         <v>15.3549995422363</v>
       </c>
       <c r="G1100" t="n">
-        <v>10.1495494842529</v>
+        <v>10.1495504379272</v>
       </c>
       <c r="H1100" t="n">
         <v>1923722</v>
@@ -32327,7 +32327,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93472766876221</v>
+        <v>9.93472671508789</v>
       </c>
       <c r="H1102" t="n">
         <v>1641990</v>
@@ -32414,7 +32414,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1105" t="n">
-        <v>10.1131973266602</v>
+        <v>10.1131963729858</v>
       </c>
       <c r="H1105" t="n">
         <v>1094473</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.94133853912354</v>
+        <v>9.94133758544922</v>
       </c>
       <c r="H1106" t="n">
         <v>1692734</v>
@@ -32501,7 +32501,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.91159248352051</v>
+        <v>9.91159343719482</v>
       </c>
       <c r="H1108" t="n">
         <v>1665982</v>
@@ -32646,7 +32646,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.0375356674194</v>
+        <v>10.0375347137451</v>
       </c>
       <c r="H1113" t="n">
         <v>1714194</v>
@@ -32675,7 +32675,7 @@
         <v>14.335000038147</v>
       </c>
       <c r="G1114" t="n">
-        <v>10.1579999923706</v>
+        <v>10.1579990386963</v>
       </c>
       <c r="H1114" t="n">
         <v>1533423</v>
@@ -32704,7 +32704,7 @@
         <v>14.4750003814697</v>
       </c>
       <c r="G1115" t="n">
-        <v>10.2572059631348</v>
+        <v>10.2572050094604</v>
       </c>
       <c r="H1115" t="n">
         <v>883314</v>
@@ -32762,7 +32762,7 @@
         <v>14.6049995422363</v>
       </c>
       <c r="G1117" t="n">
-        <v>10.3493251800537</v>
+        <v>10.3493242263794</v>
       </c>
       <c r="H1117" t="n">
         <v>2429906</v>
@@ -32820,7 +32820,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.5583667755127</v>
+        <v>10.558367729187</v>
       </c>
       <c r="H1119" t="n">
         <v>1793472</v>
@@ -32849,7 +32849,7 @@
         <v>15.0749998092651</v>
       </c>
       <c r="G1120" t="n">
-        <v>10.6823740005493</v>
+        <v>10.6823749542236</v>
       </c>
       <c r="H1120" t="n">
         <v>1491650</v>
@@ -32907,7 +32907,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1122" t="n">
-        <v>11.1288022994995</v>
+        <v>11.1288013458252</v>
       </c>
       <c r="H1122" t="n">
         <v>2340222</v>
@@ -32936,7 +32936,7 @@
         <v>16.0949993133545</v>
       </c>
       <c r="G1123" t="n">
-        <v>11.405161857605</v>
+        <v>11.4051609039307</v>
       </c>
       <c r="H1123" t="n">
         <v>4059275</v>
@@ -32965,7 +32965,7 @@
         <v>16.8950004577637</v>
       </c>
       <c r="G1124" t="n">
-        <v>11.9720544815063</v>
+        <v>11.9720554351807</v>
       </c>
       <c r="H1124" t="n">
         <v>4414848</v>
@@ -33081,7 +33081,7 @@
         <v>15.5050001144409</v>
       </c>
       <c r="G1128" t="n">
-        <v>10.9870796203613</v>
+        <v>10.987078666687</v>
       </c>
       <c r="H1128" t="n">
         <v>2811323</v>
@@ -33168,7 +33168,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.1040000915527</v>
+        <v>11.1039991378784</v>
       </c>
       <c r="H1131" t="n">
         <v>2377779</v>
@@ -33197,7 +33197,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.0047950744629</v>
+        <v>11.0047941207886</v>
       </c>
       <c r="H1132" t="n">
         <v>1759950</v>
@@ -33313,7 +33313,7 @@
         <v>15.7449998855591</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.1571464538574</v>
+        <v>11.1571455001831</v>
       </c>
       <c r="H1136" t="n">
         <v>1250378</v>
@@ -33400,7 +33400,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.5654525756836</v>
+        <v>10.5654516220093</v>
       </c>
       <c r="H1139" t="n">
         <v>1134044</v>
@@ -33458,7 +33458,7 @@
         <v>15.210000038147</v>
       </c>
       <c r="G1141" t="n">
-        <v>10.778037071228</v>
+        <v>10.7780380249023</v>
       </c>
       <c r="H1141" t="n">
         <v>785730</v>
@@ -33516,7 +33516,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G1143" t="n">
-        <v>11.0012502670288</v>
+        <v>11.0012512207031</v>
       </c>
       <c r="H1143" t="n">
         <v>1186028</v>
@@ -33574,7 +33574,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1145" t="n">
-        <v>11.1110877990723</v>
+        <v>11.1110868453979</v>
       </c>
       <c r="H1145" t="n">
         <v>953343</v>
@@ -33603,7 +33603,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>11.1040000915527</v>
+        <v>11.1039991378784</v>
       </c>
       <c r="H1146" t="n">
         <v>945965</v>
@@ -33632,7 +33632,7 @@
         <v>15.6549997329712</v>
       </c>
       <c r="G1147" t="n">
-        <v>11.0933704376221</v>
+        <v>11.0933723449707</v>
       </c>
       <c r="H1147" t="n">
         <v>1008367</v>
@@ -33690,7 +33690,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.008337020874</v>
+        <v>11.0083379745483</v>
       </c>
       <c r="H1149" t="n">
         <v>722472</v>
@@ -33719,7 +33719,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1854906082153</v>
+        <v>11.1854915618896</v>
       </c>
       <c r="H1150" t="n">
         <v>932858</v>
@@ -33748,7 +33748,7 @@
         <v>15.7650003433228</v>
       </c>
       <c r="G1151" t="n">
-        <v>11.1713199615479</v>
+        <v>11.1713190078735</v>
       </c>
       <c r="H1151" t="n">
         <v>1519982</v>
@@ -33777,7 +33777,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.6567220687866</v>
+        <v>11.6567211151123</v>
       </c>
       <c r="H1152" t="n">
         <v>2943399</v>
@@ -33835,7 +33835,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.6567220687866</v>
+        <v>11.6567211151123</v>
       </c>
       <c r="H1154" t="n">
         <v>1181922</v>
@@ -33864,7 +33864,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1155" t="n">
-        <v>12.0748023986816</v>
+        <v>12.0748043060303</v>
       </c>
       <c r="H1155" t="n">
         <v>2692841</v>
@@ -33922,7 +33922,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>12.0110292434692</v>
+        <v>12.0110282897949</v>
       </c>
       <c r="H1157" t="n">
         <v>1228791</v>
@@ -33951,7 +33951,7 @@
         <v>17.0849990844727</v>
       </c>
       <c r="G1158" t="n">
-        <v>12.1066913604736</v>
+        <v>12.1066904067993</v>
       </c>
       <c r="H1158" t="n">
         <v>1390224</v>
@@ -33980,7 +33980,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.855131149292</v>
+        <v>11.8551321029663</v>
       </c>
       <c r="H1159" t="n">
         <v>2229966</v>
@@ -34038,7 +34038,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.6708917617798</v>
+        <v>11.6708927154541</v>
       </c>
       <c r="H1161" t="n">
         <v>853190</v>
@@ -34096,7 +34096,7 @@
         <v>16.0750007629395</v>
       </c>
       <c r="G1163" t="n">
-        <v>11.3909912109375</v>
+        <v>11.3909902572632</v>
       </c>
       <c r="H1163" t="n">
         <v>1597908</v>
@@ -34125,7 +34125,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G1164" t="n">
-        <v>11.3732748031616</v>
+        <v>11.3732738494873</v>
       </c>
       <c r="H1164" t="n">
         <v>896098</v>
@@ -34183,7 +34183,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.6496343612671</v>
+        <v>11.6496353149414</v>
       </c>
       <c r="H1166" t="n">
         <v>1026790</v>
@@ -34241,7 +34241,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1168" t="n">
-        <v>11.7842702865601</v>
+        <v>11.7842693328857</v>
       </c>
       <c r="H1168" t="n">
         <v>890200</v>
@@ -34270,7 +34270,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1169" t="n">
-        <v>11.7630138397217</v>
+        <v>11.7630128860474</v>
       </c>
       <c r="H1169" t="n">
         <v>660035</v>
@@ -34299,7 +34299,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1170" t="n">
-        <v>11.7842702865601</v>
+        <v>11.7842693328857</v>
       </c>
       <c r="H1170" t="n">
         <v>795616</v>
@@ -34386,7 +34386,7 @@
         <v>16.8950004577637</v>
       </c>
       <c r="G1173" t="n">
-        <v>11.9720544815063</v>
+        <v>11.9720554351807</v>
       </c>
       <c r="H1173" t="n">
         <v>640427</v>
@@ -34473,7 +34473,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.7488403320312</v>
+        <v>11.7488393783569</v>
       </c>
       <c r="H1176" t="n">
         <v>764280</v>
@@ -34502,7 +34502,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1177" t="n">
-        <v>11.8055305480957</v>
+        <v>11.8055295944214</v>
       </c>
       <c r="H1177" t="n">
         <v>549110</v>
@@ -34531,7 +34531,7 @@
         <v>16.4349994659424</v>
       </c>
       <c r="G1178" t="n">
-        <v>11.6460914611816</v>
+        <v>11.6460905075073</v>
       </c>
       <c r="H1178" t="n">
         <v>488338</v>
@@ -34589,7 +34589,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G1180" t="n">
-        <v>11.9472551345825</v>
+        <v>11.9472532272339</v>
       </c>
       <c r="H1180" t="n">
         <v>946421</v>
@@ -34705,7 +34705,7 @@
         <v>16.4899997711182</v>
       </c>
       <c r="G1184" t="n">
-        <v>11.6850643157959</v>
+        <v>11.6850662231445</v>
       </c>
       <c r="H1184" t="n">
         <v>648900</v>
@@ -34734,7 +34734,7 @@
         <v>16.2049999237061</v>
       </c>
       <c r="G1185" t="n">
-        <v>11.4831085205078</v>
+        <v>11.4831094741821</v>
       </c>
       <c r="H1185" t="n">
         <v>832486</v>
@@ -34763,7 +34763,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G1186" t="n">
-        <v>11.3803596496582</v>
+        <v>11.3803606033325</v>
       </c>
       <c r="H1186" t="n">
         <v>988429</v>
@@ -34792,7 +34792,7 @@
         <v>16.3250007629395</v>
       </c>
       <c r="G1187" t="n">
-        <v>11.5681438446045</v>
+        <v>11.5681447982788</v>
       </c>
       <c r="H1187" t="n">
         <v>985517</v>
@@ -34879,7 +34879,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1190" t="n">
-        <v>11.4653940200806</v>
+        <v>11.4653930664062</v>
       </c>
       <c r="H1190" t="n">
         <v>433905</v>
@@ -34908,7 +34908,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1191" t="n">
-        <v>11.2102909088135</v>
+        <v>11.2102928161621</v>
       </c>
       <c r="H1191" t="n">
         <v>803012</v>
@@ -35082,7 +35082,7 @@
         <v>16.6550006866455</v>
       </c>
       <c r="G1197" t="n">
-        <v>11.8019857406616</v>
+        <v>11.8019876480103</v>
       </c>
       <c r="H1197" t="n">
         <v>638580</v>
@@ -35111,7 +35111,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.9118213653564</v>
+        <v>11.9118223190308</v>
       </c>
       <c r="H1198" t="n">
         <v>804811</v>
@@ -35140,7 +35140,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.7204971313477</v>
+        <v>11.7204961776733</v>
       </c>
       <c r="H1199" t="n">
         <v>613707</v>
@@ -35169,7 +35169,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1200" t="n">
-        <v>11.1819486618042</v>
+        <v>11.1819477081299</v>
       </c>
       <c r="H1200" t="n">
         <v>1096703</v>
@@ -35256,7 +35256,7 @@
         <v>15.4650001525879</v>
       </c>
       <c r="G1203" t="n">
-        <v>10.9587345123291</v>
+        <v>10.9587335586548</v>
       </c>
       <c r="H1203" t="n">
         <v>937290</v>
@@ -35314,7 +35314,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1205" t="n">
-        <v>11.0969142913818</v>
+        <v>11.0969152450562</v>
       </c>
       <c r="H1205" t="n">
         <v>900391</v>
@@ -35343,7 +35343,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G1206" t="n">
-        <v>10.9410190582275</v>
+        <v>10.9410181045532</v>
       </c>
       <c r="H1206" t="n">
         <v>557536</v>
@@ -35459,7 +35459,7 @@
         <v>15.5900001525879</v>
       </c>
       <c r="G1210" t="n">
-        <v>11.0473117828369</v>
+        <v>11.0473108291626</v>
       </c>
       <c r="H1210" t="n">
         <v>563173</v>
@@ -35604,7 +35604,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1215" t="n">
-        <v>11.592945098877</v>
+        <v>11.5929460525513</v>
       </c>
       <c r="H1215" t="n">
         <v>574243</v>
@@ -35633,7 +35633,7 @@
         <v>16.125</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.4264221191406</v>
+        <v>11.4264211654663</v>
       </c>
       <c r="H1216" t="n">
         <v>807224</v>
@@ -35662,7 +35662,7 @@
         <v>16.5100002288818</v>
       </c>
       <c r="G1217" t="n">
-        <v>11.6992378234863</v>
+        <v>11.699236869812</v>
       </c>
       <c r="H1217" t="n">
         <v>880055</v>
@@ -35720,7 +35720,7 @@
         <v>16.1049995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>11.4122476577759</v>
+        <v>11.4122467041016</v>
       </c>
       <c r="H1219" t="n">
         <v>900252</v>
@@ -35836,7 +35836,7 @@
         <v>15.5749998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>11.0366821289062</v>
+        <v>11.0366830825806</v>
       </c>
       <c r="H1223" t="n">
         <v>609556</v>
@@ -35865,7 +35865,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.1854906082153</v>
+        <v>11.1854915618896</v>
       </c>
       <c r="H1224" t="n">
         <v>576845</v>
@@ -35952,7 +35952,7 @@
         <v>14.4099998474121</v>
       </c>
       <c r="G1227" t="n">
-        <v>10.2111444473267</v>
+        <v>10.2111463546753</v>
       </c>
       <c r="H1227" t="n">
         <v>1496108</v>
@@ -35981,7 +35981,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1228" t="n">
-        <v>10.0410776138306</v>
+        <v>10.0410766601562</v>
       </c>
       <c r="H1228" t="n">
         <v>1254837</v>
@@ -36126,7 +36126,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.3449287414551</v>
+        <v>11.3449296951294</v>
       </c>
       <c r="H1233" t="n">
         <v>1226139</v>
@@ -36155,7 +36155,7 @@
         <v>15.8249998092651</v>
       </c>
       <c r="G1234" t="n">
-        <v>11.2138366699219</v>
+        <v>11.2138357162476</v>
       </c>
       <c r="H1234" t="n">
         <v>703512</v>
@@ -36213,7 +36213,7 @@
         <v>16.5499992370605</v>
       </c>
       <c r="G1236" t="n">
-        <v>11.7275819778442</v>
+        <v>11.7275810241699</v>
       </c>
       <c r="H1236" t="n">
         <v>1453762</v>
@@ -36329,7 +36329,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.3936786651611</v>
+        <v>12.3936796188354</v>
       </c>
       <c r="H1240" t="n">
         <v>2784389</v>
@@ -36358,7 +36358,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1241" t="n">
-        <v>12.4574556350708</v>
+        <v>12.4574575424194</v>
       </c>
       <c r="H1241" t="n">
         <v>1853211</v>
@@ -36416,7 +36416,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1243" t="n">
-        <v>12.4858016967773</v>
+        <v>12.485800743103</v>
       </c>
       <c r="H1243" t="n">
         <v>1721356</v>
@@ -36445,7 +36445,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>12.5070581436157</v>
+        <v>12.50705909729</v>
       </c>
       <c r="H1244" t="n">
         <v>1079962</v>
@@ -36474,7 +36474,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>12.4716291427612</v>
+        <v>12.4716272354126</v>
       </c>
       <c r="H1245" t="n">
         <v>998587</v>
@@ -36503,7 +36503,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1246" t="n">
-        <v>12.4858016967773</v>
+        <v>12.485800743103</v>
       </c>
       <c r="H1246" t="n">
         <v>1406935</v>
@@ -36706,7 +36706,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1253" t="n">
-        <v>12.5283174514771</v>
+        <v>12.5283164978027</v>
       </c>
       <c r="H1253" t="n">
         <v>583314</v>
@@ -36735,7 +36735,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1254" t="n">
-        <v>12.5283174514771</v>
+        <v>12.5283164978027</v>
       </c>
       <c r="H1254" t="n">
         <v>840138</v>
@@ -36764,7 +36764,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G1255" t="n">
-        <v>12.5354032516479</v>
+        <v>12.5354022979736</v>
       </c>
       <c r="H1255" t="n">
         <v>567556</v>
@@ -36880,7 +36880,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G1259" t="n">
-        <v>12.1988105773926</v>
+        <v>12.1988115310669</v>
       </c>
       <c r="H1259" t="n">
         <v>898405</v>
@@ -36909,7 +36909,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.5070581436157</v>
+        <v>12.50705909729</v>
       </c>
       <c r="H1260" t="n">
         <v>827415</v>
@@ -36938,7 +36938,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1261" t="n">
-        <v>12.4255676269531</v>
+        <v>12.4255685806274</v>
       </c>
       <c r="H1261" t="n">
         <v>613163</v>
@@ -37025,7 +37025,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>12.2767581939697</v>
+        <v>12.276759147644</v>
       </c>
       <c r="H1264" t="n">
         <v>963120</v>
@@ -37054,7 +37054,7 @@
         <v>17.0699996948242</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.0960607528687</v>
+        <v>12.096061706543</v>
       </c>
       <c r="H1265" t="n">
         <v>1386314</v>
@@ -37112,7 +37112,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>12.673583984375</v>
+        <v>12.6735830307007</v>
       </c>
       <c r="H1267" t="n">
         <v>1143701</v>
@@ -37141,7 +37141,7 @@
         <v>17.9650001525879</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.7302732467651</v>
+        <v>12.7302722930908</v>
       </c>
       <c r="H1268" t="n">
         <v>621431</v>
@@ -37199,7 +37199,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1270" t="n">
-        <v>12.5920934677124</v>
+        <v>12.5920925140381</v>
       </c>
       <c r="H1270" t="n">
         <v>430557</v>
@@ -37228,7 +37228,7 @@
         <v>17.7549991607666</v>
       </c>
       <c r="G1271" t="n">
-        <v>12.5814628601074</v>
+        <v>12.5814638137817</v>
       </c>
       <c r="H1271" t="n">
         <v>700037</v>
@@ -37286,7 +37286,7 @@
         <v>17.8549995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>12.652325630188</v>
+        <v>12.6523237228394</v>
       </c>
       <c r="H1273" t="n">
         <v>642805</v>
@@ -37344,7 +37344,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G1275" t="n">
-        <v>12.6381511688232</v>
+        <v>12.6381521224976</v>
       </c>
       <c r="H1275" t="n">
         <v>695221</v>
@@ -37373,7 +37373,7 @@
         <v>17.8250007629395</v>
       </c>
       <c r="G1276" t="n">
-        <v>12.631067276001</v>
+        <v>12.6310663223267</v>
       </c>
       <c r="H1276" t="n">
         <v>472324</v>
@@ -37402,7 +37402,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G1277" t="n">
-        <v>12.903881072998</v>
+        <v>12.9038820266724</v>
       </c>
       <c r="H1277" t="n">
         <v>2203323</v>
@@ -37431,7 +37431,7 @@
         <v>18.9150009155273</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.4034585952759</v>
+        <v>13.4034566879272</v>
       </c>
       <c r="H1278" t="n">
         <v>2985956</v>
@@ -37460,7 +37460,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1279" t="n">
-        <v>13.166072845459</v>
+        <v>13.1660709381104</v>
       </c>
       <c r="H1279" t="n">
         <v>1219975</v>
@@ -37518,7 +37518,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1281" t="n">
-        <v>13.1058378219604</v>
+        <v>13.1058397293091</v>
       </c>
       <c r="H1281" t="n">
         <v>554143</v>
@@ -37605,7 +37605,7 @@
         <v>18.2800006866455</v>
       </c>
       <c r="G1284" t="n">
-        <v>12.9534864425659</v>
+        <v>12.9534854888916</v>
       </c>
       <c r="H1284" t="n">
         <v>620928</v>
@@ -37634,7 +37634,7 @@
         <v>17.8899993896484</v>
       </c>
       <c r="G1285" t="n">
-        <v>12.6771259307861</v>
+        <v>12.6771268844604</v>
       </c>
       <c r="H1285" t="n">
         <v>903830</v>
@@ -37663,7 +37663,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>12.4716291427612</v>
+        <v>12.4716272354126</v>
       </c>
       <c r="H1286" t="n">
         <v>787730</v>
@@ -37692,7 +37692,7 @@
         <v>17.8449993133545</v>
       </c>
       <c r="G1287" t="n">
-        <v>12.6452388763428</v>
+        <v>12.6452379226685</v>
       </c>
       <c r="H1287" t="n">
         <v>754552</v>
@@ -37779,7 +37779,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>12.3015613555908</v>
+        <v>12.3015594482422</v>
       </c>
       <c r="H1290" t="n">
         <v>546428</v>
@@ -37808,7 +37808,7 @@
         <v>17.9549999237061</v>
       </c>
       <c r="G1291" t="n">
-        <v>12.7231864929199</v>
+        <v>12.7231874465942</v>
       </c>
       <c r="H1291" t="n">
         <v>1218546</v>
@@ -37866,7 +37866,7 @@
         <v>18.2649993896484</v>
       </c>
       <c r="G1293" t="n">
-        <v>12.9428577423096</v>
+        <v>12.9428567886353</v>
       </c>
       <c r="H1293" t="n">
         <v>1585119</v>
@@ -37895,7 +37895,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G1294" t="n">
-        <v>13.5380954742432</v>
+        <v>13.5380945205688</v>
       </c>
       <c r="H1294" t="n">
         <v>1914929</v>
@@ -38011,7 +38011,7 @@
         <v>20.0900001525879</v>
       </c>
       <c r="G1298" t="n">
-        <v>14.2360792160034</v>
+        <v>14.2360811233521</v>
       </c>
       <c r="H1298" t="n">
         <v>1193184</v>
@@ -38069,7 +38069,7 @@
         <v>20</v>
       </c>
       <c r="G1300" t="n">
-        <v>14.1723041534424</v>
+        <v>14.1723031997681</v>
       </c>
       <c r="H1300" t="n">
         <v>758827</v>
@@ -38098,7 +38098,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G1301" t="n">
-        <v>14.3352851867676</v>
+        <v>14.3352870941162</v>
       </c>
       <c r="H1301" t="n">
         <v>1022043</v>
@@ -38156,7 +38156,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.0022373199463</v>
+        <v>14.002236366272</v>
       </c>
       <c r="H1303" t="n">
         <v>807759</v>
@@ -38185,7 +38185,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G1304" t="n">
-        <v>13.8853130340576</v>
+        <v>13.8853139877319</v>
       </c>
       <c r="H1304" t="n">
         <v>809838</v>
@@ -38214,7 +38214,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.0731000900269</v>
+        <v>14.0730991363525</v>
       </c>
       <c r="H1305" t="n">
         <v>609447</v>
@@ -38243,7 +38243,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.9809789657593</v>
+        <v>13.980978012085</v>
       </c>
       <c r="H1306" t="n">
         <v>569196</v>
@@ -38272,7 +38272,7 @@
         <v>19.3449993133545</v>
       </c>
       <c r="G1307" t="n">
-        <v>13.7081594467163</v>
+        <v>13.7081604003906</v>
       </c>
       <c r="H1307" t="n">
         <v>881089</v>
@@ -38359,7 +38359,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1310" t="n">
-        <v>13.470775604248</v>
+        <v>13.4707746505737</v>
       </c>
       <c r="H1310" t="n">
         <v>842015</v>
@@ -38388,7 +38388,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>14.1014404296875</v>
+        <v>14.1014442443848</v>
       </c>
       <c r="H1311" t="n">
         <v>997246</v>
@@ -38417,7 +38417,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.9455480575562</v>
+        <v>13.9455471038818</v>
       </c>
       <c r="H1312" t="n">
         <v>636708</v>
@@ -38475,7 +38475,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1314" t="n">
-        <v>13.8321685791016</v>
+        <v>13.8321676254272</v>
       </c>
       <c r="H1314" t="n">
         <v>650188</v>
@@ -38562,7 +38562,7 @@
         <v>19.6499996185303</v>
       </c>
       <c r="G1317" t="n">
-        <v>13.9242887496948</v>
+        <v>13.9242877960205</v>
       </c>
       <c r="H1317" t="n">
         <v>820798</v>
@@ -38591,7 +38591,7 @@
         <v>19.8500003814697</v>
       </c>
       <c r="G1318" t="n">
-        <v>14.066011428833</v>
+        <v>14.0660133361816</v>
       </c>
       <c r="H1318" t="n">
         <v>899896</v>
@@ -38620,7 +38620,7 @@
         <v>19.5149993896484</v>
       </c>
       <c r="G1319" t="n">
-        <v>13.8286275863647</v>
+        <v>13.8286266326904</v>
       </c>
       <c r="H1319" t="n">
         <v>3177564</v>
@@ -38649,7 +38649,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1320" t="n">
-        <v>13.5912399291992</v>
+        <v>13.5912408828735</v>
       </c>
       <c r="H1320" t="n">
         <v>2150203</v>
@@ -38736,7 +38736,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1323" t="n">
-        <v>13.396369934082</v>
+        <v>13.396372795105</v>
       </c>
       <c r="H1323" t="n">
         <v>903143</v>
@@ -38765,7 +38765,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1324" t="n">
-        <v>13.4672336578369</v>
+        <v>13.4672298431396</v>
       </c>
       <c r="H1324" t="n">
         <v>881790</v>
@@ -38852,7 +38852,7 @@
         <v>19.1299991607666</v>
       </c>
       <c r="G1327" t="n">
-        <v>13.5558090209961</v>
+        <v>13.5558099746704</v>
       </c>
       <c r="H1327" t="n">
         <v>979383</v>
@@ -38881,7 +38881,7 @@
         <v>19.1049995422363</v>
       </c>
       <c r="G1328" t="n">
-        <v>13.5380954742432</v>
+        <v>13.5380945205688</v>
       </c>
       <c r="H1328" t="n">
         <v>519127</v>
@@ -38910,7 +38910,7 @@
         <v>19.0249996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.4814033508301</v>
+        <v>13.4814043045044</v>
       </c>
       <c r="H1329" t="n">
         <v>747016</v>
@@ -38968,7 +38968,7 @@
         <v>19.2549991607666</v>
       </c>
       <c r="G1331" t="n">
-        <v>13.6443862915039</v>
+        <v>13.6443853378296</v>
       </c>
       <c r="H1331" t="n">
         <v>703346</v>
@@ -39055,7 +39055,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>13.7648496627808</v>
+        <v>13.7648515701294</v>
       </c>
       <c r="H1334" t="n">
         <v>704457</v>
@@ -39084,7 +39084,7 @@
         <v>19.5200004577637</v>
       </c>
       <c r="G1335" t="n">
-        <v>13.8321685791016</v>
+        <v>13.8321676254272</v>
       </c>
       <c r="H1335" t="n">
         <v>628689</v>
@@ -39142,7 +39142,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1337" t="n">
-        <v>14.0022373199463</v>
+        <v>14.002236366272</v>
       </c>
       <c r="H1337" t="n">
         <v>1147975</v>
@@ -39171,7 +39171,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.0057792663574</v>
+        <v>14.0057802200317</v>
       </c>
       <c r="H1338" t="n">
         <v>911777</v>
@@ -39287,7 +39287,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1342" t="n">
-        <v>14.214822769165</v>
+        <v>14.2148208618164</v>
       </c>
       <c r="H1342" t="n">
         <v>1027821</v>
@@ -39374,7 +39374,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>13.8888578414917</v>
+        <v>13.888858795166</v>
       </c>
       <c r="H1345" t="n">
         <v>1548965</v>
@@ -39403,7 +39403,7 @@
         <v>19.6350002288818</v>
       </c>
       <c r="G1346" t="n">
-        <v>13.9136610031128</v>
+        <v>13.9136600494385</v>
       </c>
       <c r="H1346" t="n">
         <v>978631</v>
@@ -39432,7 +39432,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.9738903045654</v>
+        <v>13.9738922119141</v>
       </c>
       <c r="H1347" t="n">
         <v>495705</v>
@@ -39461,7 +39461,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.9774351119995</v>
+        <v>13.9774341583252</v>
       </c>
       <c r="H1348" t="n">
         <v>637198</v>
@@ -39490,7 +39490,7 @@
         <v>19.9449996948242</v>
       </c>
       <c r="G1349" t="n">
-        <v>14.1333293914795</v>
+        <v>14.1333312988281</v>
       </c>
       <c r="H1349" t="n">
         <v>779203</v>
@@ -39606,7 +39606,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G1353" t="n">
-        <v>14.1120710372925</v>
+        <v>14.1120729446411</v>
       </c>
       <c r="H1353" t="n">
         <v>638518</v>
@@ -39664,7 +39664,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>14.1227025985718</v>
+        <v>14.1227016448975</v>
       </c>
       <c r="H1355" t="n">
         <v>808370</v>
@@ -39722,7 +39722,7 @@
         <v>20.0799999237061</v>
       </c>
       <c r="G1357" t="n">
-        <v>14.2289943695068</v>
+        <v>14.2289924621582</v>
       </c>
       <c r="H1357" t="n">
         <v>595882</v>
@@ -39751,7 +39751,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>14.2785968780518</v>
+        <v>14.2785959243774</v>
       </c>
       <c r="H1358" t="n">
         <v>638821</v>
@@ -39780,7 +39780,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1359" t="n">
-        <v>14.4840955734253</v>
+        <v>14.4840974807739</v>
       </c>
       <c r="H1359" t="n">
         <v>1770727</v>
@@ -39925,7 +39925,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G1364" t="n">
-        <v>14.9659538269043</v>
+        <v>14.9659557342529</v>
       </c>
       <c r="H1364" t="n">
         <v>2206474</v>
@@ -39954,7 +39954,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G1365" t="n">
-        <v>14.944694519043</v>
+        <v>14.9446964263916</v>
       </c>
       <c r="H1365" t="n">
         <v>1093986</v>
@@ -40012,7 +40012,7 @@
         <v>20.9099998474121</v>
       </c>
       <c r="G1367" t="n">
-        <v>14.8171424865723</v>
+        <v>14.8171443939209</v>
       </c>
       <c r="H1367" t="n">
         <v>1243778</v>
@@ -40041,7 +40041,7 @@
         <v>20.8600006103516</v>
       </c>
       <c r="G1368" t="n">
-        <v>14.7817134857178</v>
+        <v>14.7817153930664</v>
       </c>
       <c r="H1368" t="n">
         <v>1719627</v>
@@ -80067,6 +80067,35 @@
         <v>658408</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>34.439998626709</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>34.5800018310547</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>34.0200004577637</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>34.4799995422363</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>34.4799995422363</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>489551</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -427,7 +427,7 @@
         <v>20.5415992736816</v>
       </c>
       <c r="G2" t="n">
-        <v>10.2148933410645</v>
+        <v>10.2148914337158</v>
       </c>
       <c r="H2" t="n">
         <v>949264</v>
@@ -514,7 +514,7 @@
         <v>19.3316287994385</v>
       </c>
       <c r="G5" t="n">
-        <v>9.61319923400879</v>
+        <v>9.61320018768311</v>
       </c>
       <c r="H5" t="n">
         <v>1415018</v>
@@ -543,7 +543,7 @@
         <v>18.8011016845703</v>
       </c>
       <c r="G6" t="n">
-        <v>9.34938144683838</v>
+        <v>9.34938049316406</v>
       </c>
       <c r="H6" t="n">
         <v>933755</v>
@@ -572,7 +572,7 @@
         <v>18.8476390838623</v>
       </c>
       <c r="G7" t="n">
-        <v>9.37252235412598</v>
+        <v>9.37252330780029</v>
       </c>
       <c r="H7" t="n">
         <v>1038503</v>
@@ -601,7 +601,7 @@
         <v>19.3967819213867</v>
       </c>
       <c r="G8" t="n">
-        <v>9.64559841156006</v>
+        <v>9.64560031890869</v>
       </c>
       <c r="H8" t="n">
         <v>1092313</v>
@@ -659,7 +659,7 @@
         <v>18.242654800415</v>
       </c>
       <c r="G10" t="n">
-        <v>9.07167625427246</v>
+        <v>9.07167720794678</v>
       </c>
       <c r="H10" t="n">
         <v>1319004</v>
@@ -688,7 +688,7 @@
         <v>17.7028198242188</v>
       </c>
       <c r="G11" t="n">
-        <v>8.80322933197021</v>
+        <v>8.80323028564453</v>
       </c>
       <c r="H11" t="n">
         <v>1256919</v>
@@ -804,7 +804,7 @@
         <v>17.5632076263428</v>
       </c>
       <c r="G15" t="n">
-        <v>8.73380279541016</v>
+        <v>8.73380374908447</v>
       </c>
       <c r="H15" t="n">
         <v>1491895</v>
@@ -833,7 +833,7 @@
         <v>18.0937347412109</v>
       </c>
       <c r="G16" t="n">
-        <v>8.9976224899292</v>
+        <v>8.99762344360352</v>
       </c>
       <c r="H16" t="n">
         <v>994715</v>
@@ -862,7 +862,7 @@
         <v>18.000659942627</v>
       </c>
       <c r="G17" t="n">
-        <v>8.95133972167969</v>
+        <v>8.95133590698242</v>
       </c>
       <c r="H17" t="n">
         <v>907980</v>
@@ -891,7 +891,7 @@
         <v>18.0378894805908</v>
       </c>
       <c r="G18" t="n">
-        <v>8.96985244750977</v>
+        <v>8.96985340118408</v>
       </c>
       <c r="H18" t="n">
         <v>929991</v>
@@ -949,7 +949,7 @@
         <v>17.3119068145752</v>
       </c>
       <c r="G20" t="n">
-        <v>8.60883808135986</v>
+        <v>8.60883712768555</v>
       </c>
       <c r="H20" t="n">
         <v>963207</v>
@@ -978,7 +978,7 @@
         <v>18.0099678039551</v>
       </c>
       <c r="G21" t="n">
-        <v>8.95596599578857</v>
+        <v>8.95596694946289</v>
       </c>
       <c r="H21" t="n">
         <v>934449</v>
@@ -1065,7 +1065,7 @@
         <v>16.781379699707</v>
       </c>
       <c r="G24" t="n">
-        <v>8.3450174331665</v>
+        <v>8.34501647949219</v>
       </c>
       <c r="H24" t="n">
         <v>1165968</v>
@@ -1094,7 +1094,7 @@
         <v>17.060604095459</v>
       </c>
       <c r="G25" t="n">
-        <v>8.48386764526367</v>
+        <v>8.48386859893799</v>
       </c>
       <c r="H25" t="n">
         <v>794101</v>
@@ -1152,7 +1152,7 @@
         <v>15.2828760147095</v>
       </c>
       <c r="G27" t="n">
-        <v>7.59984350204468</v>
+        <v>7.59984445571899</v>
       </c>
       <c r="H27" t="n">
         <v>1548043</v>
@@ -1181,7 +1181,7 @@
         <v>14.9198846817017</v>
       </c>
       <c r="G28" t="n">
-        <v>7.41933536529541</v>
+        <v>7.41933631896973</v>
       </c>
       <c r="H28" t="n">
         <v>1560532</v>
@@ -1210,7 +1210,7 @@
         <v>15.7947874069214</v>
       </c>
       <c r="G29" t="n">
-        <v>7.85440540313721</v>
+        <v>7.85440635681152</v>
       </c>
       <c r="H29" t="n">
         <v>1377048</v>
@@ -1268,7 +1268,7 @@
         <v>14.5662002563477</v>
       </c>
       <c r="G31" t="n">
-        <v>7.24345588684082</v>
+        <v>7.24345731735229</v>
       </c>
       <c r="H31" t="n">
         <v>1726080</v>
@@ -1297,7 +1297,7 @@
         <v>15.3666429519653</v>
       </c>
       <c r="G32" t="n">
-        <v>7.64149856567383</v>
+        <v>7.64149951934814</v>
       </c>
       <c r="H32" t="n">
         <v>1481695</v>
@@ -1326,7 +1326,7 @@
         <v>14.9291915893555</v>
       </c>
       <c r="G33" t="n">
-        <v>7.42396354675293</v>
+        <v>7.42396402359009</v>
       </c>
       <c r="H33" t="n">
         <v>992196</v>
@@ -1413,7 +1413,7 @@
         <v>16.0647048950195</v>
       </c>
       <c r="G36" t="n">
-        <v>7.9886302947998</v>
+        <v>7.98862981796265</v>
       </c>
       <c r="H36" t="n">
         <v>1422813</v>
@@ -1442,7 +1442,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G37" t="n">
-        <v>8.12748146057129</v>
+        <v>8.12748050689697</v>
       </c>
       <c r="H37" t="n">
         <v>1026092</v>
@@ -1471,7 +1471,7 @@
         <v>16.1298561096191</v>
       </c>
       <c r="G38" t="n">
-        <v>8.02102947235107</v>
+        <v>8.02102851867676</v>
       </c>
       <c r="H38" t="n">
         <v>709750</v>
@@ -1529,7 +1529,7 @@
         <v>16.0647048950195</v>
       </c>
       <c r="G40" t="n">
-        <v>7.9886302947998</v>
+        <v>7.98862981796265</v>
       </c>
       <c r="H40" t="n">
         <v>604328</v>
@@ -1587,7 +1587,7 @@
         <v>16.5393848419189</v>
       </c>
       <c r="G42" t="n">
-        <v>8.2246789932251</v>
+        <v>8.22467803955078</v>
       </c>
       <c r="H42" t="n">
         <v>679369</v>
@@ -1616,7 +1616,7 @@
         <v>17.3119068145752</v>
       </c>
       <c r="G43" t="n">
-        <v>8.60883808135986</v>
+        <v>8.60883712768555</v>
       </c>
       <c r="H43" t="n">
         <v>925913</v>
@@ -1645,7 +1645,7 @@
         <v>17.628360748291</v>
       </c>
       <c r="G44" t="n">
-        <v>8.76620292663574</v>
+        <v>8.76620197296143</v>
       </c>
       <c r="H44" t="n">
         <v>1052689</v>
@@ -1674,7 +1674,7 @@
         <v>17.6562824249268</v>
       </c>
       <c r="G45" t="n">
-        <v>8.7800874710083</v>
+        <v>8.78008651733398</v>
       </c>
       <c r="H45" t="n">
         <v>689765</v>
@@ -1732,7 +1732,7 @@
         <v>17.2560615539551</v>
       </c>
       <c r="G47" t="n">
-        <v>8.58106517791748</v>
+        <v>8.5810661315918</v>
       </c>
       <c r="H47" t="n">
         <v>1269243</v>
@@ -1761,7 +1761,7 @@
         <v>17.488748550415</v>
       </c>
       <c r="G48" t="n">
-        <v>8.69677734375</v>
+        <v>8.69677543640137</v>
       </c>
       <c r="H48" t="n">
         <v>1249776</v>
@@ -1819,7 +1819,7 @@
         <v>17.9820442199707</v>
       </c>
       <c r="G50" t="n">
-        <v>8.94208145141602</v>
+        <v>8.9420804977417</v>
       </c>
       <c r="H50" t="n">
         <v>2741312</v>
@@ -1848,7 +1848,7 @@
         <v>18.5498008728027</v>
       </c>
       <c r="G51" t="n">
-        <v>9.22441482543945</v>
+        <v>9.22441577911377</v>
       </c>
       <c r="H51" t="n">
         <v>1790410</v>
@@ -1877,7 +1877,7 @@
         <v>18.3264217376709</v>
       </c>
       <c r="G52" t="n">
-        <v>9.1133337020874</v>
+        <v>9.11333274841309</v>
       </c>
       <c r="H52" t="n">
         <v>1265956</v>
@@ -1964,7 +1964,7 @@
         <v>18.0099678039551</v>
       </c>
       <c r="G55" t="n">
-        <v>8.95596599578857</v>
+        <v>8.95596694946289</v>
       </c>
       <c r="H55" t="n">
         <v>1630405</v>
@@ -1993,7 +1993,7 @@
         <v>18.5777225494385</v>
       </c>
       <c r="G56" t="n">
-        <v>9.23830032348633</v>
+        <v>9.23829746246338</v>
       </c>
       <c r="H56" t="n">
         <v>1585761</v>
@@ -2022,7 +2022,7 @@
         <v>18.5404930114746</v>
       </c>
       <c r="G57" t="n">
-        <v>9.21978569030762</v>
+        <v>9.21978378295898</v>
       </c>
       <c r="H57" t="n">
         <v>877559</v>
@@ -2051,7 +2051,7 @@
         <v>18.3729572296143</v>
       </c>
       <c r="G58" t="n">
-        <v>9.13647270202637</v>
+        <v>9.13647365570068</v>
       </c>
       <c r="H58" t="n">
         <v>1032573</v>
@@ -2080,7 +2080,7 @@
         <v>18.2984981536865</v>
       </c>
       <c r="G59" t="n">
-        <v>9.09944820404053</v>
+        <v>9.09944725036621</v>
       </c>
       <c r="H59" t="n">
         <v>645748</v>
@@ -2138,7 +2138,7 @@
         <v>18.242654800415</v>
       </c>
       <c r="G61" t="n">
-        <v>9.07167625427246</v>
+        <v>9.07167720794678</v>
       </c>
       <c r="H61" t="n">
         <v>769902</v>
@@ -2167,7 +2167,7 @@
         <v>18.4474182128906</v>
       </c>
       <c r="G62" t="n">
-        <v>9.17350292205811</v>
+        <v>9.17350196838379</v>
       </c>
       <c r="H62" t="n">
         <v>902526</v>
@@ -2196,7 +2196,7 @@
         <v>18.8476390838623</v>
       </c>
       <c r="G63" t="n">
-        <v>9.37252235412598</v>
+        <v>9.37252330780029</v>
       </c>
       <c r="H63" t="n">
         <v>1496702</v>
@@ -2225,7 +2225,7 @@
         <v>19.4153957366943</v>
       </c>
       <c r="G64" t="n">
-        <v>9.65485572814941</v>
+        <v>9.65485668182373</v>
       </c>
       <c r="H64" t="n">
         <v>3576161</v>
@@ -2283,7 +2283,7 @@
         <v>18.6614894866943</v>
       </c>
       <c r="G66" t="n">
-        <v>9.27995491027832</v>
+        <v>9.27995586395264</v>
       </c>
       <c r="H66" t="n">
         <v>1946521</v>
@@ -2312,7 +2312,7 @@
         <v>18.8011016845703</v>
       </c>
       <c r="G67" t="n">
-        <v>9.34938144683838</v>
+        <v>9.34938049316406</v>
       </c>
       <c r="H67" t="n">
         <v>942840</v>
@@ -2370,7 +2370,7 @@
         <v>18.9407138824463</v>
       </c>
       <c r="G69" t="n">
-        <v>9.4188060760498</v>
+        <v>9.41880702972412</v>
       </c>
       <c r="H69" t="n">
         <v>688771</v>
@@ -2428,7 +2428,7 @@
         <v>18.4846477508545</v>
       </c>
       <c r="G71" t="n">
-        <v>9.19201469421387</v>
+        <v>9.19201564788818</v>
       </c>
       <c r="H71" t="n">
         <v>1170492</v>
@@ -2457,7 +2457,7 @@
         <v>19.6853122711182</v>
       </c>
       <c r="G72" t="n">
-        <v>9.78908061981201</v>
+        <v>9.7890796661377</v>
       </c>
       <c r="H72" t="n">
         <v>1349517</v>
@@ -2486,7 +2486,7 @@
         <v>20.001766204834</v>
       </c>
       <c r="G73" t="n">
-        <v>9.94644451141357</v>
+        <v>9.94644546508789</v>
       </c>
       <c r="H73" t="n">
         <v>2069715</v>
@@ -2515,7 +2515,7 @@
         <v>19.7970027923584</v>
       </c>
       <c r="G74" t="n">
-        <v>9.84462070465088</v>
+        <v>9.8446216583252</v>
       </c>
       <c r="H74" t="n">
         <v>824139</v>
@@ -2544,7 +2544,7 @@
         <v>20.0203819274902</v>
       </c>
       <c r="G75" t="n">
-        <v>9.95570087432861</v>
+        <v>9.95570278167725</v>
       </c>
       <c r="H75" t="n">
         <v>825610</v>
@@ -2573,7 +2573,7 @@
         <v>19.9273071289062</v>
       </c>
       <c r="G76" t="n">
-        <v>9.90941905975342</v>
+        <v>9.9094181060791</v>
       </c>
       <c r="H76" t="n">
         <v>950975</v>
@@ -2602,7 +2602,7 @@
         <v>20.0110740661621</v>
       </c>
       <c r="G77" t="n">
-        <v>9.95107364654541</v>
+        <v>9.95107460021973</v>
       </c>
       <c r="H77" t="n">
         <v>874470</v>
@@ -2689,7 +2689,7 @@
         <v>19.7597713470459</v>
       </c>
       <c r="G80" t="n">
-        <v>9.82610702514648</v>
+        <v>9.82610511779785</v>
       </c>
       <c r="H80" t="n">
         <v>1181674</v>
@@ -2718,7 +2718,7 @@
         <v>19.8807697296143</v>
       </c>
       <c r="G81" t="n">
-        <v>9.88627624511719</v>
+        <v>9.8862771987915</v>
       </c>
       <c r="H81" t="n">
         <v>854167</v>
@@ -2747,7 +2747,7 @@
         <v>20.3740653991699</v>
       </c>
       <c r="G82" t="n">
-        <v>10.1315813064575</v>
+        <v>10.1315822601318</v>
       </c>
       <c r="H82" t="n">
         <v>2117873</v>
@@ -2776,7 +2776,7 @@
         <v>20.569522857666</v>
       </c>
       <c r="G83" t="n">
-        <v>10.22878074646</v>
+        <v>10.2287788391113</v>
       </c>
       <c r="H83" t="n">
         <v>1626344</v>
@@ -2805,7 +2805,7 @@
         <v>20.4578323364258</v>
       </c>
       <c r="G84" t="n">
-        <v>10.1732368469238</v>
+        <v>10.1732378005981</v>
       </c>
       <c r="H84" t="n">
         <v>1114038</v>
@@ -2834,7 +2834,7 @@
         <v>20.1041488647461</v>
       </c>
       <c r="G85" t="n">
-        <v>9.99735927581787</v>
+        <v>9.99735832214355</v>
       </c>
       <c r="H85" t="n">
         <v>901819</v>
@@ -2892,7 +2892,7 @@
         <v>19.5177783966064</v>
       </c>
       <c r="G87" t="n">
-        <v>9.70577049255371</v>
+        <v>9.70576953887939</v>
       </c>
       <c r="H87" t="n">
         <v>978597</v>
@@ -2921,7 +2921,7 @@
         <v>18.4567260742188</v>
       </c>
       <c r="G88" t="n">
-        <v>9.17813110351562</v>
+        <v>9.17813205718994</v>
       </c>
       <c r="H88" t="n">
         <v>3242757</v>
@@ -2950,7 +2950,7 @@
         <v>18.1588859558105</v>
       </c>
       <c r="G89" t="n">
-        <v>9.03002071380615</v>
+        <v>9.03002166748047</v>
       </c>
       <c r="H89" t="n">
         <v>1939059</v>
@@ -3008,7 +3008,7 @@
         <v>17.8424320220947</v>
       </c>
       <c r="G91" t="n">
-        <v>8.87265586853027</v>
+        <v>8.87265491485596</v>
       </c>
       <c r="H91" t="n">
         <v>759358</v>
@@ -3182,7 +3182,7 @@
         <v>17.6469745635986</v>
       </c>
       <c r="G97" t="n">
-        <v>8.77545738220215</v>
+        <v>8.77545833587646</v>
       </c>
       <c r="H97" t="n">
         <v>739465</v>
@@ -3240,7 +3240,7 @@
         <v>18.0378894805908</v>
       </c>
       <c r="G99" t="n">
-        <v>8.96985244750977</v>
+        <v>8.96985340118408</v>
       </c>
       <c r="H99" t="n">
         <v>1090211</v>
@@ -3269,7 +3269,7 @@
         <v>17.6097450256348</v>
       </c>
       <c r="G100" t="n">
-        <v>8.98885726928711</v>
+        <v>8.98885536193848</v>
       </c>
       <c r="H100" t="n">
         <v>696281</v>
@@ -3298,7 +3298,7 @@
         <v>18.1030426025391</v>
       </c>
       <c r="G101" t="n">
-        <v>9.24065971374512</v>
+        <v>9.2406587600708</v>
       </c>
       <c r="H101" t="n">
         <v>766092</v>
@@ -3327,7 +3327,7 @@
         <v>18.6987209320068</v>
       </c>
       <c r="G102" t="n">
-        <v>9.54471969604492</v>
+        <v>9.54472160339355</v>
       </c>
       <c r="H102" t="n">
         <v>1374411</v>
@@ -3356,7 +3356,7 @@
         <v>18.2798843383789</v>
       </c>
       <c r="G103" t="n">
-        <v>9.3309268951416</v>
+        <v>9.33092594146729</v>
       </c>
       <c r="H103" t="n">
         <v>755422</v>
@@ -3385,7 +3385,7 @@
         <v>18.3915729522705</v>
       </c>
       <c r="G104" t="n">
-        <v>9.38793659210205</v>
+        <v>9.38793754577637</v>
       </c>
       <c r="H104" t="n">
         <v>644357</v>
@@ -3414,7 +3414,7 @@
         <v>18.7545642852783</v>
       </c>
       <c r="G105" t="n">
-        <v>9.57322692871094</v>
+        <v>9.57322597503662</v>
       </c>
       <c r="H105" t="n">
         <v>554705</v>
@@ -3443,7 +3443,7 @@
         <v>18.3915729522705</v>
       </c>
       <c r="G106" t="n">
-        <v>9.38793659210205</v>
+        <v>9.38793754577637</v>
       </c>
       <c r="H106" t="n">
         <v>1058066</v>
@@ -3501,7 +3501,7 @@
         <v>18.0471973419189</v>
       </c>
       <c r="G108" t="n">
-        <v>9.2121524810791</v>
+        <v>9.21215152740479</v>
       </c>
       <c r="H108" t="n">
         <v>684970</v>
@@ -3530,7 +3530,7 @@
         <v>17.4235954284668</v>
       </c>
       <c r="G109" t="n">
-        <v>8.89383697509766</v>
+        <v>8.89383602142334</v>
       </c>
       <c r="H109" t="n">
         <v>929087</v>
@@ -3559,7 +3559,7 @@
         <v>17.4142875671387</v>
       </c>
       <c r="G110" t="n">
-        <v>8.88908386230469</v>
+        <v>8.88908576965332</v>
       </c>
       <c r="H110" t="n">
         <v>691022</v>
@@ -3617,7 +3617,7 @@
         <v>17.6469745635986</v>
       </c>
       <c r="G112" t="n">
-        <v>9.0078592300415</v>
+        <v>9.00786113739014</v>
       </c>
       <c r="H112" t="n">
         <v>516736</v>
@@ -3646,7 +3646,7 @@
         <v>17.3584423065186</v>
       </c>
       <c r="G113" t="n">
-        <v>8.86057758331299</v>
+        <v>8.86058044433594</v>
       </c>
       <c r="H113" t="n">
         <v>559096</v>
@@ -3704,7 +3704,7 @@
         <v>15.6737899780273</v>
       </c>
       <c r="G115" t="n">
-        <v>8.00065231323242</v>
+        <v>8.00065135955811</v>
       </c>
       <c r="H115" t="n">
         <v>1024434</v>
@@ -3733,7 +3733,7 @@
         <v>15.3107986450195</v>
       </c>
       <c r="G116" t="n">
-        <v>7.81536245346069</v>
+        <v>7.81536388397217</v>
       </c>
       <c r="H116" t="n">
         <v>1765822</v>
@@ -3762,7 +3762,7 @@
         <v>15.6365604400635</v>
       </c>
       <c r="G117" t="n">
-        <v>7.98164796829224</v>
+        <v>7.98164844512939</v>
       </c>
       <c r="H117" t="n">
         <v>1316058</v>
@@ -3820,7 +3820,7 @@
         <v>16.0460891723633</v>
       </c>
       <c r="G119" t="n">
-        <v>8.1906909942627</v>
+        <v>8.19069194793701</v>
       </c>
       <c r="H119" t="n">
         <v>1980158</v>
@@ -3849,7 +3849,7 @@
         <v>17.3584423065186</v>
       </c>
       <c r="G120" t="n">
-        <v>8.86057758331299</v>
+        <v>8.86058044433594</v>
       </c>
       <c r="H120" t="n">
         <v>1671975</v>
@@ -3878,7 +3878,7 @@
         <v>17.3677501678467</v>
       </c>
       <c r="G121" t="n">
-        <v>8.86532878875732</v>
+        <v>8.86533069610596</v>
       </c>
       <c r="H121" t="n">
         <v>863019</v>
@@ -3907,7 +3907,7 @@
         <v>17.5632076263428</v>
       </c>
       <c r="G122" t="n">
-        <v>8.96510124206543</v>
+        <v>8.96510219573975</v>
       </c>
       <c r="H122" t="n">
         <v>724364</v>
@@ -3965,7 +3965,7 @@
         <v>15.6458683013916</v>
       </c>
       <c r="G124" t="n">
-        <v>7.98640012741089</v>
+        <v>7.98639965057373</v>
       </c>
       <c r="H124" t="n">
         <v>2529165</v>
@@ -3994,7 +3994,7 @@
         <v>13.79368019104</v>
       </c>
       <c r="G125" t="n">
-        <v>7.04095363616943</v>
+        <v>7.04095458984375</v>
       </c>
       <c r="H125" t="n">
         <v>2110454</v>
@@ -4023,7 +4023,7 @@
         <v>13.9984436035156</v>
       </c>
       <c r="G126" t="n">
-        <v>7.14547348022461</v>
+        <v>7.14547538757324</v>
       </c>
       <c r="H126" t="n">
         <v>1958416</v>
@@ -4052,7 +4052,7 @@
         <v>13.858832359314</v>
       </c>
       <c r="G127" t="n">
-        <v>7.07420969009399</v>
+        <v>7.07421064376831</v>
       </c>
       <c r="H127" t="n">
         <v>1431812</v>
@@ -4081,7 +4081,7 @@
         <v>13.579607963562</v>
       </c>
       <c r="G128" t="n">
-        <v>6.93168210983276</v>
+        <v>6.93168115615845</v>
       </c>
       <c r="H128" t="n">
         <v>2242320</v>
@@ -4110,7 +4110,7 @@
         <v>13.7471418380737</v>
       </c>
       <c r="G129" t="n">
-        <v>7.01719856262207</v>
+        <v>7.01719999313354</v>
       </c>
       <c r="H129" t="n">
         <v>1372121</v>
@@ -4139,7 +4139,7 @@
         <v>13.3096914291382</v>
       </c>
       <c r="G130" t="n">
-        <v>6.79390382766724</v>
+        <v>6.79390239715576</v>
       </c>
       <c r="H130" t="n">
         <v>940260</v>
@@ -4168,7 +4168,7 @@
         <v>12.6953983306885</v>
       </c>
       <c r="G131" t="n">
-        <v>6.48033761978149</v>
+        <v>6.48033809661865</v>
       </c>
       <c r="H131" t="n">
         <v>1637699</v>
@@ -4197,7 +4197,7 @@
         <v>12.0159521102905</v>
       </c>
       <c r="G132" t="n">
-        <v>6.13351678848267</v>
+        <v>6.13351631164551</v>
       </c>
       <c r="H132" t="n">
         <v>3039588</v>
@@ -4226,7 +4226,7 @@
         <v>12.2486391067505</v>
       </c>
       <c r="G133" t="n">
-        <v>6.25229167938232</v>
+        <v>6.25229072570801</v>
       </c>
       <c r="H133" t="n">
         <v>1390549</v>
@@ -4255,7 +4255,7 @@
         <v>12.6767826080322</v>
       </c>
       <c r="G134" t="n">
-        <v>6.47083568572998</v>
+        <v>6.47083616256714</v>
       </c>
       <c r="H134" t="n">
         <v>1339495</v>
@@ -4342,7 +4342,7 @@
         <v>13.3189992904663</v>
       </c>
       <c r="G137" t="n">
-        <v>6.7986536026001</v>
+        <v>6.79865407943726</v>
       </c>
       <c r="H137" t="n">
         <v>902199</v>
@@ -4371,7 +4371,7 @@
         <v>13.7657566070557</v>
       </c>
       <c r="G138" t="n">
-        <v>7.02670049667358</v>
+        <v>7.02670097351074</v>
       </c>
       <c r="H138" t="n">
         <v>1294765</v>
@@ -4400,7 +4400,7 @@
         <v>13.7657566070557</v>
       </c>
       <c r="G139" t="n">
-        <v>7.02670049667358</v>
+        <v>7.02670097351074</v>
       </c>
       <c r="H139" t="n">
         <v>978688</v>
@@ -4429,7 +4429,7 @@
         <v>14.165979385376</v>
       </c>
       <c r="G140" t="n">
-        <v>7.23099279403687</v>
+        <v>7.23099327087402</v>
       </c>
       <c r="H140" t="n">
         <v>1308419</v>
@@ -4458,7 +4458,7 @@
         <v>13.905369758606</v>
       </c>
       <c r="G141" t="n">
-        <v>7.09796619415283</v>
+        <v>7.09796524047852</v>
       </c>
       <c r="H141" t="n">
         <v>1133774</v>
@@ -4487,7 +4487,7 @@
         <v>14.1287488937378</v>
       </c>
       <c r="G142" t="n">
-        <v>7.211989402771</v>
+        <v>7.21198892593384</v>
       </c>
       <c r="H142" t="n">
         <v>826386</v>
@@ -4516,7 +4516,7 @@
         <v>14.4079732894897</v>
       </c>
       <c r="G143" t="n">
-        <v>7.35451889038086</v>
+        <v>7.35451793670654</v>
       </c>
       <c r="H143" t="n">
         <v>1143708</v>
@@ -4574,7 +4574,7 @@
         <v>14.6778898239136</v>
       </c>
       <c r="G145" t="n">
-        <v>7.49229764938354</v>
+        <v>7.49229669570923</v>
       </c>
       <c r="H145" t="n">
         <v>879507</v>
@@ -4632,7 +4632,7 @@
         <v>14.6871976852417</v>
       </c>
       <c r="G147" t="n">
-        <v>7.49704742431641</v>
+        <v>7.49704790115356</v>
       </c>
       <c r="H147" t="n">
         <v>781367</v>
@@ -4661,7 +4661,7 @@
         <v>13.3096914291382</v>
       </c>
       <c r="G148" t="n">
-        <v>6.79390382766724</v>
+        <v>6.79390239715576</v>
       </c>
       <c r="H148" t="n">
         <v>2214053</v>
@@ -4690,7 +4690,7 @@
         <v>13.0863122940063</v>
       </c>
       <c r="G149" t="n">
-        <v>6.67987871170044</v>
+        <v>6.67988014221191</v>
       </c>
       <c r="H149" t="n">
         <v>1664978</v>
@@ -4719,7 +4719,7 @@
         <v>12.7977800369263</v>
       </c>
       <c r="G150" t="n">
-        <v>6.53259944915771</v>
+        <v>6.53259897232056</v>
       </c>
       <c r="H150" t="n">
         <v>1403849</v>
@@ -4748,7 +4748,7 @@
         <v>12.4068660736084</v>
       </c>
       <c r="G151" t="n">
-        <v>6.33305740356445</v>
+        <v>6.33305788040161</v>
       </c>
       <c r="H151" t="n">
         <v>1257013</v>
@@ -4777,7 +4777,7 @@
         <v>12.5464782714844</v>
       </c>
       <c r="G152" t="n">
-        <v>6.40432357788086</v>
+        <v>6.40432214736938</v>
       </c>
       <c r="H152" t="n">
         <v>1038379</v>
@@ -4806,7 +4806,7 @@
         <v>12.75124168396</v>
       </c>
       <c r="G153" t="n">
-        <v>6.50884294509888</v>
+        <v>6.50884389877319</v>
       </c>
       <c r="H153" t="n">
         <v>992648</v>
@@ -4864,7 +4864,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G155" t="n">
-        <v>6.81765604019165</v>
+        <v>6.81765794754028</v>
       </c>
       <c r="H155" t="n">
         <v>1301733</v>
@@ -4893,7 +4893,7 @@
         <v>13.4493026733398</v>
       </c>
       <c r="G156" t="n">
-        <v>6.86516761779785</v>
+        <v>6.86516714096069</v>
       </c>
       <c r="H156" t="n">
         <v>588857</v>
@@ -4922,7 +4922,7 @@
         <v>13.5423784255981</v>
       </c>
       <c r="G157" t="n">
-        <v>6.91267776489258</v>
+        <v>6.91267728805542</v>
       </c>
       <c r="H157" t="n">
         <v>668173</v>
@@ -4951,7 +4951,7 @@
         <v>13.5237627029419</v>
       </c>
       <c r="G158" t="n">
-        <v>6.90317535400391</v>
+        <v>6.90317440032959</v>
       </c>
       <c r="H158" t="n">
         <v>763651</v>
@@ -4980,7 +4980,7 @@
         <v>13.672682762146</v>
       </c>
       <c r="G159" t="n">
-        <v>6.97919130325317</v>
+        <v>6.97919082641602</v>
       </c>
       <c r="H159" t="n">
         <v>673395</v>
@@ -5009,7 +5009,7 @@
         <v>13.225923538208</v>
       </c>
       <c r="G160" t="n">
-        <v>6.75114440917969</v>
+        <v>6.75114393234253</v>
       </c>
       <c r="H160" t="n">
         <v>1068721</v>
@@ -5038,7 +5038,7 @@
         <v>12.8350095748901</v>
       </c>
       <c r="G161" t="n">
-        <v>6.55160236358643</v>
+        <v>6.55160331726074</v>
       </c>
       <c r="H161" t="n">
         <v>788798</v>
@@ -5067,7 +5067,7 @@
         <v>13.3003835678101</v>
       </c>
       <c r="G162" t="n">
-        <v>6.78915166854858</v>
+        <v>6.78915214538574</v>
       </c>
       <c r="H162" t="n">
         <v>798059</v>
@@ -5125,7 +5125,7 @@
         <v>12.75124168396</v>
       </c>
       <c r="G164" t="n">
-        <v>6.50884294509888</v>
+        <v>6.50884389877319</v>
       </c>
       <c r="H164" t="n">
         <v>888466</v>
@@ -5154,7 +5154,7 @@
         <v>12.9839286804199</v>
       </c>
       <c r="G165" t="n">
-        <v>6.62761831283569</v>
+        <v>6.62761878967285</v>
       </c>
       <c r="H165" t="n">
         <v>763641</v>
@@ -5183,7 +5183,7 @@
         <v>13.0956192016602</v>
       </c>
       <c r="G166" t="n">
-        <v>6.68462991714478</v>
+        <v>6.68462944030762</v>
       </c>
       <c r="H166" t="n">
         <v>876200</v>
@@ -5212,7 +5212,7 @@
         <v>12.8350095748901</v>
       </c>
       <c r="G167" t="n">
-        <v>6.55160236358643</v>
+        <v>6.55160331726074</v>
       </c>
       <c r="H167" t="n">
         <v>957198</v>
@@ -5241,7 +5241,7 @@
         <v>13.0118522644043</v>
       </c>
       <c r="G168" t="n">
-        <v>6.64187240600586</v>
+        <v>6.64187097549438</v>
       </c>
       <c r="H168" t="n">
         <v>619541</v>
@@ -5299,7 +5299,7 @@
         <v>12.6860904693604</v>
       </c>
       <c r="G170" t="n">
-        <v>6.47558736801147</v>
+        <v>6.47558689117432</v>
       </c>
       <c r="H170" t="n">
         <v>799125</v>
@@ -5328,7 +5328,7 @@
         <v>12.8070869445801</v>
       </c>
       <c r="G171" t="n">
-        <v>6.53734827041626</v>
+        <v>6.53734922409058</v>
       </c>
       <c r="H171" t="n">
         <v>959793</v>
@@ -5357,7 +5357,7 @@
         <v>12.9839286804199</v>
       </c>
       <c r="G172" t="n">
-        <v>6.62761831283569</v>
+        <v>6.62761878967285</v>
       </c>
       <c r="H172" t="n">
         <v>1467796</v>
@@ -5386,7 +5386,7 @@
         <v>13.3469209671021</v>
       </c>
       <c r="G173" t="n">
-        <v>6.81290578842163</v>
+        <v>6.81290674209595</v>
       </c>
       <c r="H173" t="n">
         <v>1142089</v>
@@ -5415,7 +5415,7 @@
         <v>13.5144557952881</v>
       </c>
       <c r="G174" t="n">
-        <v>6.89842319488525</v>
+        <v>6.89842510223389</v>
       </c>
       <c r="H174" t="n">
         <v>1108705</v>
@@ -5444,7 +5444,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G175" t="n">
-        <v>6.81765604019165</v>
+        <v>6.81765794754028</v>
       </c>
       <c r="H175" t="n">
         <v>704858</v>
@@ -5473,7 +5473,7 @@
         <v>13.365535736084</v>
       </c>
       <c r="G176" t="n">
-        <v>6.82240867614746</v>
+        <v>6.8224081993103</v>
       </c>
       <c r="H176" t="n">
         <v>1052233</v>
@@ -5502,7 +5502,7 @@
         <v>13.579607963562</v>
       </c>
       <c r="G177" t="n">
-        <v>6.93168210983276</v>
+        <v>6.93168115615845</v>
       </c>
       <c r="H177" t="n">
         <v>1117409</v>
@@ -5531,7 +5531,7 @@
         <v>13.486533164978</v>
       </c>
       <c r="G178" t="n">
-        <v>6.88417196273804</v>
+        <v>6.88417100906372</v>
       </c>
       <c r="H178" t="n">
         <v>945978</v>
@@ -5560,7 +5560,7 @@
         <v>13.0863122940063</v>
       </c>
       <c r="G179" t="n">
-        <v>6.67987871170044</v>
+        <v>6.67988014221191</v>
       </c>
       <c r="H179" t="n">
         <v>1112661</v>
@@ -5589,7 +5589,7 @@
         <v>12.9001617431641</v>
       </c>
       <c r="G180" t="n">
-        <v>6.58485889434814</v>
+        <v>6.5848593711853</v>
       </c>
       <c r="H180" t="n">
         <v>949324</v>
@@ -5618,7 +5618,7 @@
         <v>12.9560070037842</v>
       </c>
       <c r="G181" t="n">
-        <v>6.61336660385132</v>
+        <v>6.61336421966553</v>
       </c>
       <c r="H181" t="n">
         <v>810204</v>
@@ -5647,7 +5647,7 @@
         <v>12.9001617431641</v>
       </c>
       <c r="G182" t="n">
-        <v>6.58485889434814</v>
+        <v>6.5848593711853</v>
       </c>
       <c r="H182" t="n">
         <v>814899</v>
@@ -5676,7 +5676,7 @@
         <v>12.0811042785645</v>
       </c>
       <c r="G183" t="n">
-        <v>6.16677331924438</v>
+        <v>6.16677379608154</v>
       </c>
       <c r="H183" t="n">
         <v>1917089</v>
@@ -5705,7 +5705,7 @@
         <v>12.5650930404663</v>
       </c>
       <c r="G184" t="n">
-        <v>6.41382265090942</v>
+        <v>6.41382360458374</v>
       </c>
       <c r="H184" t="n">
         <v>1046187</v>
@@ -5734,7 +5734,7 @@
         <v>12.3510208129883</v>
       </c>
       <c r="G185" t="n">
-        <v>6.30455160140991</v>
+        <v>6.30455112457275</v>
       </c>
       <c r="H185" t="n">
         <v>658084</v>
@@ -5763,7 +5763,7 @@
         <v>12.4534034729004</v>
       </c>
       <c r="G186" t="n">
-        <v>6.35681247711182</v>
+        <v>6.35681200027466</v>
       </c>
       <c r="H186" t="n">
         <v>571911</v>
@@ -5879,7 +5879,7 @@
         <v>11.9414920806885</v>
       </c>
       <c r="G190" t="n">
-        <v>6.09550857543945</v>
+        <v>6.09550809860229</v>
       </c>
       <c r="H190" t="n">
         <v>1576015</v>
@@ -5937,7 +5937,7 @@
         <v>12.3324060440063</v>
       </c>
       <c r="G192" t="n">
-        <v>6.2950496673584</v>
+        <v>6.29504919052124</v>
       </c>
       <c r="H192" t="n">
         <v>1170339</v>
@@ -5966,7 +5966,7 @@
         <v>12.1927938461304</v>
       </c>
       <c r="G193" t="n">
-        <v>6.22378540039062</v>
+        <v>6.22378492355347</v>
       </c>
       <c r="H193" t="n">
         <v>1328972</v>
@@ -5995,7 +5995,7 @@
         <v>12.7047052383423</v>
       </c>
       <c r="G194" t="n">
-        <v>6.48508787155151</v>
+        <v>6.48508882522583</v>
       </c>
       <c r="H194" t="n">
         <v>1713998</v>
@@ -6024,7 +6024,7 @@
         <v>12.9466991424561</v>
       </c>
       <c r="G195" t="n">
-        <v>6.60861301422119</v>
+        <v>6.60861396789551</v>
       </c>
       <c r="H195" t="n">
         <v>1924520</v>
@@ -6053,7 +6053,7 @@
         <v>13.2166156768799</v>
       </c>
       <c r="G196" t="n">
-        <v>6.74639225006104</v>
+        <v>6.74639272689819</v>
       </c>
       <c r="H196" t="n">
         <v>1565361</v>
@@ -6082,7 +6082,7 @@
         <v>13.4958410263062</v>
       </c>
       <c r="G197" t="n">
-        <v>6.88892364501953</v>
+        <v>6.8889217376709</v>
       </c>
       <c r="H197" t="n">
         <v>2130285</v>
@@ -6111,7 +6111,7 @@
         <v>13.5144557952881</v>
       </c>
       <c r="G198" t="n">
-        <v>6.89842319488525</v>
+        <v>6.89842510223389</v>
       </c>
       <c r="H198" t="n">
         <v>1458532</v>
@@ -6140,7 +6140,7 @@
         <v>14.0915193557739</v>
       </c>
       <c r="G199" t="n">
-        <v>7.19298458099365</v>
+        <v>7.19298553466797</v>
       </c>
       <c r="H199" t="n">
         <v>2052554</v>
@@ -6169,7 +6169,7 @@
         <v>14.1566705703735</v>
       </c>
       <c r="G200" t="n">
-        <v>7.22624158859253</v>
+        <v>7.22624206542969</v>
       </c>
       <c r="H200" t="n">
         <v>2121391</v>
@@ -6198,7 +6198,7 @@
         <v>13.9891366958618</v>
       </c>
       <c r="G201" t="n">
-        <v>7.14072513580322</v>
+        <v>7.14072418212891</v>
       </c>
       <c r="H201" t="n">
         <v>1316501</v>
@@ -6256,7 +6256,7 @@
         <v>13.9239845275879</v>
       </c>
       <c r="G203" t="n">
-        <v>7.10746717453003</v>
+        <v>7.10746812820435</v>
       </c>
       <c r="H203" t="n">
         <v>1101505</v>
@@ -6314,7 +6314,7 @@
         <v>13.7564496994019</v>
       </c>
       <c r="G205" t="n">
-        <v>7.02194881439209</v>
+        <v>7.02194976806641</v>
       </c>
       <c r="H205" t="n">
         <v>1322738</v>
@@ -6343,7 +6343,7 @@
         <v>13.9891366958618</v>
       </c>
       <c r="G206" t="n">
-        <v>7.14072513580322</v>
+        <v>7.14072418212891</v>
       </c>
       <c r="H206" t="n">
         <v>583960</v>
@@ -6372,7 +6372,7 @@
         <v>14.0356740951538</v>
       </c>
       <c r="G207" t="n">
-        <v>7.16447877883911</v>
+        <v>7.16448020935059</v>
       </c>
       <c r="H207" t="n">
         <v>887180</v>
@@ -6401,7 +6401,7 @@
         <v>14.0915193557739</v>
       </c>
       <c r="G208" t="n">
-        <v>7.19298458099365</v>
+        <v>7.19298553466797</v>
       </c>
       <c r="H208" t="n">
         <v>770889</v>
@@ -6430,7 +6430,7 @@
         <v>14.2683610916138</v>
       </c>
       <c r="G209" t="n">
-        <v>7.28325319290161</v>
+        <v>7.28325366973877</v>
       </c>
       <c r="H209" t="n">
         <v>1164382</v>
@@ -6459,7 +6459,7 @@
         <v>13.9239845275879</v>
       </c>
       <c r="G210" t="n">
-        <v>7.10746717453003</v>
+        <v>7.10746812820435</v>
       </c>
       <c r="H210" t="n">
         <v>1043584</v>
@@ -6488,7 +6488,7 @@
         <v>14.0542888641357</v>
       </c>
       <c r="G211" t="n">
-        <v>7.17398118972778</v>
+        <v>7.17398023605347</v>
       </c>
       <c r="H211" t="n">
         <v>824076</v>
@@ -6517,7 +6517,7 @@
         <v>14.240439414978</v>
       </c>
       <c r="G212" t="n">
-        <v>7.26900053024292</v>
+        <v>7.26900100708008</v>
       </c>
       <c r="H212" t="n">
         <v>1234266</v>
@@ -6546,7 +6546,7 @@
         <v>13.8309097290039</v>
       </c>
       <c r="G213" t="n">
-        <v>7.05995845794678</v>
+        <v>7.05995655059814</v>
       </c>
       <c r="H213" t="n">
         <v>1865753</v>
@@ -6604,7 +6604,7 @@
         <v>13.4213809967041</v>
       </c>
       <c r="G215" t="n">
-        <v>6.850914478302</v>
+        <v>6.85091495513916</v>
       </c>
       <c r="H215" t="n">
         <v>629318</v>
@@ -6633,7 +6633,7 @@
         <v>12.9560070037842</v>
       </c>
       <c r="G216" t="n">
-        <v>6.61336660385132</v>
+        <v>6.61336421966553</v>
       </c>
       <c r="H216" t="n">
         <v>2014598</v>
@@ -6662,7 +6662,7 @@
         <v>13.179386138916</v>
       </c>
       <c r="G217" t="n">
-        <v>6.72739028930664</v>
+        <v>6.72738933563232</v>
       </c>
       <c r="H217" t="n">
         <v>892718</v>
@@ -6720,7 +6720,7 @@
         <v>13.2538461685181</v>
       </c>
       <c r="G219" t="n">
-        <v>6.7653980255127</v>
+        <v>6.76539754867554</v>
       </c>
       <c r="H219" t="n">
         <v>715497</v>
@@ -6749,7 +6749,7 @@
         <v>14.2218236923218</v>
       </c>
       <c r="G220" t="n">
-        <v>7.25949859619141</v>
+        <v>7.25949764251709</v>
       </c>
       <c r="H220" t="n">
         <v>4015584</v>
@@ -6778,7 +6778,7 @@
         <v>14.6313533782959</v>
       </c>
       <c r="G221" t="n">
-        <v>7.46854305267334</v>
+        <v>7.46854257583618</v>
       </c>
       <c r="H221" t="n">
         <v>2169075</v>
@@ -6807,7 +6807,7 @@
         <v>15.4411029815674</v>
       </c>
       <c r="G222" t="n">
-        <v>7.88187694549561</v>
+        <v>7.88187599182129</v>
       </c>
       <c r="H222" t="n">
         <v>4047856</v>
@@ -6836,7 +6836,7 @@
         <v>15.4969482421875</v>
       </c>
       <c r="G223" t="n">
-        <v>7.91038370132446</v>
+        <v>7.9103832244873</v>
       </c>
       <c r="H223" t="n">
         <v>1939464</v>
@@ -6865,7 +6865,7 @@
         <v>15.7389421463013</v>
       </c>
       <c r="G224" t="n">
-        <v>8.03390789031982</v>
+        <v>8.03390979766846</v>
       </c>
       <c r="H224" t="n">
         <v>3139728</v>
@@ -6894,7 +6894,7 @@
         <v>15.6179447174072</v>
       </c>
       <c r="G225" t="n">
-        <v>7.9721474647522</v>
+        <v>7.97214603424072</v>
       </c>
       <c r="H225" t="n">
         <v>2372479</v>
@@ -6923,7 +6923,7 @@
         <v>15.1618785858154</v>
       </c>
       <c r="G226" t="n">
-        <v>7.73934745788574</v>
+        <v>7.73934698104858</v>
       </c>
       <c r="H226" t="n">
         <v>1616476</v>
@@ -6952,7 +6952,7 @@
         <v>14.8733472824097</v>
       </c>
       <c r="G227" t="n">
-        <v>7.5920672416687</v>
+        <v>7.59206676483154</v>
       </c>
       <c r="H227" t="n">
         <v>2646001</v>
@@ -6981,7 +6981,7 @@
         <v>14.7058134078979</v>
       </c>
       <c r="G228" t="n">
-        <v>7.50655031204224</v>
+        <v>7.50655078887939</v>
       </c>
       <c r="H228" t="n">
         <v>2118027</v>
@@ -7010,7 +7010,7 @@
         <v>13.7285280227661</v>
       </c>
       <c r="G229" t="n">
-        <v>7.4811897277832</v>
+        <v>7.48119068145752</v>
       </c>
       <c r="H229" t="n">
         <v>2904384</v>
@@ -7039,7 +7039,7 @@
         <v>13.3562278747559</v>
       </c>
       <c r="G230" t="n">
-        <v>7.27830982208252</v>
+        <v>7.27831077575684</v>
       </c>
       <c r="H230" t="n">
         <v>2662302</v>
@@ -7068,7 +7068,7 @@
         <v>13.3841514587402</v>
       </c>
       <c r="G231" t="n">
-        <v>7.29352760314941</v>
+        <v>7.2935266494751</v>
       </c>
       <c r="H231" t="n">
         <v>2165235</v>
@@ -7155,7 +7155,7 @@
         <v>12.9094696044922</v>
       </c>
       <c r="G234" t="n">
-        <v>7.03485536575317</v>
+        <v>7.03485441207886</v>
       </c>
       <c r="H234" t="n">
         <v>1409891</v>
@@ -7184,7 +7184,7 @@
         <v>12.8815469741821</v>
       </c>
       <c r="G235" t="n">
-        <v>7.01963996887207</v>
+        <v>7.0196385383606</v>
       </c>
       <c r="H235" t="n">
         <v>1410424</v>
@@ -7213,7 +7213,7 @@
         <v>13.1049270629883</v>
       </c>
       <c r="G236" t="n">
-        <v>7.14136743545532</v>
+        <v>7.14136648178101</v>
       </c>
       <c r="H236" t="n">
         <v>2008644</v>
@@ -7242,7 +7242,7 @@
         <v>13.3096914291382</v>
       </c>
       <c r="G237" t="n">
-        <v>7.25295162200928</v>
+        <v>7.25295066833496</v>
       </c>
       <c r="H237" t="n">
         <v>1489850</v>
@@ -7271,7 +7271,7 @@
         <v>13.1980009078979</v>
       </c>
       <c r="G238" t="n">
-        <v>7.19208717346191</v>
+        <v>7.19208669662476</v>
       </c>
       <c r="H238" t="n">
         <v>1515042</v>
@@ -7300,7 +7300,7 @@
         <v>13.4958410263062</v>
       </c>
       <c r="G239" t="n">
-        <v>7.3543906211853</v>
+        <v>7.35438966751099</v>
       </c>
       <c r="H239" t="n">
         <v>2793136</v>
@@ -7329,7 +7329,7 @@
         <v>14.1939010620117</v>
       </c>
       <c r="G240" t="n">
-        <v>7.73478937149048</v>
+        <v>7.73479032516479</v>
       </c>
       <c r="H240" t="n">
         <v>1813235</v>
@@ -7358,7 +7358,7 @@
         <v>14.5941228866577</v>
       </c>
       <c r="G241" t="n">
-        <v>7.95288705825806</v>
+        <v>7.95288467407227</v>
       </c>
       <c r="H241" t="n">
         <v>2620407</v>
@@ -7416,7 +7416,7 @@
         <v>14.7895803451538</v>
       </c>
       <c r="G243" t="n">
-        <v>8.05939769744873</v>
+        <v>8.05939865112305</v>
       </c>
       <c r="H243" t="n">
         <v>1204011</v>
@@ -7445,7 +7445,7 @@
         <v>14.7895803451538</v>
       </c>
       <c r="G244" t="n">
-        <v>8.05939769744873</v>
+        <v>8.05939865112305</v>
       </c>
       <c r="H244" t="n">
         <v>1453474</v>
@@ -7474,7 +7474,7 @@
         <v>14.6592750549316</v>
       </c>
       <c r="G245" t="n">
-        <v>7.98838949203491</v>
+        <v>7.98838996887207</v>
       </c>
       <c r="H245" t="n">
         <v>1915821</v>
@@ -7503,7 +7503,7 @@
         <v>14.6592750549316</v>
       </c>
       <c r="G246" t="n">
-        <v>7.98838949203491</v>
+        <v>7.98838996887207</v>
       </c>
       <c r="H246" t="n">
         <v>1215059</v>
@@ -7677,7 +7677,7 @@
         <v>14.7709646224976</v>
       </c>
       <c r="G252" t="n">
-        <v>8.04925441741943</v>
+        <v>8.0492525100708</v>
       </c>
       <c r="H252" t="n">
         <v>796929</v>
@@ -7764,7 +7764,7 @@
         <v>14.7430419921875</v>
       </c>
       <c r="G255" t="n">
-        <v>8.03403759002686</v>
+        <v>8.03403854370117</v>
       </c>
       <c r="H255" t="n">
         <v>637989</v>
@@ -7822,7 +7822,7 @@
         <v>14.7616567611694</v>
       </c>
       <c r="G257" t="n">
-        <v>8.04418182373047</v>
+        <v>8.04418277740479</v>
       </c>
       <c r="H257" t="n">
         <v>491051</v>
@@ -7851,7 +7851,7 @@
         <v>15.0222673416138</v>
       </c>
       <c r="G258" t="n">
-        <v>8.18619632720947</v>
+        <v>8.18619823455811</v>
       </c>
       <c r="H258" t="n">
         <v>989103</v>
@@ -7880,7 +7880,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G259" t="n">
-        <v>8.5970287322998</v>
+        <v>8.59702777862549</v>
       </c>
       <c r="H259" t="n">
         <v>2711349</v>
@@ -7909,7 +7909,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G260" t="n">
-        <v>8.63760375976562</v>
+        <v>8.63760471343994</v>
       </c>
       <c r="H260" t="n">
         <v>1389851</v>
@@ -7938,7 +7938,7 @@
         <v>15.9250917434692</v>
       </c>
       <c r="G261" t="n">
-        <v>8.67818069458008</v>
+        <v>8.67817974090576</v>
       </c>
       <c r="H261" t="n">
         <v>2267400</v>
@@ -7996,7 +7996,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G263" t="n">
-        <v>8.5970287322998</v>
+        <v>8.59702777862549</v>
       </c>
       <c r="H263" t="n">
         <v>1770736</v>
@@ -8054,7 +8054,7 @@
         <v>16.1577796936035</v>
       </c>
       <c r="G265" t="n">
-        <v>8.80498027801514</v>
+        <v>8.80498123168945</v>
       </c>
       <c r="H265" t="n">
         <v>2189374</v>
@@ -8083,7 +8083,7 @@
         <v>15.8040952682495</v>
       </c>
       <c r="G266" t="n">
-        <v>8.61224460601807</v>
+        <v>8.61224555969238</v>
       </c>
       <c r="H266" t="n">
         <v>1522761</v>
@@ -8112,7 +8112,7 @@
         <v>16.353235244751</v>
       </c>
       <c r="G267" t="n">
-        <v>8.91149234771729</v>
+        <v>8.91149139404297</v>
       </c>
       <c r="H267" t="n">
         <v>1601338</v>
@@ -8141,7 +8141,7 @@
         <v>16.2415466308594</v>
       </c>
       <c r="G268" t="n">
-        <v>8.85062789916992</v>
+        <v>8.85062885284424</v>
       </c>
       <c r="H268" t="n">
         <v>1033580</v>
@@ -8170,7 +8170,7 @@
         <v>16.2880840301514</v>
       </c>
       <c r="G269" t="n">
-        <v>8.87598896026611</v>
+        <v>8.8759880065918</v>
       </c>
       <c r="H269" t="n">
         <v>1219737</v>
@@ -8199,7 +8199,7 @@
         <v>16.3718509674072</v>
       </c>
       <c r="G270" t="n">
-        <v>8.9216365814209</v>
+        <v>8.92163753509521</v>
       </c>
       <c r="H270" t="n">
         <v>1906829</v>
@@ -8228,7 +8228,7 @@
         <v>16.3625431060791</v>
       </c>
       <c r="G271" t="n">
-        <v>8.91656494140625</v>
+        <v>8.91656398773193</v>
       </c>
       <c r="H271" t="n">
         <v>1010025</v>
@@ -8257,7 +8257,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G272" t="n">
-        <v>8.84048366546631</v>
+        <v>8.84048461914062</v>
       </c>
       <c r="H272" t="n">
         <v>1719302</v>
@@ -8286,7 +8286,7 @@
         <v>15.9902439117432</v>
       </c>
       <c r="G273" t="n">
-        <v>8.71368503570557</v>
+        <v>8.71368408203125</v>
       </c>
       <c r="H273" t="n">
         <v>944176</v>
@@ -8344,7 +8344,7 @@
         <v>16.3904666900635</v>
       </c>
       <c r="G275" t="n">
-        <v>8.93178081512451</v>
+        <v>8.93178176879883</v>
       </c>
       <c r="H275" t="n">
         <v>1778402</v>
@@ -8373,7 +8373,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G276" t="n">
-        <v>8.90641975402832</v>
+        <v>8.90642070770264</v>
       </c>
       <c r="H276" t="n">
         <v>1827665</v>
@@ -8402,7 +8402,7 @@
         <v>16.2880840301514</v>
       </c>
       <c r="G277" t="n">
-        <v>8.87598896026611</v>
+        <v>8.8759880065918</v>
       </c>
       <c r="H277" t="n">
         <v>1134316</v>
@@ -8489,7 +8489,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G280" t="n">
-        <v>8.63760375976562</v>
+        <v>8.63760471343994</v>
       </c>
       <c r="H280" t="n">
         <v>1769425</v>
@@ -8518,7 +8518,7 @@
         <v>15.7389421463013</v>
       </c>
       <c r="G281" t="n">
-        <v>8.57674026489258</v>
+        <v>8.57674121856689</v>
       </c>
       <c r="H281" t="n">
         <v>1463354</v>
@@ -8576,7 +8576,7 @@
         <v>15.1711864471436</v>
       </c>
       <c r="G283" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H283" t="n">
         <v>1576252</v>
@@ -8692,7 +8692,7 @@
         <v>15.8506317138672</v>
       </c>
       <c r="G287" t="n">
-        <v>8.63760375976562</v>
+        <v>8.63760471343994</v>
       </c>
       <c r="H287" t="n">
         <v>1241506</v>
@@ -8808,7 +8808,7 @@
         <v>16.0367813110352</v>
       </c>
       <c r="G291" t="n">
-        <v>8.73904609680176</v>
+        <v>8.73904514312744</v>
       </c>
       <c r="H291" t="n">
         <v>1317032</v>
@@ -8837,7 +8837,7 @@
         <v>15.9809370040894</v>
       </c>
       <c r="G292" t="n">
-        <v>8.70861339569092</v>
+        <v>8.7086124420166</v>
       </c>
       <c r="H292" t="n">
         <v>1369141</v>
@@ -8866,7 +8866,7 @@
         <v>16.0088596343994</v>
       </c>
       <c r="G293" t="n">
-        <v>8.72382831573486</v>
+        <v>8.7238302230835</v>
       </c>
       <c r="H293" t="n">
         <v>733430</v>
@@ -9011,7 +9011,7 @@
         <v>14.8733472824097</v>
       </c>
       <c r="G298" t="n">
-        <v>8.1050443649292</v>
+        <v>8.10504531860352</v>
       </c>
       <c r="H298" t="n">
         <v>1593786</v>
@@ -9127,7 +9127,7 @@
         <v>15.0781116485596</v>
       </c>
       <c r="G302" t="n">
-        <v>8.21662902832031</v>
+        <v>8.21662998199463</v>
       </c>
       <c r="H302" t="n">
         <v>1289973</v>
@@ -9156,7 +9156,7 @@
         <v>15.0688037872314</v>
       </c>
       <c r="G303" t="n">
-        <v>8.21155738830566</v>
+        <v>8.21155643463135</v>
       </c>
       <c r="H303" t="n">
         <v>1281552</v>
@@ -9185,7 +9185,7 @@
         <v>15.0222673416138</v>
       </c>
       <c r="G304" t="n">
-        <v>8.18619632720947</v>
+        <v>8.18619823455811</v>
       </c>
       <c r="H304" t="n">
         <v>1165149</v>
@@ -9214,7 +9214,7 @@
         <v>14.9478073120117</v>
       </c>
       <c r="G305" t="n">
-        <v>8.14562034606934</v>
+        <v>8.14562129974365</v>
       </c>
       <c r="H305" t="n">
         <v>1260594</v>
@@ -9243,7 +9243,7 @@
         <v>14.7802715301514</v>
       </c>
       <c r="G306" t="n">
-        <v>8.05432415008545</v>
+        <v>8.05432510375977</v>
       </c>
       <c r="H306" t="n">
         <v>2226802</v>
@@ -9272,7 +9272,7 @@
         <v>14.7151203155518</v>
       </c>
       <c r="G307" t="n">
-        <v>8.01882076263428</v>
+        <v>8.01882171630859</v>
       </c>
       <c r="H307" t="n">
         <v>1737593</v>
@@ -9301,7 +9301,7 @@
         <v>14.3428211212158</v>
       </c>
       <c r="G308" t="n">
-        <v>7.81594181060791</v>
+        <v>7.81594228744507</v>
       </c>
       <c r="H308" t="n">
         <v>3147847</v>
@@ -9330,7 +9330,7 @@
         <v>14.4265880584717</v>
       </c>
       <c r="G309" t="n">
-        <v>7.86159038543701</v>
+        <v>7.8615894317627</v>
       </c>
       <c r="H309" t="n">
         <v>1981796</v>
@@ -9417,7 +9417,7 @@
         <v>14.9291915893555</v>
       </c>
       <c r="G312" t="n">
-        <v>8.13547801971436</v>
+        <v>8.13547611236572</v>
       </c>
       <c r="H312" t="n">
         <v>6941652</v>
@@ -9446,7 +9446,7 @@
         <v>14.7895803451538</v>
       </c>
       <c r="G313" t="n">
-        <v>8.05939769744873</v>
+        <v>8.05939865112305</v>
       </c>
       <c r="H313" t="n">
         <v>1187060</v>
@@ -9475,7 +9475,7 @@
         <v>14.8268098831177</v>
       </c>
       <c r="G314" t="n">
-        <v>8.07968616485596</v>
+        <v>8.07968521118164</v>
       </c>
       <c r="H314" t="n">
         <v>1455530</v>
@@ -9504,7 +9504,7 @@
         <v>14.6778898239136</v>
       </c>
       <c r="G315" t="n">
-        <v>7.99853372573853</v>
+        <v>7.99853467941284</v>
       </c>
       <c r="H315" t="n">
         <v>1274979</v>
@@ -9562,7 +9562,7 @@
         <v>14.9943437576294</v>
       </c>
       <c r="G317" t="n">
-        <v>8.17098236083984</v>
+        <v>8.17098045349121</v>
       </c>
       <c r="H317" t="n">
         <v>1048653</v>
@@ -9620,7 +9620,7 @@
         <v>14.9105768203735</v>
       </c>
       <c r="G319" t="n">
-        <v>8.12533283233643</v>
+        <v>8.12533378601074</v>
       </c>
       <c r="H319" t="n">
         <v>877264</v>
@@ -9678,7 +9678,7 @@
         <v>14.9291915893555</v>
       </c>
       <c r="G321" t="n">
-        <v>8.13547801971436</v>
+        <v>8.13547611236572</v>
       </c>
       <c r="H321" t="n">
         <v>855893</v>
@@ -9707,7 +9707,7 @@
         <v>15.1991090774536</v>
       </c>
       <c r="G322" t="n">
-        <v>8.28256416320801</v>
+        <v>8.28256511688232</v>
       </c>
       <c r="H322" t="n">
         <v>1777515</v>
@@ -9736,7 +9736,7 @@
         <v>15.1804943084717</v>
       </c>
       <c r="G323" t="n">
-        <v>8.27242088317871</v>
+        <v>8.27242183685303</v>
       </c>
       <c r="H323" t="n">
         <v>1559872</v>
@@ -9765,7 +9765,7 @@
         <v>15.2177238464355</v>
       </c>
       <c r="G324" t="n">
-        <v>8.29270839691162</v>
+        <v>8.29270935058594</v>
       </c>
       <c r="H324" t="n">
         <v>981898</v>
@@ -9852,7 +9852,7 @@
         <v>15.8227100372314</v>
       </c>
       <c r="G327" t="n">
-        <v>8.622389793396</v>
+        <v>8.62238883972168</v>
       </c>
       <c r="H327" t="n">
         <v>1498638</v>
@@ -9910,7 +9910,7 @@
         <v>16.0088596343994</v>
       </c>
       <c r="G329" t="n">
-        <v>8.72382831573486</v>
+        <v>8.7238302230835</v>
       </c>
       <c r="H329" t="n">
         <v>1551746</v>
@@ -9939,7 +9939,7 @@
         <v>16.1019344329834</v>
       </c>
       <c r="G330" t="n">
-        <v>8.77454853057861</v>
+        <v>8.77454948425293</v>
       </c>
       <c r="H330" t="n">
         <v>2102517</v>
@@ -9968,7 +9968,7 @@
         <v>15.8134021759033</v>
       </c>
       <c r="G331" t="n">
-        <v>8.61731719970703</v>
+        <v>8.61731624603271</v>
       </c>
       <c r="H331" t="n">
         <v>1319327</v>
@@ -10026,7 +10026,7 @@
         <v>15.8134021759033</v>
       </c>
       <c r="G333" t="n">
-        <v>8.61731719970703</v>
+        <v>8.61731624603271</v>
       </c>
       <c r="H333" t="n">
         <v>1233589</v>
@@ -10084,7 +10084,7 @@
         <v>15.934398651123</v>
       </c>
       <c r="G335" t="n">
-        <v>8.68325328826904</v>
+        <v>8.68325138092041</v>
       </c>
       <c r="H335" t="n">
         <v>950729</v>
@@ -10113,7 +10113,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G336" t="n">
-        <v>8.90641975402832</v>
+        <v>8.90642070770264</v>
       </c>
       <c r="H336" t="n">
         <v>2707630</v>
@@ -10171,7 +10171,7 @@
         <v>16.6696891784668</v>
       </c>
       <c r="G338" t="n">
-        <v>9.08393859863281</v>
+        <v>9.08393955230713</v>
       </c>
       <c r="H338" t="n">
         <v>1382101</v>
@@ -10229,7 +10229,7 @@
         <v>16.6789989471436</v>
       </c>
       <c r="G340" t="n">
-        <v>9.08901309967041</v>
+        <v>9.08901405334473</v>
       </c>
       <c r="H340" t="n">
         <v>949460</v>
@@ -10258,7 +10258,7 @@
         <v>16.8186092376709</v>
       </c>
       <c r="G341" t="n">
-        <v>9.1650915145874</v>
+        <v>9.16509246826172</v>
       </c>
       <c r="H341" t="n">
         <v>1483455</v>
@@ -10287,7 +10287,7 @@
         <v>16.6696891784668</v>
       </c>
       <c r="G342" t="n">
-        <v>9.08393859863281</v>
+        <v>9.08393955230713</v>
       </c>
       <c r="H342" t="n">
         <v>2272565</v>
@@ -10316,7 +10316,7 @@
         <v>17.2653694152832</v>
       </c>
       <c r="G343" t="n">
-        <v>9.40854835510254</v>
+        <v>9.40854740142822</v>
       </c>
       <c r="H343" t="n">
         <v>4373453</v>
@@ -10345,7 +10345,7 @@
         <v>17.4049816131592</v>
       </c>
       <c r="G344" t="n">
-        <v>9.48462677001953</v>
+        <v>9.48462772369385</v>
       </c>
       <c r="H344" t="n">
         <v>2070466</v>
@@ -10374,7 +10374,7 @@
         <v>17.7307415008545</v>
       </c>
       <c r="G345" t="n">
-        <v>9.66214656829834</v>
+        <v>9.66214752197266</v>
       </c>
       <c r="H345" t="n">
         <v>2677665</v>
@@ -10461,7 +10461,7 @@
         <v>17.7121276855469</v>
       </c>
       <c r="G348" t="n">
-        <v>9.65200233459473</v>
+        <v>9.65200328826904</v>
       </c>
       <c r="H348" t="n">
         <v>2382877</v>
@@ -10490,7 +10490,7 @@
         <v>18.000659942627</v>
       </c>
       <c r="G349" t="n">
-        <v>9.80923748016357</v>
+        <v>9.80923461914062</v>
       </c>
       <c r="H349" t="n">
         <v>1202722</v>
@@ -10519,7 +10519,7 @@
         <v>18.0192737579346</v>
       </c>
       <c r="G350" t="n">
-        <v>9.81937885284424</v>
+        <v>9.81937980651855</v>
       </c>
       <c r="H350" t="n">
         <v>1545277</v>
@@ -10606,7 +10606,7 @@
         <v>17.488748550415</v>
       </c>
       <c r="G353" t="n">
-        <v>9.53027534484863</v>
+        <v>9.53027725219727</v>
       </c>
       <c r="H353" t="n">
         <v>2235701</v>
@@ -10635,7 +10635,7 @@
         <v>17.8796615600586</v>
       </c>
       <c r="G354" t="n">
-        <v>9.74329948425293</v>
+        <v>9.74330043792725</v>
       </c>
       <c r="H354" t="n">
         <v>2022467</v>
@@ -10751,7 +10751,7 @@
         <v>17.4049816131592</v>
       </c>
       <c r="G358" t="n">
-        <v>10.0054759979248</v>
+        <v>10.0054769515991</v>
       </c>
       <c r="H358" t="n">
         <v>1186100</v>
@@ -10780,7 +10780,7 @@
         <v>17.3677501678467</v>
       </c>
       <c r="G359" t="n">
-        <v>9.98407173156738</v>
+        <v>9.98407363891602</v>
       </c>
       <c r="H359" t="n">
         <v>752787</v>
@@ -10867,7 +10867,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G362" t="n">
-        <v>9.65769004821777</v>
+        <v>9.65769195556641</v>
       </c>
       <c r="H362" t="n">
         <v>1467902</v>
@@ -10925,7 +10925,7 @@
         <v>16.967529296875</v>
       </c>
       <c r="G364" t="n">
-        <v>9.75400066375732</v>
+        <v>9.75399971008301</v>
       </c>
       <c r="H364" t="n">
         <v>1117154</v>
@@ -10954,7 +10954,7 @@
         <v>16.7627658843994</v>
       </c>
       <c r="G365" t="n">
-        <v>9.63628959655762</v>
+        <v>9.63629055023193</v>
       </c>
       <c r="H365" t="n">
         <v>994072</v>
@@ -10983,7 +10983,7 @@
         <v>16.5486927032471</v>
       </c>
       <c r="G366" t="n">
-        <v>9.51322746276855</v>
+        <v>9.51322841644287</v>
       </c>
       <c r="H366" t="n">
         <v>1366081</v>
@@ -11041,7 +11041,7 @@
         <v>16.8837623596191</v>
       </c>
       <c r="G368" t="n">
-        <v>9.70584583282471</v>
+        <v>9.70584678649902</v>
       </c>
       <c r="H368" t="n">
         <v>2069336</v>
@@ -11070,7 +11070,7 @@
         <v>16.8372249603271</v>
       </c>
       <c r="G369" t="n">
-        <v>9.67909240722656</v>
+        <v>9.67909526824951</v>
       </c>
       <c r="H369" t="n">
         <v>857040</v>
@@ -11099,7 +11099,7 @@
         <v>16.5486927032471</v>
       </c>
       <c r="G370" t="n">
-        <v>9.51322746276855</v>
+        <v>9.51322841644287</v>
       </c>
       <c r="H370" t="n">
         <v>1000146</v>
@@ -11128,7 +11128,7 @@
         <v>16.5859222412109</v>
       </c>
       <c r="G371" t="n">
-        <v>9.53462791442871</v>
+        <v>9.53462982177734</v>
       </c>
       <c r="H371" t="n">
         <v>1099573</v>
@@ -11157,7 +11157,7 @@
         <v>16.4183883666992</v>
       </c>
       <c r="G372" t="n">
-        <v>9.43831920623779</v>
+        <v>9.43832111358643</v>
       </c>
       <c r="H372" t="n">
         <v>1059006</v>
@@ -11186,7 +11186,7 @@
         <v>16.3160057067871</v>
       </c>
       <c r="G373" t="n">
-        <v>9.3794641494751</v>
+        <v>9.37946510314941</v>
       </c>
       <c r="H373" t="n">
         <v>857340</v>
@@ -11244,7 +11244,7 @@
         <v>16.6324596405029</v>
       </c>
       <c r="G375" t="n">
-        <v>9.56138229370117</v>
+        <v>9.56138134002686</v>
       </c>
       <c r="H375" t="n">
         <v>588978</v>
@@ -11302,7 +11302,7 @@
         <v>16.8372249603271</v>
       </c>
       <c r="G377" t="n">
-        <v>9.67909240722656</v>
+        <v>9.67909526824951</v>
       </c>
       <c r="H377" t="n">
         <v>848907</v>
@@ -11331,7 +11331,7 @@
         <v>16.5114631652832</v>
       </c>
       <c r="G378" t="n">
-        <v>9.49182415008545</v>
+        <v>9.49182605743408</v>
       </c>
       <c r="H378" t="n">
         <v>873978</v>
@@ -11418,7 +11418,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G381" t="n">
-        <v>9.63093852996826</v>
+        <v>9.63093757629395</v>
       </c>
       <c r="H381" t="n">
         <v>691418</v>
@@ -11476,7 +11476,7 @@
         <v>16.5486927032471</v>
       </c>
       <c r="G383" t="n">
-        <v>9.51322746276855</v>
+        <v>9.51322841644287</v>
       </c>
       <c r="H383" t="n">
         <v>923141</v>
@@ -11505,7 +11505,7 @@
         <v>16.3346214294434</v>
       </c>
       <c r="G384" t="n">
-        <v>9.39016532897949</v>
+        <v>9.39016437530518</v>
       </c>
       <c r="H384" t="n">
         <v>637739</v>
@@ -11563,7 +11563,7 @@
         <v>16.8093013763428</v>
       </c>
       <c r="G386" t="n">
-        <v>9.66304111480713</v>
+        <v>9.66304016113281</v>
       </c>
       <c r="H386" t="n">
         <v>475784</v>
@@ -11621,7 +11621,7 @@
         <v>16.7720718383789</v>
       </c>
       <c r="G388" t="n">
-        <v>9.64163970947266</v>
+        <v>9.64164066314697</v>
       </c>
       <c r="H388" t="n">
         <v>756758</v>
@@ -11650,7 +11650,7 @@
         <v>16.5580005645752</v>
       </c>
       <c r="G389" t="n">
-        <v>9.51857852935791</v>
+        <v>9.51857757568359</v>
       </c>
       <c r="H389" t="n">
         <v>945459</v>
@@ -11766,7 +11766,7 @@
         <v>17.0792198181152</v>
       </c>
       <c r="G393" t="n">
-        <v>9.81820869445801</v>
+        <v>9.81820583343506</v>
       </c>
       <c r="H393" t="n">
         <v>645461</v>
@@ -11795,7 +11795,7 @@
         <v>16.9302997589111</v>
       </c>
       <c r="G394" t="n">
-        <v>9.73259830474854</v>
+        <v>9.73259925842285</v>
       </c>
       <c r="H394" t="n">
         <v>627732</v>
@@ -11824,7 +11824,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G395" t="n">
-        <v>9.65769004821777</v>
+        <v>9.65769195556641</v>
       </c>
       <c r="H395" t="n">
         <v>803256</v>
@@ -11940,7 +11940,7 @@
         <v>16.7999954223633</v>
       </c>
       <c r="G399" t="n">
-        <v>9.65769004821777</v>
+        <v>9.65769195556641</v>
       </c>
       <c r="H399" t="n">
         <v>864759</v>
@@ -12027,7 +12027,7 @@
         <v>17.060604095459</v>
       </c>
       <c r="G402" t="n">
-        <v>9.8075065612793</v>
+        <v>9.80750465393066</v>
       </c>
       <c r="H402" t="n">
         <v>675917</v>
@@ -12085,7 +12085,7 @@
         <v>17.4608268737793</v>
       </c>
       <c r="G404" t="n">
-        <v>10.037579536438</v>
+        <v>10.0375804901123</v>
       </c>
       <c r="H404" t="n">
         <v>643355</v>
@@ -12172,7 +12172,7 @@
         <v>17.5073623657227</v>
       </c>
       <c r="G407" t="n">
-        <v>10.0643301010132</v>
+        <v>10.0643310546875</v>
       </c>
       <c r="H407" t="n">
         <v>616893</v>
@@ -12259,7 +12259,7 @@
         <v>17.5632076263428</v>
       </c>
       <c r="G410" t="n">
-        <v>10.0964336395264</v>
+        <v>10.0964345932007</v>
       </c>
       <c r="H410" t="n">
         <v>617298</v>
@@ -12404,7 +12404,7 @@
         <v>17.060604095459</v>
       </c>
       <c r="G415" t="n">
-        <v>9.8075065612793</v>
+        <v>9.80750465393066</v>
       </c>
       <c r="H415" t="n">
         <v>473953</v>
@@ -12433,7 +12433,7 @@
         <v>17.5725154876709</v>
       </c>
       <c r="G416" t="n">
-        <v>10.1017847061157</v>
+        <v>10.10178565979</v>
       </c>
       <c r="H416" t="n">
         <v>1084638</v>
@@ -12491,7 +12491,7 @@
         <v>17.3212127685547</v>
       </c>
       <c r="G418" t="n">
-        <v>9.95731925964355</v>
+        <v>9.95732021331787</v>
       </c>
       <c r="H418" t="n">
         <v>603666</v>
@@ -12520,7 +12520,7 @@
         <v>17.200216293335</v>
       </c>
       <c r="G419" t="n">
-        <v>9.88776302337646</v>
+        <v>9.88776397705078</v>
       </c>
       <c r="H419" t="n">
         <v>471768</v>
@@ -12549,7 +12549,7 @@
         <v>16.9582214355469</v>
       </c>
       <c r="G420" t="n">
-        <v>9.74865055084229</v>
+        <v>9.74864959716797</v>
       </c>
       <c r="H420" t="n">
         <v>1199704</v>
@@ -12607,7 +12607,7 @@
         <v>16.7906875610352</v>
       </c>
       <c r="G422" t="n">
-        <v>9.65234088897705</v>
+        <v>9.65234184265137</v>
       </c>
       <c r="H422" t="n">
         <v>777087</v>
@@ -12665,7 +12665,7 @@
         <v>16.8651466369629</v>
       </c>
       <c r="G424" t="n">
-        <v>9.69514465332031</v>
+        <v>9.695143699646</v>
       </c>
       <c r="H424" t="n">
         <v>834174</v>
@@ -12694,7 +12694,7 @@
         <v>16.4556179046631</v>
       </c>
       <c r="G425" t="n">
-        <v>9.45972156524658</v>
+        <v>9.4597225189209</v>
       </c>
       <c r="H425" t="n">
         <v>1374883</v>
@@ -12723,7 +12723,7 @@
         <v>16.4556179046631</v>
       </c>
       <c r="G426" t="n">
-        <v>9.45972156524658</v>
+        <v>9.4597225189209</v>
       </c>
       <c r="H426" t="n">
         <v>535558</v>
@@ -12781,7 +12781,7 @@
         <v>16.5673084259033</v>
       </c>
       <c r="G428" t="n">
-        <v>9.52392864227295</v>
+        <v>9.52392959594727</v>
       </c>
       <c r="H428" t="n">
         <v>746823</v>
@@ -12868,7 +12868,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G431" t="n">
-        <v>9.39551639556885</v>
+        <v>9.39551448822021</v>
       </c>
       <c r="H431" t="n">
         <v>835890</v>
@@ -12897,7 +12897,7 @@
         <v>16.3904666900635</v>
       </c>
       <c r="G432" t="n">
-        <v>9.42226886749268</v>
+        <v>9.42226982116699</v>
       </c>
       <c r="H432" t="n">
         <v>665021</v>
@@ -12926,7 +12926,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G433" t="n">
-        <v>9.39551639556885</v>
+        <v>9.39551448822021</v>
       </c>
       <c r="H433" t="n">
         <v>421258</v>
@@ -13129,7 +13129,7 @@
         <v>17.246753692627</v>
       </c>
       <c r="G440" t="n">
-        <v>9.91451549530029</v>
+        <v>9.91451644897461</v>
       </c>
       <c r="H440" t="n">
         <v>522818</v>
@@ -13303,7 +13303,7 @@
         <v>16.7627658843994</v>
       </c>
       <c r="G446" t="n">
-        <v>9.63628959655762</v>
+        <v>9.63629055023193</v>
       </c>
       <c r="H446" t="n">
         <v>755068</v>
@@ -13332,7 +13332,7 @@
         <v>17.0047588348389</v>
       </c>
       <c r="G447" t="n">
-        <v>9.77540302276611</v>
+        <v>9.7754020690918</v>
       </c>
       <c r="H447" t="n">
         <v>854342</v>
@@ -13390,7 +13390,7 @@
         <v>17.1629867553711</v>
       </c>
       <c r="G449" t="n">
-        <v>9.86636257171631</v>
+        <v>9.86636161804199</v>
       </c>
       <c r="H449" t="n">
         <v>654849</v>
@@ -13419,7 +13419,7 @@
         <v>17.2560615539551</v>
       </c>
       <c r="G450" t="n">
-        <v>9.91986656188965</v>
+        <v>9.91986751556396</v>
       </c>
       <c r="H450" t="n">
         <v>606113</v>
@@ -13448,7 +13448,7 @@
         <v>16.8651466369629</v>
       </c>
       <c r="G451" t="n">
-        <v>9.69514465332031</v>
+        <v>9.695143699646</v>
       </c>
       <c r="H451" t="n">
         <v>671978</v>
@@ -13477,7 +13477,7 @@
         <v>16.9768371582031</v>
       </c>
       <c r="G452" t="n">
-        <v>9.75935173034668</v>
+        <v>9.75935363769531</v>
       </c>
       <c r="H452" t="n">
         <v>500233</v>
@@ -13506,7 +13506,7 @@
         <v>16.9768371582031</v>
       </c>
       <c r="G453" t="n">
-        <v>9.75935173034668</v>
+        <v>9.75935363769531</v>
       </c>
       <c r="H453" t="n">
         <v>698353</v>
@@ -13535,7 +13535,7 @@
         <v>16.9582214355469</v>
       </c>
       <c r="G454" t="n">
-        <v>9.74865055084229</v>
+        <v>9.74864959716797</v>
       </c>
       <c r="H454" t="n">
         <v>363293</v>
@@ -13564,7 +13564,7 @@
         <v>16.8837623596191</v>
       </c>
       <c r="G455" t="n">
-        <v>9.70584583282471</v>
+        <v>9.70584678649902</v>
       </c>
       <c r="H455" t="n">
         <v>550780</v>
@@ -13593,7 +13593,7 @@
         <v>16.7627658843994</v>
       </c>
       <c r="G456" t="n">
-        <v>9.63628959655762</v>
+        <v>9.63629055023193</v>
       </c>
       <c r="H456" t="n">
         <v>879805</v>
@@ -13767,7 +13767,7 @@
         <v>15.5621004104614</v>
       </c>
       <c r="G462" t="n">
-        <v>8.94607162475586</v>
+        <v>8.94607257843018</v>
       </c>
       <c r="H462" t="n">
         <v>1743428</v>
@@ -13883,7 +13883,7 @@
         <v>15.7296352386475</v>
       </c>
       <c r="G466" t="n">
-        <v>9.04238224029541</v>
+        <v>9.04238128662109</v>
       </c>
       <c r="H466" t="n">
         <v>663164</v>
@@ -13912,7 +13912,7 @@
         <v>15.934398651123</v>
       </c>
       <c r="G467" t="n">
-        <v>9.1600923538208</v>
+        <v>9.16009330749512</v>
       </c>
       <c r="H467" t="n">
         <v>1120789</v>
@@ -13941,7 +13941,7 @@
         <v>15.8692474365234</v>
       </c>
       <c r="G468" t="n">
-        <v>9.12263870239258</v>
+        <v>9.12263965606689</v>
       </c>
       <c r="H468" t="n">
         <v>1030051</v>
@@ -13970,7 +13970,7 @@
         <v>15.7761716842651</v>
       </c>
       <c r="G469" t="n">
-        <v>9.06913471221924</v>
+        <v>9.06913375854492</v>
       </c>
       <c r="H469" t="n">
         <v>810700</v>
@@ -13999,7 +13999,7 @@
         <v>15.7854795455933</v>
       </c>
       <c r="G470" t="n">
-        <v>9.07448577880859</v>
+        <v>9.07448387145996</v>
       </c>
       <c r="H470" t="n">
         <v>582153</v>
@@ -14028,7 +14028,7 @@
         <v>15.9716291427612</v>
       </c>
       <c r="G471" t="n">
-        <v>9.18149471282959</v>
+        <v>9.18149375915527</v>
       </c>
       <c r="H471" t="n">
         <v>1282309</v>
@@ -14086,7 +14086,7 @@
         <v>16.0740127563477</v>
       </c>
       <c r="G473" t="n">
-        <v>9.24035167694092</v>
+        <v>9.2403507232666</v>
       </c>
       <c r="H473" t="n">
         <v>1032541</v>
@@ -14173,7 +14173,7 @@
         <v>15.8692474365234</v>
       </c>
       <c r="G476" t="n">
-        <v>9.12263870239258</v>
+        <v>9.12263965606689</v>
       </c>
       <c r="H476" t="n">
         <v>1696146</v>
@@ -14289,7 +14289,7 @@
         <v>14.3893575668335</v>
       </c>
       <c r="G480" t="n">
-        <v>8.27190589904785</v>
+        <v>8.27190685272217</v>
       </c>
       <c r="H480" t="n">
         <v>1677935</v>
@@ -14318,7 +14318,7 @@
         <v>14.3614358901978</v>
       </c>
       <c r="G481" t="n">
-        <v>8.25585460662842</v>
+        <v>8.25585556030273</v>
       </c>
       <c r="H481" t="n">
         <v>2101927</v>
@@ -14347,7 +14347,7 @@
         <v>14.5475845336914</v>
       </c>
       <c r="G482" t="n">
-        <v>8.36286449432373</v>
+        <v>8.36286544799805</v>
       </c>
       <c r="H482" t="n">
         <v>1368946</v>
@@ -14434,7 +14434,7 @@
         <v>15.1618785858154</v>
       </c>
       <c r="G485" t="n">
-        <v>8.71599960327148</v>
+        <v>8.71599864959717</v>
       </c>
       <c r="H485" t="n">
         <v>1715781</v>
@@ -14463,7 +14463,7 @@
         <v>15.1804943084717</v>
       </c>
       <c r="G486" t="n">
-        <v>8.7267017364502</v>
+        <v>8.72670078277588</v>
       </c>
       <c r="H486" t="n">
         <v>673229</v>
@@ -14492,7 +14492,7 @@
         <v>14.9478073120117</v>
       </c>
       <c r="G487" t="n">
-        <v>8.59293842315674</v>
+        <v>8.59293746948242</v>
       </c>
       <c r="H487" t="n">
         <v>829118</v>
@@ -14550,7 +14550,7 @@
         <v>14.7430419921875</v>
       </c>
       <c r="G489" t="n">
-        <v>8.47522640228271</v>
+        <v>8.47522735595703</v>
       </c>
       <c r="H489" t="n">
         <v>624837</v>
@@ -14637,7 +14637,7 @@
         <v>14.8547315597534</v>
       </c>
       <c r="G492" t="n">
-        <v>8.53943252563477</v>
+        <v>8.53943157196045</v>
       </c>
       <c r="H492" t="n">
         <v>1328221</v>
@@ -14666,7 +14666,7 @@
         <v>14.6034297943115</v>
       </c>
       <c r="G493" t="n">
-        <v>8.3949670791626</v>
+        <v>8.39496803283691</v>
       </c>
       <c r="H493" t="n">
         <v>1094020</v>
@@ -14695,7 +14695,7 @@
         <v>14.5755081176758</v>
       </c>
       <c r="G494" t="n">
-        <v>8.37891578674316</v>
+        <v>8.37891674041748</v>
       </c>
       <c r="H494" t="n">
         <v>1401506</v>
@@ -14753,7 +14753,7 @@
         <v>14.4265880584717</v>
       </c>
       <c r="G496" t="n">
-        <v>8.29330825805664</v>
+        <v>8.29330730438232</v>
       </c>
       <c r="H496" t="n">
         <v>953589</v>
@@ -14898,7 +14898,7 @@
         <v>14.7616567611694</v>
       </c>
       <c r="G501" t="n">
-        <v>8.48592662811279</v>
+        <v>8.48592758178711</v>
       </c>
       <c r="H501" t="n">
         <v>773704</v>
@@ -14927,7 +14927,7 @@
         <v>14.7988872528076</v>
       </c>
       <c r="G502" t="n">
-        <v>8.5073299407959</v>
+        <v>8.50732803344727</v>
       </c>
       <c r="H502" t="n">
         <v>1373841</v>
@@ -15043,7 +15043,7 @@
         <v>14.7895803451538</v>
       </c>
       <c r="G506" t="n">
-        <v>8.50197887420654</v>
+        <v>8.50197982788086</v>
       </c>
       <c r="H506" t="n">
         <v>675838</v>
@@ -15101,7 +15101,7 @@
         <v>14.8268098831177</v>
       </c>
       <c r="G508" t="n">
-        <v>8.52338218688965</v>
+        <v>8.52338123321533</v>
       </c>
       <c r="H508" t="n">
         <v>437167</v>
@@ -15130,7 +15130,7 @@
         <v>14.9943437576294</v>
       </c>
       <c r="G509" t="n">
-        <v>8.61968994140625</v>
+        <v>8.61969089508057</v>
       </c>
       <c r="H509" t="n">
         <v>567586</v>
@@ -15159,7 +15159,7 @@
         <v>14.9478073120117</v>
       </c>
       <c r="G510" t="n">
-        <v>8.59293842315674</v>
+        <v>8.59293746948242</v>
       </c>
       <c r="H510" t="n">
         <v>520886</v>
@@ -15362,7 +15362,7 @@
         <v>15.3759508132935</v>
       </c>
       <c r="G517" t="n">
-        <v>8.83906269073486</v>
+        <v>8.83906173706055</v>
       </c>
       <c r="H517" t="n">
         <v>1463191</v>
@@ -15391,7 +15391,7 @@
         <v>15.3945655822754</v>
       </c>
       <c r="G518" t="n">
-        <v>8.84976387023926</v>
+        <v>8.84976196289062</v>
       </c>
       <c r="H518" t="n">
         <v>1021965</v>
@@ -15507,7 +15507,7 @@
         <v>17.0978336334229</v>
       </c>
       <c r="G522" t="n">
-        <v>9.82890796661377</v>
+        <v>9.82890701293945</v>
       </c>
       <c r="H522" t="n">
         <v>6840925</v>
@@ -15594,7 +15594,7 @@
         <v>17.5725154876709</v>
       </c>
       <c r="G525" t="n">
-        <v>10.1017847061157</v>
+        <v>10.10178565979</v>
       </c>
       <c r="H525" t="n">
         <v>1827376</v>
@@ -15623,7 +15623,7 @@
         <v>17.6469745635986</v>
       </c>
       <c r="G526" t="n">
-        <v>10.144588470459</v>
+        <v>10.1445894241333</v>
       </c>
       <c r="H526" t="n">
         <v>1716769</v>
@@ -15739,7 +15739,7 @@
         <v>17.4608268737793</v>
       </c>
       <c r="G530" t="n">
-        <v>10.037579536438</v>
+        <v>10.0375804901123</v>
       </c>
       <c r="H530" t="n">
         <v>1813520</v>
@@ -15797,7 +15797,7 @@
         <v>17.153678894043</v>
       </c>
       <c r="G532" t="n">
-        <v>9.86101055145264</v>
+        <v>9.86101150512695</v>
       </c>
       <c r="H532" t="n">
         <v>1575700</v>
@@ -15855,7 +15855,7 @@
         <v>17.1350631713867</v>
       </c>
       <c r="G534" t="n">
-        <v>9.85030841827393</v>
+        <v>9.85031032562256</v>
       </c>
       <c r="H534" t="n">
         <v>1290237</v>
@@ -15884,7 +15884,7 @@
         <v>17.0280284881592</v>
       </c>
       <c r="G535" t="n">
-        <v>9.78878021240234</v>
+        <v>9.78877925872803</v>
       </c>
       <c r="H535" t="n">
         <v>1219471</v>
@@ -15942,7 +15942,7 @@
         <v>16.5300788879395</v>
       </c>
       <c r="G537" t="n">
-        <v>9.50252532958984</v>
+        <v>9.50252723693848</v>
       </c>
       <c r="H537" t="n">
         <v>3251917</v>
@@ -16000,7 +16000,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G539" t="n">
-        <v>9.63093852996826</v>
+        <v>9.63093757629395</v>
       </c>
       <c r="H539" t="n">
         <v>1352694</v>
@@ -16029,7 +16029,7 @@
         <v>16.6278057098389</v>
       </c>
       <c r="G540" t="n">
-        <v>9.55870628356934</v>
+        <v>9.55870723724365</v>
       </c>
       <c r="H540" t="n">
         <v>1946935</v>
@@ -16174,7 +16174,7 @@
         <v>16.7953414916992</v>
       </c>
       <c r="G545" t="n">
-        <v>9.65501594543457</v>
+        <v>9.65501689910889</v>
       </c>
       <c r="H545" t="n">
         <v>707813</v>
@@ -16203,7 +16203,7 @@
         <v>16.6743431091309</v>
       </c>
       <c r="G546" t="n">
-        <v>9.58545970916748</v>
+        <v>9.58545875549316</v>
       </c>
       <c r="H546" t="n">
         <v>548096</v>
@@ -16232,7 +16232,7 @@
         <v>16.8046493530273</v>
       </c>
       <c r="G547" t="n">
-        <v>9.66036701202393</v>
+        <v>9.66036796569824</v>
       </c>
       <c r="H547" t="n">
         <v>741981</v>
@@ -16261,7 +16261,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G548" t="n">
-        <v>9.63093852996826</v>
+        <v>9.63093757629395</v>
       </c>
       <c r="H548" t="n">
         <v>1023005</v>
@@ -16290,7 +16290,7 @@
         <v>16.5673084259033</v>
       </c>
       <c r="G549" t="n">
-        <v>9.52392864227295</v>
+        <v>9.52392959594727</v>
       </c>
       <c r="H549" t="n">
         <v>1129866</v>
@@ -16348,7 +16348,7 @@
         <v>16.8186092376709</v>
       </c>
       <c r="G551" t="n">
-        <v>9.66839218139648</v>
+        <v>9.6683931350708</v>
       </c>
       <c r="H551" t="n">
         <v>1351834</v>
@@ -16464,7 +16464,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G555" t="n">
-        <v>9.34468460083008</v>
+        <v>9.34468650817871</v>
       </c>
       <c r="H555" t="n">
         <v>2578826</v>
@@ -16522,7 +16522,7 @@
         <v>16.7162265777588</v>
       </c>
       <c r="G557" t="n">
-        <v>9.60953617095947</v>
+        <v>9.60953521728516</v>
       </c>
       <c r="H557" t="n">
         <v>1706194</v>
@@ -16609,7 +16609,7 @@
         <v>16.7720718383789</v>
       </c>
       <c r="G560" t="n">
-        <v>9.64163970947266</v>
+        <v>9.64164066314697</v>
       </c>
       <c r="H560" t="n">
         <v>1257766</v>
@@ -16667,7 +16667,7 @@
         <v>16.5486927032471</v>
       </c>
       <c r="G562" t="n">
-        <v>9.51322746276855</v>
+        <v>9.51322841644287</v>
       </c>
       <c r="H562" t="n">
         <v>1605914</v>
@@ -16754,7 +16754,7 @@
         <v>16.7534561157227</v>
       </c>
       <c r="G565" t="n">
-        <v>9.63093852996826</v>
+        <v>9.63093757629395</v>
       </c>
       <c r="H565" t="n">
         <v>3551986</v>
@@ -16841,7 +16841,7 @@
         <v>16.7069206237793</v>
       </c>
       <c r="G568" t="n">
-        <v>9.60418701171875</v>
+        <v>9.60418605804443</v>
       </c>
       <c r="H568" t="n">
         <v>1136879</v>
@@ -16870,7 +16870,7 @@
         <v>16.4602718353271</v>
       </c>
       <c r="G569" t="n">
-        <v>9.46239757537842</v>
+        <v>9.4623966217041</v>
       </c>
       <c r="H569" t="n">
         <v>1417689</v>
@@ -16899,7 +16899,7 @@
         <v>16.3718509674072</v>
       </c>
       <c r="G570" t="n">
-        <v>9.41156673431396</v>
+        <v>9.4115686416626</v>
       </c>
       <c r="H570" t="n">
         <v>1629083</v>
@@ -16957,7 +16957,7 @@
         <v>16.3439273834229</v>
       </c>
       <c r="G572" t="n">
-        <v>9.39551639556885</v>
+        <v>9.39551448822021</v>
       </c>
       <c r="H572" t="n">
         <v>1083998</v>
@@ -16986,7 +16986,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G573" t="n">
-        <v>9.32595825195312</v>
+        <v>9.32596015930176</v>
       </c>
       <c r="H573" t="n">
         <v>1192828</v>
@@ -17015,7 +17015,7 @@
         <v>16.2368927001953</v>
       </c>
       <c r="G574" t="n">
-        <v>9.33398532867432</v>
+        <v>9.333984375</v>
       </c>
       <c r="H574" t="n">
         <v>638082</v>
@@ -17073,7 +17073,7 @@
         <v>16.1019344329834</v>
       </c>
       <c r="G576" t="n">
-        <v>9.25640201568604</v>
+        <v>9.25640296936035</v>
       </c>
       <c r="H576" t="n">
         <v>1229817</v>
@@ -17131,7 +17131,7 @@
         <v>16.3160057067871</v>
       </c>
       <c r="G578" t="n">
-        <v>9.3794641494751</v>
+        <v>9.37946510314941</v>
       </c>
       <c r="H578" t="n">
         <v>764606</v>
@@ -17160,7 +17160,7 @@
         <v>16.5161170959473</v>
       </c>
       <c r="G579" t="n">
-        <v>9.49450016021729</v>
+        <v>9.4945011138916</v>
       </c>
       <c r="H579" t="n">
         <v>1172659</v>
@@ -17247,7 +17247,7 @@
         <v>16.5207691192627</v>
       </c>
       <c r="G582" t="n">
-        <v>9.49717330932617</v>
+        <v>9.4971752166748</v>
       </c>
       <c r="H582" t="n">
         <v>1299325</v>
@@ -17363,7 +17363,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G586" t="n">
-        <v>9.34468460083008</v>
+        <v>9.34468650817871</v>
       </c>
       <c r="H586" t="n">
         <v>1262836</v>
@@ -17421,7 +17421,7 @@
         <v>16.1903553009033</v>
       </c>
       <c r="G588" t="n">
-        <v>9.30723285675049</v>
+        <v>9.30723190307617</v>
       </c>
       <c r="H588" t="n">
         <v>1192757</v>
@@ -17479,7 +17479,7 @@
         <v>16.1252021789551</v>
       </c>
       <c r="G590" t="n">
-        <v>9.26977825164795</v>
+        <v>9.26977729797363</v>
       </c>
       <c r="H590" t="n">
         <v>1678666</v>
@@ -17537,7 +17537,7 @@
         <v>16.1345100402832</v>
       </c>
       <c r="G592" t="n">
-        <v>9.2751293182373</v>
+        <v>9.27512836456299</v>
       </c>
       <c r="H592" t="n">
         <v>1139202</v>
@@ -17595,7 +17595,7 @@
         <v>16.2229309082031</v>
       </c>
       <c r="G594" t="n">
-        <v>9.32595825195312</v>
+        <v>9.32596015930176</v>
       </c>
       <c r="H594" t="n">
         <v>1512274</v>
@@ -17624,7 +17624,7 @@
         <v>16.3253135681152</v>
       </c>
       <c r="G595" t="n">
-        <v>9.38481521606445</v>
+        <v>9.38481616973877</v>
       </c>
       <c r="H595" t="n">
         <v>1961245</v>
@@ -17653,7 +17653,7 @@
         <v>16.2555065155029</v>
       </c>
       <c r="G596" t="n">
-        <v>9.34468460083008</v>
+        <v>9.34468650817871</v>
       </c>
       <c r="H596" t="n">
         <v>1297293</v>
@@ -17740,7 +17740,7 @@
         <v>16.5254230499268</v>
       </c>
       <c r="G599" t="n">
-        <v>9.49984931945801</v>
+        <v>9.49985027313232</v>
       </c>
       <c r="H599" t="n">
         <v>2558942</v>
@@ -17769,7 +17769,7 @@
         <v>16.3066997528076</v>
       </c>
       <c r="G600" t="n">
-        <v>9.37411499023438</v>
+        <v>9.37411403656006</v>
       </c>
       <c r="H600" t="n">
         <v>2502188</v>
@@ -17827,7 +17827,7 @@
         <v>15.4690256118774</v>
       </c>
       <c r="G602" t="n">
-        <v>8.8925666809082</v>
+        <v>8.89256763458252</v>
       </c>
       <c r="H602" t="n">
         <v>6600347</v>
@@ -17885,7 +17885,7 @@
         <v>15.1246490478516</v>
       </c>
       <c r="G604" t="n">
-        <v>8.69459819793701</v>
+        <v>8.6945972442627</v>
       </c>
       <c r="H604" t="n">
         <v>4075256</v>
@@ -17914,7 +17914,7 @@
         <v>14.9710760116577</v>
       </c>
       <c r="G605" t="n">
-        <v>8.60631370544434</v>
+        <v>8.60631465911865</v>
       </c>
       <c r="H605" t="n">
         <v>2873508</v>
@@ -17972,7 +17972,7 @@
         <v>15.0967273712158</v>
       </c>
       <c r="G607" t="n">
-        <v>8.67854690551758</v>
+        <v>8.67854785919189</v>
       </c>
       <c r="H607" t="n">
         <v>3283302</v>
@@ -18001,7 +18001,7 @@
         <v>14.2554397583008</v>
       </c>
       <c r="G608" t="n">
-        <v>8.76534748077393</v>
+        <v>8.76534652709961</v>
       </c>
       <c r="H608" t="n">
         <v>2816215</v>
@@ -18030,7 +18030,7 @@
         <v>14.5943880081177</v>
       </c>
       <c r="G609" t="n">
-        <v>8.97375869750977</v>
+        <v>8.97375965118408</v>
       </c>
       <c r="H609" t="n">
         <v>3253098</v>
@@ -18117,7 +18117,7 @@
         <v>14.4814052581787</v>
       </c>
       <c r="G612" t="n">
-        <v>8.90428829193115</v>
+        <v>8.90429019927979</v>
       </c>
       <c r="H612" t="n">
         <v>2545280</v>
@@ -18349,7 +18349,7 @@
         <v>13.6856145858765</v>
       </c>
       <c r="G620" t="n">
-        <v>8.41497611999512</v>
+        <v>8.4149751663208</v>
       </c>
       <c r="H620" t="n">
         <v>2306058</v>
@@ -18378,7 +18378,7 @@
         <v>13.705265045166</v>
       </c>
       <c r="G621" t="n">
-        <v>8.42705726623535</v>
+        <v>8.42705821990967</v>
       </c>
       <c r="H621" t="n">
         <v>1224599</v>
@@ -18407,7 +18407,7 @@
         <v>13.2631587982178</v>
       </c>
       <c r="G622" t="n">
-        <v>8.1552152633667</v>
+        <v>8.15521621704102</v>
       </c>
       <c r="H622" t="n">
         <v>1377416</v>
@@ -18465,7 +18465,7 @@
         <v>13.4301767349243</v>
       </c>
       <c r="G624" t="n">
-        <v>8.25791263580322</v>
+        <v>8.25791168212891</v>
       </c>
       <c r="H624" t="n">
         <v>1397497</v>
@@ -18494,7 +18494,7 @@
         <v>13.3810539245605</v>
       </c>
       <c r="G625" t="n">
-        <v>8.22770690917969</v>
+        <v>8.227707862854</v>
       </c>
       <c r="H625" t="n">
         <v>1383351</v>
@@ -18523,7 +18523,7 @@
         <v>13.3712291717529</v>
       </c>
       <c r="G626" t="n">
-        <v>8.22166633605957</v>
+        <v>8.22166728973389</v>
       </c>
       <c r="H626" t="n">
         <v>2015917</v>
@@ -18552,7 +18552,7 @@
         <v>13.2582473754883</v>
       </c>
       <c r="G627" t="n">
-        <v>8.15219593048096</v>
+        <v>8.15219688415527</v>
       </c>
       <c r="H627" t="n">
         <v>2762510</v>
@@ -18581,7 +18581,7 @@
         <v>13.543158531189</v>
       </c>
       <c r="G628" t="n">
-        <v>8.32738208770752</v>
+        <v>8.32738304138184</v>
       </c>
       <c r="H628" t="n">
         <v>2400502</v>
@@ -18610,7 +18610,7 @@
         <v>13.5087728500366</v>
       </c>
       <c r="G629" t="n">
-        <v>8.30623912811279</v>
+        <v>8.30624008178711</v>
       </c>
       <c r="H629" t="n">
         <v>1127514</v>
@@ -18900,7 +18900,7 @@
         <v>13.0568428039551</v>
       </c>
       <c r="G639" t="n">
-        <v>8.02835750579834</v>
+        <v>8.02835655212402</v>
       </c>
       <c r="H639" t="n">
         <v>791017</v>
@@ -18929,7 +18929,7 @@
         <v>13.0863170623779</v>
       </c>
       <c r="G640" t="n">
-        <v>8.04648113250732</v>
+        <v>8.04648017883301</v>
       </c>
       <c r="H640" t="n">
         <v>513512</v>
@@ -18987,7 +18987,7 @@
         <v>13.1059656143188</v>
       </c>
       <c r="G642" t="n">
-        <v>8.05856132507324</v>
+        <v>8.05856227874756</v>
       </c>
       <c r="H642" t="n">
         <v>447362</v>
@@ -19016,7 +19016,7 @@
         <v>13.3663167953491</v>
       </c>
       <c r="G643" t="n">
-        <v>8.21864604949951</v>
+        <v>8.2186450958252</v>
       </c>
       <c r="H643" t="n">
         <v>497096</v>
@@ -19045,7 +19045,7 @@
         <v>13.5087728500366</v>
       </c>
       <c r="G644" t="n">
-        <v>8.30623912811279</v>
+        <v>8.30624008178711</v>
       </c>
       <c r="H644" t="n">
         <v>823183</v>
@@ -19161,7 +19161,7 @@
         <v>12.781756401062</v>
       </c>
       <c r="G648" t="n">
-        <v>7.85921239852905</v>
+        <v>7.85921287536621</v>
       </c>
       <c r="H648" t="n">
         <v>1344757</v>
@@ -19190,7 +19190,7 @@
         <v>12.9193000793457</v>
       </c>
       <c r="G649" t="n">
-        <v>7.94378519058228</v>
+        <v>7.94378566741943</v>
       </c>
       <c r="H649" t="n">
         <v>930827</v>
@@ -19277,7 +19277,7 @@
         <v>12.9782466888428</v>
       </c>
       <c r="G652" t="n">
-        <v>7.98003101348877</v>
+        <v>7.98003005981445</v>
       </c>
       <c r="H652" t="n">
         <v>796305</v>
@@ -19306,7 +19306,7 @@
         <v>12.9880714416504</v>
       </c>
       <c r="G653" t="n">
-        <v>7.9860725402832</v>
+        <v>7.98607206344604</v>
       </c>
       <c r="H653" t="n">
         <v>455817</v>
@@ -19335,7 +19335,7 @@
         <v>13.1649141311646</v>
       </c>
       <c r="G654" t="n">
-        <v>8.09480762481689</v>
+        <v>8.09480857849121</v>
       </c>
       <c r="H654" t="n">
         <v>623074</v>
@@ -19393,7 +19393,7 @@
         <v>13.9508790969849</v>
       </c>
       <c r="G656" t="n">
-        <v>8.57807922363281</v>
+        <v>8.57808017730713</v>
       </c>
       <c r="H656" t="n">
         <v>3419024</v>
@@ -19422,7 +19422,7 @@
         <v>13.8329839706421</v>
       </c>
       <c r="G657" t="n">
-        <v>8.50558948516846</v>
+        <v>8.50558853149414</v>
       </c>
       <c r="H657" t="n">
         <v>1551786</v>
@@ -19451,7 +19451,7 @@
         <v>13.8919305801392</v>
       </c>
       <c r="G658" t="n">
-        <v>8.54183292388916</v>
+        <v>8.54183387756348</v>
       </c>
       <c r="H658" t="n">
         <v>938616</v>
@@ -19625,7 +19625,7 @@
         <v>14.0884227752686</v>
       </c>
       <c r="G664" t="n">
-        <v>8.66265296936035</v>
+        <v>8.66265392303467</v>
       </c>
       <c r="H664" t="n">
         <v>1112152</v>
@@ -19741,7 +19741,7 @@
         <v>14.0392999649048</v>
       </c>
       <c r="G668" t="n">
-        <v>8.63244819641113</v>
+        <v>8.63244915008545</v>
       </c>
       <c r="H668" t="n">
         <v>1718758</v>
@@ -19799,7 +19799,7 @@
         <v>14.05894947052</v>
       </c>
       <c r="G670" t="n">
-        <v>8.64453125</v>
+        <v>8.64453029632568</v>
       </c>
       <c r="H670" t="n">
         <v>1211547</v>
@@ -19886,7 +19886,7 @@
         <v>14.206316947937</v>
       </c>
       <c r="G673" t="n">
-        <v>8.73514270782471</v>
+        <v>8.73514175415039</v>
       </c>
       <c r="H673" t="n">
         <v>734391</v>
@@ -19944,7 +19944,7 @@
         <v>14.1228084564209</v>
       </c>
       <c r="G675" t="n">
-        <v>8.68379592895508</v>
+        <v>8.68379497528076</v>
       </c>
       <c r="H675" t="n">
         <v>358524</v>
@@ -19973,7 +19973,7 @@
         <v>14.1277208328247</v>
       </c>
       <c r="G676" t="n">
-        <v>8.68681716918945</v>
+        <v>8.68681621551514</v>
       </c>
       <c r="H676" t="n">
         <v>551485</v>
@@ -20031,7 +20031,7 @@
         <v>13.8919305801392</v>
       </c>
       <c r="G678" t="n">
-        <v>8.54183292388916</v>
+        <v>8.54183387756348</v>
       </c>
       <c r="H678" t="n">
         <v>862478</v>
@@ -20118,7 +20118,7 @@
         <v>13.4498262405396</v>
       </c>
       <c r="G681" t="n">
-        <v>8.26999378204346</v>
+        <v>8.26999473571777</v>
       </c>
       <c r="H681" t="n">
         <v>931832</v>
@@ -20176,7 +20176,7 @@
         <v>13.3171939849854</v>
       </c>
       <c r="G683" t="n">
-        <v>8.18844127655029</v>
+        <v>8.18844223022461</v>
       </c>
       <c r="H683" t="n">
         <v>976272</v>
@@ -20321,7 +20321,7 @@
         <v>13.5333347320557</v>
       </c>
       <c r="G688" t="n">
-        <v>8.3213415145874</v>
+        <v>8.32134246826172</v>
       </c>
       <c r="H688" t="n">
         <v>604480</v>
@@ -20379,7 +20379,7 @@
         <v>13.3810539245605</v>
       </c>
       <c r="G690" t="n">
-        <v>8.22770690917969</v>
+        <v>8.227707862854</v>
       </c>
       <c r="H690" t="n">
         <v>670224</v>
@@ -20466,7 +20466,7 @@
         <v>13.7347383499146</v>
       </c>
       <c r="G693" t="n">
-        <v>8.4451789855957</v>
+        <v>8.44518089294434</v>
       </c>
       <c r="H693" t="n">
         <v>691896</v>
@@ -20524,7 +20524,7 @@
         <v>13.7543869018555</v>
       </c>
       <c r="G695" t="n">
-        <v>8.45726108551025</v>
+        <v>8.45726203918457</v>
       </c>
       <c r="H695" t="n">
         <v>664477</v>
@@ -20582,7 +20582,7 @@
         <v>13.543158531189</v>
       </c>
       <c r="G697" t="n">
-        <v>8.32738208770752</v>
+        <v>8.32738304138184</v>
       </c>
       <c r="H697" t="n">
         <v>469443</v>
@@ -20611,7 +20611,7 @@
         <v>13.6021070480347</v>
       </c>
       <c r="G698" t="n">
-        <v>8.36362838745117</v>
+        <v>8.36362743377686</v>
       </c>
       <c r="H698" t="n">
         <v>616001</v>
@@ -20669,7 +20669,7 @@
         <v>13.3712291717529</v>
       </c>
       <c r="G700" t="n">
-        <v>8.22166633605957</v>
+        <v>8.22166728973389</v>
       </c>
       <c r="H700" t="n">
         <v>1268049</v>
@@ -20698,7 +20698,7 @@
         <v>12.7719306945801</v>
       </c>
       <c r="G701" t="n">
-        <v>7.85317134857178</v>
+        <v>7.85317087173462</v>
       </c>
       <c r="H701" t="n">
         <v>2658791</v>
@@ -20727,7 +20727,7 @@
         <v>12.6147384643555</v>
       </c>
       <c r="G702" t="n">
-        <v>7.75651741027832</v>
+        <v>7.75651788711548</v>
       </c>
       <c r="H702" t="n">
         <v>1222820</v>
@@ -20756,7 +20756,7 @@
         <v>12.7228078842163</v>
       </c>
       <c r="G703" t="n">
-        <v>7.82296705245972</v>
+        <v>7.82296657562256</v>
       </c>
       <c r="H703" t="n">
         <v>1212601</v>
@@ -20843,7 +20843,7 @@
         <v>12.8898258209229</v>
       </c>
       <c r="G706" t="n">
-        <v>7.92566251754761</v>
+        <v>7.92566347122192</v>
       </c>
       <c r="H706" t="n">
         <v>1486222</v>
@@ -20872,7 +20872,7 @@
         <v>12.5017557144165</v>
       </c>
       <c r="G707" t="n">
-        <v>7.68704652786255</v>
+        <v>7.68704605102539</v>
       </c>
       <c r="H707" t="n">
         <v>2105148</v>
@@ -20901,7 +20901,7 @@
         <v>12.3740358352661</v>
       </c>
       <c r="G708" t="n">
-        <v>7.60851526260376</v>
+        <v>7.6085147857666</v>
       </c>
       <c r="H708" t="n">
         <v>1139456</v>
@@ -20930,7 +20930,7 @@
         <v>12.3838605880737</v>
       </c>
       <c r="G709" t="n">
-        <v>7.61455726623535</v>
+        <v>7.61455583572388</v>
       </c>
       <c r="H709" t="n">
         <v>1467022</v>
@@ -20959,7 +20959,7 @@
         <v>11.9270191192627</v>
       </c>
       <c r="G710" t="n">
-        <v>7.33365488052368</v>
+        <v>7.33365440368652</v>
       </c>
       <c r="H710" t="n">
         <v>1711773</v>
@@ -20988,7 +20988,7 @@
         <v>11.8877201080322</v>
       </c>
       <c r="G711" t="n">
-        <v>7.30949020385742</v>
+        <v>7.30949068069458</v>
       </c>
       <c r="H711" t="n">
         <v>1181386</v>
@@ -21017,7 +21017,7 @@
         <v>11.7796497344971</v>
       </c>
       <c r="G712" t="n">
-        <v>7.24304008483887</v>
+        <v>7.24304056167603</v>
       </c>
       <c r="H712" t="n">
         <v>942204</v>
@@ -21046,7 +21046,7 @@
         <v>12.0792989730835</v>
       </c>
       <c r="G713" t="n">
-        <v>7.42728853225708</v>
+        <v>7.42728805541992</v>
       </c>
       <c r="H713" t="n">
         <v>671049</v>
@@ -21075,7 +21075,7 @@
         <v>11.8582468032837</v>
       </c>
       <c r="G714" t="n">
-        <v>7.2913670539856</v>
+        <v>7.29136753082275</v>
       </c>
       <c r="H714" t="n">
         <v>636891</v>
@@ -21104,7 +21104,7 @@
         <v>11.5585975646973</v>
       </c>
       <c r="G715" t="n">
-        <v>7.10712051391602</v>
+        <v>7.10712099075317</v>
       </c>
       <c r="H715" t="n">
         <v>1354953</v>
@@ -21133,7 +21133,7 @@
         <v>11.3866682052612</v>
       </c>
       <c r="G716" t="n">
-        <v>7.00140476226807</v>
+        <v>7.00140571594238</v>
       </c>
       <c r="H716" t="n">
         <v>1329088</v>
@@ -21191,7 +21191,7 @@
         <v>11.0722818374634</v>
       </c>
       <c r="G718" t="n">
-        <v>6.80809640884399</v>
+        <v>6.80809545516968</v>
       </c>
       <c r="H718" t="n">
         <v>1182294</v>
@@ -21220,7 +21220,7 @@
         <v>10.8610544204712</v>
       </c>
       <c r="G719" t="n">
-        <v>6.6782169342041</v>
+        <v>6.67821645736694</v>
       </c>
       <c r="H719" t="n">
         <v>846145</v>
@@ -21249,7 +21249,7 @@
         <v>10.9101762771606</v>
       </c>
       <c r="G720" t="n">
-        <v>6.708420753479</v>
+        <v>6.70842027664185</v>
       </c>
       <c r="H720" t="n">
         <v>1149839</v>
@@ -21307,7 +21307,7 @@
         <v>10.6940355300903</v>
       </c>
       <c r="G722" t="n">
-        <v>6.57552051544189</v>
+        <v>6.57552099227905</v>
       </c>
       <c r="H722" t="n">
         <v>1972665</v>
@@ -21365,7 +21365,7 @@
         <v>10.6940355300903</v>
       </c>
       <c r="G724" t="n">
-        <v>6.57552051544189</v>
+        <v>6.57552099227905</v>
       </c>
       <c r="H724" t="n">
         <v>1070921</v>
@@ -21452,7 +21452,7 @@
         <v>10.6498260498047</v>
       </c>
       <c r="G727" t="n">
-        <v>6.54833698272705</v>
+        <v>6.54833745956421</v>
       </c>
       <c r="H727" t="n">
         <v>756757</v>
@@ -21481,7 +21481,7 @@
         <v>10.6645622253418</v>
       </c>
       <c r="G728" t="n">
-        <v>6.55739879608154</v>
+        <v>6.55739784240723</v>
       </c>
       <c r="H728" t="n">
         <v>799558</v>
@@ -21568,7 +21568,7 @@
         <v>10.6989479064941</v>
       </c>
       <c r="G731" t="n">
-        <v>6.57854080200195</v>
+        <v>6.57854032516479</v>
       </c>
       <c r="H731" t="n">
         <v>1805422</v>
@@ -21626,7 +21626,7 @@
         <v>10.6694746017456</v>
       </c>
       <c r="G733" t="n">
-        <v>6.5604190826416</v>
+        <v>6.56041860580444</v>
       </c>
       <c r="H733" t="n">
         <v>731419</v>
@@ -21655,7 +21655,7 @@
         <v>10.6989479064941</v>
       </c>
       <c r="G734" t="n">
-        <v>6.57854080200195</v>
+        <v>6.57854032516479</v>
       </c>
       <c r="H734" t="n">
         <v>1181605</v>
@@ -21713,7 +21713,7 @@
         <v>10.3796501159668</v>
       </c>
       <c r="G736" t="n">
-        <v>6.38221168518066</v>
+        <v>6.38221263885498</v>
       </c>
       <c r="H736" t="n">
         <v>1185830</v>
@@ -21771,7 +21771,7 @@
         <v>10.1684217453003</v>
       </c>
       <c r="G738" t="n">
-        <v>6.25233268737793</v>
+        <v>6.25233316421509</v>
       </c>
       <c r="H738" t="n">
         <v>988440</v>
@@ -21945,7 +21945,7 @@
         <v>10.841404914856</v>
       </c>
       <c r="G744" t="n">
-        <v>6.66613435745239</v>
+        <v>6.66613483428955</v>
       </c>
       <c r="H744" t="n">
         <v>513660</v>
@@ -21974,7 +21974,7 @@
         <v>10.772632598877</v>
       </c>
       <c r="G745" t="n">
-        <v>6.6238489151001</v>
+        <v>6.62384939193726</v>
       </c>
       <c r="H745" t="n">
         <v>882742</v>
@@ -22003,7 +22003,7 @@
         <v>10.6645622253418</v>
       </c>
       <c r="G746" t="n">
-        <v>6.55739879608154</v>
+        <v>6.55739784240723</v>
       </c>
       <c r="H746" t="n">
         <v>587515</v>
@@ -22032,7 +22032,7 @@
         <v>11.0919313430786</v>
       </c>
       <c r="G747" t="n">
-        <v>6.82017803192139</v>
+        <v>6.82017755508423</v>
       </c>
       <c r="H747" t="n">
         <v>1455653</v>
@@ -22061,7 +22061,7 @@
         <v>10.8266677856445</v>
       </c>
       <c r="G748" t="n">
-        <v>6.65707445144653</v>
+        <v>6.65707397460938</v>
       </c>
       <c r="H748" t="n">
         <v>933390</v>
@@ -22090,7 +22090,7 @@
         <v>10.8266677856445</v>
       </c>
       <c r="G749" t="n">
-        <v>6.65707445144653</v>
+        <v>6.65707397460938</v>
       </c>
       <c r="H749" t="n">
         <v>667406</v>
@@ -22148,7 +22148,7 @@
         <v>10.5712289810181</v>
       </c>
       <c r="G751" t="n">
-        <v>6.50001001358032</v>
+        <v>6.50001049041748</v>
       </c>
       <c r="H751" t="n">
         <v>1276602</v>
@@ -22177,7 +22177,7 @@
         <v>10.3059663772583</v>
       </c>
       <c r="G752" t="n">
-        <v>6.33690547943115</v>
+        <v>6.33690500259399</v>
       </c>
       <c r="H752" t="n">
         <v>1025160</v>
@@ -22206,7 +22206,7 @@
         <v>10.3354396820068</v>
       </c>
       <c r="G753" t="n">
-        <v>6.35502815246582</v>
+        <v>6.35502767562866</v>
       </c>
       <c r="H753" t="n">
         <v>780315</v>
@@ -22235,7 +22235,7 @@
         <v>10.6743869781494</v>
       </c>
       <c r="G754" t="n">
-        <v>6.5634388923645</v>
+        <v>6.56343936920166</v>
       </c>
       <c r="H754" t="n">
         <v>1537323</v>
@@ -22322,7 +22322,7 @@
         <v>10.5663166046143</v>
       </c>
       <c r="G757" t="n">
-        <v>6.49698829650879</v>
+        <v>6.49698925018311</v>
       </c>
       <c r="H757" t="n">
         <v>910578</v>
@@ -22351,7 +22351,7 @@
         <v>9.90807056427002</v>
       </c>
       <c r="G758" t="n">
-        <v>6.09224891662598</v>
+        <v>6.09224843978882</v>
       </c>
       <c r="H758" t="n">
         <v>2809051</v>
@@ -22438,7 +22438,7 @@
         <v>9.44729900360107</v>
       </c>
       <c r="G761" t="n">
-        <v>5.80892992019653</v>
+        <v>5.80893087387085</v>
       </c>
       <c r="H761" t="n">
         <v>1380952</v>
@@ -22467,7 +22467,7 @@
         <v>9.14863204956055</v>
       </c>
       <c r="G762" t="n">
-        <v>5.62528800964355</v>
+        <v>5.6252875328064</v>
       </c>
       <c r="H762" t="n">
         <v>1122387</v>
@@ -22496,7 +22496,7 @@
         <v>9.36673831939697</v>
       </c>
       <c r="G763" t="n">
-        <v>5.75939559936523</v>
+        <v>5.75939607620239</v>
       </c>
       <c r="H763" t="n">
         <v>942366</v>
@@ -22583,7 +22583,7 @@
         <v>9.8167028427124</v>
       </c>
       <c r="G766" t="n">
-        <v>6.03606939315796</v>
+        <v>6.0360689163208</v>
       </c>
       <c r="H766" t="n">
         <v>2352783</v>
@@ -22641,7 +22641,7 @@
         <v>10.1733341217041</v>
       </c>
       <c r="G768" t="n">
-        <v>6.2553539276123</v>
+        <v>6.25535297393799</v>
       </c>
       <c r="H768" t="n">
         <v>1293330</v>
@@ -22699,7 +22699,7 @@
         <v>9.97193145751953</v>
       </c>
       <c r="G770" t="n">
-        <v>6.13151550292969</v>
+        <v>6.13151502609253</v>
       </c>
       <c r="H770" t="n">
         <v>1780381</v>
@@ -22728,7 +22728,7 @@
         <v>10.1291236877441</v>
       </c>
       <c r="G771" t="n">
-        <v>6.22816944122314</v>
+        <v>6.22816896438599</v>
       </c>
       <c r="H771" t="n">
         <v>1172711</v>
@@ -22757,7 +22757,7 @@
         <v>10.1192989349365</v>
       </c>
       <c r="G772" t="n">
-        <v>6.22212791442871</v>
+        <v>6.22212839126587</v>
       </c>
       <c r="H772" t="n">
         <v>1238501</v>
@@ -22786,7 +22786,7 @@
         <v>9.84421062469482</v>
       </c>
       <c r="G773" t="n">
-        <v>6.05298185348511</v>
+        <v>6.05298280715942</v>
       </c>
       <c r="H773" t="n">
         <v>1856324</v>
@@ -22844,7 +22844,7 @@
         <v>9.84912395477295</v>
       </c>
       <c r="G775" t="n">
-        <v>6.05600452423096</v>
+        <v>6.05600357055664</v>
       </c>
       <c r="H775" t="n">
         <v>1140745</v>
@@ -22873,7 +22873,7 @@
         <v>9.93754482269287</v>
       </c>
       <c r="G776" t="n">
-        <v>6.11037111282349</v>
+        <v>6.1103720664978</v>
       </c>
       <c r="H776" t="n">
         <v>1298414</v>
@@ -22902,7 +22902,7 @@
         <v>9.8884220123291</v>
       </c>
       <c r="G777" t="n">
-        <v>6.08016729354858</v>
+        <v>6.08016681671143</v>
       </c>
       <c r="H777" t="n">
         <v>823537</v>
@@ -22931,7 +22931,7 @@
         <v>9.70470333099365</v>
       </c>
       <c r="G778" t="n">
-        <v>5.96720361709595</v>
+        <v>5.96720266342163</v>
       </c>
       <c r="H778" t="n">
         <v>1348415</v>
@@ -22960,7 +22960,7 @@
         <v>9.61431694030762</v>
       </c>
       <c r="G779" t="n">
-        <v>5.9116268157959</v>
+        <v>5.91162586212158</v>
       </c>
       <c r="H779" t="n">
         <v>928126</v>
@@ -22989,7 +22989,7 @@
         <v>10.3452644348145</v>
       </c>
       <c r="G780" t="n">
-        <v>6.3610692024231</v>
+        <v>6.36107015609741</v>
       </c>
       <c r="H780" t="n">
         <v>4852445</v>
@@ -23018,7 +23018,7 @@
         <v>10.772632598877</v>
       </c>
       <c r="G781" t="n">
-        <v>6.6238489151001</v>
+        <v>6.62384939193726</v>
       </c>
       <c r="H781" t="n">
         <v>3403879</v>
@@ -23047,7 +23047,7 @@
         <v>10.8905267715454</v>
       </c>
       <c r="G782" t="n">
-        <v>6.69633817672729</v>
+        <v>6.69633865356445</v>
       </c>
       <c r="H782" t="n">
         <v>2315439</v>
@@ -23105,7 +23105,7 @@
         <v>11.0428075790405</v>
       </c>
       <c r="G784" t="n">
-        <v>6.78997325897217</v>
+        <v>6.78997278213501</v>
       </c>
       <c r="H784" t="n">
         <v>1793049</v>
@@ -23134,7 +23134,7 @@
         <v>10.8757905960083</v>
       </c>
       <c r="G785" t="n">
-        <v>6.68727874755859</v>
+        <v>6.68727779388428</v>
       </c>
       <c r="H785" t="n">
         <v>2086028</v>
@@ -23163,7 +23163,7 @@
         <v>10.9200010299683</v>
       </c>
       <c r="G786" t="n">
-        <v>6.71446228027344</v>
+        <v>6.7144627571106</v>
       </c>
       <c r="H786" t="n">
         <v>1140529</v>
@@ -23221,7 +23221,7 @@
         <v>10.9789476394653</v>
       </c>
       <c r="G788" t="n">
-        <v>6.75070714950562</v>
+        <v>6.75070667266846</v>
       </c>
       <c r="H788" t="n">
         <v>1274964</v>
@@ -23308,7 +23308,7 @@
         <v>10.728422164917</v>
       </c>
       <c r="G791" t="n">
-        <v>6.59666347503662</v>
+        <v>6.59666442871094</v>
       </c>
       <c r="H791" t="n">
         <v>1039081</v>
@@ -23337,7 +23337,7 @@
         <v>11.1557912826538</v>
       </c>
       <c r="G792" t="n">
-        <v>6.85944366455078</v>
+        <v>6.8594446182251</v>
       </c>
       <c r="H792" t="n">
         <v>1716177</v>
@@ -23366,7 +23366,7 @@
         <v>11.4259662628174</v>
       </c>
       <c r="G793" t="n">
-        <v>7.02556848526001</v>
+        <v>7.02556896209717</v>
       </c>
       <c r="H793" t="n">
         <v>1596679</v>
@@ -23424,7 +23424,7 @@
         <v>11.6224565505981</v>
       </c>
       <c r="G795" t="n">
-        <v>7.14638614654541</v>
+        <v>7.14638662338257</v>
       </c>
       <c r="H795" t="n">
         <v>3918010</v>
@@ -23453,7 +23453,7 @@
         <v>11.8533344268799</v>
       </c>
       <c r="G796" t="n">
-        <v>7.28834772109985</v>
+        <v>7.2883472442627</v>
       </c>
       <c r="H796" t="n">
         <v>1882919</v>
@@ -23482,7 +23482,7 @@
         <v>12.0252637863159</v>
       </c>
       <c r="G797" t="n">
-        <v>7.39406299591064</v>
+        <v>7.3940634727478</v>
       </c>
       <c r="H797" t="n">
         <v>1390523</v>
@@ -23511,7 +23511,7 @@
         <v>12.005615234375</v>
       </c>
       <c r="G798" t="n">
-        <v>7.38198041915894</v>
+        <v>7.38198184967041</v>
       </c>
       <c r="H798" t="n">
         <v>1031140</v>
@@ -23598,7 +23598,7 @@
         <v>12.1382465362549</v>
       </c>
       <c r="G801" t="n">
-        <v>7.46353387832642</v>
+        <v>7.4635329246521</v>
       </c>
       <c r="H801" t="n">
         <v>1251759</v>
@@ -23627,7 +23627,7 @@
         <v>12.24631690979</v>
       </c>
       <c r="G802" t="n">
-        <v>7.52998304367065</v>
+        <v>7.52998352050781</v>
       </c>
       <c r="H802" t="n">
         <v>832678</v>
@@ -23685,7 +23685,7 @@
         <v>12.1480712890625</v>
       </c>
       <c r="G804" t="n">
-        <v>7.46957445144653</v>
+        <v>7.46957397460938</v>
       </c>
       <c r="H804" t="n">
         <v>1930594</v>
@@ -23714,7 +23714,7 @@
         <v>12.6294746398926</v>
       </c>
       <c r="G805" t="n">
-        <v>7.76557922363281</v>
+        <v>7.7655782699585</v>
       </c>
       <c r="H805" t="n">
         <v>3106680</v>
@@ -23772,7 +23772,7 @@
         <v>12.6736850738525</v>
       </c>
       <c r="G807" t="n">
-        <v>7.7927622795105</v>
+        <v>7.79276132583618</v>
       </c>
       <c r="H807" t="n">
         <v>1099338</v>
@@ -23801,7 +23801,7 @@
         <v>12.997896194458</v>
       </c>
       <c r="G808" t="n">
-        <v>7.992112159729</v>
+        <v>7.99211263656616</v>
       </c>
       <c r="H808" t="n">
         <v>2783109</v>
@@ -23830,7 +23830,7 @@
         <v>12.9831590652466</v>
       </c>
       <c r="G809" t="n">
-        <v>7.98305130004883</v>
+        <v>7.98304986953735</v>
       </c>
       <c r="H809" t="n">
         <v>3930417</v>
@@ -23888,7 +23888,7 @@
         <v>13.5726327896118</v>
       </c>
       <c r="G811" t="n">
-        <v>8.34550476074219</v>
+        <v>8.3455057144165</v>
       </c>
       <c r="H811" t="n">
         <v>5506554</v>
@@ -23917,7 +23917,7 @@
         <v>13.5726327896118</v>
       </c>
       <c r="G812" t="n">
-        <v>8.34550476074219</v>
+        <v>8.3455057144165</v>
       </c>
       <c r="H812" t="n">
         <v>2655732</v>
@@ -23975,7 +23975,7 @@
         <v>14.1228084564209</v>
       </c>
       <c r="G814" t="n">
-        <v>8.68379592895508</v>
+        <v>8.68379497528076</v>
       </c>
       <c r="H814" t="n">
         <v>3210111</v>
@@ -24004,7 +24004,7 @@
         <v>14.2112302780151</v>
       </c>
       <c r="G815" t="n">
-        <v>8.7381649017334</v>
+        <v>8.73816394805908</v>
       </c>
       <c r="H815" t="n">
         <v>2191230</v>
@@ -24033,7 +24033,7 @@
         <v>14.3143873214722</v>
       </c>
       <c r="G816" t="n">
-        <v>8.80159378051758</v>
+        <v>8.80159282684326</v>
       </c>
       <c r="H816" t="n">
         <v>4546055</v>
@@ -24091,7 +24091,7 @@
         <v>14.8449144363403</v>
       </c>
       <c r="G818" t="n">
-        <v>9.1278018951416</v>
+        <v>9.12780284881592</v>
       </c>
       <c r="H818" t="n">
         <v>2384223</v>
@@ -24120,7 +24120,7 @@
         <v>14.5894746780396</v>
       </c>
       <c r="G819" t="n">
-        <v>8.97073936462402</v>
+        <v>8.97073841094971</v>
       </c>
       <c r="H819" t="n">
         <v>2867556</v>
@@ -24178,7 +24178,7 @@
         <v>14.3094749450684</v>
       </c>
       <c r="G821" t="n">
-        <v>8.7985725402832</v>
+        <v>8.79857349395752</v>
       </c>
       <c r="H821" t="n">
         <v>1837891</v>
@@ -24236,7 +24236,7 @@
         <v>14.5403518676758</v>
       </c>
       <c r="G823" t="n">
-        <v>8.94053268432617</v>
+        <v>8.94053363800049</v>
       </c>
       <c r="H823" t="n">
         <v>1306999</v>
@@ -24323,7 +24323,7 @@
         <v>14.8842115402222</v>
       </c>
       <c r="G826" t="n">
-        <v>9.1519660949707</v>
+        <v>9.15196514129639</v>
       </c>
       <c r="H826" t="n">
         <v>1783675</v>
@@ -24381,7 +24381,7 @@
         <v>15.0561418533325</v>
       </c>
       <c r="G828" t="n">
-        <v>9.25768184661865</v>
+        <v>9.25768280029297</v>
       </c>
       <c r="H828" t="n">
         <v>1567073</v>
@@ -24439,7 +24439,7 @@
         <v>15.3950891494751</v>
       </c>
       <c r="G830" t="n">
-        <v>9.46609115600586</v>
+        <v>9.46609210968018</v>
       </c>
       <c r="H830" t="n">
         <v>2042130</v>
@@ -24468,7 +24468,7 @@
         <v>15.5571947097778</v>
       </c>
       <c r="G831" t="n">
-        <v>9.56576728820801</v>
+        <v>9.56576824188232</v>
       </c>
       <c r="H831" t="n">
         <v>2487517</v>
@@ -24642,7 +24642,7 @@
         <v>16.200704574585</v>
       </c>
       <c r="G837" t="n">
-        <v>9.96144676208496</v>
+        <v>9.96144771575928</v>
       </c>
       <c r="H837" t="n">
         <v>2519804</v>
@@ -24671,7 +24671,7 @@
         <v>16.6428089141846</v>
       </c>
       <c r="G838" t="n">
-        <v>10.233286857605</v>
+        <v>10.2332878112793</v>
       </c>
       <c r="H838" t="n">
         <v>4330671</v>
@@ -24729,7 +24729,7 @@
         <v>16.7017555236816</v>
       </c>
       <c r="G840" t="n">
-        <v>10.26953125</v>
+        <v>10.2695322036743</v>
       </c>
       <c r="H840" t="n">
         <v>2063718</v>
@@ -24816,7 +24816,7 @@
         <v>17.3059673309326</v>
       </c>
       <c r="G843" t="n">
-        <v>10.6410474777222</v>
+        <v>10.6410484313965</v>
       </c>
       <c r="H843" t="n">
         <v>3096815</v>
@@ -24874,7 +24874,7 @@
         <v>17.6596508026123</v>
       </c>
       <c r="G845" t="n">
-        <v>10.8585195541382</v>
+        <v>10.8585205078125</v>
       </c>
       <c r="H845" t="n">
         <v>3965629</v>
@@ -24932,7 +24932,7 @@
         <v>17.6350898742676</v>
       </c>
       <c r="G847" t="n">
-        <v>10.8434200286865</v>
+        <v>10.8434171676636</v>
       </c>
       <c r="H847" t="n">
         <v>2467254</v>
@@ -24961,7 +24961,7 @@
         <v>17.4533348083496</v>
       </c>
       <c r="G848" t="n">
-        <v>10.7316608428955</v>
+        <v>10.7316617965698</v>
       </c>
       <c r="H848" t="n">
         <v>1995771</v>
@@ -24990,7 +24990,7 @@
         <v>17.3059673309326</v>
       </c>
       <c r="G849" t="n">
-        <v>10.6410474777222</v>
+        <v>10.6410484313965</v>
       </c>
       <c r="H849" t="n">
         <v>3743215</v>
@@ -25019,7 +25019,7 @@
         <v>17.3747386932373</v>
       </c>
       <c r="G850" t="n">
-        <v>10.6833333969116</v>
+        <v>10.6833343505859</v>
       </c>
       <c r="H850" t="n">
         <v>2672705</v>
@@ -25164,7 +25164,7 @@
         <v>16.9080715179443</v>
       </c>
       <c r="G855" t="n">
-        <v>10.3963918685913</v>
+        <v>10.396390914917</v>
       </c>
       <c r="H855" t="n">
         <v>2143097</v>
@@ -25193,7 +25193,7 @@
         <v>16.9080715179443</v>
       </c>
       <c r="G856" t="n">
-        <v>10.3963918685913</v>
+        <v>10.396390914917</v>
       </c>
       <c r="H856" t="n">
         <v>2511580</v>
@@ -25222,7 +25222,7 @@
         <v>17.0898265838623</v>
       </c>
       <c r="G857" t="n">
-        <v>10.5081491470337</v>
+        <v>10.5081481933594</v>
       </c>
       <c r="H857" t="n">
         <v>2326049</v>
@@ -25309,7 +25309,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>10.179295539856</v>
+        <v>10.1792964935303</v>
       </c>
       <c r="H860" t="n">
         <v>2899010</v>
@@ -25338,7 +25338,7 @@
         <v>15.3950004577637</v>
       </c>
       <c r="G861" t="n">
-        <v>10.1759901046753</v>
+        <v>10.1759910583496</v>
       </c>
       <c r="H861" t="n">
         <v>1694296</v>
@@ -25425,7 +25425,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G864" t="n">
-        <v>9.8091402053833</v>
+        <v>9.80913925170898</v>
       </c>
       <c r="H864" t="n">
         <v>1371607</v>
@@ -25541,7 +25541,7 @@
         <v>14.875</v>
       </c>
       <c r="G868" t="n">
-        <v>9.83227348327637</v>
+        <v>9.83227443695068</v>
       </c>
       <c r="H868" t="n">
         <v>2018019</v>
@@ -25657,7 +25657,7 @@
         <v>14.9049997329712</v>
       </c>
       <c r="G872" t="n">
-        <v>9.8521032333374</v>
+        <v>9.85210418701172</v>
       </c>
       <c r="H872" t="n">
         <v>2298338</v>
@@ -25686,7 +25686,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G873" t="n">
-        <v>9.91159343719482</v>
+        <v>9.91159439086914</v>
       </c>
       <c r="H873" t="n">
         <v>1406400</v>
@@ -25715,7 +25715,7 @@
         <v>15.0050001144409</v>
       </c>
       <c r="G874" t="n">
-        <v>9.91820335388184</v>
+        <v>9.91820240020752</v>
       </c>
       <c r="H874" t="n">
         <v>829242</v>
@@ -25744,7 +25744,7 @@
         <v>15.1700000762939</v>
       </c>
       <c r="G875" t="n">
-        <v>10.0272665023804</v>
+        <v>10.0272674560547</v>
       </c>
       <c r="H875" t="n">
         <v>1951808</v>
@@ -25773,7 +25773,7 @@
         <v>15.4300003051758</v>
       </c>
       <c r="G876" t="n">
-        <v>10.1991262435913</v>
+        <v>10.199125289917</v>
       </c>
       <c r="H876" t="n">
         <v>1963251</v>
@@ -25860,7 +25860,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G879" t="n">
-        <v>10.7080917358398</v>
+        <v>10.7080907821655</v>
       </c>
       <c r="H879" t="n">
         <v>1650989</v>
@@ -25918,7 +25918,7 @@
         <v>16.5750007629395</v>
       </c>
       <c r="G881" t="n">
-        <v>10.9559640884399</v>
+        <v>10.9559631347656</v>
       </c>
       <c r="H881" t="n">
         <v>1757491</v>
@@ -25947,7 +25947,7 @@
         <v>16.7749996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>11.0881614685059</v>
+        <v>11.0881605148315</v>
       </c>
       <c r="H882" t="n">
         <v>2313831</v>
@@ -26005,7 +26005,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G884" t="n">
-        <v>11.1707849502563</v>
+        <v>11.1707859039307</v>
       </c>
       <c r="H884" t="n">
         <v>1303774</v>
@@ -26034,7 +26034,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G885" t="n">
-        <v>11.0451974868774</v>
+        <v>11.0451965332031</v>
       </c>
       <c r="H885" t="n">
         <v>1304394</v>
@@ -26092,7 +26092,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G887" t="n">
-        <v>11.1707849502563</v>
+        <v>11.1707859039307</v>
       </c>
       <c r="H887" t="n">
         <v>1135163</v>
@@ -26150,7 +26150,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G889" t="n">
-        <v>11.2302751541138</v>
+        <v>11.2302742004395</v>
       </c>
       <c r="H889" t="n">
         <v>1471588</v>
@@ -26208,7 +26208,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G891" t="n">
-        <v>11.3657779693604</v>
+        <v>11.3657789230347</v>
       </c>
       <c r="H891" t="n">
         <v>1466058</v>
@@ -26266,7 +26266,7 @@
         <v>17.4449996948242</v>
       </c>
       <c r="G893" t="n">
-        <v>11.53102684021</v>
+        <v>11.5310258865356</v>
       </c>
       <c r="H893" t="n">
         <v>1460924</v>
@@ -26295,7 +26295,7 @@
         <v>17.1949996948242</v>
       </c>
       <c r="G894" t="n">
-        <v>11.3657779693604</v>
+        <v>11.3657789230347</v>
       </c>
       <c r="H894" t="n">
         <v>1306908</v>
@@ -26324,7 +26324,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G895" t="n">
-        <v>11.6004304885864</v>
+        <v>11.6004295349121</v>
       </c>
       <c r="H895" t="n">
         <v>1998603</v>
@@ -26353,7 +26353,7 @@
         <v>17.4300003051758</v>
       </c>
       <c r="G896" t="n">
-        <v>11.5211124420166</v>
+        <v>11.5211114883423</v>
       </c>
       <c r="H896" t="n">
         <v>1879999</v>
@@ -26440,7 +26440,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G899" t="n">
-        <v>11.7128009796143</v>
+        <v>11.7127990722656</v>
       </c>
       <c r="H899" t="n">
         <v>2830779</v>
@@ -26469,7 +26469,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G900" t="n">
-        <v>11.6665315628052</v>
+        <v>11.6665296554565</v>
       </c>
       <c r="H900" t="n">
         <v>1504634</v>
@@ -26527,7 +26527,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G902" t="n">
-        <v>11.3558645248413</v>
+        <v>11.3558654785156</v>
       </c>
       <c r="H902" t="n">
         <v>1350549</v>
@@ -26556,7 +26556,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G903" t="n">
-        <v>11.1740913391113</v>
+        <v>11.1740922927856</v>
       </c>
       <c r="H903" t="n">
         <v>1696903</v>
@@ -26585,7 +26585,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G904" t="n">
-        <v>11.3789987564087</v>
+        <v>11.378999710083</v>
       </c>
       <c r="H904" t="n">
         <v>986100</v>
@@ -26614,7 +26614,7 @@
         <v>17.3250007629395</v>
       </c>
       <c r="G905" t="n">
-        <v>11.4517087936401</v>
+        <v>11.4517078399658</v>
       </c>
       <c r="H905" t="n">
         <v>1292350</v>
@@ -26701,7 +26701,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G908" t="n">
-        <v>11.4219627380371</v>
+        <v>11.4219646453857</v>
       </c>
       <c r="H908" t="n">
         <v>673027</v>
@@ -26759,7 +26759,7 @@
         <v>16.7099990844727</v>
       </c>
       <c r="G910" t="n">
-        <v>11.0451974868774</v>
+        <v>11.0451965332031</v>
       </c>
       <c r="H910" t="n">
         <v>1699225</v>
@@ -26788,7 +26788,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>11.2038354873657</v>
+        <v>11.2038345336914</v>
       </c>
       <c r="H911" t="n">
         <v>1049475</v>
@@ -26817,7 +26817,7 @@
         <v>17.0900001525879</v>
       </c>
       <c r="G912" t="n">
-        <v>11.2963752746582</v>
+        <v>11.2963743209839</v>
       </c>
       <c r="H912" t="n">
         <v>1340522</v>
@@ -26846,7 +26846,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G913" t="n">
-        <v>11.0253667831421</v>
+        <v>11.0253677368164</v>
       </c>
       <c r="H913" t="n">
         <v>2052281</v>
@@ -26904,7 +26904,7 @@
         <v>16.3950004577637</v>
       </c>
       <c r="G915" t="n">
-        <v>10.8369855880737</v>
+        <v>10.8369846343994</v>
       </c>
       <c r="H915" t="n">
         <v>1121501</v>
@@ -26962,7 +26962,7 @@
         <v>16.6650009155273</v>
       </c>
       <c r="G917" t="n">
-        <v>11.015453338623</v>
+        <v>11.0154523849487</v>
       </c>
       <c r="H917" t="n">
         <v>1039834</v>
@@ -26991,7 +26991,7 @@
         <v>16.0499992370605</v>
       </c>
       <c r="G918" t="n">
-        <v>10.6089401245117</v>
+        <v>10.608941078186</v>
       </c>
       <c r="H918" t="n">
         <v>1434282</v>
@@ -27020,7 +27020,7 @@
         <v>15.75</v>
       </c>
       <c r="G919" t="n">
-        <v>10.41064453125</v>
+        <v>10.4106435775757</v>
       </c>
       <c r="H919" t="n">
         <v>1122984</v>
@@ -27165,7 +27165,7 @@
         <v>15.9200000762939</v>
       </c>
       <c r="G924" t="n">
-        <v>10.5230121612549</v>
+        <v>10.5230112075806</v>
       </c>
       <c r="H924" t="n">
         <v>703446</v>
@@ -27194,7 +27194,7 @@
         <v>16.4050006866455</v>
       </c>
       <c r="G925" t="n">
-        <v>10.8435945510864</v>
+        <v>10.8435955047607</v>
       </c>
       <c r="H925" t="n">
         <v>1161838</v>
@@ -27223,7 +27223,7 @@
         <v>16.3349990844727</v>
       </c>
       <c r="G926" t="n">
-        <v>10.7973251342773</v>
+        <v>10.797324180603</v>
       </c>
       <c r="H926" t="n">
         <v>880812</v>
@@ -27252,7 +27252,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G927" t="n">
-        <v>10.5494518280029</v>
+        <v>10.5494527816772</v>
       </c>
       <c r="H927" t="n">
         <v>789982</v>
@@ -27281,7 +27281,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G928" t="n">
-        <v>10.6816511154175</v>
+        <v>10.6816520690918</v>
       </c>
       <c r="H928" t="n">
         <v>1032866</v>
@@ -27426,7 +27426,7 @@
         <v>16.2849998474121</v>
       </c>
       <c r="G933" t="n">
-        <v>10.7642736434937</v>
+        <v>10.764274597168</v>
       </c>
       <c r="H933" t="n">
         <v>688812</v>
@@ -27484,7 +27484,7 @@
         <v>16.8250007629395</v>
       </c>
       <c r="G935" t="n">
-        <v>11.1212110519409</v>
+        <v>11.1212120056152</v>
       </c>
       <c r="H935" t="n">
         <v>1420610</v>
@@ -27542,7 +27542,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G937" t="n">
-        <v>11.1575651168823</v>
+        <v>11.1575660705566</v>
       </c>
       <c r="H937" t="n">
         <v>960124</v>
@@ -27571,7 +27571,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G938" t="n">
-        <v>11.2765445709229</v>
+        <v>11.2765436172485</v>
       </c>
       <c r="H938" t="n">
         <v>828238</v>
@@ -27658,7 +27658,7 @@
         <v>16.8549995422363</v>
       </c>
       <c r="G941" t="n">
-        <v>11.141040802002</v>
+        <v>11.1410398483276</v>
       </c>
       <c r="H941" t="n">
         <v>938872</v>
@@ -27687,7 +27687,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G942" t="n">
-        <v>11.3162031173706</v>
+        <v>11.3162059783936</v>
       </c>
       <c r="H942" t="n">
         <v>1332392</v>
@@ -27716,7 +27716,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G943" t="n">
-        <v>11.2633266448975</v>
+        <v>11.2633247375488</v>
       </c>
       <c r="H943" t="n">
         <v>957720</v>
@@ -27774,7 +27774,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G945" t="n">
-        <v>11.3823022842407</v>
+        <v>11.382303237915</v>
       </c>
       <c r="H945" t="n">
         <v>1033725</v>
@@ -27803,7 +27803,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G946" t="n">
-        <v>11.573992729187</v>
+        <v>11.5739917755127</v>
       </c>
       <c r="H946" t="n">
         <v>1568795</v>
@@ -27832,7 +27832,7 @@
         <v>17.5149993896484</v>
       </c>
       <c r="G947" t="n">
-        <v>11.5772953033447</v>
+        <v>11.577296257019</v>
       </c>
       <c r="H947" t="n">
         <v>1654133</v>
@@ -27890,7 +27890,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G949" t="n">
-        <v>11.4087429046631</v>
+        <v>11.4087419509888</v>
       </c>
       <c r="H949" t="n">
         <v>795386</v>
@@ -27948,7 +27948,7 @@
         <v>17.1450004577637</v>
       </c>
       <c r="G951" t="n">
-        <v>11.3327302932739</v>
+        <v>11.3327293395996</v>
       </c>
       <c r="H951" t="n">
         <v>604671</v>
@@ -27977,7 +27977,7 @@
         <v>17.2299995422363</v>
       </c>
       <c r="G952" t="n">
-        <v>11.3889141082764</v>
+        <v>11.3889131546021</v>
       </c>
       <c r="H952" t="n">
         <v>560816</v>
@@ -28006,7 +28006,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G953" t="n">
-        <v>11.3823022842407</v>
+        <v>11.382303237915</v>
       </c>
       <c r="H953" t="n">
         <v>879661</v>
@@ -28035,7 +28035,7 @@
         <v>17.1049995422363</v>
       </c>
       <c r="G954" t="n">
-        <v>11.3062877655029</v>
+        <v>11.3062896728516</v>
       </c>
       <c r="H954" t="n">
         <v>1361149</v>
@@ -28151,7 +28151,7 @@
         <v>16.5450000762939</v>
       </c>
       <c r="G958" t="n">
-        <v>10.9361324310303</v>
+        <v>10.9361333847046</v>
       </c>
       <c r="H958" t="n">
         <v>576446</v>
@@ -28180,7 +28180,7 @@
         <v>16.3050003051758</v>
       </c>
       <c r="G959" t="n">
-        <v>10.777494430542</v>
+        <v>10.7774953842163</v>
       </c>
       <c r="H959" t="n">
         <v>1258081</v>
@@ -28267,7 +28267,7 @@
         <v>16.7950000762939</v>
       </c>
       <c r="G962" t="n">
-        <v>11.1013822555542</v>
+        <v>11.1013813018799</v>
       </c>
       <c r="H962" t="n">
         <v>853089</v>
@@ -28325,7 +28325,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G964" t="n">
-        <v>11.2302751541138</v>
+        <v>11.2302742004395</v>
       </c>
       <c r="H964" t="n">
         <v>1011216</v>
@@ -28354,7 +28354,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G965" t="n">
-        <v>11.2699346542358</v>
+        <v>11.2699337005615</v>
       </c>
       <c r="H965" t="n">
         <v>1386276</v>
@@ -28383,7 +28383,7 @@
         <v>17.2450008392334</v>
       </c>
       <c r="G966" t="n">
-        <v>11.3988285064697</v>
+        <v>11.398829460144</v>
       </c>
       <c r="H966" t="n">
         <v>1569694</v>
@@ -28412,7 +28412,7 @@
         <v>17.4249992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>11.5178060531616</v>
+        <v>11.5178050994873</v>
       </c>
       <c r="H967" t="n">
         <v>1475410</v>
@@ -28499,7 +28499,7 @@
         <v>18.1499996185303</v>
       </c>
       <c r="G970" t="n">
-        <v>11.9970264434814</v>
+        <v>11.9970283508301</v>
       </c>
       <c r="H970" t="n">
         <v>2046572</v>
@@ -28528,7 +28528,7 @@
         <v>18.25</v>
       </c>
       <c r="G971" t="n">
-        <v>12.0631256103516</v>
+        <v>12.0631284713745</v>
       </c>
       <c r="H971" t="n">
         <v>1623945</v>
@@ -28557,7 +28557,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G972" t="n">
-        <v>12.0697374343872</v>
+        <v>12.0697364807129</v>
       </c>
       <c r="H972" t="n">
         <v>752467</v>
@@ -28644,7 +28644,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>12.4266719818115</v>
+        <v>12.4266729354858</v>
       </c>
       <c r="H975" t="n">
         <v>2263535</v>
@@ -28673,7 +28673,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G976" t="n">
-        <v>12.1754961013794</v>
+        <v>12.1754951477051</v>
       </c>
       <c r="H976" t="n">
         <v>1812082</v>
@@ -28702,7 +28702,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G977" t="n">
-        <v>12.3010854721069</v>
+        <v>12.3010835647583</v>
       </c>
       <c r="H977" t="n">
         <v>745543</v>
@@ -28731,7 +28731,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G978" t="n">
-        <v>12.4597244262695</v>
+        <v>12.4597234725952</v>
       </c>
       <c r="H978" t="n">
         <v>1415620</v>
@@ -28789,7 +28789,7 @@
         <v>19.8349990844727</v>
       </c>
       <c r="G980" t="n">
-        <v>13.1107997894287</v>
+        <v>13.110800743103</v>
       </c>
       <c r="H980" t="n">
         <v>3040827</v>
@@ -28818,7 +28818,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G981" t="n">
-        <v>13.5834112167358</v>
+        <v>13.5834093093872</v>
       </c>
       <c r="H981" t="n">
         <v>3841058</v>
@@ -28905,7 +28905,7 @@
         <v>21.4300003051758</v>
       </c>
       <c r="G984" t="n">
-        <v>14.1650857925415</v>
+        <v>14.1650867462158</v>
       </c>
       <c r="H984" t="n">
         <v>3055449</v>
@@ -28934,7 +28934,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G985" t="n">
-        <v>14.2774534225464</v>
+        <v>14.2774543762207</v>
       </c>
       <c r="H985" t="n">
         <v>2487850</v>
@@ -28992,7 +28992,7 @@
         <v>22.7600002288818</v>
       </c>
       <c r="G987" t="n">
-        <v>15.0442066192627</v>
+        <v>15.0442056655884</v>
       </c>
       <c r="H987" t="n">
         <v>3472710</v>
@@ -29021,7 +29021,7 @@
         <v>22.4300003051758</v>
       </c>
       <c r="G988" t="n">
-        <v>14.826078414917</v>
+        <v>14.8260774612427</v>
       </c>
       <c r="H988" t="n">
         <v>4467123</v>
@@ -29079,7 +29079,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G990" t="n">
-        <v>15.189624786377</v>
+        <v>15.1896257400513</v>
       </c>
       <c r="H990" t="n">
         <v>2811484</v>
@@ -29137,7 +29137,7 @@
         <v>23.0100002288818</v>
       </c>
       <c r="G992" t="n">
-        <v>15.209454536438</v>
+        <v>15.2094535827637</v>
       </c>
       <c r="H992" t="n">
         <v>2233764</v>
@@ -29166,7 +29166,7 @@
         <v>23.4200000762939</v>
       </c>
       <c r="G993" t="n">
-        <v>15.4804639816284</v>
+        <v>15.4804630279541</v>
       </c>
       <c r="H993" t="n">
         <v>1696088</v>
@@ -29195,7 +29195,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G994" t="n">
-        <v>15.6523208618164</v>
+        <v>15.6523189544678</v>
       </c>
       <c r="H994" t="n">
         <v>2661522</v>
@@ -29224,7 +29224,7 @@
         <v>23.5599994659424</v>
       </c>
       <c r="G995" t="n">
-        <v>15.5730009078979</v>
+        <v>15.5730018615723</v>
       </c>
       <c r="H995" t="n">
         <v>2216885</v>
@@ -29369,7 +29369,7 @@
         <v>22.5799999237061</v>
       </c>
       <c r="G1000" t="n">
-        <v>14.9252271652222</v>
+        <v>14.9252281188965</v>
       </c>
       <c r="H1000" t="n">
         <v>1853018</v>
@@ -29485,7 +29485,7 @@
         <v>21.9500007629395</v>
       </c>
       <c r="G1004" t="n">
-        <v>14.5088024139404</v>
+        <v>14.5088005065918</v>
       </c>
       <c r="H1004" t="n">
         <v>1966184</v>
@@ -29543,7 +29543,7 @@
         <v>21.8299999237061</v>
       </c>
       <c r="G1006" t="n">
-        <v>14.4294815063477</v>
+        <v>14.429482460022</v>
       </c>
       <c r="H1006" t="n">
         <v>954820</v>
@@ -29572,7 +29572,7 @@
         <v>21.5200004577637</v>
       </c>
       <c r="G1007" t="n">
-        <v>14.2245750427246</v>
+        <v>14.2245759963989</v>
       </c>
       <c r="H1007" t="n">
         <v>1573908</v>
@@ -29601,7 +29601,7 @@
         <v>21.8099994659424</v>
       </c>
       <c r="G1008" t="n">
-        <v>14.4162616729736</v>
+        <v>14.4162626266479</v>
       </c>
       <c r="H1008" t="n">
         <v>1305129</v>
@@ -29630,7 +29630,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1009" t="n">
-        <v>14.3567724227905</v>
+        <v>14.3567714691162</v>
       </c>
       <c r="H1009" t="n">
         <v>872237</v>
@@ -29659,7 +29659,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1010" t="n">
-        <v>14.2377939224243</v>
+        <v>14.2377948760986</v>
       </c>
       <c r="H1010" t="n">
         <v>821275</v>
@@ -29746,7 +29746,7 @@
         <v>21.4699993133545</v>
       </c>
       <c r="G1013" t="n">
-        <v>14.1915264129639</v>
+        <v>14.1915245056152</v>
       </c>
       <c r="H1013" t="n">
         <v>539394</v>
@@ -29775,7 +29775,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1014" t="n">
-        <v>14.0130567550659</v>
+        <v>14.0130577087402</v>
       </c>
       <c r="H1014" t="n">
         <v>715340</v>
@@ -29804,7 +29804,7 @@
         <v>21.2800006866455</v>
       </c>
       <c r="G1015" t="n">
-        <v>14.065936088562</v>
+        <v>14.0659370422363</v>
       </c>
       <c r="H1015" t="n">
         <v>934671</v>
@@ -29833,7 +29833,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1016" t="n">
-        <v>14.3105020523071</v>
+        <v>14.3105030059814</v>
       </c>
       <c r="H1016" t="n">
         <v>808769</v>
@@ -29862,7 +29862,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G1017" t="n">
-        <v>14.0262756347656</v>
+        <v>14.0262775421143</v>
       </c>
       <c r="H1017" t="n">
         <v>987673</v>
@@ -29920,7 +29920,7 @@
         <v>21.9099998474121</v>
       </c>
       <c r="G1019" t="n">
-        <v>14.4823617935181</v>
+        <v>14.4823608398438</v>
       </c>
       <c r="H1019" t="n">
         <v>2249213</v>
@@ -29978,7 +29978,7 @@
         <v>23.5499992370605</v>
       </c>
       <c r="G1021" t="n">
-        <v>15.5663909912109</v>
+        <v>15.5663919448853</v>
       </c>
       <c r="H1021" t="n">
         <v>4465059</v>
@@ -30007,7 +30007,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1022" t="n">
-        <v>15.6391010284424</v>
+        <v>15.6391000747681</v>
       </c>
       <c r="H1022" t="n">
         <v>2622801</v>
@@ -30036,7 +30036,7 @@
         <v>23.4300003051758</v>
       </c>
       <c r="G1023" t="n">
-        <v>15.4870700836182</v>
+        <v>15.4870710372925</v>
       </c>
       <c r="H1023" t="n">
         <v>2386544</v>
@@ -30065,7 +30065,7 @@
         <v>23.8400001525879</v>
       </c>
       <c r="G1024" t="n">
-        <v>15.75807762146</v>
+        <v>15.7580766677856</v>
       </c>
       <c r="H1024" t="n">
         <v>1902374</v>
@@ -30123,7 +30123,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1026" t="n">
-        <v>15.6523208618164</v>
+        <v>15.6523189544678</v>
       </c>
       <c r="H1026" t="n">
         <v>1644794</v>
@@ -30152,7 +30152,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1027" t="n">
-        <v>15.6523208618164</v>
+        <v>15.6523189544678</v>
       </c>
       <c r="H1027" t="n">
         <v>947057</v>
@@ -30181,7 +30181,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1028" t="n">
-        <v>15.6787586212158</v>
+        <v>15.6787595748901</v>
       </c>
       <c r="H1028" t="n">
         <v>683874</v>
@@ -30210,7 +30210,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1029" t="n">
-        <v>15.6258821487427</v>
+        <v>15.6258792877197</v>
       </c>
       <c r="H1029" t="n">
         <v>1045403</v>
@@ -30268,7 +30268,7 @@
         <v>24.2700004577637</v>
       </c>
       <c r="G1031" t="n">
-        <v>16.0423069000244</v>
+        <v>16.042308807373</v>
       </c>
       <c r="H1031" t="n">
         <v>2586108</v>
@@ -30297,7 +30297,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1032" t="n">
-        <v>15.599440574646</v>
+        <v>15.5994396209717</v>
       </c>
       <c r="H1032" t="n">
         <v>3349994</v>
@@ -30355,7 +30355,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1034" t="n">
-        <v>15.4672441482544</v>
+        <v>15.4672422409058</v>
       </c>
       <c r="H1034" t="n">
         <v>1824357</v>
@@ -30413,7 +30413,7 @@
         <v>22.9300003051758</v>
       </c>
       <c r="G1036" t="n">
-        <v>15.1565771102905</v>
+        <v>15.1565761566162</v>
       </c>
       <c r="H1036" t="n">
         <v>1474747</v>
@@ -30471,7 +30471,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1038" t="n">
-        <v>14.6872682571411</v>
+        <v>14.6872692108154</v>
       </c>
       <c r="H1038" t="n">
         <v>1267649</v>
@@ -30500,7 +30500,7 @@
         <v>22.8799991607666</v>
       </c>
       <c r="G1039" t="n">
-        <v>15.1235256195068</v>
+        <v>15.1235246658325</v>
       </c>
       <c r="H1039" t="n">
         <v>1665402</v>
@@ -30529,7 +30529,7 @@
         <v>22.9799995422363</v>
       </c>
       <c r="G1040" t="n">
-        <v>15.189624786377</v>
+        <v>15.1896257400513</v>
       </c>
       <c r="H1040" t="n">
         <v>1697631</v>
@@ -30616,7 +30616,7 @@
         <v>23.75</v>
       </c>
       <c r="G1043" t="n">
-        <v>15.6985902786255</v>
+        <v>15.6985912322998</v>
       </c>
       <c r="H1043" t="n">
         <v>1762598</v>
@@ -30645,7 +30645,7 @@
         <v>23.3899993896484</v>
       </c>
       <c r="G1044" t="n">
-        <v>15.4606304168701</v>
+        <v>15.4606294631958</v>
       </c>
       <c r="H1044" t="n">
         <v>1652920</v>
@@ -30674,7 +30674,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1045" t="n">
-        <v>15.8109569549561</v>
+        <v>15.810959815979</v>
       </c>
       <c r="H1045" t="n">
         <v>2257022</v>
@@ -30732,7 +30732,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1047" t="n">
-        <v>15.8109569549561</v>
+        <v>15.810959815979</v>
       </c>
       <c r="H1047" t="n">
         <v>716941</v>
@@ -30761,7 +30761,7 @@
         <v>23.7900009155273</v>
       </c>
       <c r="G1048" t="n">
-        <v>15.7250299453735</v>
+        <v>15.7250289916992</v>
       </c>
       <c r="H1048" t="n">
         <v>958014</v>
@@ -30848,7 +30848,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1051" t="n">
-        <v>15.6391010284424</v>
+        <v>15.6391000747681</v>
       </c>
       <c r="H1051" t="n">
         <v>3435868</v>
@@ -30964,7 +30964,7 @@
         <v>20.7600002288818</v>
       </c>
       <c r="G1055" t="n">
-        <v>13.7222185134888</v>
+        <v>13.7222194671631</v>
       </c>
       <c r="H1055" t="n">
         <v>2994810</v>
@@ -31051,7 +31051,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1058" t="n">
-        <v>12.2878646850586</v>
+        <v>12.2878637313843</v>
       </c>
       <c r="H1058" t="n">
         <v>4109843</v>
@@ -31080,7 +31080,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1059" t="n">
-        <v>12.2878646850586</v>
+        <v>12.2878637313843</v>
       </c>
       <c r="H1059" t="n">
         <v>3080120</v>
@@ -31138,7 +31138,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1061" t="n">
-        <v>11.6467008590698</v>
+        <v>11.6467018127441</v>
       </c>
       <c r="H1061" t="n">
         <v>3569482</v>
@@ -31167,7 +31167,7 @@
         <v>16.7250003814697</v>
       </c>
       <c r="G1062" t="n">
-        <v>11.0551118850708</v>
+        <v>11.0551128387451</v>
       </c>
       <c r="H1062" t="n">
         <v>4072091</v>
@@ -31225,7 +31225,7 @@
         <v>13.8249998092651</v>
       </c>
       <c r="G1064" t="n">
-        <v>9.13823223114014</v>
+        <v>9.13823127746582</v>
       </c>
       <c r="H1064" t="n">
         <v>3344891</v>
@@ -31283,7 +31283,7 @@
         <v>11.7749996185303</v>
       </c>
       <c r="G1066" t="n">
-        <v>7.78319549560547</v>
+        <v>7.78319597244263</v>
       </c>
       <c r="H1066" t="n">
         <v>5545350</v>
@@ -31341,7 +31341,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.96496915817261</v>
+        <v>7.96497011184692</v>
       </c>
       <c r="H1068" t="n">
         <v>4897796</v>
@@ -31399,7 +31399,7 @@
         <v>10.9949998855591</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.26762008666992</v>
+        <v>7.26762104034424</v>
       </c>
       <c r="H1070" t="n">
         <v>1882242</v>
@@ -31457,7 +31457,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.07262802124023</v>
+        <v>7.07262754440308</v>
       </c>
       <c r="H1072" t="n">
         <v>4379838</v>
@@ -31486,7 +31486,7 @@
         <v>10.8450002670288</v>
       </c>
       <c r="G1073" t="n">
-        <v>7.16847133636475</v>
+        <v>7.1684718132019</v>
       </c>
       <c r="H1073" t="n">
         <v>2363974</v>
@@ -31515,7 +31515,7 @@
         <v>11.8249998092651</v>
       </c>
       <c r="G1074" t="n">
-        <v>7.81624460220337</v>
+        <v>7.81624364852905</v>
       </c>
       <c r="H1074" t="n">
         <v>2901929</v>
@@ -31573,7 +31573,7 @@
         <v>13.835000038147</v>
       </c>
       <c r="G1076" t="n">
-        <v>9.14484214782715</v>
+        <v>9.14484119415283</v>
       </c>
       <c r="H1076" t="n">
         <v>3776062</v>
@@ -31602,7 +31602,7 @@
         <v>12.914999961853</v>
       </c>
       <c r="G1077" t="n">
-        <v>8.53672695159912</v>
+        <v>8.53672790527344</v>
       </c>
       <c r="H1077" t="n">
         <v>3630973</v>
@@ -31631,7 +31631,7 @@
         <v>12.6599998474121</v>
       </c>
       <c r="G1078" t="n">
-        <v>8.3681755065918</v>
+        <v>8.36817359924316</v>
       </c>
       <c r="H1078" t="n">
         <v>1887247</v>
@@ -31660,7 +31660,7 @@
         <v>13.1800003051758</v>
       </c>
       <c r="G1079" t="n">
-        <v>8.71189212799072</v>
+        <v>8.71189117431641</v>
       </c>
       <c r="H1079" t="n">
         <v>1798002</v>
@@ -31747,7 +31747,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G1082" t="n">
-        <v>8.18970584869385</v>
+        <v>8.18970680236816</v>
       </c>
       <c r="H1082" t="n">
         <v>2161807</v>
@@ -31776,7 +31776,7 @@
         <v>12.875</v>
       </c>
       <c r="G1083" t="n">
-        <v>8.51028919219971</v>
+        <v>8.51028728485107</v>
       </c>
       <c r="H1083" t="n">
         <v>1423991</v>
@@ -31805,7 +31805,7 @@
         <v>13.539999961853</v>
       </c>
       <c r="G1084" t="n">
-        <v>8.94984912872314</v>
+        <v>8.94984817504883</v>
       </c>
       <c r="H1084" t="n">
         <v>2799447</v>
@@ -31834,7 +31834,7 @@
         <v>14.5100002288818</v>
       </c>
       <c r="G1085" t="n">
-        <v>9.5910120010376</v>
+        <v>9.59101104736328</v>
       </c>
       <c r="H1085" t="n">
         <v>3385462</v>
@@ -31921,7 +31921,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1088" t="n">
-        <v>8.77138042449951</v>
+        <v>8.7713794708252</v>
       </c>
       <c r="H1088" t="n">
         <v>1965003</v>
@@ -31950,7 +31950,7 @@
         <v>13.4799995422363</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.91018867492676</v>
+        <v>8.91018962860107</v>
       </c>
       <c r="H1089" t="n">
         <v>1451797</v>
@@ -31979,7 +31979,7 @@
         <v>13.5799999237061</v>
       </c>
       <c r="G1090" t="n">
-        <v>8.97628784179688</v>
+        <v>8.97628879547119</v>
       </c>
       <c r="H1090" t="n">
         <v>1363021</v>
@@ -32037,7 +32037,7 @@
         <v>13.2049999237061</v>
       </c>
       <c r="G1092" t="n">
-        <v>8.72841548919678</v>
+        <v>8.72841644287109</v>
       </c>
       <c r="H1092" t="n">
         <v>1003917</v>
@@ -32066,7 +32066,7 @@
         <v>13.3199996948242</v>
       </c>
       <c r="G1093" t="n">
-        <v>8.80443000793457</v>
+        <v>8.80443096160889</v>
       </c>
       <c r="H1093" t="n">
         <v>1415630</v>
@@ -32095,7 +32095,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1094" t="n">
-        <v>8.95645904541016</v>
+        <v>8.95645809173584</v>
       </c>
       <c r="H1094" t="n">
         <v>908114</v>
@@ -32182,7 +32182,7 @@
         <v>15.4350004196167</v>
       </c>
       <c r="G1097" t="n">
-        <v>10.2024307250977</v>
+        <v>10.2024297714233</v>
       </c>
       <c r="H1097" t="n">
         <v>4617577</v>
@@ -32240,7 +32240,7 @@
         <v>15.5249996185303</v>
       </c>
       <c r="G1099" t="n">
-        <v>10.2619199752808</v>
+        <v>10.2619190216064</v>
       </c>
       <c r="H1099" t="n">
         <v>3236888</v>
@@ -32327,7 +32327,7 @@
         <v>15.0299997329712</v>
       </c>
       <c r="G1102" t="n">
-        <v>9.93472671508789</v>
+        <v>9.93472766876221</v>
       </c>
       <c r="H1102" t="n">
         <v>1641990</v>
@@ -32385,7 +32385,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1104" t="n">
-        <v>10.007438659668</v>
+        <v>10.0074377059937</v>
       </c>
       <c r="H1104" t="n">
         <v>876617</v>
@@ -32443,7 +32443,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1106" t="n">
-        <v>9.94133758544922</v>
+        <v>9.94133853912354</v>
       </c>
       <c r="H1106" t="n">
         <v>1692734</v>
@@ -32472,7 +32472,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1107" t="n">
-        <v>9.82236003875732</v>
+        <v>9.82235813140869</v>
       </c>
       <c r="H1107" t="n">
         <v>1692095</v>
@@ -32501,7 +32501,7 @@
         <v>14.9949998855591</v>
       </c>
       <c r="G1108" t="n">
-        <v>9.91159343719482</v>
+        <v>9.91159439086914</v>
       </c>
       <c r="H1108" t="n">
         <v>1665982</v>
@@ -32559,7 +32559,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G1110" t="n">
-        <v>10.3812131881714</v>
+        <v>10.3812122344971</v>
       </c>
       <c r="H1110" t="n">
         <v>1569077</v>
@@ -32617,7 +32617,7 @@
         <v>14.3299999237061</v>
       </c>
       <c r="G1112" t="n">
-        <v>10.1544561386108</v>
+        <v>10.1544551849365</v>
       </c>
       <c r="H1112" t="n">
         <v>2037752</v>
@@ -32646,7 +32646,7 @@
         <v>14.164999961853</v>
       </c>
       <c r="G1113" t="n">
-        <v>10.0375347137451</v>
+        <v>10.0375337600708</v>
       </c>
       <c r="H1113" t="n">
         <v>1714194</v>
@@ -32733,7 +32733,7 @@
         <v>14.6099996566772</v>
       </c>
       <c r="G1116" t="n">
-        <v>10.3528680801392</v>
+        <v>10.3528690338135</v>
       </c>
       <c r="H1116" t="n">
         <v>1374369</v>
@@ -32820,7 +32820,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>10.558367729187</v>
+        <v>10.5583667755127</v>
       </c>
       <c r="H1119" t="n">
         <v>1793472</v>
@@ -32878,7 +32878,7 @@
         <v>15.335000038147</v>
       </c>
       <c r="G1121" t="n">
-        <v>10.8666143417358</v>
+        <v>10.8666133880615</v>
       </c>
       <c r="H1121" t="n">
         <v>1658747</v>
@@ -32907,7 +32907,7 @@
         <v>15.7049999237061</v>
       </c>
       <c r="G1122" t="n">
-        <v>11.1288013458252</v>
+        <v>11.1288022994995</v>
       </c>
       <c r="H1122" t="n">
         <v>2340222</v>
@@ -32994,7 +32994,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1125" t="n">
-        <v>12.2590427398682</v>
+        <v>12.2590417861938</v>
       </c>
       <c r="H1125" t="n">
         <v>3898537</v>
@@ -33052,7 +33052,7 @@
         <v>16.5</v>
       </c>
       <c r="G1127" t="n">
-        <v>11.6921510696411</v>
+        <v>11.6921520233154</v>
       </c>
       <c r="H1127" t="n">
         <v>1758758</v>
@@ -33081,7 +33081,7 @@
         <v>15.5050001144409</v>
       </c>
       <c r="G1128" t="n">
-        <v>10.987078666687</v>
+        <v>10.9870796203613</v>
       </c>
       <c r="H1128" t="n">
         <v>2811323</v>
@@ -33139,7 +33139,7 @@
         <v>15.3299999237061</v>
       </c>
       <c r="G1130" t="n">
-        <v>10.8630714416504</v>
+        <v>10.8630704879761</v>
       </c>
       <c r="H1130" t="n">
         <v>3414241</v>
@@ -33168,7 +33168,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1131" t="n">
-        <v>11.1039991378784</v>
+        <v>11.1040000915527</v>
       </c>
       <c r="H1131" t="n">
         <v>2377779</v>
@@ -33197,7 +33197,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G1132" t="n">
-        <v>11.0047941207886</v>
+        <v>11.0047950744629</v>
       </c>
       <c r="H1132" t="n">
         <v>1759950</v>
@@ -33255,7 +33255,7 @@
         <v>15.5950002670288</v>
       </c>
       <c r="G1134" t="n">
-        <v>11.050853729248</v>
+        <v>11.0508546829224</v>
       </c>
       <c r="H1134" t="n">
         <v>8394991</v>
@@ -33313,7 +33313,7 @@
         <v>15.7449998855591</v>
       </c>
       <c r="G1136" t="n">
-        <v>11.1571455001831</v>
+        <v>11.1571464538574</v>
       </c>
       <c r="H1136" t="n">
         <v>1250378</v>
@@ -33342,7 +33342,7 @@
         <v>15</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.6292285919189</v>
+        <v>10.6292276382446</v>
       </c>
       <c r="H1137" t="n">
         <v>1689807</v>
@@ -33400,7 +33400,7 @@
         <v>14.9099998474121</v>
       </c>
       <c r="G1139" t="n">
-        <v>10.5654516220093</v>
+        <v>10.5654535293579</v>
       </c>
       <c r="H1139" t="n">
         <v>1134044</v>
@@ -33429,7 +33429,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1140" t="n">
-        <v>10.8276395797729</v>
+        <v>10.8276405334473</v>
       </c>
       <c r="H1140" t="n">
         <v>674600</v>
@@ -33487,7 +33487,7 @@
         <v>15.1300001144409</v>
       </c>
       <c r="G1142" t="n">
-        <v>10.7213487625122</v>
+        <v>10.7213478088379</v>
       </c>
       <c r="H1142" t="n">
         <v>834951</v>
@@ -33603,7 +33603,7 @@
         <v>15.6700000762939</v>
       </c>
       <c r="G1146" t="n">
-        <v>11.1039991378784</v>
+        <v>11.1040000915527</v>
       </c>
       <c r="H1146" t="n">
         <v>945965</v>
@@ -33690,7 +33690,7 @@
         <v>15.5349998474121</v>
       </c>
       <c r="G1149" t="n">
-        <v>11.0083379745483</v>
+        <v>11.0083360671997</v>
       </c>
       <c r="H1149" t="n">
         <v>722472</v>
@@ -33719,7 +33719,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G1150" t="n">
-        <v>11.1854915618896</v>
+        <v>11.1854906082153</v>
       </c>
       <c r="H1150" t="n">
         <v>932858</v>
@@ -33777,7 +33777,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1152" t="n">
-        <v>11.6567211151123</v>
+        <v>11.656720161438</v>
       </c>
       <c r="H1152" t="n">
         <v>2943399</v>
@@ -33835,7 +33835,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G1154" t="n">
-        <v>11.6567211151123</v>
+        <v>11.656720161438</v>
       </c>
       <c r="H1154" t="n">
         <v>1181922</v>
@@ -33864,7 +33864,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1155" t="n">
-        <v>12.0748043060303</v>
+        <v>12.074803352356</v>
       </c>
       <c r="H1155" t="n">
         <v>2692841</v>
@@ -33893,7 +33893,7 @@
         <v>16.9050006866455</v>
       </c>
       <c r="G1156" t="n">
-        <v>11.9791402816772</v>
+        <v>11.9791421890259</v>
       </c>
       <c r="H1156" t="n">
         <v>2370638</v>
@@ -33922,7 +33922,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G1157" t="n">
-        <v>12.0110282897949</v>
+        <v>12.0110273361206</v>
       </c>
       <c r="H1157" t="n">
         <v>1228791</v>
@@ -33980,7 +33980,7 @@
         <v>16.7299995422363</v>
       </c>
       <c r="G1159" t="n">
-        <v>11.8551321029663</v>
+        <v>11.8551330566406</v>
       </c>
       <c r="H1159" t="n">
         <v>2229966</v>
@@ -34009,7 +34009,7 @@
         <v>16.7849998474121</v>
       </c>
       <c r="G1160" t="n">
-        <v>11.8941068649292</v>
+        <v>11.8941059112549</v>
       </c>
       <c r="H1160" t="n">
         <v>1016498</v>
@@ -34038,7 +34038,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1161" t="n">
-        <v>11.6708927154541</v>
+        <v>11.6708917617798</v>
       </c>
       <c r="H1161" t="n">
         <v>853190</v>
@@ -34067,7 +34067,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G1162" t="n">
-        <v>11.7311248779297</v>
+        <v>11.731125831604</v>
       </c>
       <c r="H1162" t="n">
         <v>617499</v>
@@ -34183,7 +34183,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G1166" t="n">
-        <v>11.6496353149414</v>
+        <v>11.6496343612671</v>
       </c>
       <c r="H1166" t="n">
         <v>1026790</v>
@@ -34212,7 +34212,7 @@
         <v>16.6049995422363</v>
       </c>
       <c r="G1167" t="n">
-        <v>11.7665548324585</v>
+        <v>11.7665557861328</v>
       </c>
       <c r="H1167" t="n">
         <v>632041</v>
@@ -34241,7 +34241,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1168" t="n">
-        <v>11.7842693328857</v>
+        <v>11.7842702865601</v>
       </c>
       <c r="H1168" t="n">
         <v>890200</v>
@@ -34299,7 +34299,7 @@
         <v>16.6299991607666</v>
       </c>
       <c r="G1170" t="n">
-        <v>11.7842693328857</v>
+        <v>11.7842702865601</v>
       </c>
       <c r="H1170" t="n">
         <v>795616</v>
@@ -34328,7 +34328,7 @@
         <v>17.0750007629395</v>
       </c>
       <c r="G1171" t="n">
-        <v>12.0996055603027</v>
+        <v>12.0996065139771</v>
       </c>
       <c r="H1171" t="n">
         <v>1723845</v>
@@ -34357,7 +34357,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1172" t="n">
-        <v>12.0677175521851</v>
+        <v>12.0677185058594</v>
       </c>
       <c r="H1172" t="n">
         <v>795385</v>
@@ -34415,7 +34415,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>11.9401664733887</v>
+        <v>11.9401655197144</v>
       </c>
       <c r="H1174" t="n">
         <v>773384</v>
@@ -34444,7 +34444,7 @@
         <v>16.7700004577637</v>
       </c>
       <c r="G1175" t="n">
-        <v>11.8834781646729</v>
+        <v>11.8834772109985</v>
       </c>
       <c r="H1175" t="n">
         <v>452970</v>
@@ -34473,7 +34473,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1176" t="n">
-        <v>11.7488393783569</v>
+        <v>11.7488403320312</v>
       </c>
       <c r="H1176" t="n">
         <v>764280</v>
@@ -34531,7 +34531,7 @@
         <v>16.4349994659424</v>
       </c>
       <c r="G1178" t="n">
-        <v>11.6460905075073</v>
+        <v>11.6460914611816</v>
       </c>
       <c r="H1178" t="n">
         <v>488338</v>
@@ -34560,7 +34560,7 @@
         <v>16.2649993896484</v>
       </c>
       <c r="G1179" t="n">
-        <v>11.5256261825562</v>
+        <v>11.5256271362305</v>
       </c>
       <c r="H1179" t="n">
         <v>491872</v>
@@ -34618,7 +34618,7 @@
         <v>16.7849998474121</v>
       </c>
       <c r="G1181" t="n">
-        <v>11.8941068649292</v>
+        <v>11.8941059112549</v>
       </c>
       <c r="H1181" t="n">
         <v>642781</v>
@@ -34647,7 +34647,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>11.908278465271</v>
+        <v>11.9082794189453</v>
       </c>
       <c r="H1182" t="n">
         <v>512131</v>
@@ -34879,7 +34879,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1190" t="n">
-        <v>11.4653930664062</v>
+        <v>11.4653940200806</v>
       </c>
       <c r="H1190" t="n">
         <v>433905</v>
@@ -34966,7 +34966,7 @@
         <v>16.1200008392334</v>
       </c>
       <c r="G1193" t="n">
-        <v>11.4228782653809</v>
+        <v>11.4228773117065</v>
       </c>
       <c r="H1193" t="n">
         <v>539694</v>
@@ -35111,7 +35111,7 @@
         <v>16.8099994659424</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.9118223190308</v>
+        <v>11.9118213653564</v>
       </c>
       <c r="H1198" t="n">
         <v>804811</v>
@@ -35140,7 +35140,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.7204961776733</v>
+        <v>11.7204971313477</v>
       </c>
       <c r="H1199" t="n">
         <v>613707</v>
@@ -35227,7 +35227,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1202" t="n">
-        <v>11.1394309997559</v>
+        <v>11.1394319534302</v>
       </c>
       <c r="H1202" t="n">
         <v>529586</v>
@@ -35314,7 +35314,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1205" t="n">
-        <v>11.0969152450562</v>
+        <v>11.0969133377075</v>
       </c>
       <c r="H1205" t="n">
         <v>900391</v>
@@ -35372,7 +35372,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G1207" t="n">
-        <v>10.9268465042114</v>
+        <v>10.9268474578857</v>
       </c>
       <c r="H1207" t="n">
         <v>507670</v>
@@ -35401,7 +35401,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1208" t="n">
-        <v>10.8134689331055</v>
+        <v>10.8134679794312</v>
       </c>
       <c r="H1208" t="n">
         <v>515603</v>
@@ -35430,7 +35430,7 @@
         <v>15.125</v>
       </c>
       <c r="G1209" t="n">
-        <v>10.7178058624268</v>
+        <v>10.7178049087524</v>
       </c>
       <c r="H1209" t="n">
         <v>741047</v>
@@ -35488,7 +35488,7 @@
         <v>15.8100004196167</v>
       </c>
       <c r="G1211" t="n">
-        <v>11.2032079696655</v>
+        <v>11.2032060623169</v>
       </c>
       <c r="H1211" t="n">
         <v>741633</v>
@@ -35546,7 +35546,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G1213" t="n">
-        <v>11.2740678787231</v>
+        <v>11.2740688323975</v>
       </c>
       <c r="H1213" t="n">
         <v>502363</v>
@@ -35575,7 +35575,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1214" t="n">
-        <v>11.5079107284546</v>
+        <v>11.5079116821289</v>
       </c>
       <c r="H1214" t="n">
         <v>1079105</v>
@@ -35633,7 +35633,7 @@
         <v>16.125</v>
       </c>
       <c r="G1216" t="n">
-        <v>11.4264211654663</v>
+        <v>11.426420211792</v>
       </c>
       <c r="H1216" t="n">
         <v>807224</v>
@@ -35720,7 +35720,7 @@
         <v>16.1049995422363</v>
       </c>
       <c r="G1219" t="n">
-        <v>11.4122467041016</v>
+        <v>11.4122486114502</v>
       </c>
       <c r="H1219" t="n">
         <v>900252</v>
@@ -35749,7 +35749,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G1220" t="n">
-        <v>11.4618511199951</v>
+        <v>11.4618501663208</v>
       </c>
       <c r="H1220" t="n">
         <v>735919</v>
@@ -35807,7 +35807,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1222" t="n">
-        <v>11.1394309997559</v>
+        <v>11.1394319534302</v>
       </c>
       <c r="H1222" t="n">
         <v>638999</v>
@@ -35836,7 +35836,7 @@
         <v>15.5749998092651</v>
       </c>
       <c r="G1223" t="n">
-        <v>11.0366830825806</v>
+        <v>11.0366821289062</v>
       </c>
       <c r="H1223" t="n">
         <v>609556</v>
@@ -35865,7 +35865,7 @@
         <v>15.7849998474121</v>
       </c>
       <c r="G1224" t="n">
-        <v>11.1854915618896</v>
+        <v>11.1854906082153</v>
       </c>
       <c r="H1224" t="n">
         <v>576845</v>
@@ -35894,7 +35894,7 @@
         <v>15.3400001525879</v>
       </c>
       <c r="G1225" t="n">
-        <v>10.8701581954956</v>
+        <v>10.8701572418213</v>
       </c>
       <c r="H1225" t="n">
         <v>714224</v>
@@ -35923,7 +35923,7 @@
         <v>15</v>
       </c>
       <c r="G1226" t="n">
-        <v>10.6292285919189</v>
+        <v>10.6292276382446</v>
       </c>
       <c r="H1226" t="n">
         <v>822433</v>
@@ -36039,7 +36039,7 @@
         <v>14.9750003814697</v>
       </c>
       <c r="G1230" t="n">
-        <v>10.6115140914917</v>
+        <v>10.6115131378174</v>
       </c>
       <c r="H1230" t="n">
         <v>687960</v>
@@ -36068,7 +36068,7 @@
         <v>15.5</v>
       </c>
       <c r="G1231" t="n">
-        <v>10.9835357666016</v>
+        <v>10.9835348129272</v>
       </c>
       <c r="H1231" t="n">
         <v>963646</v>
@@ -36126,7 +36126,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G1233" t="n">
-        <v>11.3449296951294</v>
+        <v>11.3449306488037</v>
       </c>
       <c r="H1233" t="n">
         <v>1226139</v>
@@ -36184,7 +36184,7 @@
         <v>16.75</v>
       </c>
       <c r="G1235" t="n">
-        <v>11.8693046569824</v>
+        <v>11.8693056106567</v>
       </c>
       <c r="H1235" t="n">
         <v>2431463</v>
@@ -36242,7 +36242,7 @@
         <v>16.5550003051758</v>
       </c>
       <c r="G1237" t="n">
-        <v>11.7311248779297</v>
+        <v>11.731125831604</v>
       </c>
       <c r="H1237" t="n">
         <v>1576148</v>
@@ -36271,7 +36271,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.7063236236572</v>
+        <v>11.7063226699829</v>
       </c>
       <c r="H1238" t="n">
         <v>1138687</v>
@@ -36300,7 +36300,7 @@
         <v>16.8500003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.9401664733887</v>
+        <v>11.9401655197144</v>
       </c>
       <c r="H1239" t="n">
         <v>1773945</v>
@@ -36329,7 +36329,7 @@
         <v>17.4899997711182</v>
       </c>
       <c r="G1240" t="n">
-        <v>12.3936796188354</v>
+        <v>12.3936805725098</v>
       </c>
       <c r="H1240" t="n">
         <v>2784389</v>
@@ -36358,7 +36358,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1241" t="n">
-        <v>12.4574575424194</v>
+        <v>12.4574565887451</v>
       </c>
       <c r="H1241" t="n">
         <v>1853211</v>
@@ -36387,7 +36387,7 @@
         <v>18.0499992370605</v>
       </c>
       <c r="G1242" t="n">
-        <v>12.7905044555664</v>
+        <v>12.7905054092407</v>
       </c>
       <c r="H1242" t="n">
         <v>2473051</v>
@@ -36445,7 +36445,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1244" t="n">
-        <v>12.50705909729</v>
+        <v>12.5070581436157</v>
       </c>
       <c r="H1244" t="n">
         <v>1079962</v>
@@ -36474,7 +36474,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1245" t="n">
-        <v>12.4716272354126</v>
+        <v>12.4716281890869</v>
       </c>
       <c r="H1245" t="n">
         <v>998587</v>
@@ -36532,7 +36532,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1247" t="n">
-        <v>12.8967971801758</v>
+        <v>12.8967981338501</v>
       </c>
       <c r="H1247" t="n">
         <v>2022871</v>
@@ -36561,7 +36561,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1248" t="n">
-        <v>12.5991802215576</v>
+        <v>12.5991792678833</v>
       </c>
       <c r="H1248" t="n">
         <v>1287129</v>
@@ -36590,7 +36590,7 @@
         <v>17.8099994659424</v>
       </c>
       <c r="G1249" t="n">
-        <v>12.620436668396</v>
+        <v>12.6204347610474</v>
       </c>
       <c r="H1249" t="n">
         <v>647353</v>
@@ -36619,7 +36619,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G1250" t="n">
-        <v>12.5212316513062</v>
+        <v>12.5212306976318</v>
       </c>
       <c r="H1250" t="n">
         <v>785957</v>
@@ -36706,7 +36706,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1253" t="n">
-        <v>12.5283164978027</v>
+        <v>12.5283174514771</v>
       </c>
       <c r="H1253" t="n">
         <v>583314</v>
@@ -36735,7 +36735,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1254" t="n">
-        <v>12.5283164978027</v>
+        <v>12.5283174514771</v>
       </c>
       <c r="H1254" t="n">
         <v>840138</v>
@@ -36764,7 +36764,7 @@
         <v>17.6900005340576</v>
       </c>
       <c r="G1255" t="n">
-        <v>12.5354022979736</v>
+        <v>12.5354042053223</v>
       </c>
       <c r="H1255" t="n">
         <v>567556</v>
@@ -36793,7 +36793,7 @@
         <v>17.6100006103516</v>
       </c>
       <c r="G1256" t="n">
-        <v>12.4787130355835</v>
+        <v>12.4787139892578</v>
       </c>
       <c r="H1256" t="n">
         <v>560991</v>
@@ -36822,7 +36822,7 @@
         <v>17.6700000762939</v>
       </c>
       <c r="G1257" t="n">
-        <v>12.5212316513062</v>
+        <v>12.5212306976318</v>
       </c>
       <c r="H1257" t="n">
         <v>627281</v>
@@ -36880,7 +36880,7 @@
         <v>17.2150001525879</v>
       </c>
       <c r="G1259" t="n">
-        <v>12.1988115310669</v>
+        <v>12.1988124847412</v>
       </c>
       <c r="H1259" t="n">
         <v>898405</v>
@@ -36909,7 +36909,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.50705909729</v>
+        <v>12.5070581436157</v>
       </c>
       <c r="H1260" t="n">
         <v>827415</v>
@@ -36938,7 +36938,7 @@
         <v>17.5349998474121</v>
       </c>
       <c r="G1261" t="n">
-        <v>12.4255685806274</v>
+        <v>12.4255676269531</v>
       </c>
       <c r="H1261" t="n">
         <v>613163</v>
@@ -36967,7 +36967,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1262" t="n">
-        <v>12.4432830810547</v>
+        <v>12.4432821273804</v>
       </c>
       <c r="H1262" t="n">
         <v>726002</v>
@@ -36996,7 +36996,7 @@
         <v>17.5650005340576</v>
       </c>
       <c r="G1263" t="n">
-        <v>12.4468250274658</v>
+        <v>12.4468278884888</v>
       </c>
       <c r="H1263" t="n">
         <v>653791</v>
@@ -37083,7 +37083,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.5708332061768</v>
+        <v>12.5708341598511</v>
       </c>
       <c r="H1266" t="n">
         <v>947457</v>
@@ -37112,7 +37112,7 @@
         <v>17.8850002288818</v>
       </c>
       <c r="G1267" t="n">
-        <v>12.6735830307007</v>
+        <v>12.673583984375</v>
       </c>
       <c r="H1267" t="n">
         <v>1143701</v>
@@ -37199,7 +37199,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1270" t="n">
-        <v>12.5920925140381</v>
+        <v>12.5920915603638</v>
       </c>
       <c r="H1270" t="n">
         <v>430557</v>
@@ -37257,7 +37257,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1272" t="n">
-        <v>12.4503707885742</v>
+        <v>12.4503698348999</v>
       </c>
       <c r="H1272" t="n">
         <v>821452</v>
@@ -37344,7 +37344,7 @@
         <v>17.8349990844727</v>
       </c>
       <c r="G1275" t="n">
-        <v>12.6381521224976</v>
+        <v>12.6381502151489</v>
       </c>
       <c r="H1275" t="n">
         <v>695221</v>
@@ -37431,7 +37431,7 @@
         <v>18.9150009155273</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.4034566879272</v>
+        <v>13.4034576416016</v>
       </c>
       <c r="H1278" t="n">
         <v>2985956</v>
@@ -37518,7 +37518,7 @@
         <v>18.4950008392334</v>
       </c>
       <c r="G1281" t="n">
-        <v>13.1058397293091</v>
+        <v>13.1058387756348</v>
       </c>
       <c r="H1281" t="n">
         <v>554143</v>
@@ -37547,7 +37547,7 @@
         <v>18.4200000762939</v>
       </c>
       <c r="G1282" t="n">
-        <v>13.0526924133301</v>
+        <v>13.0526933670044</v>
       </c>
       <c r="H1282" t="n">
         <v>858830</v>
@@ -37663,7 +37663,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1286" t="n">
-        <v>12.4716272354126</v>
+        <v>12.4716281890869</v>
       </c>
       <c r="H1286" t="n">
         <v>787730</v>
@@ -37721,7 +37721,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1288" t="n">
-        <v>12.3653364181519</v>
+        <v>12.3653354644775</v>
       </c>
       <c r="H1288" t="n">
         <v>898409</v>
@@ -37779,7 +37779,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1290" t="n">
-        <v>12.3015594482422</v>
+        <v>12.3015604019165</v>
       </c>
       <c r="H1290" t="n">
         <v>546428</v>
@@ -37837,7 +37837,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1292" t="n">
-        <v>12.7975902557373</v>
+        <v>12.7975912094116</v>
       </c>
       <c r="H1292" t="n">
         <v>559590</v>
@@ -37924,7 +37924,7 @@
         <v>19.4150009155273</v>
       </c>
       <c r="G1295" t="n">
-        <v>13.7577657699585</v>
+        <v>13.7577648162842</v>
       </c>
       <c r="H1295" t="n">
         <v>2026724</v>
@@ -38069,7 +38069,7 @@
         <v>20</v>
       </c>
       <c r="G1300" t="n">
-        <v>14.1723031997681</v>
+        <v>14.1723041534424</v>
       </c>
       <c r="H1300" t="n">
         <v>758827</v>
@@ -38098,7 +38098,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G1301" t="n">
-        <v>14.3352870941162</v>
+        <v>14.3352851867676</v>
       </c>
       <c r="H1301" t="n">
         <v>1022043</v>
@@ -38156,7 +38156,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.002236366272</v>
+        <v>14.0022373199463</v>
       </c>
       <c r="H1303" t="n">
         <v>807759</v>
@@ -38185,7 +38185,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G1304" t="n">
-        <v>13.8853139877319</v>
+        <v>13.8853158950806</v>
       </c>
       <c r="H1304" t="n">
         <v>809838</v>
@@ -38214,7 +38214,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1305" t="n">
-        <v>14.0730991363525</v>
+        <v>14.0730981826782</v>
       </c>
       <c r="H1305" t="n">
         <v>609447</v>
@@ -38243,7 +38243,7 @@
         <v>19.7299995422363</v>
       </c>
       <c r="G1306" t="n">
-        <v>13.980978012085</v>
+        <v>13.9809789657593</v>
       </c>
       <c r="H1306" t="n">
         <v>569196</v>
@@ -38330,7 +38330,7 @@
         <v>19.2099990844727</v>
       </c>
       <c r="G1309" t="n">
-        <v>13.6124973297119</v>
+        <v>13.6124992370605</v>
       </c>
       <c r="H1309" t="n">
         <v>682776</v>
@@ -38359,7 +38359,7 @@
         <v>19.0100002288818</v>
       </c>
       <c r="G1310" t="n">
-        <v>13.4707746505737</v>
+        <v>13.470775604248</v>
       </c>
       <c r="H1310" t="n">
         <v>842015</v>
@@ -38388,7 +38388,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1311" t="n">
-        <v>14.1014442443848</v>
+        <v>14.1014432907104</v>
       </c>
       <c r="H1311" t="n">
         <v>997246</v>
@@ -38417,7 +38417,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1312" t="n">
-        <v>13.9455471038818</v>
+        <v>13.9455480575562</v>
       </c>
       <c r="H1312" t="n">
         <v>636708</v>
@@ -38649,7 +38649,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1320" t="n">
-        <v>13.5912408828735</v>
+        <v>13.5912389755249</v>
       </c>
       <c r="H1320" t="n">
         <v>2150203</v>
@@ -38678,7 +38678,7 @@
         <v>18.8950004577637</v>
       </c>
       <c r="G1321" t="n">
-        <v>13.3892850875854</v>
+        <v>13.3892860412598</v>
       </c>
       <c r="H1321" t="n">
         <v>1761546</v>
@@ -38707,7 +38707,7 @@
         <v>18.7950000762939</v>
       </c>
       <c r="G1322" t="n">
-        <v>13.3184232711792</v>
+        <v>13.3184213638306</v>
       </c>
       <c r="H1322" t="n">
         <v>1587470</v>
@@ -38736,7 +38736,7 @@
         <v>18.9050006866455</v>
       </c>
       <c r="G1323" t="n">
-        <v>13.396372795105</v>
+        <v>13.3963708877563</v>
       </c>
       <c r="H1323" t="n">
         <v>903143</v>
@@ -38765,7 +38765,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1324" t="n">
-        <v>13.4672298431396</v>
+        <v>13.4672317504883</v>
       </c>
       <c r="H1324" t="n">
         <v>881790</v>
@@ -38910,7 +38910,7 @@
         <v>19.0249996185303</v>
       </c>
       <c r="G1329" t="n">
-        <v>13.4814043045044</v>
+        <v>13.4814052581787</v>
       </c>
       <c r="H1329" t="n">
         <v>747016</v>
@@ -38968,7 +38968,7 @@
         <v>19.2549991607666</v>
       </c>
       <c r="G1331" t="n">
-        <v>13.6443853378296</v>
+        <v>13.6443862915039</v>
       </c>
       <c r="H1331" t="n">
         <v>703346</v>
@@ -39055,7 +39055,7 @@
         <v>19.4249992370605</v>
       </c>
       <c r="G1334" t="n">
-        <v>13.7648515701294</v>
+        <v>13.7648506164551</v>
       </c>
       <c r="H1334" t="n">
         <v>704457</v>
@@ -39142,7 +39142,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1337" t="n">
-        <v>14.002236366272</v>
+        <v>14.0022373199463</v>
       </c>
       <c r="H1337" t="n">
         <v>1147975</v>
@@ -39171,7 +39171,7 @@
         <v>19.7649993896484</v>
       </c>
       <c r="G1338" t="n">
-        <v>14.0057802200317</v>
+        <v>14.0057792663574</v>
       </c>
       <c r="H1338" t="n">
         <v>911777</v>
@@ -39200,7 +39200,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1339" t="n">
-        <v>14.3848905563354</v>
+        <v>14.3848896026611</v>
       </c>
       <c r="H1339" t="n">
         <v>2681601</v>
@@ -39374,7 +39374,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1345" t="n">
-        <v>13.888858795166</v>
+        <v>13.8888597488403</v>
       </c>
       <c r="H1345" t="n">
         <v>1548965</v>
@@ -39432,7 +39432,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.9738922119141</v>
+        <v>13.9738931655884</v>
       </c>
       <c r="H1347" t="n">
         <v>495705</v>
@@ -39461,7 +39461,7 @@
         <v>19.7250003814697</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.9774341583252</v>
+        <v>13.9774360656738</v>
       </c>
       <c r="H1348" t="n">
         <v>637198</v>
@@ -39606,7 +39606,7 @@
         <v>19.9150009155273</v>
       </c>
       <c r="G1353" t="n">
-        <v>14.1120729446411</v>
+        <v>14.1120719909668</v>
       </c>
       <c r="H1353" t="n">
         <v>638518</v>
@@ -39635,7 +39635,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1354" t="n">
-        <v>14.2998561859131</v>
+        <v>14.2998542785645</v>
       </c>
       <c r="H1354" t="n">
         <v>990084</v>
@@ -39664,7 +39664,7 @@
         <v>19.9300003051758</v>
       </c>
       <c r="G1355" t="n">
-        <v>14.1227016448975</v>
+        <v>14.1227006912231</v>
       </c>
       <c r="H1355" t="n">
         <v>808370</v>
@@ -39751,7 +39751,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1358" t="n">
-        <v>14.2785959243774</v>
+        <v>14.2785949707031</v>
       </c>
       <c r="H1358" t="n">
         <v>638821</v>
@@ -39780,7 +39780,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1359" t="n">
-        <v>14.4840974807739</v>
+        <v>14.4840955734253</v>
       </c>
       <c r="H1359" t="n">
         <v>1770727</v>
@@ -39809,7 +39809,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G1360" t="n">
-        <v>14.391975402832</v>
+        <v>14.3919734954834</v>
       </c>
       <c r="H1360" t="n">
         <v>1645102</v>
@@ -39867,7 +39867,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G1362" t="n">
-        <v>14.4061470031738</v>
+        <v>14.4061450958252</v>
       </c>
       <c r="H1362" t="n">
         <v>2630085</v>
@@ -39925,7 +39925,7 @@
         <v>21.1200008392334</v>
       </c>
       <c r="G1364" t="n">
-        <v>14.9659557342529</v>
+        <v>14.9659547805786</v>
       </c>
       <c r="H1364" t="n">
         <v>2206474</v>
@@ -39954,7 +39954,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G1365" t="n">
-        <v>14.9446964263916</v>
+        <v>14.944694519043</v>
       </c>
       <c r="H1365" t="n">
         <v>1093986</v>
@@ -39983,7 +39983,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1366" t="n">
-        <v>14.7533683776855</v>
+        <v>14.7533674240112</v>
       </c>
       <c r="H1366" t="n">
         <v>1470769</v>
@@ -40070,7 +40070,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1369" t="n">
-        <v>15.2431755065918</v>
+        <v>15.2431764602661</v>
       </c>
       <c r="H1369" t="n">
         <v>1750880</v>
@@ -40215,7 +40215,7 @@
         <v>20.3299999237061</v>
       </c>
       <c r="G1374" t="n">
-        <v>15.1315326690674</v>
+        <v>15.1315307617188</v>
       </c>
       <c r="H1374" t="n">
         <v>526755</v>
@@ -40244,7 +40244,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1375" t="n">
-        <v>15.0943193435669</v>
+        <v>15.0943183898926</v>
       </c>
       <c r="H1375" t="n">
         <v>944717</v>
@@ -40302,7 +40302,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1377" t="n">
-        <v>15.183632850647</v>
+        <v>15.1836338043213</v>
       </c>
       <c r="H1377" t="n">
         <v>999402</v>
@@ -40331,7 +40331,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G1378" t="n">
-        <v>15.2282915115356</v>
+        <v>15.2282905578613</v>
       </c>
       <c r="H1378" t="n">
         <v>681408</v>
@@ -40389,7 +40389,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.5185651779175</v>
+        <v>15.5185661315918</v>
       </c>
       <c r="H1380" t="n">
         <v>967382</v>
@@ -40418,7 +40418,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.4813508987427</v>
+        <v>15.481351852417</v>
       </c>
       <c r="H1381" t="n">
         <v>749681</v>
@@ -40476,7 +40476,7 @@
         <v>20.7199993133545</v>
       </c>
       <c r="G1383" t="n">
-        <v>15.4218082427979</v>
+        <v>15.4218072891235</v>
       </c>
       <c r="H1383" t="n">
         <v>432920</v>
@@ -40505,7 +40505,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1384" t="n">
-        <v>15.2431755065918</v>
+        <v>15.2431764602661</v>
       </c>
       <c r="H1384" t="n">
         <v>877004</v>
@@ -40534,7 +40534,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G1385" t="n">
-        <v>15.086874961853</v>
+        <v>15.0868759155273</v>
       </c>
       <c r="H1385" t="n">
         <v>1008591</v>
@@ -40563,7 +40563,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G1386" t="n">
-        <v>15.2059631347656</v>
+        <v>15.2059640884399</v>
       </c>
       <c r="H1386" t="n">
         <v>777100</v>
@@ -40592,7 +40592,7 @@
         <v>20.5200004577637</v>
       </c>
       <c r="G1387" t="n">
-        <v>15.2729482650757</v>
+        <v>15.27294921875</v>
       </c>
       <c r="H1387" t="n">
         <v>472800</v>
@@ -40650,7 +40650,7 @@
         <v>20.2099990844727</v>
       </c>
       <c r="G1389" t="n">
-        <v>15.0422163009644</v>
+        <v>15.04221534729</v>
       </c>
       <c r="H1389" t="n">
         <v>552738</v>
@@ -40708,7 +40708,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1391" t="n">
-        <v>14.9752330780029</v>
+        <v>14.9752321243286</v>
       </c>
       <c r="H1391" t="n">
         <v>450730</v>
@@ -40737,7 +40737,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1392" t="n">
-        <v>15.31760597229</v>
+        <v>15.3176069259644</v>
       </c>
       <c r="H1392" t="n">
         <v>688302</v>
@@ -40766,7 +40766,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G1393" t="n">
-        <v>15.3250513076782</v>
+        <v>15.3250494003296</v>
       </c>
       <c r="H1393" t="n">
         <v>524404</v>
@@ -40795,7 +40795,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1394" t="n">
-        <v>15.0943193435669</v>
+        <v>15.0943183898926</v>
       </c>
       <c r="H1394" t="n">
         <v>711381</v>
@@ -40824,7 +40824,7 @@
         <v>20.9500007629395</v>
       </c>
       <c r="G1395" t="n">
-        <v>15.59299659729</v>
+        <v>15.5929975509644</v>
       </c>
       <c r="H1395" t="n">
         <v>2669315</v>
@@ -40853,7 +40853,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1396" t="n">
-        <v>15.2431755065918</v>
+        <v>15.2431764602661</v>
       </c>
       <c r="H1396" t="n">
         <v>1125482</v>
@@ -40882,7 +40882,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1397" t="n">
-        <v>15.2134065628052</v>
+        <v>15.2134056091309</v>
       </c>
       <c r="H1397" t="n">
         <v>778761</v>
@@ -40911,7 +40911,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1398" t="n">
-        <v>15.2134065628052</v>
+        <v>15.2134056091309</v>
       </c>
       <c r="H1398" t="n">
         <v>505455</v>
@@ -40940,7 +40940,7 @@
         <v>20.5900001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>15.3250513076782</v>
+        <v>15.3250494003296</v>
       </c>
       <c r="H1399" t="n">
         <v>335413</v>
@@ -40969,7 +40969,7 @@
         <v>20.5499992370605</v>
       </c>
       <c r="G1400" t="n">
-        <v>15.2952785491943</v>
+        <v>15.29527759552</v>
       </c>
       <c r="H1400" t="n">
         <v>556640</v>
@@ -41027,7 +41027,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>15.2431755065918</v>
+        <v>15.2431764602661</v>
       </c>
       <c r="H1402" t="n">
         <v>1373106</v>
@@ -41085,7 +41085,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G1404" t="n">
-        <v>15.6525402069092</v>
+        <v>15.6525421142578</v>
       </c>
       <c r="H1404" t="n">
         <v>1006186</v>
@@ -41114,7 +41114,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1405" t="n">
-        <v>15.57066822052</v>
+        <v>15.5706691741943</v>
       </c>
       <c r="H1405" t="n">
         <v>620879</v>
@@ -41143,7 +41143,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G1406" t="n">
-        <v>15.5483379364014</v>
+        <v>15.5483369827271</v>
       </c>
       <c r="H1406" t="n">
         <v>548500</v>
@@ -41230,7 +41230,7 @@
         <v>20.4300003051758</v>
       </c>
       <c r="G1409" t="n">
-        <v>15.2059631347656</v>
+        <v>15.2059640884399</v>
       </c>
       <c r="H1409" t="n">
         <v>1506622</v>
@@ -41259,7 +41259,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1410" t="n">
-        <v>15.3324928283691</v>
+        <v>15.3324937820435</v>
       </c>
       <c r="H1410" t="n">
         <v>1077491</v>
@@ -41288,7 +41288,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1411" t="n">
-        <v>15.5855550765991</v>
+        <v>15.5855531692505</v>
       </c>
       <c r="H1411" t="n">
         <v>905882</v>
@@ -41375,7 +41375,7 @@
         <v>22.2099990844727</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.5308094024658</v>
+        <v>16.5308074951172</v>
       </c>
       <c r="H1414" t="n">
         <v>1307507</v>
@@ -41520,7 +41520,7 @@
         <v>22.1399993896484</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.4787063598633</v>
+        <v>16.4787082672119</v>
       </c>
       <c r="H1419" t="n">
         <v>885234</v>
@@ -41578,7 +41578,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1421" t="n">
-        <v>16.3000774383545</v>
+        <v>16.3000755310059</v>
       </c>
       <c r="H1421" t="n">
         <v>1016025</v>
@@ -41607,7 +41607,7 @@
         <v>22.0599994659424</v>
       </c>
       <c r="G1422" t="n">
-        <v>16.4191646575928</v>
+        <v>16.4191627502441</v>
       </c>
       <c r="H1422" t="n">
         <v>1116024</v>
@@ -41636,7 +41636,7 @@
         <v>22.2700004577637</v>
       </c>
       <c r="G1423" t="n">
-        <v>16.5754680633545</v>
+        <v>16.5754661560059</v>
       </c>
       <c r="H1423" t="n">
         <v>1107597</v>
@@ -41723,7 +41723,7 @@
         <v>22.9500007629395</v>
       </c>
       <c r="G1426" t="n">
-        <v>17.0815887451172</v>
+        <v>17.0815906524658</v>
       </c>
       <c r="H1426" t="n">
         <v>1109397</v>
@@ -41752,7 +41752,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1427" t="n">
-        <v>17.0890293121338</v>
+        <v>17.0890312194824</v>
       </c>
       <c r="H1427" t="n">
         <v>544693</v>
@@ -41781,7 +41781,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G1428" t="n">
-        <v>17.2230052947998</v>
+        <v>17.2230033874512</v>
       </c>
       <c r="H1428" t="n">
         <v>724243</v>
@@ -41839,7 +41839,7 @@
         <v>23.1200008392334</v>
       </c>
       <c r="G1430" t="n">
-        <v>17.2081184387207</v>
+        <v>17.2081203460693</v>
       </c>
       <c r="H1430" t="n">
         <v>495534</v>
@@ -41897,7 +41897,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G1432" t="n">
-        <v>17.2155590057373</v>
+        <v>17.2155609130859</v>
       </c>
       <c r="H1432" t="n">
         <v>692330</v>
@@ -41926,7 +41926,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G1433" t="n">
-        <v>17.2453327178955</v>
+        <v>17.2453308105469</v>
       </c>
       <c r="H1433" t="n">
         <v>346167</v>
@@ -41955,7 +41955,7 @@
         <v>23.3500003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>17.3793048858643</v>
+        <v>17.3793067932129</v>
       </c>
       <c r="H1434" t="n">
         <v>860210</v>
@@ -41984,7 +41984,7 @@
         <v>23.2600002288818</v>
       </c>
       <c r="G1435" t="n">
-        <v>17.3123207092285</v>
+        <v>17.3123188018799</v>
       </c>
       <c r="H1435" t="n">
         <v>365116</v>
@@ -42013,7 +42013,7 @@
         <v>23.3700008392334</v>
       </c>
       <c r="G1436" t="n">
-        <v>17.3941917419434</v>
+        <v>17.3941898345947</v>
       </c>
       <c r="H1436" t="n">
         <v>374083</v>
@@ -42071,7 +42071,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1438" t="n">
-        <v>17.6100387573242</v>
+        <v>17.610034942627</v>
       </c>
       <c r="H1438" t="n">
         <v>443835</v>
@@ -42100,7 +42100,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1439" t="n">
-        <v>17.6844673156738</v>
+        <v>17.6844692230225</v>
       </c>
       <c r="H1439" t="n">
         <v>688833</v>
@@ -42245,7 +42245,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G1444" t="n">
-        <v>17.6919116973877</v>
+        <v>17.6919097900391</v>
       </c>
       <c r="H1444" t="n">
         <v>393889</v>
@@ -42303,7 +42303,7 @@
         <v>23.6299991607666</v>
       </c>
       <c r="G1446" t="n">
-        <v>17.5877075195312</v>
+        <v>17.5877094268799</v>
       </c>
       <c r="H1446" t="n">
         <v>486394</v>
@@ -42332,7 +42332,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1447" t="n">
-        <v>17.6546936035156</v>
+        <v>17.6546955108643</v>
       </c>
       <c r="H1447" t="n">
         <v>463385</v>
@@ -42361,7 +42361,7 @@
         <v>23.5400009155273</v>
       </c>
       <c r="G1448" t="n">
-        <v>17.5207233428955</v>
+        <v>17.5207214355469</v>
       </c>
       <c r="H1448" t="n">
         <v>346265</v>
@@ -42390,7 +42390,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1449" t="n">
-        <v>17.7737827301025</v>
+        <v>17.7737808227539</v>
       </c>
       <c r="H1449" t="n">
         <v>670938</v>
@@ -42419,7 +42419,7 @@
         <v>23.9500007629395</v>
       </c>
       <c r="G1450" t="n">
-        <v>17.8258857727051</v>
+        <v>17.8258838653564</v>
       </c>
       <c r="H1450" t="n">
         <v>580489</v>
@@ -42448,7 +42448,7 @@
         <v>24.0200004577637</v>
       </c>
       <c r="G1451" t="n">
-        <v>17.8779850006104</v>
+        <v>17.8779830932617</v>
       </c>
       <c r="H1451" t="n">
         <v>912239</v>
@@ -42564,7 +42564,7 @@
         <v>23.8999996185303</v>
       </c>
       <c r="G1455" t="n">
-        <v>17.7886695861816</v>
+        <v>17.788667678833</v>
       </c>
       <c r="H1455" t="n">
         <v>430053</v>
@@ -42767,7 +42767,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1462" t="n">
-        <v>17.6844673156738</v>
+        <v>17.6844692230225</v>
       </c>
       <c r="H1462" t="n">
         <v>464492</v>
@@ -42854,7 +42854,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.5951538085938</v>
+        <v>17.5951519012451</v>
       </c>
       <c r="H1465" t="n">
         <v>851422</v>
@@ -42883,7 +42883,7 @@
         <v>23.3199996948242</v>
       </c>
       <c r="G1466" t="n">
-        <v>17.3569755554199</v>
+        <v>17.3569736480713</v>
       </c>
       <c r="H1466" t="n">
         <v>688828</v>
@@ -42941,7 +42941,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1468" t="n">
-        <v>17.5951538085938</v>
+        <v>17.5951519012451</v>
       </c>
       <c r="H1468" t="n">
         <v>358987</v>
@@ -42970,7 +42970,7 @@
         <v>23.1100006103516</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.2006740570068</v>
+        <v>17.2006759643555</v>
       </c>
       <c r="H1469" t="n">
         <v>907331</v>
@@ -42999,7 +42999,7 @@
         <v>23.1399993896484</v>
       </c>
       <c r="G1470" t="n">
-        <v>17.2230052947998</v>
+        <v>17.2230033874512</v>
       </c>
       <c r="H1470" t="n">
         <v>356004</v>
@@ -43057,7 +43057,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G1472" t="n">
-        <v>17.3867473602295</v>
+        <v>17.3867492675781</v>
       </c>
       <c r="H1472" t="n">
         <v>446804</v>
@@ -43086,7 +43086,7 @@
         <v>23.6200008392334</v>
       </c>
       <c r="G1473" t="n">
-        <v>17.5802669525146</v>
+        <v>17.580265045166</v>
       </c>
       <c r="H1473" t="n">
         <v>683525</v>
@@ -43173,7 +43173,7 @@
         <v>24.7600002288818</v>
       </c>
       <c r="G1476" t="n">
-        <v>18.4287643432617</v>
+        <v>18.4287624359131</v>
       </c>
       <c r="H1476" t="n">
         <v>2586574</v>
@@ -43492,7 +43492,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.9125556945801</v>
+        <v>18.9125537872314</v>
       </c>
       <c r="H1487" t="n">
         <v>477108</v>
@@ -43521,7 +43521,7 @@
         <v>25.4400005340576</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.9348831176758</v>
+        <v>18.934886932373</v>
       </c>
       <c r="H1488" t="n">
         <v>393124</v>
@@ -43579,7 +43579,7 @@
         <v>25.3700008392334</v>
       </c>
       <c r="G1490" t="n">
-        <v>18.8827819824219</v>
+        <v>18.8827838897705</v>
       </c>
       <c r="H1490" t="n">
         <v>424520</v>
@@ -43608,7 +43608,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G1491" t="n">
-        <v>18.9125556945801</v>
+        <v>18.9125537872314</v>
       </c>
       <c r="H1491" t="n">
         <v>581641</v>
@@ -43695,7 +43695,7 @@
         <v>26.8400001525879</v>
       </c>
       <c r="G1494" t="n">
-        <v>19.976900100708</v>
+        <v>19.9768962860107</v>
       </c>
       <c r="H1494" t="n">
         <v>1283075</v>
@@ -43753,7 +43753,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1496" t="n">
-        <v>19.7536087036133</v>
+        <v>19.7536106109619</v>
       </c>
       <c r="H1496" t="n">
         <v>609474</v>
@@ -43840,7 +43840,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1499" t="n">
-        <v>19.7536087036133</v>
+        <v>19.7536106109619</v>
       </c>
       <c r="H1499" t="n">
         <v>498783</v>
@@ -43869,7 +43869,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1500" t="n">
-        <v>19.0688591003418</v>
+        <v>19.0688571929932</v>
       </c>
       <c r="H1500" t="n">
         <v>714727</v>
@@ -43927,7 +43927,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.9423294067383</v>
+        <v>18.942325592041</v>
       </c>
       <c r="H1502" t="n">
         <v>431796</v>
@@ -44043,7 +44043,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.3692188262939</v>
+        <v>18.3692207336426</v>
       </c>
       <c r="H1506" t="n">
         <v>748606</v>
@@ -44072,7 +44072,7 @@
         <v>24.4699993133545</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.2129173278809</v>
+        <v>18.2129154205322</v>
       </c>
       <c r="H1507" t="n">
         <v>601021</v>
@@ -44101,7 +44101,7 @@
         <v>24.2999992370605</v>
       </c>
       <c r="G1508" t="n">
-        <v>18.0863876342773</v>
+        <v>18.0863857269287</v>
       </c>
       <c r="H1508" t="n">
         <v>711824</v>
@@ -44188,7 +44188,7 @@
         <v>24.4400005340576</v>
       </c>
       <c r="G1511" t="n">
-        <v>18.1905879974365</v>
+        <v>18.1905899047852</v>
       </c>
       <c r="H1511" t="n">
         <v>682443</v>
@@ -44217,7 +44217,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1512" t="n">
-        <v>18.0417289733887</v>
+        <v>18.04172706604</v>
       </c>
       <c r="H1512" t="n">
         <v>655986</v>
@@ -44246,7 +44246,7 @@
         <v>24.1100006103516</v>
       </c>
       <c r="G1513" t="n">
-        <v>17.9449710845947</v>
+        <v>17.9449729919434</v>
       </c>
       <c r="H1513" t="n">
         <v>528552</v>
@@ -44333,7 +44333,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1516" t="n">
-        <v>17.6844673156738</v>
+        <v>17.6844692230225</v>
       </c>
       <c r="H1516" t="n">
         <v>388129</v>
@@ -44449,7 +44449,7 @@
         <v>23.7299995422363</v>
       </c>
       <c r="G1520" t="n">
-        <v>17.6621398925781</v>
+        <v>17.6621360778809</v>
       </c>
       <c r="H1520" t="n">
         <v>369786</v>
@@ -44565,7 +44565,7 @@
         <v>24.5300006866455</v>
       </c>
       <c r="G1524" t="n">
-        <v>18.2575740814209</v>
+        <v>18.2575759887695</v>
       </c>
       <c r="H1524" t="n">
         <v>394181</v>
@@ -44594,7 +44594,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1525" t="n">
-        <v>18.3096771240234</v>
+        <v>18.3096752166748</v>
       </c>
       <c r="H1525" t="n">
         <v>602530</v>
@@ -44623,7 +44623,7 @@
         <v>24.6800003051758</v>
       </c>
       <c r="G1526" t="n">
-        <v>18.3692188262939</v>
+        <v>18.3692207336426</v>
       </c>
       <c r="H1526" t="n">
         <v>345113</v>
@@ -44681,7 +44681,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1528" t="n">
-        <v>18.7711391448975</v>
+        <v>18.7711372375488</v>
       </c>
       <c r="H1528" t="n">
         <v>643667</v>
@@ -44710,7 +44710,7 @@
         <v>25.2800006866455</v>
       </c>
       <c r="G1529" t="n">
-        <v>18.8157978057861</v>
+        <v>18.8157958984375</v>
       </c>
       <c r="H1529" t="n">
         <v>914811</v>
@@ -44884,7 +44884,7 @@
         <v>26.5300006866455</v>
       </c>
       <c r="G1535" t="n">
-        <v>19.746166229248</v>
+        <v>19.7461681365967</v>
       </c>
       <c r="H1535" t="n">
         <v>990413</v>
@@ -44942,7 +44942,7 @@
         <v>26.2099990844727</v>
       </c>
       <c r="G1537" t="n">
-        <v>19.5079917907715</v>
+        <v>19.5079898834229</v>
       </c>
       <c r="H1537" t="n">
         <v>436253</v>
@@ -44971,7 +44971,7 @@
         <v>25.75</v>
       </c>
       <c r="G1538" t="n">
-        <v>19.1656150817871</v>
+        <v>19.1656131744385</v>
       </c>
       <c r="H1538" t="n">
         <v>614111</v>
@@ -45000,7 +45000,7 @@
         <v>25.4099998474121</v>
       </c>
       <c r="G1539" t="n">
-        <v>18.9125556945801</v>
+        <v>18.9125537872314</v>
       </c>
       <c r="H1539" t="n">
         <v>636624</v>
@@ -45029,7 +45029,7 @@
         <v>25.4500007629395</v>
       </c>
       <c r="G1540" t="n">
-        <v>18.9423294067383</v>
+        <v>18.942325592041</v>
       </c>
       <c r="H1540" t="n">
         <v>444785</v>
@@ -45087,7 +45087,7 @@
         <v>23.7700004577637</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.6919116973877</v>
+        <v>17.6919097900391</v>
       </c>
       <c r="H1542" t="n">
         <v>1592526</v>
@@ -45174,7 +45174,7 @@
         <v>23.3099994659424</v>
       </c>
       <c r="G1545" t="n">
-        <v>17.3495349884033</v>
+        <v>17.3495330810547</v>
       </c>
       <c r="H1545" t="n">
         <v>983156</v>
@@ -45203,7 +45203,7 @@
         <v>23.1299991607666</v>
       </c>
       <c r="G1546" t="n">
-        <v>17.2155590057373</v>
+        <v>17.2155609130859</v>
       </c>
       <c r="H1546" t="n">
         <v>575384</v>
@@ -45232,7 +45232,7 @@
         <v>23.7199993133545</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.6546936035156</v>
+        <v>17.6546955108643</v>
       </c>
       <c r="H1547" t="n">
         <v>710629</v>
@@ -45290,7 +45290,7 @@
         <v>24.1200008392334</v>
       </c>
       <c r="G1549" t="n">
-        <v>17.9524173736572</v>
+        <v>17.9524154663086</v>
       </c>
       <c r="H1549" t="n">
         <v>645788</v>
@@ -45319,7 +45319,7 @@
         <v>23.9200000762939</v>
       </c>
       <c r="G1550" t="n">
-        <v>17.8035526275635</v>
+        <v>17.8035545349121</v>
       </c>
       <c r="H1550" t="n">
         <v>464622</v>
@@ -45348,7 +45348,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.6100387573242</v>
+        <v>17.610034942627</v>
       </c>
       <c r="H1551" t="n">
         <v>523292</v>
@@ -45377,7 +45377,7 @@
         <v>23.3600006103516</v>
       </c>
       <c r="G1552" t="n">
-        <v>17.3867473602295</v>
+        <v>17.3867492675781</v>
       </c>
       <c r="H1552" t="n">
         <v>577869</v>
@@ -45464,7 +45464,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1555" t="n">
-        <v>17.7291240692139</v>
+        <v>17.7291259765625</v>
       </c>
       <c r="H1555" t="n">
         <v>784207</v>
@@ -45522,7 +45522,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1557" t="n">
-        <v>17.0890293121338</v>
+        <v>17.0890312194824</v>
       </c>
       <c r="H1557" t="n">
         <v>1547273</v>
@@ -45580,7 +45580,7 @@
         <v>23.6599998474121</v>
       </c>
       <c r="G1559" t="n">
-        <v>17.6100387573242</v>
+        <v>17.610034942627</v>
       </c>
       <c r="H1559" t="n">
         <v>525996</v>
@@ -45638,7 +45638,7 @@
         <v>23.2099990844727</v>
       </c>
       <c r="G1561" t="n">
-        <v>17.2751045227051</v>
+        <v>17.2751026153564</v>
       </c>
       <c r="H1561" t="n">
         <v>489481</v>
@@ -45696,7 +45696,7 @@
         <v>22.4899997711182</v>
       </c>
       <c r="G1563" t="n">
-        <v>16.7392101287842</v>
+        <v>16.7392120361328</v>
       </c>
       <c r="H1563" t="n">
         <v>1098306</v>
@@ -45725,7 +45725,7 @@
         <v>22.7199993133545</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.9103965759277</v>
+        <v>16.9103984832764</v>
       </c>
       <c r="H1564" t="n">
         <v>621131</v>
@@ -45754,7 +45754,7 @@
         <v>21.0900001525879</v>
       </c>
       <c r="G1565" t="n">
-        <v>15.6971998214722</v>
+        <v>15.6971969604492</v>
       </c>
       <c r="H1565" t="n">
         <v>1805256</v>
@@ -45812,7 +45812,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1567" t="n">
-        <v>15.9279298782349</v>
+        <v>15.9279279708862</v>
       </c>
       <c r="H1567" t="n">
         <v>1034772</v>
@@ -46044,7 +46044,7 @@
         <v>19.25</v>
       </c>
       <c r="G1575" t="n">
-        <v>14.327693939209</v>
+        <v>14.3276929855347</v>
       </c>
       <c r="H1575" t="n">
         <v>2861136</v>
@@ -46131,7 +46131,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1578" t="n">
-        <v>15.2134065628052</v>
+        <v>15.2134056091309</v>
       </c>
       <c r="H1578" t="n">
         <v>1163313</v>
@@ -46218,7 +46218,7 @@
         <v>21.0300006866455</v>
       </c>
       <c r="G1581" t="n">
-        <v>15.6525402069092</v>
+        <v>15.6525421142578</v>
       </c>
       <c r="H1581" t="n">
         <v>2134857</v>
@@ -46247,7 +46247,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.5408945083618</v>
+        <v>15.5408964157104</v>
       </c>
       <c r="H1582" t="n">
         <v>1028498</v>
@@ -46334,7 +46334,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>15.4962368011475</v>
+        <v>15.4962358474731</v>
       </c>
       <c r="H1585" t="n">
         <v>842950</v>
@@ -46363,7 +46363,7 @@
         <v>20.8899993896484</v>
       </c>
       <c r="G1586" t="n">
-        <v>15.5483379364014</v>
+        <v>15.5483369827271</v>
       </c>
       <c r="H1586" t="n">
         <v>453645</v>
@@ -46392,7 +46392,7 @@
         <v>21.2199993133545</v>
       </c>
       <c r="G1587" t="n">
-        <v>15.7939567565918</v>
+        <v>15.7939558029175</v>
       </c>
       <c r="H1587" t="n">
         <v>1183627</v>
@@ -46537,7 +46537,7 @@
         <v>21.2399997711182</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.8088417053223</v>
+        <v>15.8088426589966</v>
       </c>
       <c r="H1592" t="n">
         <v>431964</v>
@@ -46566,7 +46566,7 @@
         <v>20.6800003051758</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.3920373916626</v>
+        <v>15.3920364379883</v>
       </c>
       <c r="H1593" t="n">
         <v>1221751</v>
@@ -46624,7 +46624,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1595" t="n">
-        <v>14.5360956192017</v>
+        <v>14.536096572876</v>
       </c>
       <c r="H1595" t="n">
         <v>1109985</v>
@@ -46653,7 +46653,7 @@
         <v>20</v>
       </c>
       <c r="G1596" t="n">
-        <v>14.8859128952026</v>
+        <v>14.8859148025513</v>
       </c>
       <c r="H1596" t="n">
         <v>888970</v>
@@ -46682,7 +46682,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G1597" t="n">
-        <v>15.0124435424805</v>
+        <v>15.0124454498291</v>
       </c>
       <c r="H1597" t="n">
         <v>504483</v>
@@ -46711,7 +46711,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.0943193435669</v>
+        <v>15.0943183898926</v>
       </c>
       <c r="H1598" t="n">
         <v>584408</v>
@@ -46740,7 +46740,7 @@
         <v>20.1399993896484</v>
       </c>
       <c r="G1599" t="n">
-        <v>14.9901161193848</v>
+        <v>14.9901170730591</v>
       </c>
       <c r="H1599" t="n">
         <v>400239</v>
@@ -46885,7 +46885,7 @@
         <v>20.1200008392334</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.9752330780029</v>
+        <v>14.9752321243286</v>
       </c>
       <c r="H1604" t="n">
         <v>574775</v>
@@ -46914,7 +46914,7 @@
         <v>20.1700000762939</v>
       </c>
       <c r="G1605" t="n">
-        <v>15.0124435424805</v>
+        <v>15.0124454498291</v>
       </c>
       <c r="H1605" t="n">
         <v>451981</v>
@@ -46943,7 +46943,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.9007997512817</v>
+        <v>14.9008016586304</v>
       </c>
       <c r="H1606" t="n">
         <v>489755</v>
@@ -47030,7 +47030,7 @@
         <v>20.3899993896484</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.1761903762817</v>
+        <v>15.1761894226074</v>
       </c>
       <c r="H1609" t="n">
         <v>548788</v>
@@ -47117,7 +47117,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1612" t="n">
-        <v>15.0198888778687</v>
+        <v>15.01988697052</v>
       </c>
       <c r="H1612" t="n">
         <v>603352</v>
@@ -47146,7 +47146,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1613" t="n">
-        <v>14.7519407272339</v>
+        <v>14.7519416809082</v>
       </c>
       <c r="H1613" t="n">
         <v>560631</v>
@@ -47204,7 +47204,7 @@
         <v>19.0049991607666</v>
       </c>
       <c r="G1615" t="n">
-        <v>14.145339012146</v>
+        <v>14.1453399658203</v>
       </c>
       <c r="H1615" t="n">
         <v>974536</v>
@@ -47233,7 +47233,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1616" t="n">
-        <v>14.3053636550903</v>
+        <v>14.305362701416</v>
       </c>
       <c r="H1616" t="n">
         <v>486189</v>
@@ -47262,7 +47262,7 @@
         <v>19.8799991607666</v>
       </c>
       <c r="G1617" t="n">
-        <v>14.7965984344482</v>
+        <v>14.7965993881226</v>
       </c>
       <c r="H1617" t="n">
         <v>852331</v>
@@ -47291,7 +47291,7 @@
         <v>19.9449996948242</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.8449792861938</v>
+        <v>14.8449783325195</v>
       </c>
       <c r="H1618" t="n">
         <v>864456</v>
@@ -47320,7 +47320,7 @@
         <v>19.9799995422363</v>
       </c>
       <c r="G1619" t="n">
-        <v>14.8710298538208</v>
+        <v>14.8710269927979</v>
       </c>
       <c r="H1619" t="n">
         <v>517377</v>
@@ -47378,7 +47378,7 @@
         <v>20.3099994659424</v>
       </c>
       <c r="G1621" t="n">
-        <v>15.1166458129883</v>
+        <v>15.116644859314</v>
       </c>
       <c r="H1621" t="n">
         <v>789021</v>
@@ -47407,7 +47407,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1622" t="n">
-        <v>15.0943193435669</v>
+        <v>15.0943183898926</v>
       </c>
       <c r="H1622" t="n">
         <v>712143</v>
@@ -47436,7 +47436,7 @@
         <v>20.0300006866455</v>
       </c>
       <c r="G1623" t="n">
-        <v>14.9082450866699</v>
+        <v>14.9082431793213</v>
       </c>
       <c r="H1623" t="n">
         <v>860145</v>
@@ -47465,7 +47465,7 @@
         <v>20.2700004577637</v>
       </c>
       <c r="G1624" t="n">
-        <v>15.086874961853</v>
+        <v>15.0868759155273</v>
       </c>
       <c r="H1624" t="n">
         <v>1108239</v>
@@ -47929,7 +47929,7 @@
         <v>17.125</v>
       </c>
       <c r="G1640" t="n">
-        <v>13.6195430755615</v>
+        <v>13.6195421218872</v>
       </c>
       <c r="H1640" t="n">
         <v>1230849</v>
@@ -47958,7 +47958,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1641" t="n">
-        <v>13.7984857559204</v>
+        <v>13.7984848022461</v>
       </c>
       <c r="H1641" t="n">
         <v>1124619</v>
@@ -48016,7 +48016,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1643" t="n">
-        <v>13.472412109375</v>
+        <v>13.4724111557007</v>
       </c>
       <c r="H1643" t="n">
         <v>1180074</v>
@@ -48074,7 +48074,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1645" t="n">
-        <v>13.6235179901123</v>
+        <v>13.6235198974609</v>
       </c>
       <c r="H1645" t="n">
         <v>384867</v>
@@ -48103,7 +48103,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1646" t="n">
-        <v>13.6235179901123</v>
+        <v>13.6235198974609</v>
       </c>
       <c r="H1646" t="n">
         <v>414450</v>
@@ -48132,7 +48132,7 @@
         <v>17.2049999237061</v>
       </c>
       <c r="G1647" t="n">
-        <v>13.6831665039062</v>
+        <v>13.6831674575806</v>
       </c>
       <c r="H1647" t="n">
         <v>433271</v>
@@ -48190,7 +48190,7 @@
         <v>17.4050006866455</v>
       </c>
       <c r="G1649" t="n">
-        <v>13.842227935791</v>
+        <v>13.8422288894653</v>
       </c>
       <c r="H1649" t="n">
         <v>492762</v>
@@ -48306,7 +48306,7 @@
         <v>16.5849990844727</v>
       </c>
       <c r="G1653" t="n">
-        <v>13.1900787353516</v>
+        <v>13.1900796890259</v>
       </c>
       <c r="H1653" t="n">
         <v>669136</v>
@@ -48422,7 +48422,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1657" t="n">
-        <v>12.9952306747437</v>
+        <v>12.995231628418</v>
       </c>
       <c r="H1657" t="n">
         <v>473687</v>
@@ -48509,7 +48509,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G1660" t="n">
-        <v>13.333233833313</v>
+        <v>13.3332328796387</v>
       </c>
       <c r="H1660" t="n">
         <v>275379</v>
@@ -48567,7 +48567,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1662" t="n">
-        <v>13.3928823471069</v>
+        <v>13.3928813934326</v>
       </c>
       <c r="H1662" t="n">
         <v>440516</v>
@@ -48712,7 +48712,7 @@
         <v>16.7649993896484</v>
       </c>
       <c r="G1667" t="n">
-        <v>13.333233833313</v>
+        <v>13.3332328796387</v>
       </c>
       <c r="H1667" t="n">
         <v>382623</v>
@@ -49002,7 +49002,7 @@
         <v>17.1650009155273</v>
       </c>
       <c r="G1677" t="n">
-        <v>13.6513557434082</v>
+        <v>13.6513547897339</v>
       </c>
       <c r="H1677" t="n">
         <v>418416</v>
@@ -49031,7 +49031,7 @@
         <v>17.2849998474121</v>
       </c>
       <c r="G1678" t="n">
-        <v>13.7467918395996</v>
+        <v>13.7467908859253</v>
       </c>
       <c r="H1678" t="n">
         <v>493218</v>
@@ -49089,7 +49089,7 @@
         <v>16.9549999237061</v>
       </c>
       <c r="G1680" t="n">
-        <v>13.4843416213989</v>
+        <v>13.4843425750732</v>
       </c>
       <c r="H1680" t="n">
         <v>339008</v>
@@ -49205,7 +49205,7 @@
         <v>17.2749996185303</v>
       </c>
       <c r="G1684" t="n">
-        <v>13.7388381958008</v>
+        <v>13.7388372421265</v>
       </c>
       <c r="H1684" t="n">
         <v>225555</v>
@@ -49263,7 +49263,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1686" t="n">
-        <v>13.5598945617676</v>
+        <v>13.5598936080933</v>
       </c>
       <c r="H1686" t="n">
         <v>353048</v>
@@ -49292,7 +49292,7 @@
         <v>17.1550006866455</v>
       </c>
       <c r="G1687" t="n">
-        <v>13.643404006958</v>
+        <v>13.6434030532837</v>
       </c>
       <c r="H1687" t="n">
         <v>324235</v>
@@ -49408,7 +49408,7 @@
         <v>16.5349998474121</v>
       </c>
       <c r="G1691" t="n">
-        <v>13.150315284729</v>
+        <v>13.1503143310547</v>
       </c>
       <c r="H1691" t="n">
         <v>217829</v>
@@ -49466,7 +49466,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1693" t="n">
-        <v>12.7009706497192</v>
+        <v>12.7009696960449</v>
       </c>
       <c r="H1693" t="n">
         <v>355160</v>
@@ -49524,7 +49524,7 @@
         <v>16.1749992370605</v>
       </c>
       <c r="G1695" t="n">
-        <v>12.8640060424805</v>
+        <v>12.8640050888062</v>
       </c>
       <c r="H1695" t="n">
         <v>248693</v>
@@ -49727,7 +49727,7 @@
         <v>15.9700002670288</v>
       </c>
       <c r="G1702" t="n">
-        <v>12.7009706497192</v>
+        <v>12.7009696960449</v>
       </c>
       <c r="H1702" t="n">
         <v>326504</v>
@@ -49785,7 +49785,7 @@
         <v>16.8050003051758</v>
       </c>
       <c r="G1704" t="n">
-        <v>13.3650465011597</v>
+        <v>13.365047454834</v>
       </c>
       <c r="H1704" t="n">
         <v>424248</v>
@@ -49843,7 +49843,7 @@
         <v>16.6900005340576</v>
       </c>
       <c r="G1706" t="n">
-        <v>13.2735872268677</v>
+        <v>13.2735862731934</v>
       </c>
       <c r="H1706" t="n">
         <v>402937</v>
@@ -49988,7 +49988,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1711" t="n">
-        <v>12.7089233398438</v>
+        <v>12.7089223861694</v>
       </c>
       <c r="H1711" t="n">
         <v>277828</v>
@@ -50017,7 +50017,7 @@
         <v>15.5749998092651</v>
       </c>
       <c r="G1712" t="n">
-        <v>12.3868265151978</v>
+        <v>12.3868255615234</v>
       </c>
       <c r="H1712" t="n">
         <v>421995</v>
@@ -50075,7 +50075,7 @@
         <v>15.125</v>
       </c>
       <c r="G1714" t="n">
-        <v>12.0289392471313</v>
+        <v>12.0289402008057</v>
       </c>
       <c r="H1714" t="n">
         <v>573785</v>
@@ -50104,7 +50104,7 @@
         <v>14.8649997711182</v>
       </c>
       <c r="G1715" t="n">
-        <v>11.8221597671509</v>
+        <v>11.8221607208252</v>
       </c>
       <c r="H1715" t="n">
         <v>533190</v>
@@ -50481,7 +50481,7 @@
         <v>14.8599996566772</v>
       </c>
       <c r="G1728" t="n">
-        <v>11.8181848526001</v>
+        <v>11.8181838989258</v>
       </c>
       <c r="H1728" t="n">
         <v>958162</v>
@@ -50568,7 +50568,7 @@
         <v>15.2600002288818</v>
       </c>
       <c r="G1731" t="n">
-        <v>12.136305809021</v>
+        <v>12.1363048553467</v>
       </c>
       <c r="H1731" t="n">
         <v>267988</v>
@@ -50800,7 +50800,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1739" t="n">
-        <v>12.9634189605713</v>
+        <v>12.963418006897</v>
       </c>
       <c r="H1739" t="n">
         <v>319221</v>
@@ -50829,7 +50829,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1740" t="n">
-        <v>12.9952306747437</v>
+        <v>12.995231628418</v>
       </c>
       <c r="H1740" t="n">
         <v>912013</v>
@@ -50858,7 +50858,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1741" t="n">
-        <v>13.2020101547241</v>
+        <v>13.2020092010498</v>
       </c>
       <c r="H1741" t="n">
         <v>1139751</v>
@@ -50916,7 +50916,7 @@
         <v>17.0149993896484</v>
       </c>
       <c r="G1743" t="n">
-        <v>13.5320596694946</v>
+        <v>13.5320587158203</v>
       </c>
       <c r="H1743" t="n">
         <v>1222537</v>
@@ -51177,7 +51177,7 @@
         <v>19.9249992370605</v>
       </c>
       <c r="G1752" t="n">
-        <v>15.8463888168335</v>
+        <v>15.8463869094849</v>
       </c>
       <c r="H1752" t="n">
         <v>548244</v>
@@ -51235,7 +51235,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.4447622299194</v>
+        <v>15.4447603225708</v>
       </c>
       <c r="H1754" t="n">
         <v>550342</v>
@@ -51322,7 +51322,7 @@
         <v>19.4549999237061</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.4725971221924</v>
+        <v>15.4725952148438</v>
       </c>
       <c r="H1757" t="n">
         <v>506298</v>
@@ -51438,7 +51438,7 @@
         <v>19.4500007629395</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.468620300293</v>
+        <v>15.4686222076416</v>
       </c>
       <c r="H1761" t="n">
         <v>470546</v>
@@ -51467,7 +51467,7 @@
         <v>19.3349990844727</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.3771572113037</v>
+        <v>15.3771591186523</v>
       </c>
       <c r="H1762" t="n">
         <v>593820</v>
@@ -51525,7 +51525,7 @@
         <v>19.5750007629395</v>
       </c>
       <c r="G1764" t="n">
-        <v>15.5680322647095</v>
+        <v>15.5680341720581</v>
       </c>
       <c r="H1764" t="n">
         <v>263676</v>
@@ -51699,7 +51699,7 @@
         <v>20.2299995422363</v>
       </c>
       <c r="G1770" t="n">
-        <v>16.0889549255371</v>
+        <v>16.0889530181885</v>
       </c>
       <c r="H1770" t="n">
         <v>887165</v>
@@ -51844,7 +51844,7 @@
         <v>20.4400005340576</v>
       </c>
       <c r="G1775" t="n">
-        <v>16.2559700012207</v>
+        <v>16.2559680938721</v>
       </c>
       <c r="H1775" t="n">
         <v>583922</v>
@@ -51960,7 +51960,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1779" t="n">
-        <v>16.6854286193848</v>
+        <v>16.6854305267334</v>
       </c>
       <c r="H1779" t="n">
         <v>550300</v>
@@ -52105,7 +52105,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1784" t="n">
-        <v>17.019458770752</v>
+        <v>17.0194568634033</v>
       </c>
       <c r="H1784" t="n">
         <v>826267</v>
@@ -52279,7 +52279,7 @@
         <v>22.3799991607666</v>
       </c>
       <c r="G1790" t="n">
-        <v>17.7988548278809</v>
+        <v>17.7988529205322</v>
       </c>
       <c r="H1790" t="n">
         <v>1256206</v>
@@ -52308,7 +52308,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1791" t="n">
-        <v>17.8306674957275</v>
+        <v>17.8306655883789</v>
       </c>
       <c r="H1791" t="n">
         <v>1003497</v>
@@ -52453,7 +52453,7 @@
         <v>22.3500003814697</v>
       </c>
       <c r="G1796" t="n">
-        <v>17.7749938964844</v>
+        <v>17.774995803833</v>
       </c>
       <c r="H1796" t="n">
         <v>788695</v>
@@ -52482,7 +52482,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G1797" t="n">
-        <v>18.1328792572021</v>
+        <v>18.1328811645508</v>
       </c>
       <c r="H1797" t="n">
         <v>503753</v>
@@ -52540,7 +52540,7 @@
         <v>22.9599990844727</v>
       </c>
       <c r="G1799" t="n">
-        <v>18.2601280212402</v>
+        <v>18.2601299285889</v>
       </c>
       <c r="H1799" t="n">
         <v>387360</v>
@@ -52656,7 +52656,7 @@
         <v>22.9200000762939</v>
       </c>
       <c r="G1803" t="n">
-        <v>18.2283191680908</v>
+        <v>18.2283172607422</v>
       </c>
       <c r="H1803" t="n">
         <v>450295</v>
@@ -52830,7 +52830,7 @@
         <v>23.6399993896484</v>
       </c>
       <c r="G1809" t="n">
-        <v>18.8009357452393</v>
+        <v>18.8009338378906</v>
       </c>
       <c r="H1809" t="n">
         <v>372266</v>
@@ -52859,7 +52859,7 @@
         <v>23.5900001525879</v>
       </c>
       <c r="G1810" t="n">
-        <v>18.7611675262451</v>
+        <v>18.7611694335938</v>
       </c>
       <c r="H1810" t="n">
         <v>619212</v>
@@ -52975,7 +52975,7 @@
         <v>23.1700000762939</v>
       </c>
       <c r="G1814" t="n">
-        <v>18.4271430969238</v>
+        <v>18.4271411895752</v>
       </c>
       <c r="H1814" t="n">
         <v>706045</v>
@@ -53236,7 +53236,7 @@
         <v>22.4200000762939</v>
       </c>
       <c r="G1823" t="n">
-        <v>17.8306674957275</v>
+        <v>17.8306655883789</v>
       </c>
       <c r="H1823" t="n">
         <v>333185</v>
@@ -53323,7 +53323,7 @@
         <v>22.5100002288818</v>
       </c>
       <c r="G1826" t="n">
-        <v>17.9022426605225</v>
+        <v>17.9022407531738</v>
       </c>
       <c r="H1826" t="n">
         <v>430058</v>
@@ -53381,7 +53381,7 @@
         <v>22.6599998474121</v>
       </c>
       <c r="G1828" t="n">
-        <v>18.0215377807617</v>
+        <v>18.0215358734131</v>
       </c>
       <c r="H1828" t="n">
         <v>346863</v>
@@ -53526,7 +53526,7 @@
         <v>19.8950004577637</v>
       </c>
       <c r="G1833" t="n">
-        <v>15.8225288391113</v>
+        <v>15.82253074646</v>
       </c>
       <c r="H1833" t="n">
         <v>2067754</v>
@@ -53787,7 +53787,7 @@
         <v>19.1100006103516</v>
       </c>
       <c r="G1842" t="n">
-        <v>15.1982192993164</v>
+        <v>15.1982183456421</v>
       </c>
       <c r="H1842" t="n">
         <v>974880</v>
@@ -53816,7 +53816,7 @@
         <v>19.3349990844727</v>
       </c>
       <c r="G1843" t="n">
-        <v>15.3771572113037</v>
+        <v>15.3771591186523</v>
       </c>
       <c r="H1843" t="n">
         <v>419260</v>
@@ -53903,7 +53903,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1846" t="n">
-        <v>15.6992588043213</v>
+        <v>15.6992568969727</v>
       </c>
       <c r="H1846" t="n">
         <v>915508</v>
@@ -53990,7 +53990,7 @@
         <v>19.625</v>
       </c>
       <c r="G1849" t="n">
-        <v>15.6077995300293</v>
+        <v>15.6077976226807</v>
       </c>
       <c r="H1849" t="n">
         <v>688802</v>
@@ -54048,7 +54048,7 @@
         <v>19.5949993133545</v>
       </c>
       <c r="G1851" t="n">
-        <v>15.5839376449585</v>
+        <v>15.5839395523071</v>
       </c>
       <c r="H1851" t="n">
         <v>814059</v>
@@ -54164,7 +54164,7 @@
         <v>20.3500003814697</v>
       </c>
       <c r="G1855" t="n">
-        <v>16.1843929290771</v>
+        <v>16.1843910217285</v>
       </c>
       <c r="H1855" t="n">
         <v>1010588</v>
@@ -54367,7 +54367,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G1862" t="n">
-        <v>16.1366748809814</v>
+        <v>16.1366729736328</v>
       </c>
       <c r="H1862" t="n">
         <v>372499</v>
@@ -54396,7 +54396,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1863" t="n">
-        <v>16.0491905212402</v>
+        <v>16.0491886138916</v>
       </c>
       <c r="H1863" t="n">
         <v>564645</v>
@@ -54483,7 +54483,7 @@
         <v>19.8950004577637</v>
       </c>
       <c r="G1866" t="n">
-        <v>15.8225288391113</v>
+        <v>15.82253074646</v>
       </c>
       <c r="H1866" t="n">
         <v>579437</v>
@@ -54599,7 +54599,7 @@
         <v>20.2900009155273</v>
       </c>
       <c r="G1870" t="n">
-        <v>16.1366748809814</v>
+        <v>16.1366729736328</v>
       </c>
       <c r="H1870" t="n">
         <v>502839</v>
@@ -54657,7 +54657,7 @@
         <v>20.2600002288818</v>
       </c>
       <c r="G1872" t="n">
-        <v>16.112813949585</v>
+        <v>16.1128158569336</v>
       </c>
       <c r="H1872" t="n">
         <v>1134021</v>
@@ -54686,7 +54686,7 @@
         <v>19.9899997711182</v>
       </c>
       <c r="G1873" t="n">
-        <v>15.8980827331543</v>
+        <v>15.8980808258057</v>
       </c>
       <c r="H1873" t="n">
         <v>760229</v>
@@ -54802,7 +54802,7 @@
         <v>19.9850006103516</v>
       </c>
       <c r="G1877" t="n">
-        <v>15.8941049575806</v>
+        <v>15.8941068649292</v>
       </c>
       <c r="H1877" t="n">
         <v>513840</v>
@@ -54831,7 +54831,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1878" t="n">
-        <v>16.0491905212402</v>
+        <v>16.0491886138916</v>
       </c>
       <c r="H1878" t="n">
         <v>660269</v>
@@ -54860,7 +54860,7 @@
         <v>20.4599990844727</v>
       </c>
       <c r="G1879" t="n">
-        <v>16.2718753814697</v>
+        <v>16.2718734741211</v>
       </c>
       <c r="H1879" t="n">
         <v>1291861</v>
@@ -80096,6 +80096,35 @@
         <v>489551</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>34.4199981689453</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>34.9799995422363</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>34.4199981689453</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>34.6599998474121</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>34.6599998474121</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>557884</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>
